--- a/Purchasing/BOM/Ultimate BOM.xlsx
+++ b/Purchasing/BOM/Ultimate BOM.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elijahrobinson/Documents/GitHub/Robot-Dog/Purchasing/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{00919605-5C5F-DD44-9BB5-B88D84938C3E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD78C19-7370-5E42-BB84-486403796FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29240" windowHeight="16880" activeTab="1" xr2:uid="{B7364A64-1EA0-9049-A7FC-B4FA1E16182F}"/>
+    <workbookView xWindow="160" yWindow="920" windowWidth="29240" windowHeight="16880" xr2:uid="{B7364A64-1EA0-9049-A7FC-B4FA1E16182F}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Price" sheetId="4" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="250" uniqueCount="191">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="206">
   <si>
     <t>ITEM NO.</t>
   </si>
@@ -612,6 +612,51 @@
   </si>
   <si>
     <t>RC0402FR-0710KL</t>
+  </si>
+  <si>
+    <t>ME3116</t>
+  </si>
+  <si>
+    <t>SOT95P270X145-6N_ME3116</t>
+  </si>
+  <si>
+    <t>SOT-23-5</t>
+  </si>
+  <si>
+    <t>ME6211C30M5</t>
+  </si>
+  <si>
+    <t>SPX3819M5-L-5-0</t>
+  </si>
+  <si>
+    <t>SOIC127P600X175-8N_CAN</t>
+  </si>
+  <si>
+    <t>CAN Bus Chip</t>
+  </si>
+  <si>
+    <t>Trimmer Potentiometer</t>
+  </si>
+  <si>
+    <t>LCSC</t>
+  </si>
+  <si>
+    <t>AS5600</t>
+  </si>
+  <si>
+    <t>Magnetic Encoder</t>
+  </si>
+  <si>
+    <t>QFN50P400X400X90-25N-D_Gatedriver1</t>
+  </si>
+  <si>
+    <t>FD6288Q</t>
+  </si>
+  <si>
+    <t>N/A</t>
+  </si>
+  <si>
+    <t>Raspberry Pi Pico</t>
   </si>
 </sst>
 </file>
@@ -746,7 +791,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="38">
+  <cellXfs count="40">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -790,6 +835,24 @@
     <xf numFmtId="44" fontId="0" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -808,12 +871,6 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -829,29 +886,47 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
+    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="1">
+  <dxfs count="5">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1196,170 +1271,214 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" t="s">
+      <c r="A1" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="38" t="s">
         <v>121</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="38" t="s">
         <v>125</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A2">
-        <v>1</v>
-      </c>
-      <c r="B2" t="s">
+      <c r="A2" s="1">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="32">
+      <c r="C2" s="39">
         <f>'Cycloidal Gearbox'!I28</f>
         <v>81.931542499999978</v>
       </c>
-      <c r="D2">
+      <c r="D2" s="1">
         <v>12</v>
       </c>
-      <c r="E2" s="32">
+      <c r="E2" s="39">
         <f>C2*D2</f>
         <v>983.17850999999973</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A3">
+      <c r="A3" s="1">
         <v>2</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="32">
+      <c r="C3" s="39">
         <f>'Leg Assembly'!I25</f>
         <v>31.44</v>
       </c>
-      <c r="D3">
+      <c r="D3" s="1">
         <v>12</v>
       </c>
-      <c r="E3" s="32">
+      <c r="E3" s="39">
         <f t="shared" ref="E3:E13" si="0">C3*D3</f>
         <v>377.28000000000003</v>
       </c>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A4">
+      <c r="A4" s="1">
         <v>3</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="32">
-        <f>'FOC PCB'!I35</f>
-        <v>58.365533333333339</v>
-      </c>
-      <c r="D4">
+      <c r="C4" s="39">
+        <f>'FOC PCB'!I41</f>
+        <v>66.489933333333326</v>
+      </c>
+      <c r="D4" s="1">
         <v>12</v>
       </c>
-      <c r="E4" s="32">
+      <c r="E4" s="39">
         <f t="shared" si="0"/>
-        <v>700.38640000000009</v>
+        <v>797.87919999999986</v>
       </c>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A5">
+      <c r="A5" s="1">
         <v>4</v>
       </c>
-      <c r="E5" s="32">
+      <c r="B5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="C5" s="5">
+        <v>8</v>
+      </c>
+      <c r="D5" s="1">
+        <v>1</v>
+      </c>
+      <c r="E5" s="39">
+        <f t="shared" si="0"/>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="1"/>
+      <c r="C6" s="5"/>
+      <c r="D6" s="1"/>
+      <c r="E6" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A6">
-        <v>5</v>
-      </c>
-      <c r="E6" s="32">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1"/>
+      <c r="C7" s="5"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7">
-        <v>6</v>
-      </c>
-      <c r="E7" s="32">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="1"/>
+      <c r="C8" s="5"/>
+      <c r="D8" s="1"/>
+      <c r="E8" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8">
-        <v>7</v>
-      </c>
-      <c r="E8" s="32">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="1"/>
+      <c r="C9" s="5"/>
+      <c r="D9" s="1"/>
+      <c r="E9" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9">
-        <v>8</v>
-      </c>
-      <c r="E9" s="32">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="1"/>
+      <c r="C10" s="5"/>
+      <c r="D10" s="1"/>
+      <c r="E10" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10">
-        <v>9</v>
-      </c>
-      <c r="E10" s="32">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="1"/>
+      <c r="C11" s="5"/>
+      <c r="D11" s="1"/>
+      <c r="E11" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11">
-        <v>10</v>
-      </c>
-      <c r="E11" s="32">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A12" s="1">
+        <v>11</v>
+      </c>
+      <c r="B12" s="1"/>
+      <c r="C12" s="5"/>
+      <c r="D12" s="1"/>
+      <c r="E12" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12">
-        <v>11</v>
-      </c>
-      <c r="E12" s="32">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="A13" s="1">
+        <v>12</v>
+      </c>
+      <c r="B13" s="1"/>
+      <c r="C13" s="5"/>
+      <c r="D13" s="1"/>
+      <c r="E13" s="39">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13">
-        <v>12</v>
-      </c>
-      <c r="E13" s="32">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
     <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="D15" t="s">
+      <c r="A15" s="30" t="s">
         <v>177</v>
       </c>
-      <c r="E15" s="32">
+      <c r="B15" s="30"/>
+      <c r="C15" s="30"/>
+      <c r="D15" s="30"/>
+      <c r="E15" s="15">
         <f>SUM(E2:E13)</f>
-        <v>2060.8449099999998</v>
+        <v>2166.3377099999998</v>
       </c>
     </row>
   </sheetData>
+  <mergeCells count="1">
+    <mergeCell ref="A15:D15"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2:E13">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>MOD(ROW(),2)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1413,13 +1532,13 @@
       <c r="B2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="27" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="25">
         <v>29.98</v>
       </c>
       <c r="F2" s="11">
@@ -1442,9 +1561,9 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="19"/>
+      <c r="C3" s="28"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="25"/>
       <c r="F3" s="6">
         <v>3.0099999999999998E-2</v>
       </c>
@@ -1465,9 +1584,9 @@
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="19"/>
+      <c r="C4" s="28"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="25"/>
       <c r="F4" s="6">
         <v>1.15E-2</v>
       </c>
@@ -1488,9 +1607,9 @@
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="19"/>
+      <c r="C5" s="28"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="25"/>
       <c r="F5" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
@@ -1505,15 +1624,15 @@
       </c>
     </row>
     <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
-        <v>6</v>
+      <c r="A6" s="16">
+        <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="19"/>
+      <c r="C6" s="28"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="25"/>
       <c r="F6" s="6">
         <v>2.0000000000000001E-4</v>
       </c>
@@ -1529,14 +1648,14 @@
     </row>
     <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>11</v>
+        <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="19"/>
+      <c r="C7" s="28"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="25"/>
       <c r="F7" s="6">
         <v>4.0000000000000002E-4</v>
       </c>
@@ -1552,14 +1671,14 @@
     </row>
     <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="19"/>
+      <c r="C8" s="28"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="25"/>
       <c r="F8" s="6">
         <v>4.2200000000000001E-2</v>
       </c>
@@ -1575,14 +1694,14 @@
     </row>
     <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="19"/>
+      <c r="C9" s="28"/>
+      <c r="D9" s="28"/>
+      <c r="E9" s="25"/>
       <c r="F9" s="6">
         <v>5.0000000000000001E-4</v>
       </c>
@@ -1597,15 +1716,15 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>16</v>
+      <c r="A10" s="16">
+        <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="19"/>
+      <c r="C10" s="28"/>
+      <c r="D10" s="28"/>
+      <c r="E10" s="25"/>
       <c r="F10" s="6">
         <v>3.2000000000000002E-3</v>
       </c>
@@ -1621,14 +1740,14 @@
     </row>
     <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="19"/>
+      <c r="C11" s="28"/>
+      <c r="D11" s="28"/>
+      <c r="E11" s="25"/>
       <c r="F11" s="6">
         <v>1E-4</v>
       </c>
@@ -1644,14 +1763,14 @@
     </row>
     <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="19"/>
+      <c r="C12" s="28"/>
+      <c r="D12" s="28"/>
+      <c r="E12" s="25"/>
       <c r="F12" s="6">
         <v>1.2500000000000001E-2</v>
       </c>
@@ -1667,14 +1786,14 @@
     </row>
     <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="20"/>
+      <c r="C13" s="29"/>
+      <c r="D13" s="29"/>
+      <c r="E13" s="26"/>
       <c r="F13" s="6">
         <v>1.95E-2</v>
       </c>
@@ -1689,8 +1808,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
-        <v>7</v>
+      <c r="A14" s="16">
+        <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
         <v>22</v>
@@ -1719,7 +1838,7 @@
     </row>
     <row r="15" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>8</v>
+        <v>14</v>
       </c>
       <c r="B15" s="2" t="s">
         <v>25</v>
@@ -1748,7 +1867,7 @@
     </row>
     <row r="16" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>28</v>
@@ -1777,7 +1896,7 @@
     </row>
     <row r="17" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="B17" s="2" t="s">
         <v>31</v>
@@ -1805,8 +1924,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>12</v>
+      <c r="A18" s="16">
+        <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
         <v>34</v>
@@ -1835,7 +1954,7 @@
     </row>
     <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="B19" s="2" t="s">
         <v>36</v>
@@ -1864,7 +1983,7 @@
     </row>
     <row r="20" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>39</v>
@@ -1893,7 +2012,7 @@
     </row>
     <row r="21" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B21" s="2" t="s">
         <v>42</v>
@@ -1921,7 +2040,7 @@
       </c>
     </row>
     <row r="22" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
+      <c r="A22" s="16">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -1980,7 +2099,7 @@
     </row>
     <row r="24" spans="1:9" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="B24" s="2" t="s">
         <v>50</v>
@@ -2009,7 +2128,7 @@
     </row>
     <row r="25" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="B25" s="2" t="s">
         <v>53</v>
@@ -2037,8 +2156,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
-        <v>26</v>
+      <c r="A26" s="16">
+        <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
         <v>56</v>
@@ -2067,7 +2186,7 @@
     </row>
     <row r="27" spans="1:9" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="B27" s="2" t="s">
         <v>58</v>
@@ -2095,35 +2214,35 @@
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="24" t="s">
+      <c r="A28" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="24"/>
-      <c r="C28" s="24"/>
-      <c r="D28" s="24"/>
-      <c r="E28" s="24"/>
-      <c r="F28" s="24"/>
-      <c r="G28" s="24"/>
-      <c r="H28" s="24"/>
+      <c r="B28" s="30"/>
+      <c r="C28" s="30"/>
+      <c r="D28" s="30"/>
+      <c r="E28" s="30"/>
+      <c r="F28" s="30"/>
+      <c r="G28" s="30"/>
+      <c r="H28" s="30"/>
       <c r="I28" s="15">
         <f>SUM(I2:I27)</f>
         <v>81.931542499999978</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G31" s="25" t="s">
+      <c r="G31" s="24" t="s">
         <v>64</v>
       </c>
-      <c r="H31" s="25"/>
+      <c r="H31" s="24"/>
       <c r="I31" s="13">
         <v>12</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G32" s="25" t="s">
+      <c r="G32" s="24" t="s">
         <v>63</v>
       </c>
-      <c r="H32" s="25"/>
+      <c r="H32" s="24"/>
       <c r="I32" s="14">
         <f>I28*I31</f>
         <v>983.17850999999973</v>
@@ -2139,7 +2258,7 @@
     <mergeCell ref="G31:H31"/>
   </mergeCells>
   <conditionalFormatting sqref="A2:I27">
-    <cfRule type="expression" dxfId="0" priority="1">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2166,13 +2285,13 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2A752E-49A0-D348-9E27-6206B0A59C47}">
-  <dimension ref="A1:I39"/>
+  <dimension ref="A1:I45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="9" customWidth="1"/>
-    <col min="2" max="2" width="36.1640625" customWidth="1"/>
-    <col min="3" max="3" width="26.5" customWidth="1"/>
-    <col min="4" max="4" width="33.83203125" customWidth="1"/>
+    <col min="1" max="1" width="16.33203125" customWidth="1"/>
+    <col min="2" max="2" width="29.6640625" customWidth="1"/>
+    <col min="3" max="3" width="25.5" customWidth="1"/>
+    <col min="4" max="4" width="20" customWidth="1"/>
     <col min="5" max="5" width="13.5" customWidth="1"/>
     <col min="6" max="6" width="15.33203125" customWidth="1"/>
     <col min="7" max="7" width="15.83203125" customWidth="1"/>
@@ -2181,31 +2300,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="51" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="36" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="36" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="36" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="36" t="s">
         <v>8</v>
       </c>
     </row>
@@ -2260,14 +2379,14 @@
         <v>6</v>
       </c>
       <c r="G3" s="5">
-        <f t="shared" ref="G3:G34" si="0">E3/F3</f>
+        <f t="shared" ref="G3:G40" si="0">E3/F3</f>
         <v>5.0599999999999996</v>
       </c>
       <c r="H3" s="6">
         <v>1</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I34" si="1">G3*H3</f>
+        <f t="shared" ref="I3:I40" si="1">G3*H3</f>
         <v>5.0599999999999996</v>
       </c>
     </row>
@@ -2359,7 +2478,7 @@
         <v>6.2500000000000003E-3</v>
       </c>
       <c r="H6" s="6">
-        <f t="shared" ref="H5:H32" si="4">F6/12</f>
+        <f t="shared" ref="H6:H31" si="4">F6/12</f>
         <v>6</v>
       </c>
       <c r="I6" s="5">
@@ -2531,19 +2650,19 @@
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="33" t="s">
+      <c r="B12" s="20" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="34" t="s">
+      <c r="C12" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="37" t="s">
+      <c r="D12" s="23" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="35">
+      <c r="E12" s="22">
         <v>0.84</v>
       </c>
-      <c r="F12" s="36">
+      <c r="F12" s="19">
         <v>24</v>
       </c>
       <c r="G12" s="5">
@@ -3231,60 +3350,269 @@
         <v>2.62</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
-      <c r="B34" s="2"/>
-      <c r="C34" s="2"/>
-      <c r="D34" s="6"/>
-      <c r="E34" s="5"/>
-      <c r="F34" s="6"/>
-      <c r="G34" s="5"/>
-      <c r="H34" s="6"/>
-      <c r="I34" s="5"/>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A35" s="26" t="s">
+      <c r="B34" s="2" t="s">
+        <v>191</v>
+      </c>
+      <c r="C34" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="D34" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E34" s="5">
+        <v>1.3720000000000001</v>
+      </c>
+      <c r="F34" s="6">
+        <v>10</v>
+      </c>
+      <c r="G34" s="5">
+        <f t="shared" si="0"/>
+        <v>0.13720000000000002</v>
+      </c>
+      <c r="H34" s="6">
+        <v>1</v>
+      </c>
+      <c r="I34" s="5">
+        <f t="shared" si="1"/>
+        <v>0.13720000000000002</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A35" s="1">
+        <v>34</v>
+      </c>
+      <c r="B35" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="C35" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D35" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E35" s="5">
+        <v>0.63700000000000001</v>
+      </c>
+      <c r="F35" s="6">
+        <v>10</v>
+      </c>
+      <c r="G35" s="5">
+        <f t="shared" si="0"/>
+        <v>6.3700000000000007E-2</v>
+      </c>
+      <c r="H35" s="6">
+        <v>1</v>
+      </c>
+      <c r="I35" s="5">
+        <f t="shared" si="1"/>
+        <v>6.3700000000000007E-2</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="1">
+        <v>35</v>
+      </c>
+      <c r="B36" s="2" t="s">
+        <v>195</v>
+      </c>
+      <c r="C36" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D36" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E36" s="5">
+        <v>2.0169999999999999</v>
+      </c>
+      <c r="F36" s="6">
+        <v>10</v>
+      </c>
+      <c r="G36" s="5">
+        <f t="shared" si="0"/>
+        <v>0.20169999999999999</v>
+      </c>
+      <c r="H36" s="6">
+        <v>1</v>
+      </c>
+      <c r="I36" s="5">
+        <f t="shared" si="1"/>
+        <v>0.20169999999999999</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="1">
+        <v>36</v>
+      </c>
+      <c r="B37" s="2" t="s">
+        <v>196</v>
+      </c>
+      <c r="C37" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E37" s="5">
+        <v>16.899999999999999</v>
+      </c>
+      <c r="F37" s="6">
+        <v>10</v>
+      </c>
+      <c r="G37" s="5">
+        <f t="shared" si="0"/>
+        <v>1.69</v>
+      </c>
+      <c r="H37" s="6">
+        <v>1</v>
+      </c>
+      <c r="I37" s="5">
+        <f t="shared" si="1"/>
+        <v>1.69</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="1">
+        <v>37</v>
+      </c>
+      <c r="B38" s="2" t="s">
+        <v>198</v>
+      </c>
+      <c r="C38" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E38" s="5">
+        <v>15.8</v>
+      </c>
+      <c r="F38" s="6">
+        <v>10</v>
+      </c>
+      <c r="G38" s="5">
+        <f t="shared" si="0"/>
+        <v>1.58</v>
+      </c>
+      <c r="H38" s="6">
+        <v>1</v>
+      </c>
+      <c r="I38" s="5">
+        <f t="shared" si="1"/>
+        <v>1.58</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A39" s="1">
+        <v>38</v>
+      </c>
+      <c r="B39" s="2" t="s">
+        <v>201</v>
+      </c>
+      <c r="C39" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>164</v>
+      </c>
+      <c r="E39" s="5">
+        <v>38</v>
+      </c>
+      <c r="F39" s="6">
+        <v>10</v>
+      </c>
+      <c r="G39" s="5">
+        <f t="shared" si="0"/>
+        <v>3.8</v>
+      </c>
+      <c r="H39" s="6">
+        <v>1</v>
+      </c>
+      <c r="I39" s="5">
+        <f t="shared" si="1"/>
+        <v>3.8</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="A40" s="1">
+        <v>39</v>
+      </c>
+      <c r="B40" s="2" t="s">
+        <v>202</v>
+      </c>
+      <c r="C40" s="2" t="s">
+        <v>203</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E40" s="5">
+        <v>6.5179999999999998</v>
+      </c>
+      <c r="F40" s="6">
+        <v>10</v>
+      </c>
+      <c r="G40" s="5">
+        <f t="shared" si="0"/>
+        <v>0.65179999999999993</v>
+      </c>
+      <c r="H40" s="6">
+        <v>1</v>
+      </c>
+      <c r="I40" s="5">
+        <f t="shared" si="1"/>
+        <v>0.65179999999999993</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A41" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B35" s="26"/>
-      <c r="C35" s="26"/>
-      <c r="D35" s="26"/>
-      <c r="E35" s="26"/>
-      <c r="F35" s="26"/>
-      <c r="G35" s="26"/>
-      <c r="H35" s="26"/>
-      <c r="I35" s="5">
-        <f>SUM(I2:I34)</f>
-        <v>58.365533333333339</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G38" s="26" t="s">
+      <c r="B41" s="30"/>
+      <c r="C41" s="30"/>
+      <c r="D41" s="30"/>
+      <c r="E41" s="30"/>
+      <c r="F41" s="30"/>
+      <c r="G41" s="30"/>
+      <c r="H41" s="30"/>
+      <c r="I41" s="37">
+        <f>SUM(I2:I40)</f>
+        <v>66.489933333333326</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G44" s="30" t="s">
         <v>64</v>
       </c>
-      <c r="H38" s="26"/>
-      <c r="I38" s="1">
+      <c r="H44" s="30"/>
+      <c r="I44" s="38">
         <v>12</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G39" s="26" t="s">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="G45" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="H39" s="26"/>
-      <c r="I39" s="5">
-        <f>I35*I38</f>
-        <v>700.38640000000009</v>
+      <c r="H45" s="30"/>
+      <c r="I45" s="37">
+        <f>I41*I44</f>
+        <v>797.87919999999986</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="3">
-    <mergeCell ref="A35:H35"/>
-    <mergeCell ref="G38:H38"/>
-    <mergeCell ref="G39:H39"/>
+    <mergeCell ref="A41:H41"/>
+    <mergeCell ref="G44:H44"/>
+    <mergeCell ref="G45:H45"/>
   </mergeCells>
+  <conditionalFormatting sqref="A2:I40">
+    <cfRule type="expression" dxfId="1" priority="1">
+      <formula>MOD(ROW(),2)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="D33" r:id="rId1" xr:uid="{00E97FD4-0201-C14C-9733-7793DB82F99F}"/>
     <hyperlink ref="D3" r:id="rId2" xr:uid="{05ECF41C-459F-5F4B-9F02-23DBADF87AF1}"/>
@@ -3337,31 +3665,31 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="36" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="2" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="2" t="s">
+      <c r="B1" s="36" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="36" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="36" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="36" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="36" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="36" t="s">
         <v>72</v>
       </c>
     </row>
@@ -3372,13 +3700,13 @@
       <c r="B2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="29" t="s">
+      <c r="C2" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="28" t="s">
+      <c r="D2" s="32" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="27">
+      <c r="E2" s="31">
         <v>29.98</v>
       </c>
       <c r="F2" s="1">
@@ -3403,9 +3731,9 @@
       <c r="B3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="30"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="27"/>
+      <c r="C3" s="34"/>
+      <c r="D3" s="28"/>
+      <c r="E3" s="31"/>
       <c r="F3" s="1">
         <v>0.17349999999999999</v>
       </c>
@@ -3428,9 +3756,9 @@
       <c r="B4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="30"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="27"/>
+      <c r="C4" s="34"/>
+      <c r="D4" s="28"/>
+      <c r="E4" s="31"/>
       <c r="F4" s="1">
         <v>1.9900000000000001E-2</v>
       </c>
@@ -3453,9 +3781,9 @@
       <c r="B5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="30"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="27"/>
+      <c r="C5" s="34"/>
+      <c r="D5" s="28"/>
+      <c r="E5" s="31"/>
       <c r="F5" s="1">
         <v>6.54E-2</v>
       </c>
@@ -3478,9 +3806,9 @@
       <c r="B6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="30"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="27"/>
+      <c r="C6" s="34"/>
+      <c r="D6" s="28"/>
+      <c r="E6" s="31"/>
       <c r="F6" s="1">
         <v>0.18579999999999999</v>
       </c>
@@ -3498,14 +3826,14 @@
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>16</v>
+        <v>6</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="30"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="27"/>
+      <c r="C7" s="34"/>
+      <c r="D7" s="28"/>
+      <c r="E7" s="31"/>
       <c r="F7" s="1">
         <v>5.9299999999999999E-2</v>
       </c>
@@ -3523,14 +3851,14 @@
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="30"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="27"/>
+      <c r="C8" s="34"/>
+      <c r="D8" s="28"/>
+      <c r="E8" s="31"/>
       <c r="F8" s="1">
         <v>0.122</v>
       </c>
@@ -3548,14 +3876,14 @@
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>18</v>
+        <v>8</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="31"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="27"/>
+      <c r="C9" s="35"/>
+      <c r="D9" s="29"/>
+      <c r="E9" s="31"/>
       <c r="F9" s="1">
         <v>4.3700000000000003E-2</v>
       </c>
@@ -3573,7 +3901,7 @@
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>20</v>
+        <v>9</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>82</v>
@@ -3604,7 +3932,7 @@
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>85</v>
@@ -3634,7 +3962,7 @@
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>87</v>
@@ -3665,7 +3993,7 @@
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>88</v>
@@ -3696,7 +4024,7 @@
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>23</v>
+        <v>13</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>91</v>
@@ -3727,7 +4055,7 @@
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>6</v>
+        <v>14</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>93</v>
@@ -3758,7 +4086,7 @@
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>7</v>
+        <v>15</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>96</v>
@@ -3789,7 +4117,7 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>8</v>
+        <v>16</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>99</v>
@@ -3820,7 +4148,7 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>9</v>
+        <v>17</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>101</v>
@@ -3851,7 +4179,7 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>104</v>
@@ -3882,7 +4210,7 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>11</v>
+        <v>19</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>107</v>
@@ -3913,7 +4241,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>12</v>
+        <v>20</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>109</v>
@@ -3944,7 +4272,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>13</v>
+        <v>21</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>112</v>
@@ -3975,7 +4303,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>14</v>
+        <v>22</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>114</v>
@@ -4006,7 +4334,7 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>15</v>
+        <v>23</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>116</v>
@@ -4036,17 +4364,17 @@
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="26" t="s">
+      <c r="A25" s="30" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="26"/>
-      <c r="C25" s="26"/>
-      <c r="D25" s="26"/>
-      <c r="E25" s="26"/>
-      <c r="F25" s="26"/>
-      <c r="G25" s="26"/>
-      <c r="H25" s="26"/>
-      <c r="I25" s="5">
+      <c r="B25" s="30"/>
+      <c r="C25" s="30"/>
+      <c r="D25" s="30"/>
+      <c r="E25" s="30"/>
+      <c r="F25" s="30"/>
+      <c r="G25" s="30"/>
+      <c r="H25" s="30"/>
+      <c r="I25" s="37">
         <v>31.44</v>
       </c>
     </row>
@@ -4057,6 +4385,11 @@
     <mergeCell ref="C2:C9"/>
     <mergeCell ref="A25:H25"/>
   </mergeCells>
+  <conditionalFormatting sqref="A2:I24">
+    <cfRule type="expression" dxfId="0" priority="1">
+      <formula>MOD(ROW(),2)</formula>
+    </cfRule>
+  </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="D2" r:id="rId1" xr:uid="{EB2ADFB5-44DE-7348-8B9E-3FF8C0867ADD}"/>
     <hyperlink ref="D10" r:id="rId2" xr:uid="{B366AB96-88A6-B944-8D67-E0ED3B2BBEF3}"/>

--- a/Purchasing/BOM/Ultimate BOM.xlsx
+++ b/Purchasing/BOM/Ultimate BOM.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elijahrobinson/Documents/GitHub/Robot-Dog/Purchasing/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DD78C19-7370-5E42-BB84-486403796FB0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD764F3-005F-6F40-A280-338C34DD7981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="920" windowWidth="29240" windowHeight="16880" xr2:uid="{B7364A64-1EA0-9049-A7FC-B4FA1E16182F}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="272" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="212">
   <si>
     <t>ITEM NO.</t>
   </si>
@@ -657,6 +657,24 @@
   </si>
   <si>
     <t>Raspberry Pi Pico</t>
+  </si>
+  <si>
+    <t>Units In Stock</t>
+  </si>
+  <si>
+    <t>Units Needed For Complete Quadruped</t>
+  </si>
+  <si>
+    <t>Extra Cost Needed For Complete Quadruped</t>
+  </si>
+  <si>
+    <t>Extra Cost Needed For Complete Quadruped($):</t>
+  </si>
+  <si>
+    <t>"Units In Stock (Non-repetitive)"</t>
+  </si>
+  <si>
+    <t>3D Printer Filament</t>
   </si>
 </sst>
 </file>
@@ -690,7 +708,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="4">
+  <fills count="3">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -699,18 +717,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="2" tint="-0.249977111117893"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
   </fills>
-  <borders count="6">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -785,13 +797,50 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="40">
+  <cellXfs count="53">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -825,14 +874,12 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -851,7 +898,30 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -868,37 +938,54 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="5">
+  <dxfs count="6">
+    <dxf>
+      <fill>
+        <patternFill>
+          <bgColor theme="2" tint="-0.24994659260841701"/>
+        </patternFill>
+      </fill>
+    </dxf>
     <dxf>
       <fill>
         <patternFill>
@@ -1264,87 +1351,142 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4E62B7-8324-4D43-A746-C69356B7E16F}">
-  <dimension ref="A1:E15"/>
+  <dimension ref="A1:J7"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="16.33203125" customWidth="1"/>
+    <col min="8" max="8" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A1" s="38" t="s">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A1" s="24" t="s">
         <v>118</v>
       </c>
-      <c r="B1" s="38" t="s">
+      <c r="B1" s="24" t="s">
         <v>119</v>
       </c>
-      <c r="C1" s="38" t="s">
+      <c r="C1" s="24" t="s">
         <v>120</v>
       </c>
-      <c r="D1" s="38" t="s">
+      <c r="D1" s="24" t="s">
         <v>121</v>
       </c>
-      <c r="E1" s="38" t="s">
+      <c r="E1" s="24" t="s">
         <v>125</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G1" s="24" t="s">
+        <v>118</v>
+      </c>
+      <c r="H1" s="24" t="s">
+        <v>119</v>
+      </c>
+      <c r="I1" s="24" t="s">
+        <v>120</v>
+      </c>
+      <c r="J1" s="24" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>122</v>
       </c>
-      <c r="C2" s="39">
+      <c r="C2" s="25">
         <f>'Cycloidal Gearbox'!I28</f>
         <v>81.931542499999978</v>
       </c>
       <c r="D2" s="1">
         <v>12</v>
       </c>
-      <c r="E2" s="39">
+      <c r="E2" s="25">
         <f>C2*D2</f>
         <v>983.17850999999973</v>
       </c>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G2" s="1">
+        <v>1</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>122</v>
+      </c>
+      <c r="I2" s="25">
+        <f>'Cycloidal Gearbox'!I28</f>
+        <v>81.931542499999978</v>
+      </c>
+      <c r="J2" s="25">
+        <f>'Cycloidal Gearbox'!L28</f>
+        <v>483.56200000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>123</v>
       </c>
-      <c r="C3" s="39">
+      <c r="C3" s="25">
         <f>'Leg Assembly'!I25</f>
-        <v>31.44</v>
+        <v>42.425021999999984</v>
       </c>
       <c r="D3" s="1">
         <v>12</v>
       </c>
-      <c r="E3" s="39">
-        <f t="shared" ref="E3:E13" si="0">C3*D3</f>
-        <v>377.28000000000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="E3" s="25">
+        <f t="shared" ref="E3:E6" si="0">C3*D3</f>
+        <v>509.10026399999981</v>
+      </c>
+      <c r="G3" s="1">
+        <v>2</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>123</v>
+      </c>
+      <c r="I3" s="25">
+        <f>'Leg Assembly'!I25</f>
+        <v>42.425021999999984</v>
+      </c>
+      <c r="J3" s="25">
+        <f>'Leg Assembly'!L25</f>
+        <v>149.92208799999995</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>124</v>
       </c>
-      <c r="C4" s="39">
+      <c r="C4" s="25">
         <f>'FOC PCB'!I41</f>
-        <v>66.489933333333326</v>
+        <v>38.513933333333327</v>
       </c>
       <c r="D4" s="1">
         <v>12</v>
       </c>
-      <c r="E4" s="39">
+      <c r="E4" s="25">
         <f t="shared" si="0"/>
-        <v>797.87919999999986</v>
-      </c>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.2">
+        <v>462.16719999999992</v>
+      </c>
+      <c r="G4" s="1">
+        <v>3</v>
+      </c>
+      <c r="H4" s="1" t="s">
+        <v>124</v>
+      </c>
+      <c r="I4" s="25">
+        <f>'FOC PCB'!I41</f>
+        <v>38.513933333333327</v>
+      </c>
+      <c r="J4" s="25">
+        <f>'FOC PCB'!L41</f>
+        <v>224.22380000000001</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -1357,125 +1499,76 @@
       <c r="D5" s="1">
         <v>1</v>
       </c>
-      <c r="E5" s="39">
+      <c r="E5" s="25">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.2">
+      <c r="G5" s="1">
+        <v>4</v>
+      </c>
+      <c r="H5" s="1" t="s">
+        <v>205</v>
+      </c>
+      <c r="I5" s="5">
+        <v>8</v>
+      </c>
+      <c r="J5" s="25">
+        <f>1*I5</f>
+        <v>8</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
-      <c r="B6" s="1"/>
-      <c r="C6" s="5"/>
-      <c r="D6" s="1"/>
-      <c r="E6" s="39">
+      <c r="B6" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="C6" s="5">
+        <v>15</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3</v>
+      </c>
+      <c r="E6" s="25">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
-        <v>6</v>
-      </c>
-      <c r="B7" s="1"/>
-      <c r="C7" s="5"/>
-      <c r="D7" s="1"/>
-      <c r="E7" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
-        <v>7</v>
-      </c>
-      <c r="B8" s="1"/>
-      <c r="C8" s="5"/>
-      <c r="D8" s="1"/>
-      <c r="E8" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
-        <v>8</v>
-      </c>
-      <c r="B9" s="1"/>
-      <c r="C9" s="5"/>
-      <c r="D9" s="1"/>
-      <c r="E9" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
-        <v>9</v>
-      </c>
-      <c r="B10" s="1"/>
-      <c r="C10" s="5"/>
-      <c r="D10" s="1"/>
-      <c r="E10" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
-        <v>10</v>
-      </c>
-      <c r="B11" s="1"/>
-      <c r="C11" s="5"/>
-      <c r="D11" s="1"/>
-      <c r="E11" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
-        <v>11</v>
-      </c>
-      <c r="B12" s="1"/>
-      <c r="C12" s="5"/>
-      <c r="D12" s="1"/>
-      <c r="E12" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="1"/>
-      <c r="C13" s="5"/>
-      <c r="D13" s="1"/>
-      <c r="E13" s="39">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.2">
-      <c r="A15" s="30" t="s">
+        <v>45</v>
+      </c>
+      <c r="G6" s="1">
+        <v>5</v>
+      </c>
+      <c r="H6" s="1"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="5"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A7" s="29" t="s">
         <v>177</v>
       </c>
-      <c r="B15" s="30"/>
-      <c r="C15" s="30"/>
-      <c r="D15" s="30"/>
-      <c r="E15" s="15">
-        <f>SUM(E2:E13)</f>
-        <v>2166.3377099999998</v>
+      <c r="B7" s="29"/>
+      <c r="C7" s="29"/>
+      <c r="D7" s="29"/>
+      <c r="E7" s="13">
+        <f>SUM(E2:E6)</f>
+        <v>2007.4459739999993</v>
+      </c>
+      <c r="G7" s="30" t="s">
+        <v>177</v>
+      </c>
+      <c r="H7" s="31"/>
+      <c r="I7" s="32"/>
+      <c r="J7" s="13">
+        <f>SUM(J2:J6)</f>
+        <v>865.70788799999991</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="1">
-    <mergeCell ref="A15:D15"/>
+  <mergeCells count="2">
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="G7:I7"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:E13">
-    <cfRule type="expression" dxfId="3" priority="1">
+  <conditionalFormatting sqref="A2:E6 G2:J6">
+    <cfRule type="expression" dxfId="5" priority="2">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1485,60 +1578,70 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BCE8930-9406-2043-8E02-400D939E2382}">
-  <dimension ref="A1:I32"/>
+  <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="2" max="2" width="23.6640625" customWidth="1"/>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="31.33203125" customWidth="1"/>
     <col min="4" max="4" width="57.5" customWidth="1"/>
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="15" max="18" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="35" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="17" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="17" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="17" t="s">
+    <row r="1" spans="1:12" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="17" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="18" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="17" t="s">
+      <c r="F1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="17" t="s">
+      <c r="G1" s="15" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="17" t="s">
+      <c r="H1" s="15" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="17" t="s">
+      <c r="I1" s="15" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="16">
+      <c r="J1" s="22" t="s">
+        <v>206</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="14">
         <v>1</v>
       </c>
       <c r="B2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="28" t="s">
+      <c r="C2" s="37" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="27" t="s">
+      <c r="D2" s="36" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="25">
+      <c r="E2" s="34">
         <v>29.98</v>
       </c>
       <c r="F2" s="11">
@@ -1553,17 +1656,27 @@
       <c r="I2" s="12">
         <v>0.45119900000000002</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J2" s="1">
+        <v>1</v>
+      </c>
+      <c r="K2" s="1">
+        <v>12</v>
+      </c>
+      <c r="L2" s="25">
+        <f>(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
+        <v>4.9610000000000003</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="28"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="25"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="34"/>
       <c r="F3" s="6">
         <v>3.0099999999999998E-2</v>
       </c>
@@ -1576,17 +1689,27 @@
       <c r="I3" s="8">
         <v>0.45119900000000002</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J3" s="1">
+        <v>1</v>
+      </c>
+      <c r="K3" s="1">
+        <v>12</v>
+      </c>
+      <c r="L3" s="25">
+        <f>(IF(K3-J3&lt;0,0,K3-J3))*G3</f>
+        <v>4.9610000000000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="25"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="34"/>
       <c r="F4" s="6">
         <v>1.15E-2</v>
       </c>
@@ -1599,17 +1722,27 @@
       <c r="I4" s="8">
         <v>0.3444702</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J4" s="1">
+        <v>2</v>
+      </c>
+      <c r="K4" s="1">
+        <v>24</v>
+      </c>
+      <c r="L4" s="25">
+        <f>(IF(K4-J4&lt;0,0,K4-J4))*G4</f>
+        <v>3.7839999999999998</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="25"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="34"/>
       <c r="F5" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
@@ -1622,17 +1755,27 @@
       <c r="I5" s="8">
         <v>5.3514300000000001E-2</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="16">
+      <c r="J5" s="1">
+        <v>1</v>
+      </c>
+      <c r="K5" s="1">
+        <v>12</v>
+      </c>
+      <c r="L5" s="25">
+        <f>(IF(K5-J5&lt;0,0,K5-J5))*G5</f>
+        <v>0.59399999999999997</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="14">
         <v>5</v>
       </c>
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="25"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="34"/>
       <c r="F6" s="6">
         <v>2.0000000000000001E-4</v>
       </c>
@@ -1645,17 +1788,27 @@
       <c r="I6" s="8">
         <v>2.3984000000000002E-3</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J6" s="1">
+        <v>1</v>
+      </c>
+      <c r="K6" s="1">
+        <v>12</v>
+      </c>
+      <c r="L6" s="25">
+        <f>(IF(K6-J6&lt;0,0,K6-J6))*G6</f>
+        <v>2.1999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="25"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="34"/>
       <c r="F7" s="6">
         <v>4.0000000000000002E-4</v>
       </c>
@@ -1668,17 +1821,27 @@
       <c r="I7" s="8">
         <v>5.5462999999999997E-3</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J7" s="1">
+        <v>1</v>
+      </c>
+      <c r="K7" s="1">
+        <v>12</v>
+      </c>
+      <c r="L7" s="25">
+        <f>(IF(K7-J7&lt;0,0,K7-J7))*G7</f>
+        <v>6.6000000000000003E-2</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="25"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="34"/>
       <c r="F8" s="6">
         <v>4.2200000000000001E-2</v>
       </c>
@@ -1691,17 +1854,27 @@
       <c r="I8" s="8">
         <v>0.63272790000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J8" s="1">
+        <v>1</v>
+      </c>
+      <c r="K8" s="1">
+        <v>12</v>
+      </c>
+      <c r="L8" s="25">
+        <f>(IF(K8-J8&lt;0,0,K8-J8))*G8</f>
+        <v>6.9630000000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="28"/>
-      <c r="E9" s="25"/>
+      <c r="C9" s="37"/>
+      <c r="D9" s="37"/>
+      <c r="E9" s="34"/>
       <c r="F9" s="6">
         <v>5.0000000000000001E-4</v>
       </c>
@@ -1714,17 +1887,27 @@
       <c r="I9" s="8">
         <v>6.8954000000000003E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="16">
+      <c r="J9" s="1">
+        <v>1</v>
+      </c>
+      <c r="K9" s="1">
+        <v>12</v>
+      </c>
+      <c r="L9" s="25">
+        <f>(IF(K9-J9&lt;0,0,K9-J9))*G9</f>
+        <v>7.6999999999999999E-2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="14">
         <v>9</v>
       </c>
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="28"/>
-      <c r="E10" s="25"/>
+      <c r="C10" s="37"/>
+      <c r="D10" s="37"/>
+      <c r="E10" s="34"/>
       <c r="F10" s="6">
         <v>3.2000000000000002E-3</v>
       </c>
@@ -1737,17 +1920,27 @@
       <c r="I10" s="8">
         <v>4.8567600000000002E-2</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J10" s="1">
+        <v>1</v>
+      </c>
+      <c r="K10" s="1">
+        <v>12</v>
+      </c>
+      <c r="L10" s="25">
+        <f>(IF(K10-J10&lt;0,0,K10-J10))*G10</f>
+        <v>0.53900000000000003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
       <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="28"/>
-      <c r="E11" s="25"/>
+      <c r="C11" s="37"/>
+      <c r="D11" s="37"/>
+      <c r="E11" s="34"/>
       <c r="F11" s="6">
         <v>1E-4</v>
       </c>
@@ -1760,17 +1953,27 @@
       <c r="I11" s="8">
         <v>7.7948000000000002E-3</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J11" s="1">
+        <v>4</v>
+      </c>
+      <c r="K11" s="1">
+        <v>48</v>
+      </c>
+      <c r="L11" s="25">
+        <f>(IF(K11-J11&lt;0,0,K11-J11))*G11</f>
+        <v>8.7999999999999995E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="28"/>
-      <c r="D12" s="28"/>
-      <c r="E12" s="25"/>
+      <c r="C12" s="37"/>
+      <c r="D12" s="37"/>
+      <c r="E12" s="34"/>
       <c r="F12" s="6">
         <v>1.2500000000000001E-2</v>
       </c>
@@ -1783,17 +1986,27 @@
       <c r="I12" s="8">
         <v>0.1876748</v>
       </c>
-    </row>
-    <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J12" s="1">
+        <v>1</v>
+      </c>
+      <c r="K12" s="1">
+        <v>12</v>
+      </c>
+      <c r="L12" s="25">
+        <f>(IF(K12-J12&lt;0,0,K12-J12))*G12</f>
+        <v>2.0680000000000001</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="29"/>
-      <c r="D13" s="29"/>
-      <c r="E13" s="26"/>
+      <c r="C13" s="38"/>
+      <c r="D13" s="38"/>
+      <c r="E13" s="35"/>
       <c r="F13" s="6">
         <v>1.95E-2</v>
       </c>
@@ -1806,9 +2019,19 @@
       <c r="I13" s="8">
         <v>0.2926048</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="16">
+      <c r="J13" s="1">
+        <v>1</v>
+      </c>
+      <c r="K13" s="1">
+        <v>12</v>
+      </c>
+      <c r="L13" s="25">
+        <f>(IF(K13-J13&lt;0,0,K13-J13))*G13</f>
+        <v>3.2229999999999999</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A14" s="14">
         <v>13</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -1835,8 +2058,18 @@
       <c r="I14" s="8">
         <v>5.6180000000000003</v>
       </c>
-    </row>
-    <row r="15" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="J14" s="1">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>24</v>
+      </c>
+      <c r="L14" s="25">
+        <f>(IF(K14-J14&lt;0,0,K14-J14))*G14</f>
+        <v>53.371000000000002</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -1864,8 +2097,18 @@
       <c r="I15" s="8">
         <v>0.318</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="J15" s="1">
+        <v>80</v>
+      </c>
+      <c r="K15" s="1">
+        <v>72</v>
+      </c>
+      <c r="L15" s="25">
+        <f>(IF(K15-J15&lt;0,0,K15-J15))*G15</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -1893,8 +2136,18 @@
       <c r="I16" s="8">
         <v>1.556</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="J16" s="1">
+        <v>13</v>
+      </c>
+      <c r="K16" s="1">
+        <v>24</v>
+      </c>
+      <c r="L16" s="25">
+        <f>(IF(K16-J16&lt;0,0,K16-J16))*G16</f>
+        <v>8.5579999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -1922,9 +2175,19 @@
       <c r="I17" s="8">
         <v>0.65800000000000003</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="16">
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <v>120</v>
+      </c>
+      <c r="L17" s="25">
+        <f>(IF(K17-J17&lt;0,0,K17-J17))*G17</f>
+        <v>7.92</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A18" s="14">
         <v>17</v>
       </c>
       <c r="B18" s="2" t="s">
@@ -1951,8 +2214,18 @@
       <c r="I18" s="8">
         <v>0.65800000000000003</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J18" s="1">
+        <v>22</v>
+      </c>
+      <c r="K18" s="1">
+        <v>48</v>
+      </c>
+      <c r="L18" s="25">
+        <f>(IF(K18-J18&lt;0,0,K18-J18))*G18</f>
+        <v>4.29</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -1980,8 +2253,18 @@
       <c r="I19" s="8">
         <v>0.1368</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J19" s="1">
+        <v>40</v>
+      </c>
+      <c r="K19" s="1">
+        <v>48</v>
+      </c>
+      <c r="L19" s="25">
+        <f>(IF(K19-J19&lt;0,0,K19-J19))*G19</f>
+        <v>0.27200000000000002</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2009,8 +2292,18 @@
       <c r="I20" s="8">
         <v>60</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="J20" s="1">
+        <v>7</v>
+      </c>
+      <c r="K20" s="1">
+        <v>12</v>
+      </c>
+      <c r="L20" s="25">
+        <f>(IF(K20-J20&lt;0,0,K20-J20))*G20</f>
+        <v>300</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2038,9 +2331,19 @@
       <c r="I21" s="8">
         <v>1.0362499999999999</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="16">
+      <c r="J21" s="1">
+        <v>6</v>
+      </c>
+      <c r="K21" s="1">
+        <v>12</v>
+      </c>
+      <c r="L21" s="25">
+        <f>(IF(K21-J21&lt;0,0,K21-J21))*G21</f>
+        <v>6.2160000000000002</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="14">
         <v>21</v>
       </c>
       <c r="B22" s="2" t="s">
@@ -2067,8 +2370,18 @@
       <c r="I22" s="8">
         <v>0.252</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="J22" s="1">
+        <v>80</v>
+      </c>
+      <c r="K22" s="1">
+        <v>72</v>
+      </c>
+      <c r="L22" s="25">
+        <f>(IF(K22-J22&lt;0,0,K22-J22))*G22</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -2096,8 +2409,18 @@
       <c r="I23" s="8">
         <v>4.5674999999999999</v>
       </c>
-    </row>
-    <row r="24" spans="1:9" ht="51" x14ac:dyDescent="0.2">
+      <c r="J23" s="1">
+        <v>24</v>
+      </c>
+      <c r="K23" s="1">
+        <v>72</v>
+      </c>
+      <c r="L23" s="25">
+        <f>(IF(K23-J23&lt;0,0,K23-J23))*G23</f>
+        <v>36.527999999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="51" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -2125,8 +2448,18 @@
       <c r="I24" s="8">
         <v>1.319</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="J24" s="1">
+        <v>9</v>
+      </c>
+      <c r="K24" s="1">
+        <v>12</v>
+      </c>
+      <c r="L24" s="25">
+        <f>(IF(K24-J24&lt;0,0,K24-J24))*G24</f>
+        <v>3.9569999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -2154,9 +2487,19 @@
       <c r="I25" s="8">
         <v>2.7570000000000001</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="16">
+      <c r="J25" s="1">
+        <v>18</v>
+      </c>
+      <c r="K25" s="1">
+        <v>360</v>
+      </c>
+      <c r="L25" s="25">
+        <f>(IF(K25-J25&lt;0,0,K25-J25))*G25</f>
+        <v>31.463999999999999</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A26" s="14">
         <v>25</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2183,8 +2526,18 @@
       <c r="I26" s="8">
         <v>0.43740000000000001</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="34" x14ac:dyDescent="0.2">
+      <c r="J26" s="1">
+        <v>44</v>
+      </c>
+      <c r="K26" s="1">
+        <v>72</v>
+      </c>
+      <c r="L26" s="25">
+        <f>(IF(K26-J26&lt;0,0,K26-J26))*G26</f>
+        <v>2.044</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -2212,53 +2565,64 @@
       <c r="I27" s="8">
         <v>0.13300000000000001</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A28" s="30" t="s">
+      <c r="J27" s="1">
+        <v>0</v>
+      </c>
+      <c r="K27" s="1">
+        <v>12</v>
+      </c>
+      <c r="L27" s="25">
+        <f>(IF(K27-J27&lt;0,0,K27-J27))*G27</f>
+        <v>1.5960000000000001</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="30"/>
-      <c r="C28" s="30"/>
-      <c r="D28" s="30"/>
-      <c r="E28" s="30"/>
-      <c r="F28" s="30"/>
-      <c r="G28" s="30"/>
-      <c r="H28" s="30"/>
-      <c r="I28" s="15">
+      <c r="B28" s="29"/>
+      <c r="C28" s="29"/>
+      <c r="D28" s="29"/>
+      <c r="E28" s="29"/>
+      <c r="F28" s="29"/>
+      <c r="G28" s="29"/>
+      <c r="H28" s="29"/>
+      <c r="I28" s="13">
         <f>SUM(I2:I27)</f>
         <v>81.931542499999978</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G31" s="24" t="s">
-        <v>64</v>
-      </c>
-      <c r="H31" s="24"/>
-      <c r="I31" s="13">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G32" s="24" t="s">
-        <v>63</v>
-      </c>
-      <c r="H32" s="24"/>
-      <c r="I32" s="14">
-        <f>I28*I31</f>
-        <v>983.17850999999973</v>
-      </c>
-    </row>
+      <c r="J28" s="33" t="s">
+        <v>209</v>
+      </c>
+      <c r="K28" s="33"/>
+      <c r="L28" s="23">
+        <f>SUM(L2:L27)</f>
+        <v>483.56200000000001</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G31" s="50"/>
+      <c r="H31" s="50"/>
+      <c r="I31" s="48"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G32" s="50"/>
+      <c r="H32" s="50"/>
+      <c r="I32" s="49"/>
+    </row>
+    <row r="59" ht="31" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
-  <mergeCells count="6">
-    <mergeCell ref="G32:H32"/>
+  <mergeCells count="5">
+    <mergeCell ref="J28:K28"/>
     <mergeCell ref="E2:E13"/>
     <mergeCell ref="D2:D13"/>
     <mergeCell ref="A28:H28"/>
     <mergeCell ref="C2:C13"/>
-    <mergeCell ref="G31:H31"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:I27">
-    <cfRule type="expression" dxfId="2" priority="1">
+  <conditionalFormatting sqref="A2:L27">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2270,14 +2634,14 @@
     <hyperlink ref="D17" r:id="rId5" xr:uid="{154D0A22-0042-0A4E-9917-6FD7FA5B7D4E}"/>
     <hyperlink ref="D18" r:id="rId6" xr:uid="{DD5E79F0-2245-7141-8F8D-A9DEBEBA6E03}"/>
     <hyperlink ref="D19" r:id="rId7" xr:uid="{68FB1776-667D-6640-A409-3E2F02B8DADF}"/>
-    <hyperlink ref="D20" r:id="rId8" xr:uid="{79944E7E-8A70-D940-9684-1B8A318EC14A}"/>
-    <hyperlink ref="D21" r:id="rId9" xr:uid="{E534FEA7-06F3-D54C-86FE-F443C9C30E34}"/>
-    <hyperlink ref="D22" r:id="rId10" xr:uid="{878F8118-01E9-4444-B730-943E147F0708}"/>
-    <hyperlink ref="D23" r:id="rId11" xr:uid="{FD7F938C-39C3-2140-8D98-C6EEA76DA704}"/>
-    <hyperlink ref="D24" r:id="rId12" xr:uid="{04CFBF2A-5416-AB4C-8837-8AF7C04A3D59}"/>
-    <hyperlink ref="D25" r:id="rId13" xr:uid="{6B9CBCD2-4CAE-7743-B936-6E61C89E99BA}"/>
-    <hyperlink ref="D26" r:id="rId14" xr:uid="{23168F80-8F04-DE41-9B44-62A1CFA7A51B}"/>
-    <hyperlink ref="D27" r:id="rId15" xr:uid="{B688A71E-BF2F-AF4A-B36D-352F6779CFDF}"/>
+    <hyperlink ref="D27" r:id="rId8" xr:uid="{B688A71E-BF2F-AF4A-B36D-352F6779CFDF}"/>
+    <hyperlink ref="D26" r:id="rId9" xr:uid="{23168F80-8F04-DE41-9B44-62A1CFA7A51B}"/>
+    <hyperlink ref="D25" r:id="rId10" xr:uid="{6B9CBCD2-4CAE-7743-B936-6E61C89E99BA}"/>
+    <hyperlink ref="D24" r:id="rId11" xr:uid="{04CFBF2A-5416-AB4C-8837-8AF7C04A3D59}"/>
+    <hyperlink ref="D22" r:id="rId12" xr:uid="{878F8118-01E9-4444-B730-943E147F0708}"/>
+    <hyperlink ref="D21" r:id="rId13" xr:uid="{E534FEA7-06F3-D54C-86FE-F443C9C30E34}"/>
+    <hyperlink ref="D20" r:id="rId14" xr:uid="{79944E7E-8A70-D940-9684-1B8A318EC14A}"/>
+    <hyperlink ref="D23" r:id="rId15" xr:uid="{FD7F938C-39C3-2140-8D98-C6EEA76DA704}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -2285,7 +2649,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2A752E-49A0-D348-9E27-6206B0A59C47}">
-  <dimension ref="A1:I45"/>
+  <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
@@ -2299,36 +2663,45 @@
     <col min="9" max="9" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="51" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="36" t="s">
+    <row r="1" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="22" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="22" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="22" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J1" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -2345,21 +2718,31 @@
         <v>34.97</v>
       </c>
       <c r="F2" s="6">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="G2" s="5">
         <f>E2/F2</f>
-        <v>34.97</v>
+        <v>6.9939999999999998</v>
       </c>
       <c r="H2" s="6">
         <v>1</v>
       </c>
       <c r="I2" s="5">
         <f>G2*H2</f>
-        <v>34.97</v>
-      </c>
-    </row>
-    <row r="3" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>6.9939999999999998</v>
+      </c>
+      <c r="J2" s="1">
+        <v>5</v>
+      </c>
+      <c r="K2" s="1">
+        <v>12</v>
+      </c>
+      <c r="L2" s="5">
+        <f>(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
+        <v>48.957999999999998</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -2389,8 +2772,18 @@
         <f t="shared" ref="I3:I40" si="1">G3*H3</f>
         <v>5.0599999999999996</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J3" s="1">
+        <v>6</v>
+      </c>
+      <c r="K3" s="1">
+        <v>12</v>
+      </c>
+      <c r="L3" s="5">
+        <f t="shared" ref="L3:L40" si="2">(IF(K3-J3&lt;0,0,K3-J3))*G3</f>
+        <v>30.36</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -2421,8 +2814,18 @@
         <f>G4*H4</f>
         <v>0.03</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J4" s="1">
+        <v>180</v>
+      </c>
+      <c r="K4" s="1">
+        <v>180</v>
+      </c>
+      <c r="L4" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -2442,7 +2845,7 @@
         <v>50</v>
       </c>
       <c r="G5" s="5">
-        <f t="shared" ref="G5:G26" si="2">E5/F5</f>
+        <f t="shared" ref="G5:G26" si="3">E5/F5</f>
         <v>0.1176</v>
       </c>
       <c r="H5" s="6">
@@ -2450,11 +2853,21 @@
         <v>4</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" ref="I5:I26" si="3">G5*H5</f>
+        <f t="shared" ref="I5:I26" si="4">G5*H5</f>
         <v>0.47039999999999998</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J5" s="1">
+        <v>50</v>
+      </c>
+      <c r="K5" s="1">
+        <v>48</v>
+      </c>
+      <c r="L5" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -2474,19 +2887,29 @@
         <v>72</v>
       </c>
       <c r="G6" s="5">
+        <f t="shared" si="3"/>
+        <v>6.2500000000000003E-3</v>
+      </c>
+      <c r="H6" s="6">
+        <f t="shared" ref="H6:H31" si="5">F6/12</f>
+        <v>6</v>
+      </c>
+      <c r="I6" s="5">
+        <f t="shared" si="4"/>
+        <v>3.7500000000000006E-2</v>
+      </c>
+      <c r="J6" s="1">
+        <v>72</v>
+      </c>
+      <c r="K6" s="1">
+        <v>72</v>
+      </c>
+      <c r="L6" s="5">
         <f t="shared" si="2"/>
-        <v>6.2500000000000003E-3</v>
-      </c>
-      <c r="H6" s="6">
-        <f t="shared" ref="H6:H31" si="4">F6/12</f>
-        <v>6</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="3"/>
-        <v>3.7500000000000006E-2</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -2506,19 +2929,29 @@
         <v>36</v>
       </c>
       <c r="G7" s="5">
+        <f t="shared" si="3"/>
+        <v>2.1111111111111112E-2</v>
+      </c>
+      <c r="H7" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="I7" s="5">
+        <f t="shared" si="4"/>
+        <v>6.3333333333333339E-2</v>
+      </c>
+      <c r="J7" s="1">
+        <v>36</v>
+      </c>
+      <c r="K7" s="1">
+        <v>36</v>
+      </c>
+      <c r="L7" s="5">
         <f t="shared" si="2"/>
-        <v>2.1111111111111112E-2</v>
-      </c>
-      <c r="H7" s="6">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="3"/>
-        <v>6.3333333333333339E-2</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -2538,19 +2971,29 @@
         <v>24</v>
       </c>
       <c r="G8" s="5">
+        <f t="shared" si="3"/>
+        <v>2.7083333333333334E-2</v>
+      </c>
+      <c r="H8" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="I8" s="5">
+        <f t="shared" si="4"/>
+        <v>5.4166666666666669E-2</v>
+      </c>
+      <c r="J8" s="1">
+        <v>24</v>
+      </c>
+      <c r="K8" s="1">
+        <v>24</v>
+      </c>
+      <c r="L8" s="5">
         <f t="shared" si="2"/>
-        <v>2.7083333333333334E-2</v>
-      </c>
-      <c r="H8" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="3"/>
-        <v>5.4166666666666669E-2</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -2570,19 +3013,29 @@
         <v>12</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="H9" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I9" s="5">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H9" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
+        <f t="shared" si="4"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="J9" s="1">
+        <v>12</v>
+      </c>
+      <c r="K9" s="1">
+        <v>12</v>
+      </c>
+      <c r="L9" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -2602,19 +3055,29 @@
         <v>12</v>
       </c>
       <c r="G10" s="5">
-        <f t="shared" si="2"/>
-        <v>0.13416666666666668</v>
-      </c>
-      <c r="H10" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I10" s="5">
         <f t="shared" si="3"/>
         <v>0.13416666666666668</v>
       </c>
-    </row>
-    <row r="11" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H10" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
+        <f t="shared" si="4"/>
+        <v>0.13416666666666668</v>
+      </c>
+      <c r="J10" s="1">
+        <v>12</v>
+      </c>
+      <c r="K10" s="1">
+        <v>12</v>
+      </c>
+      <c r="L10" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -2634,51 +3097,71 @@
         <v>12</v>
       </c>
       <c r="G11" s="5">
-        <f t="shared" si="2"/>
-        <v>1.4166666666666668E-2</v>
-      </c>
-      <c r="H11" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I11" s="5">
         <f t="shared" si="3"/>
         <v>1.4166666666666668E-2</v>
       </c>
-    </row>
-    <row r="12" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H11" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I11" s="5">
+        <f t="shared" si="4"/>
+        <v>1.4166666666666668E-2</v>
+      </c>
+      <c r="J11" s="1">
+        <v>12</v>
+      </c>
+      <c r="K11" s="1">
+        <v>12</v>
+      </c>
+      <c r="L11" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
         <v>11</v>
       </c>
-      <c r="B12" s="20" t="s">
+      <c r="B12" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="C12" s="21" t="s">
+      <c r="C12" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="22">
+      <c r="E12" s="20">
         <v>0.84</v>
       </c>
-      <c r="F12" s="19">
+      <c r="F12" s="17">
         <v>24</v>
       </c>
       <c r="G12" s="5">
+        <f t="shared" si="3"/>
+        <v>3.4999999999999996E-2</v>
+      </c>
+      <c r="H12" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="I12" s="5">
+        <f t="shared" si="4"/>
+        <v>6.9999999999999993E-2</v>
+      </c>
+      <c r="J12" s="1">
+        <v>24</v>
+      </c>
+      <c r="K12" s="1">
+        <v>24</v>
+      </c>
+      <c r="L12" s="5">
         <f t="shared" si="2"/>
-        <v>3.4999999999999996E-2</v>
-      </c>
-      <c r="H12" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="I12" s="5">
-        <f t="shared" si="3"/>
-        <v>6.9999999999999993E-2</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
         <v>12</v>
       </c>
@@ -2698,19 +3181,29 @@
         <v>36</v>
       </c>
       <c r="G13" s="5">
+        <f t="shared" si="3"/>
+        <v>6.8888888888888888E-2</v>
+      </c>
+      <c r="H13" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="I13" s="5">
+        <f t="shared" si="4"/>
+        <v>0.20666666666666667</v>
+      </c>
+      <c r="J13" s="1">
+        <v>36</v>
+      </c>
+      <c r="K13" s="1">
+        <v>36</v>
+      </c>
+      <c r="L13" s="5">
         <f t="shared" si="2"/>
-        <v>6.8888888888888888E-2</v>
-      </c>
-      <c r="H13" s="6">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="I13" s="5">
-        <f t="shared" si="3"/>
-        <v>0.20666666666666667</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
         <v>13</v>
       </c>
@@ -2730,19 +3223,29 @@
         <v>24</v>
       </c>
       <c r="G14" s="5">
+        <f t="shared" si="3"/>
+        <v>0.24708333333333332</v>
+      </c>
+      <c r="H14" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="4"/>
+        <v>0.49416666666666664</v>
+      </c>
+      <c r="J14" s="1">
+        <v>24</v>
+      </c>
+      <c r="K14" s="1">
+        <v>24</v>
+      </c>
+      <c r="L14" s="5">
         <f t="shared" si="2"/>
-        <v>0.24708333333333332</v>
-      </c>
-      <c r="H14" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="3"/>
-        <v>0.49416666666666664</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
         <v>14</v>
       </c>
@@ -2762,7 +3265,7 @@
         <v>25</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>2.0799999999999999E-2</v>
       </c>
       <c r="H15" s="6">
@@ -2770,11 +3273,21 @@
         <v>2</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>4.1599999999999998E-2</v>
       </c>
-    </row>
-    <row r="16" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J15" s="1">
+        <v>25</v>
+      </c>
+      <c r="K15" s="1">
+        <v>24</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
         <v>15</v>
       </c>
@@ -2794,19 +3307,29 @@
         <v>12</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="2"/>
-        <v>6.9166666666666668E-2</v>
-      </c>
-      <c r="H16" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I16" s="5">
         <f t="shared" si="3"/>
         <v>6.9166666666666668E-2</v>
       </c>
-    </row>
-    <row r="17" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H16" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="4"/>
+        <v>6.9166666666666668E-2</v>
+      </c>
+      <c r="J16" s="1">
+        <v>12</v>
+      </c>
+      <c r="K16" s="1">
+        <v>12</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
         <v>16</v>
       </c>
@@ -2826,19 +3349,29 @@
         <v>12</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="H17" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I17" s="5">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H17" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="4"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="J17" s="1">
+        <v>12</v>
+      </c>
+      <c r="K17" s="1">
+        <v>12</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
         <v>17</v>
       </c>
@@ -2858,7 +3391,7 @@
         <v>50</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>3.2000000000000002E-3</v>
       </c>
       <c r="H18" s="6">
@@ -2866,11 +3399,21 @@
         <v>4</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.2800000000000001E-2</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J18" s="1">
+        <v>50</v>
+      </c>
+      <c r="K18" s="1">
+        <v>48</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
         <v>18</v>
       </c>
@@ -2890,19 +3433,29 @@
         <v>24</v>
       </c>
       <c r="G19" s="5">
+        <f t="shared" si="3"/>
+        <v>0.01</v>
+      </c>
+      <c r="H19" s="6">
+        <f t="shared" si="5"/>
+        <v>2</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="4"/>
+        <v>0.02</v>
+      </c>
+      <c r="J19" s="1">
+        <v>24</v>
+      </c>
+      <c r="K19" s="1">
+        <v>24</v>
+      </c>
+      <c r="L19" s="5">
         <f t="shared" si="2"/>
-        <v>0.01</v>
-      </c>
-      <c r="H19" s="6">
-        <f t="shared" si="4"/>
-        <v>2</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="3"/>
-        <v>0.02</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
         <v>19</v>
       </c>
@@ -2926,15 +3479,25 @@
         <v>7.6111111111111115E-2</v>
       </c>
       <c r="H20" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="I20" s="5">
         <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="3"/>
         <v>0.22833333333333333</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J20" s="1">
+        <v>36</v>
+      </c>
+      <c r="K20" s="1">
+        <v>36</v>
+      </c>
+      <c r="L20" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
         <v>20</v>
       </c>
@@ -2954,19 +3517,29 @@
         <v>12</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="2"/>
-        <v>4.1666666666666666E-3</v>
-      </c>
-      <c r="H21" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I21" s="5">
         <f t="shared" si="3"/>
         <v>4.1666666666666666E-3</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H21" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="4"/>
+        <v>4.1666666666666666E-3</v>
+      </c>
+      <c r="J21" s="1">
+        <v>12</v>
+      </c>
+      <c r="K21" s="1">
+        <v>12</v>
+      </c>
+      <c r="L21" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
         <v>21</v>
       </c>
@@ -2990,15 +3563,25 @@
         <v>4.1666666666666666E-3</v>
       </c>
       <c r="H22" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I22" s="5">
         <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="3"/>
         <v>4.1666666666666666E-3</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J22" s="1">
+        <v>12</v>
+      </c>
+      <c r="K22" s="1">
+        <v>12</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
         <v>22</v>
       </c>
@@ -3018,19 +3601,29 @@
         <v>36</v>
       </c>
       <c r="G23" s="5">
+        <f t="shared" si="3"/>
+        <v>4.7222222222222223E-3</v>
+      </c>
+      <c r="H23" s="6">
+        <f t="shared" si="5"/>
+        <v>3</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="4"/>
+        <v>1.4166666666666668E-2</v>
+      </c>
+      <c r="J23" s="1">
+        <v>36</v>
+      </c>
+      <c r="K23" s="1">
+        <v>36</v>
+      </c>
+      <c r="L23" s="5">
         <f t="shared" si="2"/>
-        <v>4.7222222222222223E-3</v>
-      </c>
-      <c r="H23" s="6">
-        <f t="shared" si="4"/>
-        <v>3</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="3"/>
-        <v>1.4166666666666668E-2</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
         <v>23</v>
       </c>
@@ -3050,7 +3643,7 @@
         <v>25</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" si="2"/>
+        <f t="shared" si="3"/>
         <v>9.1999999999999998E-3</v>
       </c>
       <c r="H24" s="6">
@@ -3058,11 +3651,21 @@
         <v>2</v>
       </c>
       <c r="I24" s="5">
-        <f t="shared" si="3"/>
+        <f t="shared" si="4"/>
         <v>1.84E-2</v>
       </c>
-    </row>
-    <row r="25" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J24" s="1">
+        <v>25</v>
+      </c>
+      <c r="K24" s="1">
+        <v>24</v>
+      </c>
+      <c r="L24" s="5">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A25" s="1">
         <v>24</v>
       </c>
@@ -3082,19 +3685,29 @@
         <v>12</v>
       </c>
       <c r="G25" s="5">
-        <f t="shared" si="2"/>
-        <v>3.3333333333333335E-3</v>
-      </c>
-      <c r="H25" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I25" s="5">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H25" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I25" s="5">
+        <f t="shared" si="4"/>
+        <v>3.3333333333333335E-3</v>
+      </c>
+      <c r="J25" s="26">
+        <v>12</v>
+      </c>
+      <c r="K25" s="26">
+        <v>12</v>
+      </c>
+      <c r="L25" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A26" s="1">
         <v>25</v>
       </c>
@@ -3114,19 +3727,29 @@
         <v>12</v>
       </c>
       <c r="G26" s="5">
-        <f t="shared" si="2"/>
-        <v>6.6666666666666671E-3</v>
-      </c>
-      <c r="H26" s="6">
-        <f t="shared" si="4"/>
-        <v>1</v>
-      </c>
-      <c r="I26" s="5">
         <f t="shared" si="3"/>
         <v>6.6666666666666671E-3</v>
       </c>
-    </row>
-    <row r="27" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="H26" s="6">
+        <f t="shared" si="5"/>
+        <v>1</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="4"/>
+        <v>6.6666666666666671E-3</v>
+      </c>
+      <c r="J26" s="26">
+        <v>12</v>
+      </c>
+      <c r="K26" s="26">
+        <v>12</v>
+      </c>
+      <c r="L26" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A27" s="1">
         <v>26</v>
       </c>
@@ -3150,15 +3773,25 @@
         <v>4.1666666666666666E-3</v>
       </c>
       <c r="H27" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I27" s="5">
         <f t="shared" si="1"/>
         <v>4.1666666666666666E-3</v>
       </c>
-    </row>
-    <row r="28" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J27" s="26">
+        <v>12</v>
+      </c>
+      <c r="K27" s="26">
+        <v>12</v>
+      </c>
+      <c r="L27" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A28" s="1">
         <v>27</v>
       </c>
@@ -3182,15 +3815,25 @@
         <v>9.1666666666666667E-3</v>
       </c>
       <c r="H28" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I28" s="5">
         <f t="shared" si="1"/>
         <v>9.1666666666666667E-3</v>
       </c>
-    </row>
-    <row r="29" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J28" s="26">
+        <v>12</v>
+      </c>
+      <c r="K28" s="26">
+        <v>12</v>
+      </c>
+      <c r="L28" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A29" s="1">
         <v>28</v>
       </c>
@@ -3214,15 +3857,25 @@
         <v>0.30111111111111111</v>
       </c>
       <c r="H29" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>3</v>
       </c>
       <c r="I29" s="5">
         <f t="shared" si="1"/>
         <v>0.90333333333333332</v>
       </c>
-    </row>
-    <row r="30" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J29" s="26">
+        <v>36</v>
+      </c>
+      <c r="K29" s="26">
+        <v>36</v>
+      </c>
+      <c r="L29" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A30" s="1">
         <v>29</v>
       </c>
@@ -3246,15 +3899,25 @@
         <v>0.15083333333333335</v>
       </c>
       <c r="H30" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>2</v>
       </c>
       <c r="I30" s="5">
         <f t="shared" si="1"/>
         <v>0.30166666666666669</v>
       </c>
-    </row>
-    <row r="31" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J30" s="26">
+        <v>24</v>
+      </c>
+      <c r="K30" s="26">
+        <v>24</v>
+      </c>
+      <c r="L30" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A31" s="1">
         <v>30</v>
       </c>
@@ -3278,15 +3941,25 @@
         <v>0.5591666666666667</v>
       </c>
       <c r="H31" s="6">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
         <v>1</v>
       </c>
       <c r="I31" s="5">
         <f t="shared" si="1"/>
         <v>0.5591666666666667</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J31" s="26">
+        <v>12</v>
+      </c>
+      <c r="K31" s="26">
+        <v>12</v>
+      </c>
+      <c r="L31" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A32" s="1">
         <v>31</v>
       </c>
@@ -3317,8 +3990,18 @@
         <f t="shared" si="1"/>
         <v>11.934000000000001</v>
       </c>
-    </row>
-    <row r="33" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J32" s="26">
+        <v>30</v>
+      </c>
+      <c r="K32" s="26">
+        <v>72</v>
+      </c>
+      <c r="L32" s="27">
+        <f t="shared" si="2"/>
+        <v>83.538000000000011</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A33" s="1">
         <v>32</v>
       </c>
@@ -3349,8 +4032,18 @@
         <f t="shared" si="1"/>
         <v>2.62</v>
       </c>
-    </row>
-    <row r="34" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J33" s="26">
+        <v>5</v>
+      </c>
+      <c r="K33" s="26">
+        <v>12</v>
+      </c>
+      <c r="L33" s="27">
+        <f t="shared" si="2"/>
+        <v>18.34</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A34" s="1">
         <v>33</v>
       </c>
@@ -3380,8 +4073,18 @@
         <f t="shared" si="1"/>
         <v>0.13720000000000002</v>
       </c>
-    </row>
-    <row r="35" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J34" s="26">
+        <v>10</v>
+      </c>
+      <c r="K34" s="26">
+        <v>12</v>
+      </c>
+      <c r="L34" s="27">
+        <f t="shared" si="2"/>
+        <v>0.27440000000000003</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A35" s="1">
         <v>34</v>
       </c>
@@ -3411,8 +4114,18 @@
         <f t="shared" si="1"/>
         <v>6.3700000000000007E-2</v>
       </c>
-    </row>
-    <row r="36" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J35" s="26">
+        <v>10</v>
+      </c>
+      <c r="K35" s="26">
+        <v>12</v>
+      </c>
+      <c r="L35" s="27">
+        <f t="shared" si="2"/>
+        <v>0.12740000000000001</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A36" s="1">
         <v>35</v>
       </c>
@@ -3442,8 +4155,18 @@
         <f t="shared" si="1"/>
         <v>0.20169999999999999</v>
       </c>
-    </row>
-    <row r="37" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J36" s="26">
+        <v>10</v>
+      </c>
+      <c r="K36" s="26">
+        <v>12</v>
+      </c>
+      <c r="L36" s="27">
+        <f t="shared" si="2"/>
+        <v>0.40339999999999998</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A37" s="1">
         <v>36</v>
       </c>
@@ -3473,8 +4196,18 @@
         <f t="shared" si="1"/>
         <v>1.69</v>
       </c>
-    </row>
-    <row r="38" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J37" s="26">
+        <v>15</v>
+      </c>
+      <c r="K37" s="26">
+        <v>12</v>
+      </c>
+      <c r="L37" s="27">
+        <f t="shared" si="2"/>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A38" s="1">
         <v>37</v>
       </c>
@@ -3504,8 +4237,18 @@
         <f t="shared" si="1"/>
         <v>1.58</v>
       </c>
-    </row>
-    <row r="39" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J38" s="26">
+        <v>5</v>
+      </c>
+      <c r="K38" s="26">
+        <v>12</v>
+      </c>
+      <c r="L38" s="27">
+        <f t="shared" si="2"/>
+        <v>11.06</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" ht="17" x14ac:dyDescent="0.2">
       <c r="A39" s="1">
         <v>38</v>
       </c>
@@ -3535,8 +4278,18 @@
         <f t="shared" si="1"/>
         <v>3.8</v>
       </c>
-    </row>
-    <row r="40" spans="1:9" ht="17" x14ac:dyDescent="0.2">
+      <c r="J39" s="26">
+        <v>5</v>
+      </c>
+      <c r="K39" s="26">
+        <v>12</v>
+      </c>
+      <c r="L39" s="27">
+        <f t="shared" si="2"/>
+        <v>26.599999999999998</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" ht="34" x14ac:dyDescent="0.2">
       <c r="A40" s="1">
         <v>39</v>
       </c>
@@ -3552,64 +4305,83 @@
       <c r="E40" s="5">
         <v>6.5179999999999998</v>
       </c>
-      <c r="F40" s="6">
+      <c r="F40" s="28">
         <v>10</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="0"/>
         <v>0.65179999999999993</v>
       </c>
-      <c r="H40" s="6">
+      <c r="H40" s="28">
         <v>1</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" si="1"/>
         <v>0.65179999999999993</v>
       </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A41" s="30" t="s">
+      <c r="J40" s="26">
+        <v>5</v>
+      </c>
+      <c r="K40" s="26">
+        <v>12</v>
+      </c>
+      <c r="L40" s="27">
+        <f t="shared" si="2"/>
+        <v>4.5625999999999998</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="29" t="s">
         <v>61</v>
       </c>
-      <c r="B41" s="30"/>
-      <c r="C41" s="30"/>
-      <c r="D41" s="30"/>
-      <c r="E41" s="30"/>
-      <c r="F41" s="30"/>
-      <c r="G41" s="30"/>
-      <c r="H41" s="30"/>
-      <c r="I41" s="37">
+      <c r="B41" s="29"/>
+      <c r="C41" s="29"/>
+      <c r="D41" s="29"/>
+      <c r="E41" s="29"/>
+      <c r="F41" s="29"/>
+      <c r="G41" s="29"/>
+      <c r="H41" s="29"/>
+      <c r="I41" s="23">
         <f>SUM(I2:I40)</f>
-        <v>66.489933333333326</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G44" s="30" t="s">
+        <v>38.513933333333327</v>
+      </c>
+      <c r="J41" s="39" t="s">
+        <v>209</v>
+      </c>
+      <c r="K41" s="39"/>
+      <c r="L41" s="23">
+        <f>SUM(L2:L40)</f>
+        <v>224.22380000000001</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G44" s="29" t="s">
         <v>64</v>
       </c>
-      <c r="H44" s="30"/>
-      <c r="I44" s="38">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="G45" s="30" t="s">
+      <c r="H44" s="29"/>
+      <c r="I44" s="24">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G45" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="H45" s="30"/>
-      <c r="I45" s="37">
+      <c r="H45" s="29"/>
+      <c r="I45" s="23">
         <f>I41*I44</f>
-        <v>797.87919999999986</v>
+        <v>462.16719999999992</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="3">
+  <mergeCells count="4">
     <mergeCell ref="A41:H41"/>
     <mergeCell ref="G44:H44"/>
     <mergeCell ref="G45:H45"/>
+    <mergeCell ref="J41:K41"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:I40">
-    <cfRule type="expression" dxfId="1" priority="1">
+  <conditionalFormatting sqref="A2:L40">
+    <cfRule type="expression" dxfId="2" priority="1">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -3647,12 +4419,13 @@
     <hyperlink ref="D32" r:id="rId31" xr:uid="{857FE252-3C09-C943-A573-DE1B7EA7E29D}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EFB1B7-3B23-654A-84A7-B98EF9661A5C}">
-  <dimension ref="A1:I25"/>
+  <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
@@ -3662,246 +4435,344 @@
     <col min="6" max="6" width="14.33203125" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
     <col min="9" max="9" width="10.1640625" customWidth="1"/>
+    <col min="10" max="12" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="36" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="36" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="36" t="s">
+    <row r="1" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="22" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="22" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="22" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="36" t="s">
+      <c r="D1" s="22" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="36" t="s">
+      <c r="E1" s="22" t="s">
         <v>69</v>
       </c>
-      <c r="F1" s="36" t="s">
+      <c r="F1" s="22" t="s">
         <v>70</v>
       </c>
-      <c r="G1" s="36" t="s">
+      <c r="G1" s="22" t="s">
         <v>71</v>
       </c>
-      <c r="H1" s="36" t="s">
+      <c r="H1" s="22" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="36" t="s">
+      <c r="I1" s="22" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J1" s="22" t="s">
+        <v>210</v>
+      </c>
+      <c r="K1" s="22" t="s">
+        <v>207</v>
+      </c>
+      <c r="L1" s="22" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A2" s="1">
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="33" t="s">
+      <c r="C2" s="41" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="32" t="s">
+      <c r="D2" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="31">
+      <c r="E2" s="41">
         <v>29.98</v>
       </c>
       <c r="F2" s="1">
         <v>0.1845</v>
       </c>
       <c r="G2" s="5">
-        <f>F2*29.98/2</f>
+        <f>F2*E2/2</f>
         <v>2.7656550000000002</v>
       </c>
       <c r="H2" s="1">
         <v>1</v>
       </c>
       <c r="I2" s="5">
-        <f>G2*H2</f>
+        <f>H2*G2</f>
         <v>2.7656550000000002</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J2" s="1">
+        <v>0</v>
+      </c>
+      <c r="K2" s="1">
+        <f>H2*4</f>
+        <v>4</v>
+      </c>
+      <c r="L2" s="5">
+        <f>(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
+        <v>11.062620000000001</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A3" s="1">
         <v>2</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="34"/>
-      <c r="D3" s="28"/>
-      <c r="E3" s="31"/>
+      <c r="C3" s="37"/>
+      <c r="D3" s="37"/>
+      <c r="E3" s="37"/>
       <c r="F3" s="1">
         <v>0.17349999999999999</v>
       </c>
       <c r="G3" s="5">
-        <f t="shared" ref="G3:G9" si="0">F3*29.98/2</f>
+        <f>F3*E$2/2</f>
         <v>2.600765</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="5">
-        <f t="shared" ref="I3:I24" si="1">G3*H3</f>
+        <f>H3*G3</f>
         <v>2.600765</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J3" s="1">
+        <v>0</v>
+      </c>
+      <c r="K3" s="1">
+        <f>H3*4</f>
+        <v>4</v>
+      </c>
+      <c r="L3" s="5">
+        <f>(IF(K3-J3&lt;0,0,K3-J3))*G3</f>
+        <v>10.40306</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A4" s="1">
         <v>3</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="34"/>
-      <c r="D4" s="28"/>
-      <c r="E4" s="31"/>
+      <c r="C4" s="37"/>
+      <c r="D4" s="37"/>
+      <c r="E4" s="37"/>
       <c r="F4" s="1">
         <v>1.9900000000000001E-2</v>
       </c>
       <c r="G4" s="5">
-        <f t="shared" si="0"/>
+        <f>F4*E$2/2</f>
         <v>0.29830100000000004</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="5">
-        <f t="shared" si="1"/>
+        <f>H4*G4</f>
         <v>0.29830100000000004</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J4" s="1">
+        <v>0</v>
+      </c>
+      <c r="K4" s="1">
+        <f>H4*4</f>
+        <v>4</v>
+      </c>
+      <c r="L4" s="5">
+        <f>(IF(K4-J4&lt;0,0,K4-J4))*G4</f>
+        <v>1.1932040000000002</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A5" s="1">
         <v>4</v>
       </c>
       <c r="B5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="34"/>
-      <c r="D5" s="28"/>
-      <c r="E5" s="31"/>
+      <c r="C5" s="37"/>
+      <c r="D5" s="37"/>
+      <c r="E5" s="37"/>
       <c r="F5" s="1">
         <v>6.54E-2</v>
       </c>
       <c r="G5" s="5">
-        <f t="shared" si="0"/>
+        <f>F5*E$2/2</f>
         <v>0.98034600000000005</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="5">
-        <f t="shared" si="1"/>
+        <f>H5*G5</f>
         <v>0.98034600000000005</v>
       </c>
-    </row>
-    <row r="6" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J5" s="1">
+        <v>0</v>
+      </c>
+      <c r="K5" s="1">
+        <f>H5*4</f>
+        <v>4</v>
+      </c>
+      <c r="L5" s="5">
+        <f>(IF(K5-J5&lt;0,0,K5-J5))*G5</f>
+        <v>3.9213840000000002</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A6" s="1">
         <v>5</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="34"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="31"/>
+      <c r="C6" s="37"/>
+      <c r="D6" s="37"/>
+      <c r="E6" s="37"/>
       <c r="F6" s="1">
         <v>0.18579999999999999</v>
       </c>
       <c r="G6" s="5">
-        <f t="shared" si="0"/>
+        <f>F6*E$2/2</f>
         <v>2.785142</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="5">
-        <f t="shared" si="1"/>
+        <f>H6*G6</f>
         <v>2.785142</v>
       </c>
-    </row>
-    <row r="7" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J6" s="1">
+        <v>0</v>
+      </c>
+      <c r="K6" s="1">
+        <f>H6*4</f>
+        <v>4</v>
+      </c>
+      <c r="L6" s="5">
+        <f>(IF(K6-J6&lt;0,0,K6-J6))*G6</f>
+        <v>11.140568</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A7" s="1">
-        <v>6</v>
+        <v>16</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="34"/>
-      <c r="D7" s="28"/>
-      <c r="E7" s="31"/>
+      <c r="C7" s="37"/>
+      <c r="D7" s="37"/>
+      <c r="E7" s="37"/>
       <c r="F7" s="1">
         <v>5.9299999999999999E-2</v>
       </c>
       <c r="G7" s="5">
-        <f t="shared" si="0"/>
+        <f>F7*E$2/2</f>
         <v>0.888907</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
       <c r="I7" s="5">
-        <f t="shared" si="1"/>
+        <f>H7*G7</f>
         <v>0.888907</v>
       </c>
-    </row>
-    <row r="8" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <f>H7*4</f>
+        <v>4</v>
+      </c>
+      <c r="L7" s="5">
+        <f>(IF(K7-J7&lt;0,0,K7-J7))*G7</f>
+        <v>3.555628</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A8" s="1">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="34"/>
-      <c r="D8" s="28"/>
-      <c r="E8" s="31"/>
+      <c r="C8" s="37"/>
+      <c r="D8" s="37"/>
+      <c r="E8" s="37"/>
       <c r="F8" s="1">
         <v>0.122</v>
       </c>
       <c r="G8" s="5">
-        <f t="shared" si="0"/>
+        <f>F8*E$2/2</f>
         <v>1.8287800000000001</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="5">
-        <f t="shared" si="1"/>
+        <f>H8*G8</f>
         <v>1.8287800000000001</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J8" s="1">
+        <v>0</v>
+      </c>
+      <c r="K8" s="1">
+        <f>H8*4</f>
+        <v>4</v>
+      </c>
+      <c r="L8" s="5">
+        <f>(IF(K8-J8&lt;0,0,K8-J8))*G8</f>
+        <v>7.3151200000000003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A9" s="1">
-        <v>8</v>
+        <v>18</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="35"/>
-      <c r="D9" s="29"/>
-      <c r="E9" s="31"/>
+      <c r="C9" s="38"/>
+      <c r="D9" s="38"/>
+      <c r="E9" s="38"/>
       <c r="F9" s="1">
         <v>4.3700000000000003E-2</v>
       </c>
       <c r="G9" s="5">
-        <f t="shared" si="0"/>
+        <f>F9*E$2/2</f>
         <v>0.65506300000000006</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
       </c>
       <c r="I9" s="5">
-        <f t="shared" si="1"/>
+        <f>H9*G9</f>
         <v>1.3101260000000001</v>
       </c>
-    </row>
-    <row r="10" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J9" s="1">
+        <v>0</v>
+      </c>
+      <c r="K9" s="1">
+        <f>H9*4</f>
+        <v>8</v>
+      </c>
+      <c r="L9" s="5">
+        <f>(IF(K9-J9&lt;0,0,K9-J9))*G9</f>
+        <v>5.2405040000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A10" s="1">
-        <v>9</v>
+        <v>20</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>82</v>
@@ -3919,20 +4790,30 @@
         <v>3.8800000000000001E-2</v>
       </c>
       <c r="G10" s="5">
-        <f>F10*E10/0.25</f>
-        <v>1.395248</v>
+        <v>1.3939999999999999</v>
       </c>
       <c r="H10" s="1">
         <v>1</v>
       </c>
       <c r="I10" s="5">
-        <f t="shared" si="1"/>
-        <v>1.395248</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" x14ac:dyDescent="0.2">
+        <f>H10*G10</f>
+        <v>1.3939999999999999</v>
+      </c>
+      <c r="J10" s="1">
+        <v>0</v>
+      </c>
+      <c r="K10" s="1">
+        <f>H10*4</f>
+        <v>4</v>
+      </c>
+      <c r="L10" s="5">
+        <f>(IF(K10-J10&lt;0,0,K10-J10))*G10</f>
+        <v>5.5759999999999996</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A11" s="1">
-        <v>10</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>85</v>
@@ -3953,16 +4834,27 @@
         <v>2.8090000000000002</v>
       </c>
       <c r="H11" s="1">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="I11" s="5">
-        <f t="shared" si="1"/>
-        <v>2.8090000000000002</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.2">
+        <f>H11*G11</f>
+        <v>8.4269999999999996</v>
+      </c>
+      <c r="J11" s="1">
+        <v>0</v>
+      </c>
+      <c r="K11" s="1">
+        <f>H11*4</f>
+        <v>12</v>
+      </c>
+      <c r="L11" s="5">
+        <f>(IF(K11-J11&lt;0,0,K11-J11))*G11</f>
+        <v>33.707999999999998</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A12" s="1">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>87</v>
@@ -3980,20 +4872,30 @@
         <v>100</v>
       </c>
       <c r="G12" s="5">
-        <f>E12/F12</f>
-        <v>9.1899999999999996E-2</v>
+        <v>9.1999999999999998E-2</v>
       </c>
       <c r="H12" s="1">
         <v>12</v>
       </c>
       <c r="I12" s="5">
-        <f t="shared" si="1"/>
-        <v>1.1028</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.2">
+        <f>H12*G12</f>
+        <v>1.1040000000000001</v>
+      </c>
+      <c r="J12" s="1">
+        <v>0</v>
+      </c>
+      <c r="K12" s="1">
+        <f>H12*4</f>
+        <v>48</v>
+      </c>
+      <c r="L12" s="5">
+        <f>(IF(K12-J12&lt;0,0,K12-J12))*G12</f>
+        <v>4.4160000000000004</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A13" s="1">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>88</v>
@@ -4011,20 +4913,30 @@
         <v>5</v>
       </c>
       <c r="G13" s="5">
-        <f t="shared" ref="G13:G24" si="2">E13/F13</f>
         <v>0.496</v>
       </c>
       <c r="H13" s="1">
         <v>2</v>
       </c>
       <c r="I13" s="5">
-        <f t="shared" si="1"/>
+        <f>H13*G13</f>
         <v>0.99199999999999999</v>
       </c>
-    </row>
-    <row r="14" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J13" s="1">
+        <v>9</v>
+      </c>
+      <c r="K13" s="1">
+        <f>H13*4</f>
+        <v>8</v>
+      </c>
+      <c r="L13" s="5">
+        <f>(IF(K13-J13&lt;0,0,K13-J13))*G13</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A14" s="1">
-        <v>13</v>
+        <v>23</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>91</v>
@@ -4042,20 +4954,30 @@
         <v>50</v>
       </c>
       <c r="G14" s="5">
-        <f t="shared" si="2"/>
-        <v>3.4200000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="H14" s="1">
         <v>1</v>
       </c>
       <c r="I14" s="5">
-        <f t="shared" si="1"/>
-        <v>3.4200000000000001E-2</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" x14ac:dyDescent="0.2">
+        <f>H14*G14</f>
+        <v>3.4000000000000002E-2</v>
+      </c>
+      <c r="J14" s="1">
+        <v>0</v>
+      </c>
+      <c r="K14" s="1">
+        <f>H14*4</f>
+        <v>4</v>
+      </c>
+      <c r="L14" s="5">
+        <f>(IF(K14-J14&lt;0,0,K14-J14))*G14</f>
+        <v>0.13600000000000001</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A15" s="1">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c r="B15" s="1" t="s">
         <v>93</v>
@@ -4073,20 +4995,30 @@
         <v>10</v>
       </c>
       <c r="G15" s="5">
-        <f t="shared" si="2"/>
-        <v>0.69900000000000007</v>
+        <v>0.69899999999999995</v>
       </c>
       <c r="H15" s="1">
         <v>7</v>
       </c>
       <c r="I15" s="5">
-        <f t="shared" si="1"/>
-        <v>4.8930000000000007</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" x14ac:dyDescent="0.2">
+        <f>H15*G15</f>
+        <v>4.8929999999999998</v>
+      </c>
+      <c r="J15" s="1">
+        <v>0</v>
+      </c>
+      <c r="K15" s="1">
+        <f>H15*4</f>
+        <v>28</v>
+      </c>
+      <c r="L15" s="5">
+        <f>(IF(K15-J15&lt;0,0,K15-J15))*G15</f>
+        <v>19.571999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A16" s="1">
-        <v>15</v>
+        <v>7</v>
       </c>
       <c r="B16" s="1" t="s">
         <v>96</v>
@@ -4104,20 +5036,30 @@
         <v>50</v>
       </c>
       <c r="G16" s="5">
-        <f t="shared" si="2"/>
-        <v>0.14580000000000001</v>
+        <v>0.14599999999999999</v>
       </c>
       <c r="H16" s="1">
         <v>7</v>
       </c>
       <c r="I16" s="5">
-        <f t="shared" si="1"/>
-        <v>1.0206000000000002</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+        <f>H16*G16</f>
+        <v>1.022</v>
+      </c>
+      <c r="J16" s="1">
+        <v>19</v>
+      </c>
+      <c r="K16" s="1">
+        <f>H16*4</f>
+        <v>28</v>
+      </c>
+      <c r="L16" s="5">
+        <f>(IF(K16-J16&lt;0,0,K16-J16))*G16</f>
+        <v>1.3139999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A17" s="1">
-        <v>16</v>
+        <v>8</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>99</v>
@@ -4135,20 +5077,30 @@
         <v>50</v>
       </c>
       <c r="G17" s="5">
-        <f t="shared" si="2"/>
         <v>6.7000000000000004E-2</v>
       </c>
       <c r="H17" s="1">
         <v>24</v>
       </c>
       <c r="I17" s="5">
-        <f t="shared" si="1"/>
+        <f>H17*G17</f>
         <v>1.6080000000000001</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J17" s="1">
+        <v>0</v>
+      </c>
+      <c r="K17" s="1">
+        <f>H17*4</f>
+        <v>96</v>
+      </c>
+      <c r="L17" s="5">
+        <f>(IF(K17-J17&lt;0,0,K17-J17))*G17</f>
+        <v>6.4320000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A18" s="1">
-        <v>17</v>
+        <v>9</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>101</v>
@@ -4166,20 +5118,30 @@
         <v>40</v>
       </c>
       <c r="G18" s="5">
-        <f t="shared" si="2"/>
-        <v>0.31974999999999998</v>
+        <v>0.32</v>
       </c>
       <c r="H18" s="1">
         <v>7</v>
       </c>
       <c r="I18" s="5">
-        <f t="shared" si="1"/>
-        <v>2.2382499999999999</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+        <f>H18*G18</f>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J18" s="1">
+        <v>0</v>
+      </c>
+      <c r="K18" s="1">
+        <f>H18*4</f>
+        <v>28</v>
+      </c>
+      <c r="L18" s="5">
+        <f>(IF(K18-J18&lt;0,0,K18-J18))*G18</f>
+        <v>8.9600000000000009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A19" s="1">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="B19" s="1" t="s">
         <v>104</v>
@@ -4197,20 +5159,30 @@
         <v>10</v>
       </c>
       <c r="G19" s="5">
-        <f t="shared" si="2"/>
         <v>0.82899999999999996</v>
       </c>
       <c r="H19" s="1">
         <v>5</v>
       </c>
       <c r="I19" s="5">
-        <f t="shared" si="1"/>
+        <f>H19*G19</f>
         <v>4.1449999999999996</v>
       </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J19" s="1">
+        <v>10</v>
+      </c>
+      <c r="K19" s="1">
+        <f>H19*4</f>
+        <v>20</v>
+      </c>
+      <c r="L19" s="5">
+        <f>(IF(K19-J19&lt;0,0,K19-J19))*G19</f>
+        <v>8.2899999999999991</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A20" s="1">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="B20" s="1" t="s">
         <v>107</v>
@@ -4228,20 +5200,30 @@
         <v>5</v>
       </c>
       <c r="G20" s="5">
-        <f t="shared" si="2"/>
         <v>0.53800000000000003</v>
       </c>
       <c r="H20" s="1">
         <v>1</v>
       </c>
       <c r="I20" s="5">
-        <f t="shared" si="1"/>
+        <f>H20*G20</f>
         <v>0.53800000000000003</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J20" s="1">
+        <v>0</v>
+      </c>
+      <c r="K20" s="1">
+        <f>H20*4</f>
+        <v>4</v>
+      </c>
+      <c r="L20" s="5">
+        <f>(IF(K20-J20&lt;0,0,K20-J20))*G20</f>
+        <v>2.1520000000000001</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A21" s="1">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>109</v>
@@ -4259,20 +5241,30 @@
         <v>50</v>
       </c>
       <c r="G21" s="5">
-        <f t="shared" si="2"/>
         <v>5.0999999999999997E-2</v>
       </c>
       <c r="H21" s="1">
         <v>3</v>
       </c>
       <c r="I21" s="5">
-        <f t="shared" si="1"/>
+        <f>H21*G21</f>
         <v>0.153</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J21" s="1">
+        <v>40</v>
+      </c>
+      <c r="K21" s="1">
+        <f>H21*4</f>
+        <v>12</v>
+      </c>
+      <c r="L21" s="5">
+        <f>(IF(K21-J21&lt;0,0,K21-J21))*G21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A22" s="1">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>112</v>
@@ -4290,20 +5282,30 @@
         <v>10</v>
       </c>
       <c r="G22" s="5">
-        <f t="shared" si="2"/>
         <v>0.221</v>
       </c>
       <c r="H22" s="1">
         <v>1</v>
       </c>
       <c r="I22" s="5">
-        <f t="shared" si="1"/>
+        <f>H22*G22</f>
         <v>0.221</v>
       </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="J22" s="1">
+        <v>0</v>
+      </c>
+      <c r="K22" s="1">
+        <f>H22*4</f>
+        <v>4</v>
+      </c>
+      <c r="L22" s="5">
+        <f>(IF(K22-J22&lt;0,0,K22-J22))*G22</f>
+        <v>0.88400000000000001</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A23" s="1">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>114</v>
@@ -4321,20 +5323,30 @@
         <v>40</v>
       </c>
       <c r="G23" s="5">
-        <f t="shared" si="2"/>
-        <v>0.28225</v>
+        <v>0.28199999999999997</v>
       </c>
       <c r="H23" s="1">
         <v>3</v>
       </c>
       <c r="I23" s="5">
-        <f t="shared" si="1"/>
-        <v>0.84675</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+        <f>H23*G23</f>
+        <v>0.84599999999999986</v>
+      </c>
+      <c r="J23" s="1">
+        <v>15</v>
+      </c>
+      <c r="K23" s="1">
+        <f>H23*4</f>
+        <v>12</v>
+      </c>
+      <c r="L23" s="5">
+        <f>(IF(K23-J23&lt;0,0,K23-J23))*G23</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
       <c r="A24" s="1">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>116</v>
@@ -4352,61 +5364,86 @@
         <v>50</v>
       </c>
       <c r="G24" s="5">
-        <f t="shared" si="2"/>
-        <v>7.46E-2</v>
+        <v>7.4999999999999997E-2</v>
       </c>
       <c r="H24" s="1">
         <v>18</v>
       </c>
       <c r="I24" s="5">
-        <f t="shared" si="1"/>
-        <v>1.3428</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
-      <c r="A25" s="30" t="s">
+        <f>H24*G24</f>
+        <v>1.3499999999999999</v>
+      </c>
+      <c r="J24" s="1">
+        <v>10</v>
+      </c>
+      <c r="K24" s="1">
+        <f>H24*4</f>
+        <v>72</v>
+      </c>
+      <c r="L24" s="5">
+        <f>(IF(K24-J24&lt;0,0,K24-J24))*G24</f>
+        <v>4.6499999999999995</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="44" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="30"/>
-      <c r="C25" s="30"/>
-      <c r="D25" s="30"/>
-      <c r="E25" s="30"/>
-      <c r="F25" s="30"/>
-      <c r="G25" s="30"/>
-      <c r="H25" s="30"/>
-      <c r="I25" s="37">
-        <v>31.44</v>
-      </c>
+      <c r="B25" s="45"/>
+      <c r="C25" s="45"/>
+      <c r="D25" s="45"/>
+      <c r="E25" s="45"/>
+      <c r="F25" s="45"/>
+      <c r="G25" s="45"/>
+      <c r="H25" s="46"/>
+      <c r="I25" s="47">
+        <f>SUM(I2:I24)</f>
+        <v>42.425021999999984</v>
+      </c>
+      <c r="J25" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="K25" s="43"/>
+      <c r="L25" s="47">
+        <f>SUM(L2:L24)</f>
+        <v>149.92208799999995</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J28" s="51"/>
+      <c r="K28" s="51"/>
+      <c r="L28" s="52"/>
     </row>
   </sheetData>
-  <mergeCells count="4">
+  <mergeCells count="5">
     <mergeCell ref="E2:E9"/>
     <mergeCell ref="D2:D9"/>
     <mergeCell ref="C2:C9"/>
     <mergeCell ref="A25:H25"/>
+    <mergeCell ref="J25:K25"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:I24">
+  <conditionalFormatting sqref="A2:L2 A3:B9 F3:J9 A10:J24 K3:L24">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
   <hyperlinks>
-    <hyperlink ref="D2" r:id="rId1" xr:uid="{EB2ADFB5-44DE-7348-8B9E-3FF8C0867ADD}"/>
-    <hyperlink ref="D10" r:id="rId2" xr:uid="{B366AB96-88A6-B944-8D67-E0ED3B2BBEF3}"/>
-    <hyperlink ref="D11" r:id="rId3" xr:uid="{77E784DE-C811-A847-AB81-6DAAC763B1BF}"/>
-    <hyperlink ref="D12" r:id="rId4" xr:uid="{FAC718AE-4E43-B344-BFC3-E9A17AEE058C}"/>
-    <hyperlink ref="D13" r:id="rId5" xr:uid="{FB3A6977-70ED-B24A-80EB-37AF9C12C309}"/>
-    <hyperlink ref="D14" r:id="rId6" xr:uid="{35B13607-5926-F24F-B790-A6A4A4DC804C}"/>
-    <hyperlink ref="D16" r:id="rId7" xr:uid="{D0892531-6458-7243-B35C-A5056D62B1FC}"/>
-    <hyperlink ref="D15" r:id="rId8" xr:uid="{F0065D4E-8EC6-2249-9F5B-83710B7368B7}"/>
-    <hyperlink ref="D17" r:id="rId9" xr:uid="{E61843A0-E7F5-5B44-A060-7917418066E4}"/>
-    <hyperlink ref="D18" r:id="rId10" xr:uid="{0D93307E-DFDA-3A49-8CC4-3A581DC163CE}"/>
-    <hyperlink ref="D19" r:id="rId11" xr:uid="{0923CB09-C2E1-3646-B059-29EF630A3C31}"/>
-    <hyperlink ref="D20" r:id="rId12" xr:uid="{BBF5ABAA-E2DD-3949-B263-BF2B61D32AB9}"/>
-    <hyperlink ref="D21" r:id="rId13" xr:uid="{3567846A-2D64-2846-B35D-6BD1C0F552F1}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{7A7F4EA9-3861-1F4E-8B92-5736910A89D0}"/>
-    <hyperlink ref="D23" r:id="rId15" xr:uid="{DB6C186F-F195-C54F-92FC-6759B28F6BD4}"/>
-    <hyperlink ref="D24" r:id="rId16" xr:uid="{35B2EA95-D989-624B-91FB-41ECB2F45622}"/>
+    <hyperlink ref="D2" r:id="rId1" xr:uid="{8BBB6A3E-A473-3B4E-9FBC-1CEBEAA73F47}"/>
+    <hyperlink ref="D10" r:id="rId2" xr:uid="{9CED9974-D344-1240-A40E-58290B9B5D8F}"/>
+    <hyperlink ref="D11" r:id="rId3" xr:uid="{DB928058-A94C-0D42-992B-70DCBC946E5C}"/>
+    <hyperlink ref="D12" r:id="rId4" xr:uid="{91E74018-89BB-4442-95FC-737D0DE5CD7E}"/>
+    <hyperlink ref="D13" r:id="rId5" xr:uid="{D8F65531-2BF0-654F-BC30-35A440B66D57}"/>
+    <hyperlink ref="D14" r:id="rId6" xr:uid="{70FA685D-E1F8-AA4D-A9BE-F0E819D7552E}"/>
+    <hyperlink ref="D15" r:id="rId7" xr:uid="{B52DB144-B68E-8946-A185-77F171944887}"/>
+    <hyperlink ref="D16" r:id="rId8" xr:uid="{0AD888AF-64A6-0941-A43C-E5D405C82E18}"/>
+    <hyperlink ref="D17" r:id="rId9" xr:uid="{91223EBD-DA16-6141-B02E-82C5B97D21D3}"/>
+    <hyperlink ref="D18" r:id="rId10" xr:uid="{69D71C1C-F146-1347-A3BB-945824BEDAD4}"/>
+    <hyperlink ref="D19" r:id="rId11" xr:uid="{8AF02770-5A1E-0D4F-943E-F280C0374B4B}"/>
+    <hyperlink ref="D20" r:id="rId12" xr:uid="{A0CCE2EF-4874-9846-A3B1-3CBF7FA70805}"/>
+    <hyperlink ref="D21" r:id="rId13" xr:uid="{E37256A4-CC0F-804E-A6E9-D20623DDBEEE}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{CBB3130F-3CE1-B749-96E3-72BF68699864}"/>
+    <hyperlink ref="D23" r:id="rId15" xr:uid="{E3588641-4442-5448-ABE4-7F1C5B716318}"/>
+    <hyperlink ref="D24" r:id="rId16" xr:uid="{B6D7B57A-C95F-F242-8A08-AFDE910F26FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Purchasing/BOM/Ultimate BOM.xlsx
+++ b/Purchasing/BOM/Ultimate BOM.xlsx
@@ -8,15 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elijahrobinson/Documents/GitHub/Robot-Dog/Purchasing/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFD764F3-005F-6F40-A280-338C34DD7981}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9A2B99-3C50-4547-AB8C-86AC7DE28C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="160" yWindow="920" windowWidth="29240" windowHeight="16880" xr2:uid="{B7364A64-1EA0-9049-A7FC-B4FA1E16182F}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Price" sheetId="4" r:id="rId1"/>
-    <sheet name="Cycloidal Gearbox" sheetId="1" r:id="rId2"/>
-    <sheet name="FOC PCB" sheetId="2" r:id="rId3"/>
-    <sheet name="Leg Assembly" sheetId="3" r:id="rId4"/>
+    <sheet name="Body Assembly" sheetId="6" r:id="rId2"/>
+    <sheet name="Cycloidal Gearbox" sheetId="1" r:id="rId3"/>
+    <sheet name="FOC PCB" sheetId="2" r:id="rId4"/>
+    <sheet name="Leg Assembly" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -39,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="292" uniqueCount="212">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="220">
   <si>
     <t>ITEM NO.</t>
   </si>
@@ -675,6 +676,30 @@
   </si>
   <si>
     <t>3D Printer Filament</t>
+  </si>
+  <si>
+    <t>Carbon Fiber Rods</t>
+  </si>
+  <si>
+    <t>https://a.co/d/098f3vCr</t>
+  </si>
+  <si>
+    <t>600MM Length Carbon Fiber Tube</t>
+  </si>
+  <si>
+    <t>Body Assembly</t>
+  </si>
+  <si>
+    <t>Funding Money</t>
+  </si>
+  <si>
+    <t>Who</t>
+  </si>
+  <si>
+    <t>Amount</t>
+  </si>
+  <si>
+    <t>Chad Robinson</t>
   </si>
 </sst>
 </file>
@@ -840,7 +865,7 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="53">
+  <cellXfs count="58">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
@@ -908,6 +933,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
@@ -941,17 +974,11 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
@@ -962,30 +989,38 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
     <cellStyle name="Hyperlink" xfId="2" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="6">
-    <dxf>
-      <fill>
-        <patternFill>
-          <bgColor theme="2" tint="-0.24994659260841701"/>
-        </patternFill>
-      </fill>
-    </dxf>
+  <dxfs count="5">
     <dxf>
       <fill>
         <patternFill>
@@ -1351,7 +1386,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4E62B7-8324-4D43-A746-C69356B7E16F}">
-  <dimension ref="A1:J7"/>
+  <dimension ref="A1:J18"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
@@ -1398,7 +1433,7 @@
         <f>'Cycloidal Gearbox'!I28</f>
         <v>81.931542499999978</v>
       </c>
-      <c r="D2" s="1">
+      <c r="D2" s="28">
         <v>12</v>
       </c>
       <c r="E2" s="25">
@@ -1431,11 +1466,11 @@
         <f>'Leg Assembly'!I25</f>
         <v>42.425021999999984</v>
       </c>
-      <c r="D3" s="1">
+      <c r="D3" s="28">
         <v>12</v>
       </c>
       <c r="E3" s="25">
-        <f t="shared" ref="E3:E6" si="0">C3*D3</f>
+        <f t="shared" ref="E3:E7" si="0">C3*D3</f>
         <v>509.10026399999981</v>
       </c>
       <c r="G3" s="1">
@@ -1464,7 +1499,7 @@
         <f>'FOC PCB'!I41</f>
         <v>38.513933333333327</v>
       </c>
-      <c r="D4" s="1">
+      <c r="D4" s="28">
         <v>12</v>
       </c>
       <c r="E4" s="25">
@@ -1496,7 +1531,7 @@
       <c r="C5" s="5">
         <v>8</v>
       </c>
-      <c r="D5" s="1">
+      <c r="D5" s="28">
         <v>1</v>
       </c>
       <c r="E5" s="25">
@@ -1527,12 +1562,12 @@
       <c r="C6" s="5">
         <v>15</v>
       </c>
-      <c r="D6" s="1">
-        <v>3</v>
+      <c r="D6" s="28">
+        <v>4</v>
       </c>
       <c r="E6" s="25">
         <f t="shared" si="0"/>
-        <v>45</v>
+        <v>60</v>
       </c>
       <c r="G6" s="1">
         <v>5</v>
@@ -1542,33 +1577,91 @@
       <c r="J6" s="5"/>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="29" t="s">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="C7" s="5">
+        <f>'Body Assembly'!L12</f>
+        <v>500</v>
+      </c>
+      <c r="D7" s="28">
+        <v>1</v>
+      </c>
+      <c r="E7" s="25">
+        <f t="shared" si="0"/>
+        <v>500</v>
+      </c>
+      <c r="G7" s="1">
+        <v>6</v>
+      </c>
+      <c r="H7" s="1"/>
+      <c r="I7" s="5"/>
+      <c r="J7" s="5"/>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A8" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="B7" s="29"/>
-      <c r="C7" s="29"/>
-      <c r="D7" s="29"/>
-      <c r="E7" s="13">
-        <f>SUM(E2:E6)</f>
-        <v>2007.4459739999993</v>
-      </c>
-      <c r="G7" s="30" t="s">
+      <c r="B8" s="33"/>
+      <c r="C8" s="33"/>
+      <c r="D8" s="33"/>
+      <c r="E8" s="13">
+        <f>SUM(E2:E7)</f>
+        <v>2522.4459739999993</v>
+      </c>
+      <c r="G8" s="34" t="s">
         <v>177</v>
       </c>
-      <c r="H7" s="31"/>
-      <c r="I7" s="32"/>
-      <c r="J7" s="13">
+      <c r="H8" s="35"/>
+      <c r="I8" s="36"/>
+      <c r="J8" s="13">
         <f>SUM(J2:J6)</f>
         <v>865.70788799999991</v>
       </c>
     </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A15" s="56" t="s">
+        <v>216</v>
+      </c>
+      <c r="B15" s="56"/>
+      <c r="C15" s="56"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+      <c r="A16" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="B16" s="57"/>
+      <c r="C16" s="1" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="B17" s="57"/>
+      <c r="C17" s="5">
+        <v>250</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="1"/>
+      <c r="B18" s="1"/>
+      <c r="C18" s="1"/>
+    </row>
   </sheetData>
-  <mergeCells count="2">
-    <mergeCell ref="A7:D7"/>
-    <mergeCell ref="G7:I7"/>
+  <mergeCells count="5">
+    <mergeCell ref="A8:D8"/>
+    <mergeCell ref="G8:I8"/>
+    <mergeCell ref="A17:B17"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="A15:C15"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:E6 G2:J6">
-    <cfRule type="expression" dxfId="5" priority="2">
+  <conditionalFormatting sqref="G2:J7 A2:E7">
+    <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -1577,6 +1670,292 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257BEE17-54E8-714C-9FC2-0AAD6BDD2F44}">
+  <dimension ref="A1:L46"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="2" max="2" width="33.33203125" customWidth="1"/>
+    <col min="3" max="3" width="31.33203125" customWidth="1"/>
+    <col min="4" max="4" width="57.5" customWidth="1"/>
+    <col min="5" max="5" width="12.6640625" customWidth="1"/>
+    <col min="6" max="6" width="17.5" customWidth="1"/>
+    <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="15" max="18" width="10.83203125" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="15" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="15" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="15" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="15" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="16" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="15" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="15" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="15" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="15" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="15" t="s">
+        <v>206</v>
+      </c>
+      <c r="K1" s="15" t="s">
+        <v>207</v>
+      </c>
+      <c r="L1" s="15" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A2" s="14">
+        <v>1</v>
+      </c>
+      <c r="B2" s="10"/>
+      <c r="C2" s="51"/>
+      <c r="D2" s="54"/>
+      <c r="E2" s="52"/>
+      <c r="F2" s="11"/>
+      <c r="G2" s="12"/>
+      <c r="H2" s="11"/>
+      <c r="I2" s="12"/>
+      <c r="J2" s="14"/>
+      <c r="K2" s="14"/>
+      <c r="L2" s="55"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A3" s="1">
+        <v>2</v>
+      </c>
+      <c r="B3" s="2"/>
+      <c r="C3" s="7"/>
+      <c r="D3" s="7"/>
+      <c r="E3" s="9"/>
+      <c r="F3" s="6"/>
+      <c r="G3" s="8"/>
+      <c r="H3" s="6"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="1"/>
+      <c r="K3" s="1"/>
+      <c r="L3" s="25"/>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A4" s="1">
+        <v>3</v>
+      </c>
+      <c r="B4" s="2"/>
+      <c r="C4" s="7"/>
+      <c r="D4" s="7"/>
+      <c r="E4" s="9"/>
+      <c r="F4" s="6"/>
+      <c r="G4" s="8"/>
+      <c r="H4" s="6"/>
+      <c r="I4" s="8"/>
+      <c r="J4" s="1"/>
+      <c r="K4" s="1"/>
+      <c r="L4" s="25"/>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A5" s="1">
+        <v>4</v>
+      </c>
+      <c r="B5" s="2"/>
+      <c r="C5" s="7"/>
+      <c r="D5" s="7"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="6"/>
+      <c r="G5" s="8"/>
+      <c r="H5" s="6"/>
+      <c r="I5" s="8"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="25"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A6" s="1">
+        <v>5</v>
+      </c>
+      <c r="B6" s="2"/>
+      <c r="C6" s="7"/>
+      <c r="D6" s="7"/>
+      <c r="E6" s="9"/>
+      <c r="F6" s="6"/>
+      <c r="G6" s="8"/>
+      <c r="H6" s="6"/>
+      <c r="I6" s="8"/>
+      <c r="J6" s="1"/>
+      <c r="K6" s="1"/>
+      <c r="L6" s="25"/>
+    </row>
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="1">
+        <v>6</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>214</v>
+      </c>
+      <c r="C7" s="7" t="s">
+        <v>212</v>
+      </c>
+      <c r="D7" s="53" t="s">
+        <v>213</v>
+      </c>
+      <c r="E7" s="9">
+        <v>25</v>
+      </c>
+      <c r="F7" s="6">
+        <v>2</v>
+      </c>
+      <c r="G7" s="8">
+        <f>E7/F7</f>
+        <v>12.5</v>
+      </c>
+      <c r="H7" s="6">
+        <v>2</v>
+      </c>
+      <c r="I7" s="8">
+        <f>G7*H7</f>
+        <v>25</v>
+      </c>
+      <c r="J7" s="1">
+        <v>0</v>
+      </c>
+      <c r="K7" s="1">
+        <v>4</v>
+      </c>
+      <c r="L7" s="25">
+        <f>K7*G7</f>
+        <v>50</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A8" s="1">
+        <v>7</v>
+      </c>
+      <c r="B8" s="2"/>
+      <c r="C8" s="7"/>
+      <c r="D8" s="7"/>
+      <c r="E8" s="9"/>
+      <c r="F8" s="6"/>
+      <c r="G8" s="8"/>
+      <c r="H8" s="6"/>
+      <c r="I8" s="8"/>
+      <c r="J8" s="1"/>
+      <c r="K8" s="1"/>
+      <c r="L8" s="25"/>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A9" s="1">
+        <v>8</v>
+      </c>
+      <c r="B9" s="2"/>
+      <c r="C9" s="7"/>
+      <c r="D9" s="7"/>
+      <c r="E9" s="9"/>
+      <c r="F9" s="6"/>
+      <c r="G9" s="8"/>
+      <c r="H9" s="6"/>
+      <c r="I9" s="8"/>
+      <c r="J9" s="1"/>
+      <c r="K9" s="1"/>
+      <c r="L9" s="25"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A10" s="1">
+        <v>9</v>
+      </c>
+      <c r="B10" s="2"/>
+      <c r="C10" s="7"/>
+      <c r="D10" s="7"/>
+      <c r="E10" s="9"/>
+      <c r="F10" s="6"/>
+      <c r="G10" s="8"/>
+      <c r="H10" s="6"/>
+      <c r="I10" s="8"/>
+      <c r="J10" s="1"/>
+      <c r="K10" s="1"/>
+      <c r="L10" s="25"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A11" s="1">
+        <v>10</v>
+      </c>
+      <c r="B11" s="2"/>
+      <c r="C11" s="7"/>
+      <c r="D11" s="7"/>
+      <c r="E11" s="9"/>
+      <c r="F11" s="6"/>
+      <c r="G11" s="8"/>
+      <c r="H11" s="6"/>
+      <c r="I11" s="8"/>
+      <c r="J11" s="1"/>
+      <c r="K11" s="1"/>
+      <c r="L11" s="25">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="33" t="s">
+        <v>61</v>
+      </c>
+      <c r="B12" s="33"/>
+      <c r="C12" s="33"/>
+      <c r="D12" s="33"/>
+      <c r="E12" s="33"/>
+      <c r="F12" s="33"/>
+      <c r="G12" s="33"/>
+      <c r="H12" s="33"/>
+      <c r="I12" s="13">
+        <f>SUM(I2:I10)</f>
+        <v>25</v>
+      </c>
+      <c r="J12" s="37" t="s">
+        <v>209</v>
+      </c>
+      <c r="K12" s="37"/>
+      <c r="L12" s="23">
+        <f>SUM(L2:L11)</f>
+        <v>500</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I16" s="30"/>
+    </row>
+    <row r="43" ht="31" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+  </sheetData>
+  <mergeCells count="2">
+    <mergeCell ref="A12:H12"/>
+    <mergeCell ref="J12:K12"/>
+  </mergeCells>
+  <conditionalFormatting sqref="A2:L11">
+    <cfRule type="expression" dxfId="3" priority="1">
+      <formula>MOD(ROW(),2)</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="D7" r:id="rId1" xr:uid="{57B4361D-48E2-3B41-B418-FE89579F184B}"/>
+  </hyperlinks>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BCE8930-9406-2043-8E02-400D939E2382}">
   <dimension ref="A1:L62"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -1635,13 +2014,13 @@
       <c r="B2" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="37" t="s">
+      <c r="C2" s="41" t="s">
         <v>62</v>
       </c>
-      <c r="D2" s="36" t="s">
+      <c r="D2" s="40" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="34">
+      <c r="E2" s="38">
         <v>29.98</v>
       </c>
       <c r="F2" s="11">
@@ -1663,7 +2042,7 @@
         <v>12</v>
       </c>
       <c r="L2" s="25">
-        <f>(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
+        <f t="shared" ref="L2:L27" si="0">(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
         <v>4.9610000000000003</v>
       </c>
     </row>
@@ -1674,9 +2053,9 @@
       <c r="B3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="34"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="38"/>
       <c r="F3" s="6">
         <v>3.0099999999999998E-2</v>
       </c>
@@ -1696,7 +2075,7 @@
         <v>12</v>
       </c>
       <c r="L3" s="25">
-        <f>(IF(K3-J3&lt;0,0,K3-J3))*G3</f>
+        <f t="shared" si="0"/>
         <v>4.9610000000000003</v>
       </c>
     </row>
@@ -1707,9 +2086,9 @@
       <c r="B4" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="34"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="38"/>
       <c r="F4" s="6">
         <v>1.15E-2</v>
       </c>
@@ -1729,7 +2108,7 @@
         <v>24</v>
       </c>
       <c r="L4" s="25">
-        <f>(IF(K4-J4&lt;0,0,K4-J4))*G4</f>
+        <f t="shared" si="0"/>
         <v>3.7839999999999998</v>
       </c>
     </row>
@@ -1740,9 +2119,9 @@
       <c r="B5" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="34"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="38"/>
       <c r="F5" s="6">
         <v>3.5999999999999999E-3</v>
       </c>
@@ -1762,7 +2141,7 @@
         <v>12</v>
       </c>
       <c r="L5" s="25">
-        <f>(IF(K5-J5&lt;0,0,K5-J5))*G5</f>
+        <f t="shared" si="0"/>
         <v>0.59399999999999997</v>
       </c>
     </row>
@@ -1773,9 +2152,9 @@
       <c r="B6" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="34"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="38"/>
       <c r="F6" s="6">
         <v>2.0000000000000001E-4</v>
       </c>
@@ -1795,7 +2174,7 @@
         <v>12</v>
       </c>
       <c r="L6" s="25">
-        <f>(IF(K6-J6&lt;0,0,K6-J6))*G6</f>
+        <f t="shared" si="0"/>
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
@@ -1806,9 +2185,9 @@
       <c r="B7" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="34"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="38"/>
       <c r="F7" s="6">
         <v>4.0000000000000002E-4</v>
       </c>
@@ -1828,7 +2207,7 @@
         <v>12</v>
       </c>
       <c r="L7" s="25">
-        <f>(IF(K7-J7&lt;0,0,K7-J7))*G7</f>
+        <f t="shared" si="0"/>
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
@@ -1839,9 +2218,9 @@
       <c r="B8" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="34"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="38"/>
       <c r="F8" s="6">
         <v>4.2200000000000001E-2</v>
       </c>
@@ -1861,7 +2240,7 @@
         <v>12</v>
       </c>
       <c r="L8" s="25">
-        <f>(IF(K8-J8&lt;0,0,K8-J8))*G8</f>
+        <f t="shared" si="0"/>
         <v>6.9630000000000001</v>
       </c>
     </row>
@@ -1872,9 +2251,9 @@
       <c r="B9" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="37"/>
-      <c r="D9" s="37"/>
-      <c r="E9" s="34"/>
+      <c r="C9" s="41"/>
+      <c r="D9" s="41"/>
+      <c r="E9" s="38"/>
       <c r="F9" s="6">
         <v>5.0000000000000001E-4</v>
       </c>
@@ -1894,7 +2273,7 @@
         <v>12</v>
       </c>
       <c r="L9" s="25">
-        <f>(IF(K9-J9&lt;0,0,K9-J9))*G9</f>
+        <f t="shared" si="0"/>
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
@@ -1905,9 +2284,9 @@
       <c r="B10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="37"/>
-      <c r="D10" s="37"/>
-      <c r="E10" s="34"/>
+      <c r="C10" s="41"/>
+      <c r="D10" s="41"/>
+      <c r="E10" s="38"/>
       <c r="F10" s="6">
         <v>3.2000000000000002E-3</v>
       </c>
@@ -1927,7 +2306,7 @@
         <v>12</v>
       </c>
       <c r="L10" s="25">
-        <f>(IF(K10-J10&lt;0,0,K10-J10))*G10</f>
+        <f t="shared" si="0"/>
         <v>0.53900000000000003</v>
       </c>
     </row>
@@ -1938,9 +2317,9 @@
       <c r="B11" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="37"/>
-      <c r="D11" s="37"/>
-      <c r="E11" s="34"/>
+      <c r="C11" s="41"/>
+      <c r="D11" s="41"/>
+      <c r="E11" s="38"/>
       <c r="F11" s="6">
         <v>1E-4</v>
       </c>
@@ -1960,7 +2339,7 @@
         <v>48</v>
       </c>
       <c r="L11" s="25">
-        <f>(IF(K11-J11&lt;0,0,K11-J11))*G11</f>
+        <f t="shared" si="0"/>
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
@@ -1971,9 +2350,9 @@
       <c r="B12" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="37"/>
-      <c r="D12" s="37"/>
-      <c r="E12" s="34"/>
+      <c r="C12" s="41"/>
+      <c r="D12" s="41"/>
+      <c r="E12" s="38"/>
       <c r="F12" s="6">
         <v>1.2500000000000001E-2</v>
       </c>
@@ -1993,7 +2372,7 @@
         <v>12</v>
       </c>
       <c r="L12" s="25">
-        <f>(IF(K12-J12&lt;0,0,K12-J12))*G12</f>
+        <f t="shared" si="0"/>
         <v>2.0680000000000001</v>
       </c>
     </row>
@@ -2004,9 +2383,9 @@
       <c r="B13" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="38"/>
-      <c r="D13" s="38"/>
-      <c r="E13" s="35"/>
+      <c r="C13" s="42"/>
+      <c r="D13" s="42"/>
+      <c r="E13" s="39"/>
       <c r="F13" s="6">
         <v>1.95E-2</v>
       </c>
@@ -2026,7 +2405,7 @@
         <v>12</v>
       </c>
       <c r="L13" s="25">
-        <f>(IF(K13-J13&lt;0,0,K13-J13))*G13</f>
+        <f t="shared" si="0"/>
         <v>3.2229999999999999</v>
       </c>
     </row>
@@ -2065,7 +2444,7 @@
         <v>24</v>
       </c>
       <c r="L14" s="25">
-        <f>(IF(K14-J14&lt;0,0,K14-J14))*G14</f>
+        <f t="shared" si="0"/>
         <v>53.371000000000002</v>
       </c>
     </row>
@@ -2104,7 +2483,7 @@
         <v>72</v>
       </c>
       <c r="L15" s="25">
-        <f>(IF(K15-J15&lt;0,0,K15-J15))*G15</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2143,7 +2522,7 @@
         <v>24</v>
       </c>
       <c r="L16" s="25">
-        <f>(IF(K16-J16&lt;0,0,K16-J16))*G16</f>
+        <f t="shared" si="0"/>
         <v>8.5579999999999998</v>
       </c>
     </row>
@@ -2182,7 +2561,7 @@
         <v>120</v>
       </c>
       <c r="L17" s="25">
-        <f>(IF(K17-J17&lt;0,0,K17-J17))*G17</f>
+        <f t="shared" si="0"/>
         <v>7.92</v>
       </c>
     </row>
@@ -2221,7 +2600,7 @@
         <v>48</v>
       </c>
       <c r="L18" s="25">
-        <f>(IF(K18-J18&lt;0,0,K18-J18))*G18</f>
+        <f t="shared" si="0"/>
         <v>4.29</v>
       </c>
     </row>
@@ -2260,7 +2639,7 @@
         <v>48</v>
       </c>
       <c r="L19" s="25">
-        <f>(IF(K19-J19&lt;0,0,K19-J19))*G19</f>
+        <f t="shared" si="0"/>
         <v>0.27200000000000002</v>
       </c>
     </row>
@@ -2299,7 +2678,7 @@
         <v>12</v>
       </c>
       <c r="L20" s="25">
-        <f>(IF(K20-J20&lt;0,0,K20-J20))*G20</f>
+        <f t="shared" si="0"/>
         <v>300</v>
       </c>
     </row>
@@ -2338,7 +2717,7 @@
         <v>12</v>
       </c>
       <c r="L21" s="25">
-        <f>(IF(K21-J21&lt;0,0,K21-J21))*G21</f>
+        <f t="shared" si="0"/>
         <v>6.2160000000000002</v>
       </c>
     </row>
@@ -2377,7 +2756,7 @@
         <v>72</v>
       </c>
       <c r="L22" s="25">
-        <f>(IF(K22-J22&lt;0,0,K22-J22))*G22</f>
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
@@ -2416,7 +2795,7 @@
         <v>72</v>
       </c>
       <c r="L23" s="25">
-        <f>(IF(K23-J23&lt;0,0,K23-J23))*G23</f>
+        <f t="shared" si="0"/>
         <v>36.527999999999999</v>
       </c>
     </row>
@@ -2455,7 +2834,7 @@
         <v>12</v>
       </c>
       <c r="L24" s="25">
-        <f>(IF(K24-J24&lt;0,0,K24-J24))*G24</f>
+        <f t="shared" si="0"/>
         <v>3.9569999999999999</v>
       </c>
     </row>
@@ -2494,7 +2873,7 @@
         <v>360</v>
       </c>
       <c r="L25" s="25">
-        <f>(IF(K25-J25&lt;0,0,K25-J25))*G25</f>
+        <f t="shared" si="0"/>
         <v>31.463999999999999</v>
       </c>
     </row>
@@ -2533,7 +2912,7 @@
         <v>72</v>
       </c>
       <c r="L26" s="25">
-        <f>(IF(K26-J26&lt;0,0,K26-J26))*G26</f>
+        <f t="shared" si="0"/>
         <v>2.044</v>
       </c>
     </row>
@@ -2572,43 +2951,36 @@
         <v>12</v>
       </c>
       <c r="L27" s="25">
-        <f>(IF(K27-J27&lt;0,0,K27-J27))*G27</f>
+        <f t="shared" si="0"/>
         <v>1.5960000000000001</v>
       </c>
     </row>
     <row r="28" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="29" t="s">
+      <c r="A28" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B28" s="29"/>
-      <c r="C28" s="29"/>
-      <c r="D28" s="29"/>
-      <c r="E28" s="29"/>
-      <c r="F28" s="29"/>
-      <c r="G28" s="29"/>
-      <c r="H28" s="29"/>
+      <c r="B28" s="33"/>
+      <c r="C28" s="33"/>
+      <c r="D28" s="33"/>
+      <c r="E28" s="33"/>
+      <c r="F28" s="33"/>
+      <c r="G28" s="33"/>
+      <c r="H28" s="33"/>
       <c r="I28" s="13">
         <f>SUM(I2:I27)</f>
         <v>81.931542499999978</v>
       </c>
-      <c r="J28" s="33" t="s">
+      <c r="J28" s="37" t="s">
         <v>209</v>
       </c>
-      <c r="K28" s="33"/>
+      <c r="K28" s="37"/>
       <c r="L28" s="23">
         <f>SUM(L2:L27)</f>
         <v>483.56200000000001</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G31" s="50"/>
-      <c r="H31" s="50"/>
-      <c r="I31" s="48"/>
-    </row>
     <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G32" s="50"/>
-      <c r="H32" s="50"/>
-      <c r="I32" s="49"/>
+      <c r="I32" s="30"/>
     </row>
     <row r="59" ht="31" customHeight="1" x14ac:dyDescent="0.2"/>
     <row r="60" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
@@ -2622,7 +2994,7 @@
     <mergeCell ref="C2:C13"/>
   </mergeCells>
   <conditionalFormatting sqref="A2:L27">
-    <cfRule type="expression" dxfId="4" priority="2">
+    <cfRule type="expression" dxfId="2" priority="2">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -2647,7 +3019,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2A752E-49A0-D348-9E27-6206B0A59C47}">
   <dimension ref="A1:L45"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4331,43 +4703,43 @@
       </c>
     </row>
     <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="29" t="s">
+      <c r="A41" s="33" t="s">
         <v>61</v>
       </c>
-      <c r="B41" s="29"/>
-      <c r="C41" s="29"/>
-      <c r="D41" s="29"/>
-      <c r="E41" s="29"/>
-      <c r="F41" s="29"/>
-      <c r="G41" s="29"/>
-      <c r="H41" s="29"/>
+      <c r="B41" s="33"/>
+      <c r="C41" s="33"/>
+      <c r="D41" s="33"/>
+      <c r="E41" s="33"/>
+      <c r="F41" s="33"/>
+      <c r="G41" s="33"/>
+      <c r="H41" s="33"/>
       <c r="I41" s="23">
         <f>SUM(I2:I40)</f>
         <v>38.513933333333327</v>
       </c>
-      <c r="J41" s="39" t="s">
+      <c r="J41" s="43" t="s">
         <v>209</v>
       </c>
-      <c r="K41" s="39"/>
+      <c r="K41" s="43"/>
       <c r="L41" s="23">
         <f>SUM(L2:L40)</f>
         <v>224.22380000000001</v>
       </c>
     </row>
     <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G44" s="29" t="s">
+      <c r="G44" s="33" t="s">
         <v>64</v>
       </c>
-      <c r="H44" s="29"/>
+      <c r="H44" s="33"/>
       <c r="I44" s="24">
         <v>12</v>
       </c>
     </row>
     <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G45" s="29" t="s">
+      <c r="G45" s="33" t="s">
         <v>63</v>
       </c>
-      <c r="H45" s="29"/>
+      <c r="H45" s="33"/>
       <c r="I45" s="23">
         <f>I41*I44</f>
         <v>462.16719999999992</v>
@@ -4381,7 +4753,7 @@
     <mergeCell ref="J41:K41"/>
   </mergeCells>
   <conditionalFormatting sqref="A2:L40">
-    <cfRule type="expression" dxfId="2" priority="1">
+    <cfRule type="expression" dxfId="1" priority="1">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
@@ -4423,7 +4795,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EFB1B7-3B23-654A-84A7-B98EF9661A5C}">
   <dimension ref="A1:L28"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
@@ -4483,13 +4855,13 @@
       <c r="B2" s="1" t="s">
         <v>73</v>
       </c>
-      <c r="C2" s="41" t="s">
+      <c r="C2" s="44" t="s">
         <v>74</v>
       </c>
-      <c r="D2" s="40" t="s">
+      <c r="D2" s="45" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="41">
+      <c r="E2" s="44">
         <v>29.98</v>
       </c>
       <c r="F2" s="1">
@@ -4503,18 +4875,18 @@
         <v>1</v>
       </c>
       <c r="I2" s="5">
-        <f>H2*G2</f>
+        <f t="shared" ref="I2:I24" si="0">H2*G2</f>
         <v>2.7656550000000002</v>
       </c>
       <c r="J2" s="1">
         <v>0</v>
       </c>
       <c r="K2" s="1">
-        <f>H2*4</f>
+        <f t="shared" ref="K2:K24" si="1">H2*4</f>
         <v>4</v>
       </c>
       <c r="L2" s="5">
-        <f>(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
+        <f t="shared" ref="L2:L24" si="2">(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
         <v>11.062620000000001</v>
       </c>
     </row>
@@ -4525,32 +4897,32 @@
       <c r="B3" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="C3" s="37"/>
-      <c r="D3" s="37"/>
-      <c r="E3" s="37"/>
+      <c r="C3" s="41"/>
+      <c r="D3" s="41"/>
+      <c r="E3" s="41"/>
       <c r="F3" s="1">
         <v>0.17349999999999999</v>
       </c>
       <c r="G3" s="5">
-        <f>F3*E$2/2</f>
+        <f t="shared" ref="G3:G9" si="3">F3*E$2/2</f>
         <v>2.600765</v>
       </c>
       <c r="H3" s="1">
         <v>1</v>
       </c>
       <c r="I3" s="5">
-        <f>H3*G3</f>
+        <f t="shared" si="0"/>
         <v>2.600765</v>
       </c>
       <c r="J3" s="1">
         <v>0</v>
       </c>
       <c r="K3" s="1">
-        <f>H3*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L3" s="5">
-        <f>(IF(K3-J3&lt;0,0,K3-J3))*G3</f>
+        <f t="shared" si="2"/>
         <v>10.40306</v>
       </c>
     </row>
@@ -4561,32 +4933,32 @@
       <c r="B4" s="1" t="s">
         <v>76</v>
       </c>
-      <c r="C4" s="37"/>
-      <c r="D4" s="37"/>
-      <c r="E4" s="37"/>
+      <c r="C4" s="41"/>
+      <c r="D4" s="41"/>
+      <c r="E4" s="41"/>
       <c r="F4" s="1">
         <v>1.9900000000000001E-2</v>
       </c>
       <c r="G4" s="5">
-        <f>F4*E$2/2</f>
+        <f t="shared" si="3"/>
         <v>0.29830100000000004</v>
       </c>
       <c r="H4" s="1">
         <v>1</v>
       </c>
       <c r="I4" s="5">
-        <f>H4*G4</f>
+        <f t="shared" si="0"/>
         <v>0.29830100000000004</v>
       </c>
       <c r="J4" s="1">
         <v>0</v>
       </c>
       <c r="K4" s="1">
-        <f>H4*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L4" s="5">
-        <f>(IF(K4-J4&lt;0,0,K4-J4))*G4</f>
+        <f t="shared" si="2"/>
         <v>1.1932040000000002</v>
       </c>
     </row>
@@ -4597,32 +4969,32 @@
       <c r="B5" s="1" t="s">
         <v>77</v>
       </c>
-      <c r="C5" s="37"/>
-      <c r="D5" s="37"/>
-      <c r="E5" s="37"/>
+      <c r="C5" s="41"/>
+      <c r="D5" s="41"/>
+      <c r="E5" s="41"/>
       <c r="F5" s="1">
         <v>6.54E-2</v>
       </c>
       <c r="G5" s="5">
-        <f>F5*E$2/2</f>
+        <f t="shared" si="3"/>
         <v>0.98034600000000005</v>
       </c>
       <c r="H5" s="1">
         <v>1</v>
       </c>
       <c r="I5" s="5">
-        <f>H5*G5</f>
+        <f t="shared" si="0"/>
         <v>0.98034600000000005</v>
       </c>
       <c r="J5" s="1">
         <v>0</v>
       </c>
       <c r="K5" s="1">
-        <f>H5*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L5" s="5">
-        <f>(IF(K5-J5&lt;0,0,K5-J5))*G5</f>
+        <f t="shared" si="2"/>
         <v>3.9213840000000002</v>
       </c>
     </row>
@@ -4633,32 +5005,32 @@
       <c r="B6" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="C6" s="37"/>
-      <c r="D6" s="37"/>
-      <c r="E6" s="37"/>
+      <c r="C6" s="41"/>
+      <c r="D6" s="41"/>
+      <c r="E6" s="41"/>
       <c r="F6" s="1">
         <v>0.18579999999999999</v>
       </c>
       <c r="G6" s="5">
-        <f>F6*E$2/2</f>
+        <f t="shared" si="3"/>
         <v>2.785142</v>
       </c>
       <c r="H6" s="1">
         <v>1</v>
       </c>
       <c r="I6" s="5">
-        <f>H6*G6</f>
+        <f t="shared" si="0"/>
         <v>2.785142</v>
       </c>
       <c r="J6" s="1">
         <v>0</v>
       </c>
       <c r="K6" s="1">
-        <f>H6*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L6" s="5">
-        <f>(IF(K6-J6&lt;0,0,K6-J6))*G6</f>
+        <f t="shared" si="2"/>
         <v>11.140568</v>
       </c>
     </row>
@@ -4669,32 +5041,32 @@
       <c r="B7" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="37"/>
-      <c r="D7" s="37"/>
-      <c r="E7" s="37"/>
+      <c r="C7" s="41"/>
+      <c r="D7" s="41"/>
+      <c r="E7" s="41"/>
       <c r="F7" s="1">
         <v>5.9299999999999999E-2</v>
       </c>
       <c r="G7" s="5">
-        <f>F7*E$2/2</f>
+        <f t="shared" si="3"/>
         <v>0.888907</v>
       </c>
       <c r="H7" s="1">
         <v>1</v>
       </c>
       <c r="I7" s="5">
-        <f>H7*G7</f>
+        <f t="shared" si="0"/>
         <v>0.888907</v>
       </c>
       <c r="J7" s="1">
         <v>0</v>
       </c>
       <c r="K7" s="1">
-        <f>H7*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L7" s="5">
-        <f>(IF(K7-J7&lt;0,0,K7-J7))*G7</f>
+        <f t="shared" si="2"/>
         <v>3.555628</v>
       </c>
     </row>
@@ -4705,32 +5077,32 @@
       <c r="B8" s="1" t="s">
         <v>80</v>
       </c>
-      <c r="C8" s="37"/>
-      <c r="D8" s="37"/>
-      <c r="E8" s="37"/>
+      <c r="C8" s="41"/>
+      <c r="D8" s="41"/>
+      <c r="E8" s="41"/>
       <c r="F8" s="1">
         <v>0.122</v>
       </c>
       <c r="G8" s="5">
-        <f>F8*E$2/2</f>
+        <f t="shared" si="3"/>
         <v>1.8287800000000001</v>
       </c>
       <c r="H8" s="1">
         <v>1</v>
       </c>
       <c r="I8" s="5">
-        <f>H8*G8</f>
+        <f t="shared" si="0"/>
         <v>1.8287800000000001</v>
       </c>
       <c r="J8" s="1">
         <v>0</v>
       </c>
       <c r="K8" s="1">
-        <f>H8*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L8" s="5">
-        <f>(IF(K8-J8&lt;0,0,K8-J8))*G8</f>
+        <f t="shared" si="2"/>
         <v>7.3151200000000003</v>
       </c>
     </row>
@@ -4741,32 +5113,32 @@
       <c r="B9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="C9" s="38"/>
-      <c r="D9" s="38"/>
-      <c r="E9" s="38"/>
+      <c r="C9" s="42"/>
+      <c r="D9" s="42"/>
+      <c r="E9" s="42"/>
       <c r="F9" s="1">
         <v>4.3700000000000003E-2</v>
       </c>
       <c r="G9" s="5">
-        <f>F9*E$2/2</f>
+        <f t="shared" si="3"/>
         <v>0.65506300000000006</v>
       </c>
       <c r="H9" s="1">
         <v>2</v>
       </c>
       <c r="I9" s="5">
-        <f>H9*G9</f>
+        <f t="shared" si="0"/>
         <v>1.3101260000000001</v>
       </c>
       <c r="J9" s="1">
         <v>0</v>
       </c>
       <c r="K9" s="1">
-        <f>H9*4</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="L9" s="5">
-        <f>(IF(K9-J9&lt;0,0,K9-J9))*G9</f>
+        <f t="shared" si="2"/>
         <v>5.2405040000000005</v>
       </c>
     </row>
@@ -4796,18 +5168,18 @@
         <v>1</v>
       </c>
       <c r="I10" s="5">
-        <f>H10*G10</f>
+        <f t="shared" si="0"/>
         <v>1.3939999999999999</v>
       </c>
       <c r="J10" s="1">
         <v>0</v>
       </c>
       <c r="K10" s="1">
-        <f>H10*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L10" s="5">
-        <f>(IF(K10-J10&lt;0,0,K10-J10))*G10</f>
+        <f t="shared" si="2"/>
         <v>5.5759999999999996</v>
       </c>
     </row>
@@ -4837,18 +5209,18 @@
         <v>3</v>
       </c>
       <c r="I11" s="5">
-        <f>H11*G11</f>
+        <f t="shared" si="0"/>
         <v>8.4269999999999996</v>
       </c>
       <c r="J11" s="1">
         <v>0</v>
       </c>
       <c r="K11" s="1">
-        <f>H11*4</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="L11" s="5">
-        <f>(IF(K11-J11&lt;0,0,K11-J11))*G11</f>
+        <f t="shared" si="2"/>
         <v>33.707999999999998</v>
       </c>
     </row>
@@ -4878,18 +5250,18 @@
         <v>12</v>
       </c>
       <c r="I12" s="5">
-        <f>H12*G12</f>
+        <f t="shared" si="0"/>
         <v>1.1040000000000001</v>
       </c>
       <c r="J12" s="1">
         <v>0</v>
       </c>
       <c r="K12" s="1">
-        <f>H12*4</f>
+        <f t="shared" si="1"/>
         <v>48</v>
       </c>
       <c r="L12" s="5">
-        <f>(IF(K12-J12&lt;0,0,K12-J12))*G12</f>
+        <f t="shared" si="2"/>
         <v>4.4160000000000004</v>
       </c>
     </row>
@@ -4919,18 +5291,18 @@
         <v>2</v>
       </c>
       <c r="I13" s="5">
-        <f>H13*G13</f>
+        <f t="shared" si="0"/>
         <v>0.99199999999999999</v>
       </c>
       <c r="J13" s="1">
         <v>9</v>
       </c>
       <c r="K13" s="1">
-        <f>H13*4</f>
+        <f t="shared" si="1"/>
         <v>8</v>
       </c>
       <c r="L13" s="5">
-        <f>(IF(K13-J13&lt;0,0,K13-J13))*G13</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -4960,18 +5332,18 @@
         <v>1</v>
       </c>
       <c r="I14" s="5">
-        <f>H14*G14</f>
+        <f t="shared" si="0"/>
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="J14" s="1">
         <v>0</v>
       </c>
       <c r="K14" s="1">
-        <f>H14*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L14" s="5">
-        <f>(IF(K14-J14&lt;0,0,K14-J14))*G14</f>
+        <f t="shared" si="2"/>
         <v>0.13600000000000001</v>
       </c>
     </row>
@@ -5001,18 +5373,18 @@
         <v>7</v>
       </c>
       <c r="I15" s="5">
-        <f>H15*G15</f>
+        <f t="shared" si="0"/>
         <v>4.8929999999999998</v>
       </c>
       <c r="J15" s="1">
         <v>0</v>
       </c>
       <c r="K15" s="1">
-        <f>H15*4</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="L15" s="5">
-        <f>(IF(K15-J15&lt;0,0,K15-J15))*G15</f>
+        <f t="shared" si="2"/>
         <v>19.571999999999999</v>
       </c>
     </row>
@@ -5042,18 +5414,18 @@
         <v>7</v>
       </c>
       <c r="I16" s="5">
-        <f>H16*G16</f>
+        <f t="shared" si="0"/>
         <v>1.022</v>
       </c>
       <c r="J16" s="1">
         <v>19</v>
       </c>
       <c r="K16" s="1">
-        <f>H16*4</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="L16" s="5">
-        <f>(IF(K16-J16&lt;0,0,K16-J16))*G16</f>
+        <f t="shared" si="2"/>
         <v>1.3139999999999998</v>
       </c>
     </row>
@@ -5083,18 +5455,18 @@
         <v>24</v>
       </c>
       <c r="I17" s="5">
-        <f>H17*G17</f>
+        <f t="shared" si="0"/>
         <v>1.6080000000000001</v>
       </c>
       <c r="J17" s="1">
         <v>0</v>
       </c>
       <c r="K17" s="1">
-        <f>H17*4</f>
+        <f t="shared" si="1"/>
         <v>96</v>
       </c>
       <c r="L17" s="5">
-        <f>(IF(K17-J17&lt;0,0,K17-J17))*G17</f>
+        <f t="shared" si="2"/>
         <v>6.4320000000000004</v>
       </c>
     </row>
@@ -5124,18 +5496,18 @@
         <v>7</v>
       </c>
       <c r="I18" s="5">
-        <f>H18*G18</f>
+        <f t="shared" si="0"/>
         <v>2.2400000000000002</v>
       </c>
       <c r="J18" s="1">
         <v>0</v>
       </c>
       <c r="K18" s="1">
-        <f>H18*4</f>
+        <f t="shared" si="1"/>
         <v>28</v>
       </c>
       <c r="L18" s="5">
-        <f>(IF(K18-J18&lt;0,0,K18-J18))*G18</f>
+        <f t="shared" si="2"/>
         <v>8.9600000000000009</v>
       </c>
     </row>
@@ -5165,18 +5537,18 @@
         <v>5</v>
       </c>
       <c r="I19" s="5">
-        <f>H19*G19</f>
+        <f t="shared" si="0"/>
         <v>4.1449999999999996</v>
       </c>
       <c r="J19" s="1">
         <v>10</v>
       </c>
       <c r="K19" s="1">
-        <f>H19*4</f>
+        <f t="shared" si="1"/>
         <v>20</v>
       </c>
       <c r="L19" s="5">
-        <f>(IF(K19-J19&lt;0,0,K19-J19))*G19</f>
+        <f t="shared" si="2"/>
         <v>8.2899999999999991</v>
       </c>
     </row>
@@ -5206,18 +5578,18 @@
         <v>1</v>
       </c>
       <c r="I20" s="5">
-        <f>H20*G20</f>
+        <f t="shared" si="0"/>
         <v>0.53800000000000003</v>
       </c>
       <c r="J20" s="1">
         <v>0</v>
       </c>
       <c r="K20" s="1">
-        <f>H20*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L20" s="5">
-        <f>(IF(K20-J20&lt;0,0,K20-J20))*G20</f>
+        <f t="shared" si="2"/>
         <v>2.1520000000000001</v>
       </c>
     </row>
@@ -5247,18 +5619,18 @@
         <v>3</v>
       </c>
       <c r="I21" s="5">
-        <f>H21*G21</f>
+        <f t="shared" si="0"/>
         <v>0.153</v>
       </c>
       <c r="J21" s="1">
         <v>40</v>
       </c>
       <c r="K21" s="1">
-        <f>H21*4</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="L21" s="5">
-        <f>(IF(K21-J21&lt;0,0,K21-J21))*G21</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5288,18 +5660,18 @@
         <v>1</v>
       </c>
       <c r="I22" s="5">
-        <f>H22*G22</f>
+        <f t="shared" si="0"/>
         <v>0.221</v>
       </c>
       <c r="J22" s="1">
         <v>0</v>
       </c>
       <c r="K22" s="1">
-        <f>H22*4</f>
+        <f t="shared" si="1"/>
         <v>4</v>
       </c>
       <c r="L22" s="5">
-        <f>(IF(K22-J22&lt;0,0,K22-J22))*G22</f>
+        <f t="shared" si="2"/>
         <v>0.88400000000000001</v>
       </c>
     </row>
@@ -5329,18 +5701,18 @@
         <v>3</v>
       </c>
       <c r="I23" s="5">
-        <f>H23*G23</f>
+        <f t="shared" si="0"/>
         <v>0.84599999999999986</v>
       </c>
       <c r="J23" s="1">
         <v>15</v>
       </c>
       <c r="K23" s="1">
-        <f>H23*4</f>
+        <f t="shared" si="1"/>
         <v>12</v>
       </c>
       <c r="L23" s="5">
-        <f>(IF(K23-J23&lt;0,0,K23-J23))*G23</f>
+        <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
@@ -5370,49 +5742,49 @@
         <v>18</v>
       </c>
       <c r="I24" s="5">
-        <f>H24*G24</f>
+        <f t="shared" si="0"/>
         <v>1.3499999999999999</v>
       </c>
       <c r="J24" s="1">
         <v>10</v>
       </c>
       <c r="K24" s="1">
-        <f>H24*4</f>
+        <f t="shared" si="1"/>
         <v>72</v>
       </c>
       <c r="L24" s="5">
-        <f>(IF(K24-J24&lt;0,0,K24-J24))*G24</f>
+        <f t="shared" si="2"/>
         <v>4.6499999999999995</v>
       </c>
     </row>
     <row r="25" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="44" t="s">
+      <c r="A25" s="46" t="s">
         <v>61</v>
       </c>
-      <c r="B25" s="45"/>
-      <c r="C25" s="45"/>
-      <c r="D25" s="45"/>
-      <c r="E25" s="45"/>
-      <c r="F25" s="45"/>
-      <c r="G25" s="45"/>
-      <c r="H25" s="46"/>
-      <c r="I25" s="47">
+      <c r="B25" s="47"/>
+      <c r="C25" s="47"/>
+      <c r="D25" s="47"/>
+      <c r="E25" s="47"/>
+      <c r="F25" s="47"/>
+      <c r="G25" s="47"/>
+      <c r="H25" s="48"/>
+      <c r="I25" s="29">
         <f>SUM(I2:I24)</f>
         <v>42.425021999999984</v>
       </c>
-      <c r="J25" s="42" t="s">
+      <c r="J25" s="49" t="s">
         <v>209</v>
       </c>
-      <c r="K25" s="43"/>
-      <c r="L25" s="47">
+      <c r="K25" s="50"/>
+      <c r="L25" s="29">
         <f>SUM(L2:L24)</f>
         <v>149.92208799999995</v>
       </c>
     </row>
     <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J28" s="51"/>
-      <c r="K28" s="51"/>
-      <c r="L28" s="52"/>
+      <c r="J28" s="31"/>
+      <c r="K28" s="31"/>
+      <c r="L28" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="5">
@@ -5422,7 +5794,7 @@
     <mergeCell ref="A25:H25"/>
     <mergeCell ref="J25:K25"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:L2 A3:B9 F3:J9 A10:J24 K3:L24">
+  <conditionalFormatting sqref="A2:L2 A3:B9 F3:J9 K3:L24 A10:J24">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>

--- a/Purchasing/BOM/Ultimate BOM.xlsx
+++ b/Purchasing/BOM/Ultimate BOM.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elijahrobinson/Documents/GitHub/Robot-Dog/Purchasing/BOM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/417d0fd5397d0872/Documentos/GitHub/Quadraped-Robot/Purchasing/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC9A2B99-3C50-4547-AB8C-86AC7DE28C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{DC9A2B99-3C50-4547-AB8C-86AC7DE28C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DADEC4E0-32E8-4DEC-876E-D290BBB68428}"/>
   <bookViews>
-    <workbookView xWindow="160" yWindow="920" windowWidth="29240" windowHeight="16880" xr2:uid="{B7364A64-1EA0-9049-A7FC-B4FA1E16182F}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{B7364A64-1EA0-9049-A7FC-B4FA1E16182F}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Price" sheetId="4" r:id="rId1"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="220">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="229">
   <si>
     <t>ITEM NO.</t>
   </si>
@@ -123,27 +123,18 @@
     <t>Screw to secure two Ring Gears together</t>
   </si>
   <si>
-    <t>https://www.aliexpress.us/item/2251832255868282.html</t>
-  </si>
-  <si>
     <t>15mm by 24mm by 5mm Ball Bearing</t>
   </si>
   <si>
     <t>Beaing for Cycloidal Gear</t>
   </si>
   <si>
-    <t>https://www.aliexpress.us/item/3256805951929226.html</t>
-  </si>
-  <si>
     <t>M3 by 8mm Button Head Cap Screw</t>
   </si>
   <si>
     <t>Screw for both Motor Mount and Motor Coupler connection</t>
   </si>
   <si>
-    <t>https://www.aliexpress.us/item/3256807424674896.html</t>
-  </si>
-  <si>
     <t>M4 by 8mm Button Head Cap Screw</t>
   </si>
   <si>
@@ -156,9 +147,6 @@
     <t>Nut to secure the FOC Board</t>
   </si>
   <si>
-    <t>https://www.aliexpress.us/item/3256807507915715.html</t>
-  </si>
-  <si>
     <t>HM-6208 motor</t>
   </si>
   <si>
@@ -213,18 +201,12 @@
     <t>M2.5 by 4mm by 6mm Heat Insert</t>
   </si>
   <si>
-    <t>https://a.co/d/0hLzXpKN</t>
-  </si>
-  <si>
     <t>Encoder Magnent</t>
   </si>
   <si>
     <t>Used on Encoder Magnent Mount for Position Feedback</t>
   </si>
   <si>
-    <t>https://a.co/d/0gZShhPf</t>
-  </si>
-  <si>
     <t>Total Cost Per Assembly($):</t>
   </si>
   <si>
@@ -312,9 +294,6 @@
     <t>For Small Leg Linkage Connection</t>
   </si>
   <si>
-    <t>https://www.aliexpress.us/item/3256806959412076.html</t>
-  </si>
-  <si>
     <t>M3*0.5*2.5mm Hex Nut</t>
   </si>
   <si>
@@ -342,9 +321,6 @@
     <t>M3*12mm Button Head Cap Screw</t>
   </si>
   <si>
-    <t>Screw For Most Actuattor-Bracket Connection</t>
-  </si>
-  <si>
     <t>5*8*6mm sleeve</t>
   </si>
   <si>
@@ -375,30 +351,15 @@
     <t>Hex Nut For Most Shoulder Bolt Connection</t>
   </si>
   <si>
-    <t>https://www.aliexpress.us/item/3256801453044560.html</t>
-  </si>
-  <si>
-    <t>M3*0.5*45mm Button Head Cap Screw</t>
-  </si>
-  <si>
-    <t>https://www.aliexpress.us/item/3256806241082021.html</t>
-  </si>
-  <si>
     <t>5*8*10mm sleeve</t>
   </si>
   <si>
     <t>https://a.co/d/05cPeEqb</t>
   </si>
   <si>
-    <t>M3*16mm Button Head Cap Screw</t>
-  </si>
-  <si>
     <t>Screw For Most Actuattor-Leg Components Connection</t>
   </si>
   <si>
-    <t>Item NO</t>
-  </si>
-  <si>
     <t>Item</t>
   </si>
   <si>
@@ -573,9 +534,6 @@
     <t>39-30-1042</t>
   </si>
   <si>
-    <t>Total Price:</t>
-  </si>
-  <si>
     <t>GRM21BC8YA106ME11L</t>
   </si>
   <si>
@@ -700,6 +658,75 @@
   </si>
   <si>
     <t>Chad Robinson</t>
+  </si>
+  <si>
+    <t>https://a.co/d/09Na5hOE</t>
+  </si>
+  <si>
+    <t>https://a.co/d/09gTfF0x</t>
+  </si>
+  <si>
+    <t>https://a.co/d/005UyY34</t>
+  </si>
+  <si>
+    <t>Screw For Most Gear Box-Motor Housing Connection</t>
+  </si>
+  <si>
+    <t>Sleeve Bearing Support for Leg Linkage Pin connection</t>
+  </si>
+  <si>
+    <t>https://a.co/d/08z1tbBh</t>
+  </si>
+  <si>
+    <t>https://a.co/d/03sRPgfF</t>
+  </si>
+  <si>
+    <t>https://a.co/d/09MrIxQw</t>
+  </si>
+  <si>
+    <t>M3*16mm Socket Head Cap Screw</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0gNaFcET</t>
+  </si>
+  <si>
+    <t>https://a.co/d/02tsqvkJ</t>
+  </si>
+  <si>
+    <t>https://a.co/d/02je179N</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0fTSP7Vz</t>
+  </si>
+  <si>
+    <t>https://a.co/d/09MJXPxa</t>
+  </si>
+  <si>
+    <t>https://a.co/d/04sPH867</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0fmXszQq</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0dExNett</t>
+  </si>
+  <si>
+    <t>Item NO.</t>
+  </si>
+  <si>
+    <t>Total Project Cost:</t>
+  </si>
+  <si>
+    <t>Additional Funding Needed:</t>
+  </si>
+  <si>
+    <t>Printed Body Part</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> All printed body parts including center body, shoulder-chest, and hip supporting panels printed with PLA</t>
+  </si>
+  <si>
+    <t>https://a.co/d/0axj8nc5</t>
   </si>
 </sst>
 </file>
@@ -709,7 +736,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="5" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -732,8 +759,21 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -743,6 +783,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="3" tint="0.749992370372631"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -865,15 +911,9 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="58">
+  <cellXfs count="60">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -881,17 +921,8 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -899,62 +930,30 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -971,49 +970,112 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="2" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="3" fillId="3" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
+      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="7" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1387,267 +1449,275 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4E62B7-8324-4D43-A746-C69356B7E16F}">
   <dimension ref="A1:J18"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A1" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="B1" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="C1" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="D1" s="24" t="s">
-        <v>121</v>
-      </c>
-      <c r="E1" s="24" t="s">
-        <v>125</v>
-      </c>
-      <c r="G1" s="24" t="s">
-        <v>118</v>
-      </c>
-      <c r="H1" s="24" t="s">
-        <v>119</v>
-      </c>
-      <c r="I1" s="24" t="s">
-        <v>120</v>
-      </c>
-      <c r="J1" s="24" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="C2" s="25">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A1" s="49" t="s">
+        <v>223</v>
+      </c>
+      <c r="B1" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="C1" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="D1" s="49" t="s">
+        <v>108</v>
+      </c>
+      <c r="E1" s="49" t="s">
+        <v>112</v>
+      </c>
+      <c r="F1" s="41"/>
+      <c r="G1" s="49" t="s">
+        <v>223</v>
+      </c>
+      <c r="H1" s="49" t="s">
+        <v>106</v>
+      </c>
+      <c r="I1" s="49" t="s">
+        <v>107</v>
+      </c>
+      <c r="J1" s="49" t="s">
+        <v>112</v>
+      </c>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="C2" s="30">
         <f>'Cycloidal Gearbox'!I28</f>
-        <v>81.931542499999978</v>
-      </c>
-      <c r="D2" s="28">
-        <v>12</v>
-      </c>
-      <c r="E2" s="25">
+        <v>83.953942499999997</v>
+      </c>
+      <c r="D2" s="4">
+        <v>12</v>
+      </c>
+      <c r="E2" s="30">
         <f>C2*D2</f>
-        <v>983.17850999999973</v>
-      </c>
-      <c r="G2" s="1">
-        <v>1</v>
-      </c>
-      <c r="H2" s="1" t="s">
-        <v>122</v>
-      </c>
-      <c r="I2" s="25">
+        <v>1007.44731</v>
+      </c>
+      <c r="F2" s="41"/>
+      <c r="G2" s="4">
+        <v>1</v>
+      </c>
+      <c r="H2" s="4" t="s">
+        <v>109</v>
+      </c>
+      <c r="I2" s="30">
         <f>'Cycloidal Gearbox'!I28</f>
-        <v>81.931542499999978</v>
-      </c>
-      <c r="J2" s="25">
+        <v>83.953942499999997</v>
+      </c>
+      <c r="J2" s="30">
         <f>'Cycloidal Gearbox'!L28</f>
-        <v>483.56200000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+        <v>202.56344999999999</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="C3" s="25">
-        <f>'Leg Assembly'!I25</f>
-        <v>42.425021999999984</v>
-      </c>
-      <c r="D3" s="28">
-        <v>12</v>
-      </c>
-      <c r="E3" s="25">
+      <c r="B3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C3" s="30">
+        <f>'Leg Assembly'!I24</f>
+        <v>45.291522000000008</v>
+      </c>
+      <c r="D3" s="4">
+        <v>12</v>
+      </c>
+      <c r="E3" s="30">
         <f t="shared" ref="E3:E7" si="0">C3*D3</f>
-        <v>509.10026399999981</v>
-      </c>
-      <c r="G3" s="1">
+        <v>543.49826400000006</v>
+      </c>
+      <c r="F3" s="41"/>
+      <c r="G3" s="4">
         <v>2</v>
       </c>
-      <c r="H3" s="1" t="s">
-        <v>123</v>
-      </c>
-      <c r="I3" s="25">
-        <f>'Leg Assembly'!I25</f>
-        <v>42.425021999999984</v>
-      </c>
-      <c r="J3" s="25">
-        <f>'Leg Assembly'!L25</f>
-        <v>149.92208799999995</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="H3" s="4" t="s">
+        <v>110</v>
+      </c>
+      <c r="I3" s="30">
+        <f>'Leg Assembly'!I24</f>
+        <v>45.291522000000008</v>
+      </c>
+      <c r="J3" s="30">
+        <f>'Leg Assembly'!L24</f>
+        <v>163.71478800000003</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="C4" s="25">
+      <c r="B4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="C4" s="30">
         <f>'FOC PCB'!I41</f>
         <v>38.513933333333327</v>
       </c>
-      <c r="D4" s="28">
-        <v>12</v>
-      </c>
-      <c r="E4" s="25">
+      <c r="D4" s="4">
+        <v>12</v>
+      </c>
+      <c r="E4" s="30">
         <f t="shared" si="0"/>
         <v>462.16719999999992</v>
       </c>
-      <c r="G4" s="1">
+      <c r="F4" s="41"/>
+      <c r="G4" s="4">
         <v>3</v>
       </c>
-      <c r="H4" s="1" t="s">
-        <v>124</v>
-      </c>
-      <c r="I4" s="25">
+      <c r="H4" s="4" t="s">
+        <v>111</v>
+      </c>
+      <c r="I4" s="30">
         <f>'FOC PCB'!I41</f>
         <v>38.513933333333327</v>
       </c>
-      <c r="J4" s="25">
+      <c r="J4" s="30">
         <f>'FOC PCB'!L41</f>
         <v>224.22380000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>205</v>
+      <c r="B5" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="C5" s="5">
         <v>8</v>
       </c>
-      <c r="D5" s="28">
-        <v>1</v>
-      </c>
-      <c r="E5" s="25">
+      <c r="D5" s="4">
+        <v>1</v>
+      </c>
+      <c r="E5" s="30">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="G5" s="1">
+      <c r="F5" s="41"/>
+      <c r="G5" s="4">
         <v>4</v>
       </c>
-      <c r="H5" s="1" t="s">
-        <v>205</v>
+      <c r="H5" s="4" t="s">
+        <v>191</v>
       </c>
       <c r="I5" s="5">
         <v>8</v>
       </c>
-      <c r="J5" s="25">
+      <c r="J5" s="30">
         <f>1*I5</f>
         <v>8</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>211</v>
+      <c r="B6" s="4" t="s">
+        <v>197</v>
       </c>
       <c r="C6" s="5">
         <v>15</v>
       </c>
-      <c r="D6" s="28">
+      <c r="D6" s="4">
         <v>4</v>
       </c>
-      <c r="E6" s="25">
+      <c r="E6" s="30">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="G6" s="1">
+      <c r="F6" s="41"/>
+      <c r="G6" s="4">
         <v>5</v>
       </c>
-      <c r="H6" s="1"/>
+      <c r="H6" s="4"/>
       <c r="I6" s="5"/>
       <c r="J6" s="5"/>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>215</v>
+      <c r="B7" s="4" t="s">
+        <v>201</v>
       </c>
       <c r="C7" s="5">
         <f>'Body Assembly'!L12</f>
-        <v>500</v>
-      </c>
-      <c r="D7" s="28">
-        <v>1</v>
-      </c>
-      <c r="E7" s="25">
-        <f t="shared" si="0"/>
-        <v>500</v>
-      </c>
-      <c r="G7" s="1">
+        <v>489.98436000000004</v>
+      </c>
+      <c r="D7" s="4">
+        <v>1</v>
+      </c>
+      <c r="E7" s="30">
+        <f t="shared" si="0"/>
+        <v>489.98436000000004</v>
+      </c>
+      <c r="F7" s="41"/>
+      <c r="G7" s="4">
         <v>6</v>
       </c>
-      <c r="H7" s="1"/>
+      <c r="H7" s="4"/>
       <c r="I7" s="5"/>
       <c r="J7" s="5"/>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A8" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="B8" s="33"/>
-      <c r="C8" s="33"/>
-      <c r="D8" s="33"/>
-      <c r="E8" s="13">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A8" s="32" t="s">
+        <v>224</v>
+      </c>
+      <c r="B8" s="32"/>
+      <c r="C8" s="32"/>
+      <c r="D8" s="32"/>
+      <c r="E8" s="33">
         <f>SUM(E2:E7)</f>
-        <v>2522.4459739999993</v>
-      </c>
-      <c r="G8" s="34" t="s">
-        <v>177</v>
-      </c>
-      <c r="H8" s="35"/>
-      <c r="I8" s="36"/>
-      <c r="J8" s="13">
+        <v>2571.0971340000001</v>
+      </c>
+      <c r="F8" s="41"/>
+      <c r="G8" s="50" t="s">
+        <v>225</v>
+      </c>
+      <c r="H8" s="51"/>
+      <c r="I8" s="52"/>
+      <c r="J8" s="33">
         <f>SUM(J2:J6)</f>
-        <v>865.70788799999991</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A15" s="56" t="s">
-        <v>216</v>
-      </c>
-      <c r="B15" s="56"/>
-      <c r="C15" s="56"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
-      <c r="A16" s="57" t="s">
-        <v>217</v>
-      </c>
-      <c r="B16" s="57"/>
+        <v>598.50203799999997</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A15" s="18" t="s">
+        <v>202</v>
+      </c>
+      <c r="B15" s="18"/>
+      <c r="C15" s="18"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
+      <c r="A16" s="17" t="s">
+        <v>203</v>
+      </c>
+      <c r="B16" s="17"/>
       <c r="C16" s="1" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
-      <c r="A17" s="57" t="s">
-        <v>219</v>
-      </c>
-      <c r="B17" s="57"/>
-      <c r="C17" s="5">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A17" s="17" t="s">
+        <v>205</v>
+      </c>
+      <c r="B17" s="17"/>
+      <c r="C17" s="3">
         <v>250</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" s="1"/>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
@@ -1660,7 +1730,7 @@
     <mergeCell ref="A16:B16"/>
     <mergeCell ref="A15:C15"/>
   </mergeCells>
-  <conditionalFormatting sqref="G2:J7 A2:E7">
+  <conditionalFormatting sqref="A2:E7 G2:J7">
     <cfRule type="expression" dxfId="4" priority="2">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
@@ -1672,7 +1742,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257BEE17-54E8-714C-9FC2-0AAD6BDD2F44}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="31.33203125" customWidth="1"/>
@@ -1680,264 +1750,291 @@
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="11" max="11" width="13.08203125" customWidth="1"/>
+    <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="15" max="18" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:12" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="B1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="15" t="s">
-        <v>206</v>
-      </c>
-      <c r="K1" s="15" t="s">
-        <v>207</v>
-      </c>
-      <c r="L1" s="15" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="14">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10"/>
-      <c r="C2" s="51"/>
-      <c r="D2" s="54"/>
-      <c r="E2" s="52"/>
-      <c r="F2" s="11"/>
-      <c r="G2" s="12"/>
-      <c r="H2" s="11"/>
-      <c r="I2" s="12"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="55"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+      <c r="J1" s="26" t="s">
+        <v>192</v>
+      </c>
+      <c r="K1" s="26" t="s">
+        <v>193</v>
+      </c>
+      <c r="L1" s="26" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="53.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="29" t="s">
+        <v>226</v>
+      </c>
+      <c r="C2" s="29" t="s">
+        <v>227</v>
+      </c>
+      <c r="D2" s="47" t="s">
+        <v>228</v>
+      </c>
+      <c r="E2" s="7">
+        <v>26.98</v>
+      </c>
+      <c r="F2" s="6">
         <v>2</v>
       </c>
-      <c r="B3" s="2"/>
-      <c r="C3" s="7"/>
-      <c r="D3" s="7"/>
-      <c r="E3" s="9"/>
-      <c r="F3" s="6"/>
-      <c r="G3" s="8"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="8"/>
-      <c r="J3" s="1"/>
-      <c r="K3" s="1"/>
-      <c r="L3" s="25"/>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+      <c r="G2" s="7">
+        <f>E2*0.741/F2</f>
+        <v>9.9960900000000006</v>
+      </c>
+      <c r="H2" s="6">
+        <v>2</v>
+      </c>
+      <c r="I2" s="7">
+        <f>G2*H2</f>
+        <v>19.992180000000001</v>
+      </c>
+      <c r="J2" s="6">
+        <v>0</v>
+      </c>
+      <c r="K2" s="6">
+        <v>2</v>
+      </c>
+      <c r="L2" s="48">
+        <f>I2*K2</f>
+        <v>39.984360000000002</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
+        <v>2</v>
+      </c>
+      <c r="B3" s="31"/>
+      <c r="C3" s="4"/>
+      <c r="D3" s="4"/>
+      <c r="E3" s="5"/>
+      <c r="F3" s="4"/>
+      <c r="G3" s="5"/>
+      <c r="H3" s="4"/>
+      <c r="I3" s="5"/>
+      <c r="J3" s="4"/>
+      <c r="K3" s="4"/>
+      <c r="L3" s="30"/>
+    </row>
+    <row r="4" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="2"/>
-      <c r="C4" s="7"/>
-      <c r="D4" s="7"/>
-      <c r="E4" s="9"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="8"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="8"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="25"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+      <c r="B4" s="31"/>
+      <c r="C4" s="4"/>
+      <c r="D4" s="4"/>
+      <c r="E4" s="5"/>
+      <c r="F4" s="4"/>
+      <c r="G4" s="5"/>
+      <c r="H4" s="4"/>
+      <c r="I4" s="5"/>
+      <c r="J4" s="4"/>
+      <c r="K4" s="4"/>
+      <c r="L4" s="30"/>
+    </row>
+    <row r="5" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="2"/>
-      <c r="C5" s="7"/>
-      <c r="D5" s="7"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="6"/>
-      <c r="G5" s="8"/>
-      <c r="H5" s="6"/>
-      <c r="I5" s="8"/>
-      <c r="J5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="25"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+      <c r="B5" s="31"/>
+      <c r="C5" s="4"/>
+      <c r="D5" s="4"/>
+      <c r="E5" s="5"/>
+      <c r="F5" s="4"/>
+      <c r="G5" s="5"/>
+      <c r="H5" s="4"/>
+      <c r="I5" s="5"/>
+      <c r="J5" s="4"/>
+      <c r="K5" s="4"/>
+      <c r="L5" s="30"/>
+    </row>
+    <row r="6" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="2"/>
-      <c r="C6" s="7"/>
-      <c r="D6" s="7"/>
-      <c r="E6" s="9"/>
-      <c r="F6" s="6"/>
-      <c r="G6" s="8"/>
-      <c r="H6" s="6"/>
-      <c r="I6" s="8"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="25"/>
-    </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+      <c r="B6" s="31"/>
+      <c r="C6" s="4"/>
+      <c r="D6" s="4"/>
+      <c r="E6" s="5"/>
+      <c r="F6" s="4"/>
+      <c r="G6" s="5"/>
+      <c r="H6" s="4"/>
+      <c r="I6" s="5"/>
+      <c r="J6" s="4"/>
+      <c r="K6" s="4"/>
+      <c r="L6" s="30"/>
+    </row>
+    <row r="7" spans="1:12" ht="24.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>214</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>212</v>
-      </c>
-      <c r="D7" s="53" t="s">
-        <v>213</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="B7" s="31" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>199</v>
+      </c>
+      <c r="E7" s="5">
         <v>25</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>2</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="5">
         <f>E7/F7</f>
         <v>12.5</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <v>2</v>
       </c>
-      <c r="I7" s="8">
+      <c r="I7" s="5">
         <f>G7*H7</f>
         <v>25</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="4">
         <v>0</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="4">
         <v>4</v>
       </c>
-      <c r="L7" s="25">
+      <c r="L7" s="30">
         <f>K7*G7</f>
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+    <row r="8" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="2"/>
-      <c r="C8" s="7"/>
-      <c r="D8" s="7"/>
-      <c r="E8" s="9"/>
-      <c r="F8" s="6"/>
-      <c r="G8" s="8"/>
-      <c r="H8" s="6"/>
-      <c r="I8" s="8"/>
-      <c r="J8" s="1"/>
-      <c r="K8" s="1"/>
-      <c r="L8" s="25"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+      <c r="B8" s="31"/>
+      <c r="C8" s="4"/>
+      <c r="D8" s="4"/>
+      <c r="E8" s="5"/>
+      <c r="F8" s="4"/>
+      <c r="G8" s="5"/>
+      <c r="H8" s="4"/>
+      <c r="I8" s="5"/>
+      <c r="J8" s="4"/>
+      <c r="K8" s="4"/>
+      <c r="L8" s="30"/>
+    </row>
+    <row r="9" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="2"/>
-      <c r="C9" s="7"/>
-      <c r="D9" s="7"/>
-      <c r="E9" s="9"/>
-      <c r="F9" s="6"/>
-      <c r="G9" s="8"/>
-      <c r="H9" s="6"/>
-      <c r="I9" s="8"/>
-      <c r="J9" s="1"/>
-      <c r="K9" s="1"/>
-      <c r="L9" s="25"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+      <c r="B9" s="31"/>
+      <c r="C9" s="4"/>
+      <c r="D9" s="4"/>
+      <c r="E9" s="5"/>
+      <c r="F9" s="4"/>
+      <c r="G9" s="5"/>
+      <c r="H9" s="4"/>
+      <c r="I9" s="5"/>
+      <c r="J9" s="4"/>
+      <c r="K9" s="4"/>
+      <c r="L9" s="30"/>
+    </row>
+    <row r="10" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="2"/>
-      <c r="C10" s="7"/>
-      <c r="D10" s="7"/>
-      <c r="E10" s="9"/>
-      <c r="F10" s="6"/>
-      <c r="G10" s="8"/>
-      <c r="H10" s="6"/>
-      <c r="I10" s="8"/>
-      <c r="J10" s="1"/>
-      <c r="K10" s="1"/>
-      <c r="L10" s="25"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+      <c r="B10" s="31"/>
+      <c r="C10" s="4"/>
+      <c r="D10" s="4"/>
+      <c r="E10" s="5"/>
+      <c r="F10" s="4"/>
+      <c r="G10" s="5"/>
+      <c r="H10" s="4"/>
+      <c r="I10" s="5"/>
+      <c r="J10" s="4"/>
+      <c r="K10" s="4"/>
+      <c r="L10" s="30"/>
+    </row>
+    <row r="11" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="2"/>
-      <c r="C11" s="7"/>
-      <c r="D11" s="7"/>
-      <c r="E11" s="9"/>
-      <c r="F11" s="6"/>
-      <c r="G11" s="8"/>
-      <c r="H11" s="6"/>
-      <c r="I11" s="8"/>
-      <c r="J11" s="1"/>
-      <c r="K11" s="1"/>
-      <c r="L11" s="25">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A12" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B12" s="33"/>
-      <c r="C12" s="33"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="33"/>
-      <c r="F12" s="33"/>
-      <c r="G12" s="33"/>
-      <c r="H12" s="33"/>
-      <c r="I12" s="13">
+      <c r="B11" s="31"/>
+      <c r="C11" s="4"/>
+      <c r="D11" s="4"/>
+      <c r="E11" s="5"/>
+      <c r="F11" s="4"/>
+      <c r="G11" s="5"/>
+      <c r="H11" s="4"/>
+      <c r="I11" s="5"/>
+      <c r="J11" s="4"/>
+      <c r="K11" s="4"/>
+      <c r="L11" s="30">
+        <v>400</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="39.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B12" s="32"/>
+      <c r="C12" s="32"/>
+      <c r="D12" s="32"/>
+      <c r="E12" s="32"/>
+      <c r="F12" s="32"/>
+      <c r="G12" s="32"/>
+      <c r="H12" s="32"/>
+      <c r="I12" s="33">
         <f>SUM(I2:I10)</f>
-        <v>25</v>
-      </c>
-      <c r="J12" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K12" s="37"/>
-      <c r="L12" s="23">
+        <v>44.992180000000005</v>
+      </c>
+      <c r="J12" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="K12" s="34"/>
+      <c r="L12" s="35">
         <f>SUM(L2:L11)</f>
-        <v>500</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="I16" s="30"/>
-    </row>
-    <row r="43" ht="31" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="44" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="46" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>489.98436000000004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="I16" s="12"/>
+    </row>
+    <row r="43" ht="31" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="44" ht="32" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="46" ht="32" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A12:H12"/>
@@ -1950,6 +2047,7 @@
   </conditionalFormatting>
   <hyperlinks>
     <hyperlink ref="D7" r:id="rId1" xr:uid="{57B4361D-48E2-3B41-B418-FE89579F184B}"/>
+    <hyperlink ref="D2" r:id="rId2" xr:uid="{513F95C4-2F64-4FBF-AFF2-59EC9F88E043}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1958,7 +2056,7 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BCE8930-9406-2043-8E02-400D939E2382}">
   <dimension ref="A1:L62"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="31.33203125" customWidth="1"/>
@@ -1966,1025 +2064,1068 @@
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
+    <col min="12" max="12" width="18.4140625" customWidth="1"/>
     <col min="15" max="18" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="53" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="15" t="s">
+    <row r="1" spans="1:12" ht="83.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="26" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="15" t="s">
+      <c r="B1" s="26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="26" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="26" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="16" t="s">
+      <c r="E1" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="15" t="s">
+      <c r="F1" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="15" t="s">
+      <c r="G1" s="26" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="26" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="26" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
-        <v>206</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="14">
-        <v>1</v>
-      </c>
-      <c r="B2" s="10" t="s">
+      <c r="J1" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="6">
+        <v>1</v>
+      </c>
+      <c r="B2" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="D2" s="40" t="s">
+      <c r="C2" s="22" t="s">
+        <v>56</v>
+      </c>
+      <c r="D2" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="38">
+      <c r="E2" s="19">
         <v>29.98</v>
       </c>
-      <c r="F2" s="11">
+      <c r="F2" s="6">
         <v>3.0099999999999998E-2</v>
       </c>
-      <c r="G2" s="12">
+      <c r="G2" s="7">
         <v>0.45100000000000001</v>
       </c>
-      <c r="H2" s="11">
-        <v>1</v>
-      </c>
-      <c r="I2" s="12">
+      <c r="H2" s="6">
+        <v>1</v>
+      </c>
+      <c r="I2" s="7">
         <v>0.45119900000000002</v>
       </c>
-      <c r="J2" s="1">
-        <v>1</v>
-      </c>
-      <c r="K2" s="1">
-        <v>12</v>
-      </c>
-      <c r="L2" s="25">
+      <c r="J2" s="4">
+        <v>1</v>
+      </c>
+      <c r="K2" s="4">
+        <v>12</v>
+      </c>
+      <c r="L2" s="30">
         <f t="shared" ref="L2:L27" si="0">(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
         <v>4.9610000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+    <row r="3" spans="1:12" ht="30.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
+      <c r="B3" s="31" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="38"/>
-      <c r="F3" s="6">
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="4">
         <v>3.0099999999999998E-2</v>
       </c>
-      <c r="G3" s="8">
+      <c r="G3" s="5">
         <v>0.45100000000000001</v>
       </c>
-      <c r="H3" s="6">
-        <v>1</v>
-      </c>
-      <c r="I3" s="8">
+      <c r="H3" s="4">
+        <v>1</v>
+      </c>
+      <c r="I3" s="5">
         <v>0.45119900000000002</v>
       </c>
-      <c r="J3" s="1">
-        <v>1</v>
-      </c>
-      <c r="K3" s="1">
-        <v>12</v>
-      </c>
-      <c r="L3" s="25">
+      <c r="J3" s="4">
+        <v>1</v>
+      </c>
+      <c r="K3" s="4">
+        <v>12</v>
+      </c>
+      <c r="L3" s="30">
         <f t="shared" si="0"/>
         <v>4.9610000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+    <row r="4" spans="1:12" ht="39.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="38"/>
-      <c r="F4" s="6">
+      <c r="B4" s="31" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="19"/>
+      <c r="F4" s="4">
         <v>1.15E-2</v>
       </c>
-      <c r="G4" s="8">
+      <c r="G4" s="5">
         <v>0.17199999999999999</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <v>2</v>
       </c>
-      <c r="I4" s="8">
+      <c r="I4" s="5">
         <v>0.3444702</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="4">
         <v>2</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="4">
         <v>24</v>
       </c>
-      <c r="L4" s="25">
+      <c r="L4" s="30">
         <f t="shared" si="0"/>
         <v>3.7839999999999998</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="31" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="38"/>
-      <c r="F5" s="6">
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="19"/>
+      <c r="F5" s="4">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="G5" s="8">
+      <c r="G5" s="5">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="H5" s="6">
-        <v>1</v>
-      </c>
-      <c r="I5" s="8">
+      <c r="H5" s="4">
+        <v>1</v>
+      </c>
+      <c r="I5" s="5">
         <v>5.3514300000000001E-2</v>
       </c>
-      <c r="J5" s="1">
-        <v>1</v>
-      </c>
-      <c r="K5" s="1">
-        <v>12</v>
-      </c>
-      <c r="L5" s="25">
+      <c r="J5" s="4">
+        <v>1</v>
+      </c>
+      <c r="K5" s="4">
+        <v>12</v>
+      </c>
+      <c r="L5" s="30">
         <f t="shared" si="0"/>
         <v>0.59399999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="14">
+    <row r="6" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="6">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
+      <c r="B6" s="31" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="38"/>
-      <c r="F6" s="6">
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="19"/>
+      <c r="F6" s="4">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="G6" s="8">
+      <c r="G6" s="5">
         <v>2E-3</v>
       </c>
-      <c r="H6" s="6">
-        <v>1</v>
-      </c>
-      <c r="I6" s="8">
+      <c r="H6" s="4">
+        <v>1</v>
+      </c>
+      <c r="I6" s="5">
         <v>2.3984000000000002E-3</v>
       </c>
-      <c r="J6" s="1">
-        <v>1</v>
-      </c>
-      <c r="K6" s="1">
-        <v>12</v>
-      </c>
-      <c r="L6" s="25">
+      <c r="J6" s="4">
+        <v>1</v>
+      </c>
+      <c r="K6" s="4">
+        <v>12</v>
+      </c>
+      <c r="L6" s="30">
         <f t="shared" si="0"/>
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+    <row r="7" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
+      <c r="B7" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="38"/>
-      <c r="F7" s="6">
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="19"/>
+      <c r="F7" s="4">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="G7" s="8">
+      <c r="G7" s="5">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="H7" s="6">
-        <v>1</v>
-      </c>
-      <c r="I7" s="8">
+      <c r="H7" s="4">
+        <v>1</v>
+      </c>
+      <c r="I7" s="5">
         <v>5.5462999999999997E-3</v>
       </c>
-      <c r="J7" s="1">
-        <v>1</v>
-      </c>
-      <c r="K7" s="1">
-        <v>12</v>
-      </c>
-      <c r="L7" s="25">
+      <c r="J7" s="4">
+        <v>1</v>
+      </c>
+      <c r="K7" s="4">
+        <v>12</v>
+      </c>
+      <c r="L7" s="30">
         <f t="shared" si="0"/>
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+    <row r="8" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
+      <c r="B8" s="31" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="38"/>
-      <c r="F8" s="6">
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="19"/>
+      <c r="F8" s="4">
         <v>4.2200000000000001E-2</v>
       </c>
-      <c r="G8" s="8">
+      <c r="G8" s="5">
         <v>0.63300000000000001</v>
       </c>
-      <c r="H8" s="6">
-        <v>1</v>
-      </c>
-      <c r="I8" s="8">
+      <c r="H8" s="4">
+        <v>1</v>
+      </c>
+      <c r="I8" s="5">
         <v>0.63272790000000001</v>
       </c>
-      <c r="J8" s="1">
-        <v>1</v>
-      </c>
-      <c r="K8" s="1">
-        <v>12</v>
-      </c>
-      <c r="L8" s="25">
+      <c r="J8" s="4">
+        <v>1</v>
+      </c>
+      <c r="K8" s="4">
+        <v>12</v>
+      </c>
+      <c r="L8" s="30">
         <f t="shared" si="0"/>
         <v>6.9630000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+    <row r="9" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
+      <c r="B9" s="31" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="41"/>
-      <c r="D9" s="41"/>
-      <c r="E9" s="38"/>
-      <c r="F9" s="6">
+      <c r="C9" s="22"/>
+      <c r="D9" s="22"/>
+      <c r="E9" s="19"/>
+      <c r="F9" s="4">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="G9" s="8">
+      <c r="G9" s="5">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="H9" s="6">
-        <v>1</v>
-      </c>
-      <c r="I9" s="8">
+      <c r="H9" s="4">
+        <v>1</v>
+      </c>
+      <c r="I9" s="5">
         <v>6.8954000000000003E-3</v>
       </c>
-      <c r="J9" s="1">
-        <v>1</v>
-      </c>
-      <c r="K9" s="1">
-        <v>12</v>
-      </c>
-      <c r="L9" s="25">
+      <c r="J9" s="4">
+        <v>1</v>
+      </c>
+      <c r="K9" s="4">
+        <v>12</v>
+      </c>
+      <c r="L9" s="30">
         <f t="shared" si="0"/>
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="14">
+    <row r="10" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="6">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
+      <c r="B10" s="31" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="41"/>
-      <c r="D10" s="41"/>
-      <c r="E10" s="38"/>
-      <c r="F10" s="6">
+      <c r="C10" s="22"/>
+      <c r="D10" s="22"/>
+      <c r="E10" s="19"/>
+      <c r="F10" s="4">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="G10" s="8">
+      <c r="G10" s="5">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="H10" s="6">
-        <v>1</v>
-      </c>
-      <c r="I10" s="8">
+      <c r="H10" s="4">
+        <v>1</v>
+      </c>
+      <c r="I10" s="5">
         <v>4.8567600000000002E-2</v>
       </c>
-      <c r="J10" s="1">
-        <v>1</v>
-      </c>
-      <c r="K10" s="1">
-        <v>12</v>
-      </c>
-      <c r="L10" s="25">
+      <c r="J10" s="4">
+        <v>1</v>
+      </c>
+      <c r="K10" s="4">
+        <v>12</v>
+      </c>
+      <c r="L10" s="30">
         <f t="shared" si="0"/>
         <v>0.53900000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
+      <c r="B11" s="31" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="41"/>
-      <c r="D11" s="41"/>
-      <c r="E11" s="38"/>
-      <c r="F11" s="6">
+      <c r="C11" s="22"/>
+      <c r="D11" s="22"/>
+      <c r="E11" s="19"/>
+      <c r="F11" s="4">
         <v>1E-4</v>
       </c>
-      <c r="G11" s="8">
+      <c r="G11" s="5">
         <v>2E-3</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <v>4</v>
       </c>
-      <c r="I11" s="8">
+      <c r="I11" s="5">
         <v>7.7948000000000002E-3</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="4">
         <v>4</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="4">
         <v>48</v>
       </c>
-      <c r="L11" s="25">
+      <c r="L11" s="30">
         <f t="shared" si="0"/>
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+    <row r="12" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="2" t="s">
+      <c r="B12" s="31" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="41"/>
-      <c r="D12" s="41"/>
-      <c r="E12" s="38"/>
-      <c r="F12" s="6">
+      <c r="C12" s="22"/>
+      <c r="D12" s="22"/>
+      <c r="E12" s="19"/>
+      <c r="F12" s="4">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="G12" s="8">
+      <c r="G12" s="5">
         <v>0.188</v>
       </c>
-      <c r="H12" s="6">
-        <v>1</v>
-      </c>
-      <c r="I12" s="8">
+      <c r="H12" s="4">
+        <v>1</v>
+      </c>
+      <c r="I12" s="5">
         <v>0.1876748</v>
       </c>
-      <c r="J12" s="1">
-        <v>1</v>
-      </c>
-      <c r="K12" s="1">
-        <v>12</v>
-      </c>
-      <c r="L12" s="25">
+      <c r="J12" s="4">
+        <v>1</v>
+      </c>
+      <c r="K12" s="4">
+        <v>12</v>
+      </c>
+      <c r="L12" s="30">
         <f t="shared" si="0"/>
         <v>2.0680000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
+    <row r="13" spans="1:12" ht="38.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="31" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="42"/>
-      <c r="D13" s="42"/>
-      <c r="E13" s="39"/>
-      <c r="F13" s="6">
+      <c r="C13" s="23"/>
+      <c r="D13" s="23"/>
+      <c r="E13" s="20"/>
+      <c r="F13" s="4">
         <v>1.95E-2</v>
       </c>
-      <c r="G13" s="8">
+      <c r="G13" s="5">
         <v>0.29299999999999998</v>
       </c>
-      <c r="H13" s="6">
-        <v>1</v>
-      </c>
-      <c r="I13" s="8">
+      <c r="H13" s="4">
+        <v>1</v>
+      </c>
+      <c r="I13" s="5">
         <v>0.2926048</v>
       </c>
-      <c r="J13" s="1">
-        <v>1</v>
-      </c>
-      <c r="K13" s="1">
-        <v>12</v>
-      </c>
-      <c r="L13" s="25">
+      <c r="J13" s="4">
+        <v>1</v>
+      </c>
+      <c r="K13" s="4">
+        <v>12</v>
+      </c>
+      <c r="L13" s="30">
         <f t="shared" si="0"/>
         <v>3.2229999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A14" s="14">
+    <row r="14" spans="1:12" ht="37" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="6">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
+      <c r="B14" s="31" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="31" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="3" t="s">
+      <c r="D14" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="8">
+      <c r="E14" s="5">
         <v>28.09</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <v>10</v>
       </c>
-      <c r="G14" s="8">
+      <c r="G14" s="5">
+        <f>E14/F14</f>
         <v>2.8090000000000002</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="4">
         <v>2</v>
       </c>
-      <c r="I14" s="8">
+      <c r="I14" s="5">
+        <f>G14*H14</f>
         <v>5.6180000000000003</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="4">
         <v>5</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="4">
         <v>24</v>
       </c>
-      <c r="L14" s="25">
+      <c r="L14" s="30">
         <f t="shared" si="0"/>
         <v>53.371000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+    <row r="15" spans="1:12" ht="32" x14ac:dyDescent="0.4">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
+      <c r="B15" s="31" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="31" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="D15" s="2" t="s">
+        <v>215</v>
+      </c>
+      <c r="E15" s="5">
+        <v>8.39</v>
+      </c>
+      <c r="F15" s="4">
+        <v>50</v>
+      </c>
+      <c r="G15" s="5">
+        <f t="shared" ref="G15:G27" si="1">E15/F15</f>
+        <v>0.1678</v>
+      </c>
+      <c r="H15" s="4">
+        <v>6</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" ref="I15:I27" si="2">G15*H15</f>
+        <v>1.0068000000000001</v>
+      </c>
+      <c r="J15" s="4">
+        <v>20</v>
+      </c>
+      <c r="K15" s="4">
+        <v>72</v>
+      </c>
+      <c r="L15" s="30">
+        <f t="shared" si="0"/>
+        <v>8.7256</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4">
+        <v>15</v>
+      </c>
+      <c r="B16" s="31" t="s">
         <v>27</v>
       </c>
-      <c r="E15" s="8">
-        <v>2.65</v>
-      </c>
-      <c r="F15" s="6">
+      <c r="C16" s="31" t="s">
+        <v>28</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>216</v>
+      </c>
+      <c r="E16" s="5">
+        <v>9.59</v>
+      </c>
+      <c r="F16" s="4">
+        <v>10</v>
+      </c>
+      <c r="G16" s="5">
+        <f t="shared" si="1"/>
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="H16" s="4">
+        <v>1</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="2"/>
+        <v>0.95899999999999996</v>
+      </c>
+      <c r="J16" s="4">
+        <v>4</v>
+      </c>
+      <c r="K16" s="4">
+        <v>12</v>
+      </c>
+      <c r="L16" s="30">
+        <f t="shared" si="0"/>
+        <v>7.6719999999999997</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="32" x14ac:dyDescent="0.4">
+      <c r="A17" s="4">
+        <v>16</v>
+      </c>
+      <c r="B17" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>30</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>217</v>
+      </c>
+      <c r="E17" s="5">
+        <v>5.99</v>
+      </c>
+      <c r="F17" s="4">
         <v>50</v>
       </c>
-      <c r="G15" s="8">
-        <v>5.2999999999999999E-2</v>
-      </c>
-      <c r="H15" s="6">
+      <c r="G17" s="5">
+        <f t="shared" si="1"/>
+        <v>0.1198</v>
+      </c>
+      <c r="H17" s="4">
         <v>6</v>
       </c>
-      <c r="I15" s="8">
-        <v>0.318</v>
-      </c>
-      <c r="J15" s="1">
-        <v>80</v>
-      </c>
-      <c r="K15" s="1">
+      <c r="I17" s="5">
+        <f t="shared" si="2"/>
+        <v>0.71879999999999999</v>
+      </c>
+      <c r="J17" s="4">
+        <v>0</v>
+      </c>
+      <c r="K17" s="4">
         <v>72</v>
       </c>
-      <c r="L15" s="25">
+      <c r="L17" s="30">
+        <f t="shared" si="0"/>
+        <v>8.6256000000000004</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="32" x14ac:dyDescent="0.4">
+      <c r="A18" s="6">
+        <v>17</v>
+      </c>
+      <c r="B18" s="31" t="s">
+        <v>31</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>32</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>218</v>
+      </c>
+      <c r="E18" s="5">
+        <v>7.99</v>
+      </c>
+      <c r="F18" s="4">
+        <v>50</v>
+      </c>
+      <c r="G18" s="5">
+        <f t="shared" si="1"/>
+        <v>0.1598</v>
+      </c>
+      <c r="H18" s="4">
+        <v>4</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="2"/>
+        <v>0.63919999999999999</v>
+      </c>
+      <c r="J18" s="4">
+        <v>22</v>
+      </c>
+      <c r="K18" s="4">
+        <v>48</v>
+      </c>
+      <c r="L18" s="30">
+        <f t="shared" si="0"/>
+        <v>4.1547999999999998</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="26.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4">
+        <v>18</v>
+      </c>
+      <c r="B19" s="31" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>34</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E19" s="5">
+        <v>5.49</v>
+      </c>
+      <c r="F19" s="4">
+        <v>200</v>
+      </c>
+      <c r="G19" s="5">
+        <f t="shared" si="1"/>
+        <v>2.7450000000000002E-2</v>
+      </c>
+      <c r="H19" s="4">
+        <v>8</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="2"/>
+        <v>0.21960000000000002</v>
+      </c>
+      <c r="J19" s="4">
+        <v>25</v>
+      </c>
+      <c r="K19" s="4">
+        <v>48</v>
+      </c>
+      <c r="L19" s="30">
+        <f t="shared" si="0"/>
+        <v>0.63135000000000008</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" s="59" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="36">
+        <v>19</v>
+      </c>
+      <c r="B20" s="37" t="s">
+        <v>35</v>
+      </c>
+      <c r="C20" s="37" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" s="38" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="39">
+        <v>60</v>
+      </c>
+      <c r="F20" s="36">
+        <v>1</v>
+      </c>
+      <c r="G20" s="39">
+        <f t="shared" si="1"/>
+        <v>60</v>
+      </c>
+      <c r="H20" s="36">
+        <v>1</v>
+      </c>
+      <c r="I20" s="39">
+        <f t="shared" si="2"/>
+        <v>60</v>
+      </c>
+      <c r="J20" s="36">
+        <v>12</v>
+      </c>
+      <c r="K20" s="36">
+        <v>12</v>
+      </c>
+      <c r="L20" s="40">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+    <row r="21" spans="1:12" ht="32.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4">
+        <v>20</v>
+      </c>
+      <c r="B21" s="31" t="s">
+        <v>38</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>39</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E21" s="5">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="F21" s="4">
+        <v>8</v>
+      </c>
+      <c r="G21" s="5">
+        <f t="shared" si="1"/>
+        <v>1.0362499999999999</v>
+      </c>
+      <c r="H21" s="4">
+        <v>1</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="2"/>
+        <v>1.0362499999999999</v>
+      </c>
+      <c r="J21" s="4">
+        <v>6</v>
+      </c>
+      <c r="K21" s="4">
+        <v>12</v>
+      </c>
+      <c r="L21" s="30">
+        <f t="shared" si="0"/>
+        <v>6.2174999999999994</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="32" x14ac:dyDescent="0.4">
+      <c r="A22" s="6">
+        <v>21</v>
+      </c>
+      <c r="B22" s="31" t="s">
+        <v>41</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>42</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>219</v>
+      </c>
+      <c r="E22" s="5">
+        <v>8.2799999999999994</v>
+      </c>
+      <c r="F22" s="4">
+        <v>100</v>
+      </c>
+      <c r="G22" s="5">
+        <f t="shared" si="1"/>
+        <v>8.2799999999999999E-2</v>
+      </c>
+      <c r="H22" s="4">
+        <v>6</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="2"/>
+        <v>0.49680000000000002</v>
+      </c>
+      <c r="J22" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>28</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>29</v>
-      </c>
-      <c r="D16" s="3" t="s">
+      <c r="K22" s="4">
+        <v>72</v>
+      </c>
+      <c r="L22" s="30">
+        <f t="shared" si="0"/>
+        <v>4.7195999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="32" x14ac:dyDescent="0.4">
+      <c r="A23" s="4">
+        <v>22</v>
+      </c>
+      <c r="B23" s="31" t="s">
+        <v>43</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E23" s="5">
+        <v>7.19</v>
+      </c>
+      <c r="F23" s="4">
+        <v>8</v>
+      </c>
+      <c r="G23" s="5">
+        <f t="shared" si="1"/>
+        <v>0.89875000000000005</v>
+      </c>
+      <c r="H23" s="4">
+        <v>6</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="2"/>
+        <v>5.3925000000000001</v>
+      </c>
+      <c r="J23" s="4">
+        <v>24</v>
+      </c>
+      <c r="K23" s="4">
+        <v>72</v>
+      </c>
+      <c r="L23" s="30">
+        <f t="shared" si="0"/>
+        <v>43.14</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="48" x14ac:dyDescent="0.4">
+      <c r="A24" s="4">
+        <v>23</v>
+      </c>
+      <c r="B24" s="31" t="s">
+        <v>46</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>47</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="E24" s="5">
+        <v>13.19</v>
+      </c>
+      <c r="F24" s="4">
+        <v>10</v>
+      </c>
+      <c r="G24" s="5">
+        <f t="shared" si="1"/>
+        <v>1.319</v>
+      </c>
+      <c r="H24" s="4">
+        <v>1</v>
+      </c>
+      <c r="I24" s="5">
+        <f t="shared" si="2"/>
+        <v>1.319</v>
+      </c>
+      <c r="J24" s="4">
+        <v>9</v>
+      </c>
+      <c r="K24" s="4">
+        <v>12</v>
+      </c>
+      <c r="L24" s="30">
+        <f t="shared" si="0"/>
+        <v>3.9569999999999999</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A25" s="4">
+        <v>24</v>
+      </c>
+      <c r="B25" s="31" t="s">
+        <v>49</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>50</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>220</v>
+      </c>
+      <c r="E25" s="5">
+        <v>9.19</v>
+      </c>
+      <c r="F25" s="4">
+        <v>100</v>
+      </c>
+      <c r="G25" s="5">
+        <f t="shared" si="1"/>
+        <v>9.1899999999999996E-2</v>
+      </c>
+      <c r="H25" s="4">
         <v>30</v>
       </c>
-      <c r="E16" s="8">
-        <v>7.78</v>
-      </c>
-      <c r="F16" s="6">
-        <v>10</v>
-      </c>
-      <c r="G16" s="8">
-        <v>0.77800000000000002</v>
-      </c>
-      <c r="H16" s="6">
-        <v>2</v>
-      </c>
-      <c r="I16" s="8">
-        <v>1.556</v>
-      </c>
-      <c r="J16" s="1">
-        <v>13</v>
-      </c>
-      <c r="K16" s="1">
-        <v>24</v>
-      </c>
-      <c r="L16" s="25">
-        <f t="shared" si="0"/>
-        <v>8.5579999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>16</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>32</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="8">
-        <v>3.29</v>
-      </c>
-      <c r="F17" s="6">
+      <c r="I25" s="5">
+        <f t="shared" si="2"/>
+        <v>2.7569999999999997</v>
+      </c>
+      <c r="J25" s="4">
+        <v>18</v>
+      </c>
+      <c r="K25" s="4">
+        <v>360</v>
+      </c>
+      <c r="L25" s="30">
+        <f t="shared" si="0"/>
+        <v>31.4298</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A26" s="6">
+        <v>25</v>
+      </c>
+      <c r="B26" s="31" t="s">
+        <v>52</v>
+      </c>
+      <c r="C26" s="31" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="8">
-        <v>6.6000000000000003E-2</v>
-      </c>
-      <c r="H17" s="6">
-        <v>10</v>
-      </c>
-      <c r="I17" s="8">
-        <v>0.65800000000000003</v>
-      </c>
-      <c r="J17" s="1">
+      <c r="D26" s="2" t="s">
+        <v>221</v>
+      </c>
+      <c r="E26" s="5">
+        <v>9.19</v>
+      </c>
+      <c r="F26" s="4">
+        <v>100</v>
+      </c>
+      <c r="G26" s="5">
+        <f t="shared" si="1"/>
+        <v>9.1899999999999996E-2</v>
+      </c>
+      <c r="H26" s="4">
+        <v>6</v>
+      </c>
+      <c r="I26" s="5">
+        <f t="shared" si="2"/>
+        <v>0.5514</v>
+      </c>
+      <c r="J26" s="4">
+        <v>44</v>
+      </c>
+      <c r="K26" s="4">
+        <v>72</v>
+      </c>
+      <c r="L26" s="30">
+        <f t="shared" si="0"/>
+        <v>2.5731999999999999</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="32" x14ac:dyDescent="0.4">
+      <c r="A27" s="42">
+        <v>26</v>
+      </c>
+      <c r="B27" s="43" t="s">
+        <v>53</v>
+      </c>
+      <c r="C27" s="43" t="s">
+        <v>54</v>
+      </c>
+      <c r="D27" s="44" t="s">
+        <v>222</v>
+      </c>
+      <c r="E27" s="45">
+        <v>15.1</v>
+      </c>
+      <c r="F27" s="42">
+        <v>20</v>
+      </c>
+      <c r="G27" s="45">
+        <f t="shared" si="1"/>
+        <v>0.755</v>
+      </c>
+      <c r="H27" s="42">
+        <v>1</v>
+      </c>
+      <c r="I27" s="45">
+        <f t="shared" si="2"/>
+        <v>0.755</v>
+      </c>
+      <c r="J27" s="42">
+        <v>15</v>
+      </c>
+      <c r="K27" s="42">
         <v>0</v>
       </c>
-      <c r="K17" s="1">
-        <v>120</v>
-      </c>
-      <c r="L17" s="25">
-        <f t="shared" si="0"/>
-        <v>7.92</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A18" s="14">
-        <v>17</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E18" s="8">
-        <v>3.29</v>
-      </c>
-      <c r="F18" s="6">
-        <v>20</v>
-      </c>
-      <c r="G18" s="8">
-        <v>0.16500000000000001</v>
-      </c>
-      <c r="H18" s="6">
-        <v>4</v>
-      </c>
-      <c r="I18" s="8">
-        <v>0.65800000000000003</v>
-      </c>
-      <c r="J18" s="1">
-        <v>22</v>
-      </c>
-      <c r="K18" s="1">
-        <v>48</v>
-      </c>
-      <c r="L18" s="25">
-        <f t="shared" si="0"/>
-        <v>4.29</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>18</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E19" s="8">
-        <v>1.71</v>
-      </c>
-      <c r="F19" s="6">
-        <v>50</v>
-      </c>
-      <c r="G19" s="8">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="H19" s="6">
-        <v>4</v>
-      </c>
-      <c r="I19" s="8">
-        <v>0.1368</v>
-      </c>
-      <c r="J19" s="1">
-        <v>40</v>
-      </c>
-      <c r="K19" s="1">
-        <v>48</v>
-      </c>
-      <c r="L19" s="25">
-        <f t="shared" si="0"/>
-        <v>0.27200000000000002</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>19</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>39</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="E20" s="8">
-        <v>60</v>
-      </c>
-      <c r="F20" s="6">
-        <v>1</v>
-      </c>
-      <c r="G20" s="8">
-        <v>60</v>
-      </c>
-      <c r="H20" s="6">
-        <v>1</v>
-      </c>
-      <c r="I20" s="8">
-        <v>60</v>
-      </c>
-      <c r="J20" s="1">
-        <v>7</v>
-      </c>
-      <c r="K20" s="1">
-        <v>12</v>
-      </c>
-      <c r="L20" s="25">
-        <f t="shared" si="0"/>
-        <v>300</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>20</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>42</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>43</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>44</v>
-      </c>
-      <c r="E21" s="8">
-        <v>8.2899999999999991</v>
-      </c>
-      <c r="F21" s="6">
-        <v>8</v>
-      </c>
-      <c r="G21" s="8">
-        <v>1.036</v>
-      </c>
-      <c r="H21" s="6">
-        <v>1</v>
-      </c>
-      <c r="I21" s="8">
-        <v>1.0362499999999999</v>
-      </c>
-      <c r="J21" s="1">
-        <v>6</v>
-      </c>
-      <c r="K21" s="1">
-        <v>12</v>
-      </c>
-      <c r="L21" s="25">
-        <f t="shared" si="0"/>
-        <v>6.2160000000000002</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A22" s="14">
-        <v>21</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>45</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>46</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E22" s="8">
-        <v>2.1</v>
-      </c>
-      <c r="F22" s="6">
-        <v>50</v>
-      </c>
-      <c r="G22" s="8">
-        <v>4.2000000000000003E-2</v>
-      </c>
-      <c r="H22" s="6">
-        <v>6</v>
-      </c>
-      <c r="I22" s="8">
-        <v>0.252</v>
-      </c>
-      <c r="J22" s="1">
-        <v>80</v>
-      </c>
-      <c r="K22" s="1">
-        <v>72</v>
-      </c>
-      <c r="L22" s="25">
+      <c r="L27" s="46">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>22</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>47</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>48</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>49</v>
-      </c>
-      <c r="E23" s="8">
-        <v>6.09</v>
-      </c>
-      <c r="F23" s="6">
-        <v>8</v>
-      </c>
-      <c r="G23" s="8">
-        <v>0.76100000000000001</v>
-      </c>
-      <c r="H23" s="6">
-        <v>6</v>
-      </c>
-      <c r="I23" s="8">
-        <v>4.5674999999999999</v>
-      </c>
-      <c r="J23" s="1">
-        <v>24</v>
-      </c>
-      <c r="K23" s="1">
-        <v>72</v>
-      </c>
-      <c r="L23" s="25">
-        <f t="shared" si="0"/>
-        <v>36.527999999999999</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="51" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>23</v>
-      </c>
-      <c r="B24" s="2" t="s">
-        <v>50</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>51</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>52</v>
-      </c>
-      <c r="E24" s="8">
-        <v>13.19</v>
-      </c>
-      <c r="F24" s="6">
-        <v>10</v>
-      </c>
-      <c r="G24" s="8">
-        <v>1.319</v>
-      </c>
-      <c r="H24" s="6">
-        <v>1</v>
-      </c>
-      <c r="I24" s="8">
-        <v>1.319</v>
-      </c>
-      <c r="J24" s="1">
-        <v>9</v>
-      </c>
-      <c r="K24" s="1">
-        <v>12</v>
-      </c>
-      <c r="L24" s="25">
-        <f t="shared" si="0"/>
-        <v>3.9569999999999999</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
-        <v>24</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>53</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D25" s="3" t="s">
+    <row r="28" spans="1:12" s="15" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A28" s="32" t="s">
         <v>55</v>
       </c>
-      <c r="E25" s="8">
-        <v>9.19</v>
-      </c>
-      <c r="F25" s="6">
-        <v>100</v>
-      </c>
-      <c r="G25" s="8">
-        <v>9.1999999999999998E-2</v>
-      </c>
-      <c r="H25" s="6">
-        <v>30</v>
-      </c>
-      <c r="I25" s="8">
-        <v>2.7570000000000001</v>
-      </c>
-      <c r="J25" s="1">
-        <v>18</v>
-      </c>
-      <c r="K25" s="1">
-        <v>360</v>
-      </c>
-      <c r="L25" s="25">
-        <f t="shared" si="0"/>
-        <v>31.463999999999999</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A26" s="14">
-        <v>25</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>56</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>54</v>
-      </c>
-      <c r="D26" s="3" t="s">
-        <v>57</v>
-      </c>
-      <c r="E26" s="8">
-        <v>7.29</v>
-      </c>
-      <c r="F26" s="6">
-        <v>100</v>
-      </c>
-      <c r="G26" s="8">
-        <v>7.2999999999999995E-2</v>
-      </c>
-      <c r="H26" s="6">
-        <v>6</v>
-      </c>
-      <c r="I26" s="8">
-        <v>0.43740000000000001</v>
-      </c>
-      <c r="J26" s="1">
-        <v>44</v>
-      </c>
-      <c r="K26" s="1">
-        <v>72</v>
-      </c>
-      <c r="L26" s="25">
-        <f t="shared" si="0"/>
-        <v>2.044</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
-        <v>26</v>
-      </c>
-      <c r="B27" s="2" t="s">
-        <v>58</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>59</v>
-      </c>
-      <c r="D27" s="3" t="s">
-        <v>60</v>
-      </c>
-      <c r="E27" s="8">
-        <v>7.98</v>
-      </c>
-      <c r="F27" s="6">
-        <v>60</v>
-      </c>
-      <c r="G27" s="8">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="H27" s="6">
-        <v>1</v>
-      </c>
-      <c r="I27" s="8">
-        <v>0.13300000000000001</v>
-      </c>
-      <c r="J27" s="1">
-        <v>0</v>
-      </c>
-      <c r="K27" s="1">
-        <v>12</v>
-      </c>
-      <c r="L27" s="25">
-        <f t="shared" si="0"/>
-        <v>1.5960000000000001</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="32" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A28" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B28" s="33"/>
-      <c r="C28" s="33"/>
-      <c r="D28" s="33"/>
-      <c r="E28" s="33"/>
-      <c r="F28" s="33"/>
-      <c r="G28" s="33"/>
-      <c r="H28" s="33"/>
-      <c r="I28" s="13">
+      <c r="B28" s="32"/>
+      <c r="C28" s="32"/>
+      <c r="D28" s="32"/>
+      <c r="E28" s="32"/>
+      <c r="F28" s="32"/>
+      <c r="G28" s="32"/>
+      <c r="H28" s="32"/>
+      <c r="I28" s="33">
         <f>SUM(I2:I27)</f>
-        <v>81.931542499999978</v>
-      </c>
-      <c r="J28" s="37" t="s">
-        <v>209</v>
-      </c>
-      <c r="K28" s="37"/>
-      <c r="L28" s="23">
+        <v>83.953942499999997</v>
+      </c>
+      <c r="J28" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="K28" s="34"/>
+      <c r="L28" s="35">
         <f>SUM(L2:L27)</f>
-        <v>483.56200000000001</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="I32" s="30"/>
-    </row>
-    <row r="59" ht="31" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="60" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
-    <row r="62" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+        <v>202.56344999999999</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A29" s="41"/>
+      <c r="B29" s="41"/>
+      <c r="C29" s="41"/>
+      <c r="D29" s="41"/>
+      <c r="E29" s="41"/>
+      <c r="F29" s="41"/>
+      <c r="G29" s="41"/>
+      <c r="H29" s="41"/>
+      <c r="I29" s="41"/>
+      <c r="J29" s="41"/>
+      <c r="K29" s="41"/>
+      <c r="L29" s="41"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="I32" s="12"/>
+    </row>
+    <row r="59" ht="31" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="60" ht="32" customHeight="1" x14ac:dyDescent="0.4"/>
+    <row r="62" ht="32" customHeight="1" x14ac:dyDescent="0.4"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="J28:K28"/>
@@ -3022,7 +3163,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2A752E-49A0-D348-9E27-6206B0A59C47}">
   <dimension ref="A1:L45"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" customWidth="1"/>
@@ -3035,78 +3176,78 @@
     <col min="9" max="9" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="68" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:12" ht="64" x14ac:dyDescent="0.4">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
+      <c r="E1" s="28" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="22" t="s">
+      <c r="F1" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="22" t="s">
+      <c r="G1" s="28" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="22" t="s">
+      <c r="H1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="22" t="s">
+      <c r="I1" s="28" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="2" t="s">
-        <v>65</v>
-      </c>
-      <c r="C2" s="7" t="s">
-        <v>66</v>
-      </c>
-      <c r="D2" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E2" s="9">
+      <c r="J1" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="C2" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="E2" s="5">
         <v>34.97</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="4">
         <v>5</v>
       </c>
       <c r="G2" s="5">
         <f>E2/F2</f>
         <v>6.9939999999999998</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="I2" s="5">
         <f>G2*H2</f>
         <v>6.9939999999999998</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="4">
         <v>5</v>
       </c>
-      <c r="K2" s="1">
+      <c r="K2" s="4">
         <v>12</v>
       </c>
       <c r="L2" s="5">
@@ -3114,40 +3255,40 @@
         <v>48.957999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="2" t="s">
-        <v>173</v>
-      </c>
-      <c r="C3" s="7" t="s">
-        <v>174</v>
-      </c>
-      <c r="D3" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="E3" s="9">
+      <c r="B3" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="C3" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="E3" s="5">
         <v>30.36</v>
       </c>
-      <c r="F3" s="6">
+      <c r="F3" s="4">
         <v>6</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" ref="G3:G40" si="0">E3/F3</f>
         <v>5.0599999999999996</v>
       </c>
-      <c r="H3" s="6">
+      <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" ref="I3:I40" si="1">G3*H3</f>
         <v>5.0599999999999996</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="4">
         <v>6</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="4">
         <v>12</v>
       </c>
       <c r="L3" s="5">
@@ -3155,30 +3296,30 @@
         <v>30.36</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="2" t="s">
-        <v>129</v>
-      </c>
-      <c r="C4" s="7" t="s">
-        <v>184</v>
-      </c>
-      <c r="D4" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E4" s="9">
+      <c r="B4" s="31" t="s">
+        <v>116</v>
+      </c>
+      <c r="C4" s="4" t="s">
+        <v>170</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E4" s="5">
         <v>0.36</v>
       </c>
-      <c r="F4" s="6">
+      <c r="F4" s="4">
         <v>180</v>
       </c>
       <c r="G4" s="5">
         <f>E4/F4</f>
         <v>2E-3</v>
       </c>
-      <c r="H4" s="6">
+      <c r="H4" s="4">
         <f>F4/12</f>
         <v>15</v>
       </c>
@@ -3186,10 +3327,10 @@
         <f>G4*H4</f>
         <v>0.03</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="4">
         <v>180</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="4">
         <v>180</v>
       </c>
       <c r="L4" s="5">
@@ -3197,30 +3338,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="2" t="s">
-        <v>128</v>
-      </c>
-      <c r="C5" s="7" t="s">
-        <v>178</v>
-      </c>
-      <c r="D5" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E5" s="9">
+      <c r="B5" s="31" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E5" s="5">
         <v>5.88</v>
       </c>
-      <c r="F5" s="6">
+      <c r="F5" s="4">
         <v>50</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" ref="G5:G26" si="3">E5/F5</f>
         <v>0.1176</v>
       </c>
-      <c r="H5" s="6">
+      <c r="H5" s="4">
         <f>48/12</f>
         <v>4</v>
       </c>
@@ -3228,10 +3369,10 @@
         <f t="shared" ref="I5:I26" si="4">G5*H5</f>
         <v>0.47039999999999998</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="4">
         <v>50</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="4">
         <v>48</v>
       </c>
       <c r="L5" s="5">
@@ -3239,30 +3380,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="2" t="s">
-        <v>127</v>
-      </c>
-      <c r="C6" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="D6" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E6" s="9">
+      <c r="B6" s="31" t="s">
+        <v>114</v>
+      </c>
+      <c r="C6" s="4" t="s">
+        <v>128</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E6" s="5">
         <v>0.45</v>
       </c>
-      <c r="F6" s="6">
+      <c r="F6" s="4">
         <v>72</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="3"/>
         <v>6.2500000000000003E-3</v>
       </c>
-      <c r="H6" s="6">
+      <c r="H6" s="4">
         <f t="shared" ref="H6:H31" si="5">F6/12</f>
         <v>6</v>
       </c>
@@ -3270,10 +3411,10 @@
         <f t="shared" si="4"/>
         <v>3.7500000000000006E-2</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="4">
         <v>72</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="4">
         <v>72</v>
       </c>
       <c r="L6" s="5">
@@ -3281,30 +3422,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
         <v>6</v>
       </c>
-      <c r="B7" s="2" t="s">
-        <v>130</v>
-      </c>
-      <c r="C7" s="7" t="s">
-        <v>179</v>
-      </c>
-      <c r="D7" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E7" s="9">
+      <c r="B7" s="31" t="s">
+        <v>117</v>
+      </c>
+      <c r="C7" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E7" s="5">
         <v>0.76</v>
       </c>
-      <c r="F7" s="6">
+      <c r="F7" s="4">
         <v>36</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="3"/>
         <v>2.1111111111111112E-2</v>
       </c>
-      <c r="H7" s="6">
+      <c r="H7" s="4">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -3312,10 +3453,10 @@
         <f t="shared" si="4"/>
         <v>6.3333333333333339E-2</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="4">
         <v>36</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="4">
         <v>36</v>
       </c>
       <c r="L7" s="5">
@@ -3323,30 +3464,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
         <v>7</v>
       </c>
-      <c r="B8" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C8" s="7" t="s">
-        <v>185</v>
-      </c>
-      <c r="D8" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E8" s="9">
+      <c r="B8" s="31" t="s">
+        <v>118</v>
+      </c>
+      <c r="C8" s="4" t="s">
+        <v>171</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E8" s="5">
         <v>0.65</v>
       </c>
-      <c r="F8" s="6">
+      <c r="F8" s="4">
         <v>24</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="3"/>
         <v>2.7083333333333334E-2</v>
       </c>
-      <c r="H8" s="6">
+      <c r="H8" s="4">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -3354,10 +3495,10 @@
         <f t="shared" si="4"/>
         <v>5.4166666666666669E-2</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="4">
         <v>24</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="4">
         <v>24</v>
       </c>
       <c r="L8" s="5">
@@ -3365,30 +3506,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A9" s="4">
         <v>8</v>
       </c>
-      <c r="B9" s="2" t="s">
-        <v>132</v>
-      </c>
-      <c r="C9" s="7" t="s">
-        <v>180</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E9" s="9">
+      <c r="B9" s="31" t="s">
+        <v>119</v>
+      </c>
+      <c r="C9" s="4" t="s">
+        <v>166</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E9" s="5">
         <v>0.04</v>
       </c>
-      <c r="F9" s="6">
+      <c r="F9" s="4">
         <v>12</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="H9" s="6">
+      <c r="H9" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -3396,10 +3537,10 @@
         <f t="shared" si="4"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="J9" s="1">
-        <v>12</v>
-      </c>
-      <c r="K9" s="1">
+      <c r="J9" s="4">
+        <v>12</v>
+      </c>
+      <c r="K9" s="4">
         <v>12</v>
       </c>
       <c r="L9" s="5">
@@ -3407,30 +3548,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="2" t="s">
-        <v>133</v>
-      </c>
-      <c r="C10" s="7" t="s">
-        <v>181</v>
-      </c>
-      <c r="D10" s="4" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="9">
+      <c r="B10" s="31" t="s">
+        <v>120</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>167</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>113</v>
+      </c>
+      <c r="E10" s="5">
         <v>1.61</v>
       </c>
-      <c r="F10" s="6">
+      <c r="F10" s="4">
         <v>12</v>
       </c>
       <c r="G10" s="5">
         <f t="shared" si="3"/>
         <v>0.13416666666666668</v>
       </c>
-      <c r="H10" s="6">
+      <c r="H10" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -3438,10 +3579,10 @@
         <f t="shared" si="4"/>
         <v>0.13416666666666668</v>
       </c>
-      <c r="J10" s="1">
-        <v>12</v>
-      </c>
-      <c r="K10" s="1">
+      <c r="J10" s="4">
+        <v>12</v>
+      </c>
+      <c r="K10" s="4">
         <v>12</v>
       </c>
       <c r="L10" s="5">
@@ -3449,30 +3590,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
         <v>10</v>
       </c>
-      <c r="B11" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="C11" s="7" t="s">
-        <v>182</v>
-      </c>
-      <c r="D11" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E11" s="9">
+      <c r="B11" s="31" t="s">
+        <v>121</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>168</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E11" s="5">
         <v>0.17</v>
       </c>
-      <c r="F11" s="6">
+      <c r="F11" s="4">
         <v>12</v>
       </c>
       <c r="G11" s="5">
         <f t="shared" si="3"/>
         <v>1.4166666666666668E-2</v>
       </c>
-      <c r="H11" s="6">
+      <c r="H11" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -3480,10 +3621,10 @@
         <f t="shared" si="4"/>
         <v>1.4166666666666668E-2</v>
       </c>
-      <c r="J11" s="1">
-        <v>12</v>
-      </c>
-      <c r="K11" s="1">
+      <c r="J11" s="4">
+        <v>12</v>
+      </c>
+      <c r="K11" s="4">
         <v>12</v>
       </c>
       <c r="L11" s="5">
@@ -3491,30 +3632,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A12" s="4">
         <v>11</v>
       </c>
-      <c r="B12" s="18" t="s">
-        <v>139</v>
-      </c>
-      <c r="C12" s="19" t="s">
-        <v>183</v>
-      </c>
-      <c r="D12" s="21" t="s">
+      <c r="B12" s="58" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="20">
+      <c r="C12" s="8" t="s">
+        <v>169</v>
+      </c>
+      <c r="D12" s="9" t="s">
+        <v>113</v>
+      </c>
+      <c r="E12" s="57">
         <v>0.84</v>
       </c>
-      <c r="F12" s="17">
+      <c r="F12" s="8">
         <v>24</v>
       </c>
       <c r="G12" s="5">
         <f t="shared" si="3"/>
         <v>3.4999999999999996E-2</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H12" s="4">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -3522,10 +3663,10 @@
         <f t="shared" si="4"/>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="4">
         <v>24</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="4">
         <v>24</v>
       </c>
       <c r="L12" s="5">
@@ -3533,30 +3674,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
-        <v>12</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>135</v>
-      </c>
-      <c r="C13" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="D13" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E13" s="9">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A13" s="4">
+        <v>12</v>
+      </c>
+      <c r="B13" s="31" t="s">
+        <v>122</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E13" s="5">
         <v>2.48</v>
       </c>
-      <c r="F13" s="6">
+      <c r="F13" s="4">
         <v>36</v>
       </c>
       <c r="G13" s="5">
         <f t="shared" si="3"/>
         <v>6.8888888888888888E-2</v>
       </c>
-      <c r="H13" s="6">
+      <c r="H13" s="4">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -3564,10 +3705,10 @@
         <f t="shared" si="4"/>
         <v>0.20666666666666667</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="4">
         <v>36</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="4">
         <v>36</v>
       </c>
       <c r="L13" s="5">
@@ -3575,30 +3716,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+    <row r="14" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="2" t="s">
-        <v>137</v>
-      </c>
-      <c r="C14" s="7" t="s">
-        <v>138</v>
-      </c>
-      <c r="D14" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="E14" s="9">
+      <c r="B14" s="31" t="s">
+        <v>124</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>125</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="5">
         <v>5.93</v>
       </c>
-      <c r="F14" s="6">
+      <c r="F14" s="4">
         <v>24</v>
       </c>
       <c r="G14" s="5">
         <f t="shared" si="3"/>
         <v>0.24708333333333332</v>
       </c>
-      <c r="H14" s="6">
+      <c r="H14" s="4">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -3606,10 +3747,10 @@
         <f t="shared" si="4"/>
         <v>0.49416666666666664</v>
       </c>
-      <c r="J14" s="1">
+      <c r="J14" s="4">
         <v>24</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K14" s="4">
         <v>24</v>
       </c>
       <c r="L14" s="5">
@@ -3617,30 +3758,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
+    <row r="15" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4">
         <v>14</v>
       </c>
-      <c r="B15" s="2" t="s">
-        <v>140</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>142</v>
-      </c>
-      <c r="D15" s="4" t="s">
-        <v>68</v>
+      <c r="B15" s="31" t="s">
+        <v>127</v>
+      </c>
+      <c r="C15" s="31" t="s">
+        <v>129</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E15" s="5">
         <v>0.52</v>
       </c>
-      <c r="F15" s="6">
+      <c r="F15" s="4">
         <v>25</v>
       </c>
       <c r="G15" s="5">
         <f t="shared" si="3"/>
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="H15" s="6">
+      <c r="H15" s="4">
         <f>24/12</f>
         <v>2</v>
       </c>
@@ -3648,10 +3789,10 @@
         <f t="shared" si="4"/>
         <v>4.1599999999999998E-2</v>
       </c>
-      <c r="J15" s="1">
+      <c r="J15" s="4">
         <v>25</v>
       </c>
-      <c r="K15" s="1">
+      <c r="K15" s="4">
         <v>24</v>
       </c>
       <c r="L15" s="5">
@@ -3659,30 +3800,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A16" s="4">
         <v>15</v>
       </c>
-      <c r="B16" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="C16" s="2" t="s">
-        <v>144</v>
-      </c>
-      <c r="D16" s="4" t="s">
-        <v>68</v>
+      <c r="B16" s="31" t="s">
+        <v>130</v>
+      </c>
+      <c r="C16" s="31" t="s">
+        <v>131</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E16" s="5">
         <v>0.83</v>
       </c>
-      <c r="F16" s="6">
+      <c r="F16" s="4">
         <v>12</v>
       </c>
       <c r="G16" s="5">
         <f t="shared" si="3"/>
         <v>6.9166666666666668E-2</v>
       </c>
-      <c r="H16" s="6">
+      <c r="H16" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -3690,10 +3831,10 @@
         <f t="shared" si="4"/>
         <v>6.9166666666666668E-2</v>
       </c>
-      <c r="J16" s="1">
-        <v>12</v>
-      </c>
-      <c r="K16" s="1">
+      <c r="J16" s="4">
+        <v>12</v>
+      </c>
+      <c r="K16" s="4">
         <v>12</v>
       </c>
       <c r="L16" s="5">
@@ -3701,30 +3842,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
+    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A17" s="4">
         <v>16</v>
       </c>
-      <c r="B17" s="2" t="s">
-        <v>145</v>
-      </c>
-      <c r="C17" s="2" t="s">
-        <v>186</v>
-      </c>
-      <c r="D17" s="4" t="s">
-        <v>68</v>
+      <c r="B17" s="31" t="s">
+        <v>132</v>
+      </c>
+      <c r="C17" s="31" t="s">
+        <v>172</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E17" s="5">
         <v>0.04</v>
       </c>
-      <c r="F17" s="6">
+      <c r="F17" s="4">
         <v>12</v>
       </c>
       <c r="G17" s="5">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="H17" s="6">
+      <c r="H17" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -3732,10 +3873,10 @@
         <f t="shared" si="4"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="J17" s="1">
-        <v>12</v>
-      </c>
-      <c r="K17" s="1">
+      <c r="J17" s="4">
+        <v>12</v>
+      </c>
+      <c r="K17" s="4">
         <v>12</v>
       </c>
       <c r="L17" s="5">
@@ -3743,30 +3884,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
+    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="2" t="s">
-        <v>146</v>
-      </c>
-      <c r="C18" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D18" s="4" t="s">
-        <v>68</v>
+      <c r="B18" s="31" t="s">
+        <v>133</v>
+      </c>
+      <c r="C18" s="31" t="s">
+        <v>173</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E18" s="5">
         <v>0.16</v>
       </c>
-      <c r="F18" s="6">
+      <c r="F18" s="4">
         <v>50</v>
       </c>
       <c r="G18" s="5">
         <f t="shared" si="3"/>
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="H18" s="6">
+      <c r="H18" s="4">
         <f>48/12</f>
         <v>4</v>
       </c>
@@ -3774,10 +3915,10 @@
         <f t="shared" si="4"/>
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="J18" s="1">
+      <c r="J18" s="4">
         <v>50</v>
       </c>
-      <c r="K18" s="1">
+      <c r="K18" s="4">
         <v>48</v>
       </c>
       <c r="L18" s="5">
@@ -3785,30 +3926,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
+    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A19" s="4">
         <v>18</v>
       </c>
-      <c r="B19" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="C19" s="2" t="s">
-        <v>188</v>
-      </c>
-      <c r="D19" s="4" t="s">
-        <v>68</v>
+      <c r="B19" s="31" t="s">
+        <v>134</v>
+      </c>
+      <c r="C19" s="31" t="s">
+        <v>174</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E19" s="5">
         <v>0.24</v>
       </c>
-      <c r="F19" s="6">
+      <c r="F19" s="4">
         <v>24</v>
       </c>
       <c r="G19" s="5">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="H19" s="6">
+      <c r="H19" s="4">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -3816,10 +3957,10 @@
         <f t="shared" si="4"/>
         <v>0.02</v>
       </c>
-      <c r="J19" s="1">
+      <c r="J19" s="4">
         <v>24</v>
       </c>
-      <c r="K19" s="1">
+      <c r="K19" s="4">
         <v>24</v>
       </c>
       <c r="L19" s="5">
@@ -3827,30 +3968,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
+    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A20" s="4">
         <v>19</v>
       </c>
-      <c r="B20" s="2" t="s">
-        <v>148</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>149</v>
-      </c>
-      <c r="D20" s="4" t="s">
-        <v>68</v>
+      <c r="B20" s="31" t="s">
+        <v>135</v>
+      </c>
+      <c r="C20" s="31" t="s">
+        <v>136</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E20" s="5">
         <v>2.74</v>
       </c>
-      <c r="F20" s="6">
+      <c r="F20" s="4">
         <v>36</v>
       </c>
       <c r="G20" s="5">
         <f>E20/F20</f>
         <v>7.6111111111111115E-2</v>
       </c>
-      <c r="H20" s="6">
+      <c r="H20" s="4">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -3858,10 +3999,10 @@
         <f t="shared" si="4"/>
         <v>0.22833333333333333</v>
       </c>
-      <c r="J20" s="1">
+      <c r="J20" s="4">
         <v>36</v>
       </c>
-      <c r="K20" s="1">
+      <c r="K20" s="4">
         <v>36</v>
       </c>
       <c r="L20" s="5">
@@ -3869,30 +4010,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
+    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A21" s="4">
         <v>20</v>
       </c>
-      <c r="B21" s="2" t="s">
-        <v>150</v>
-      </c>
-      <c r="C21" s="2" t="s">
-        <v>151</v>
-      </c>
-      <c r="D21" s="4" t="s">
-        <v>68</v>
+      <c r="B21" s="31" t="s">
+        <v>137</v>
+      </c>
+      <c r="C21" s="31" t="s">
+        <v>138</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E21" s="5">
         <v>0.05</v>
       </c>
-      <c r="F21" s="6">
+      <c r="F21" s="4">
         <v>12</v>
       </c>
       <c r="G21" s="5">
         <f t="shared" si="3"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="H21" s="6">
+      <c r="H21" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -3900,10 +4041,10 @@
         <f t="shared" si="4"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="J21" s="1">
-        <v>12</v>
-      </c>
-      <c r="K21" s="1">
+      <c r="J21" s="4">
+        <v>12</v>
+      </c>
+      <c r="K21" s="4">
         <v>12</v>
       </c>
       <c r="L21" s="5">
@@ -3911,30 +4052,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
+    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="2" t="s">
-        <v>152</v>
-      </c>
-      <c r="C22" s="2" t="s">
-        <v>153</v>
-      </c>
-      <c r="D22" s="4" t="s">
-        <v>68</v>
+      <c r="B22" s="31" t="s">
+        <v>139</v>
+      </c>
+      <c r="C22" s="31" t="s">
+        <v>140</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E22" s="5">
         <v>0.05</v>
       </c>
-      <c r="F22" s="6">
+      <c r="F22" s="4">
         <v>12</v>
       </c>
       <c r="G22" s="5">
         <f>E22/F22</f>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="H22" s="6">
+      <c r="H22" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -3942,10 +4083,10 @@
         <f t="shared" si="4"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="J22" s="1">
-        <v>12</v>
-      </c>
-      <c r="K22" s="1">
+      <c r="J22" s="4">
+        <v>12</v>
+      </c>
+      <c r="K22" s="4">
         <v>12</v>
       </c>
       <c r="L22" s="5">
@@ -3953,30 +4094,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
+    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A23" s="4">
         <v>22</v>
       </c>
-      <c r="B23" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>189</v>
-      </c>
-      <c r="D23" s="4" t="s">
-        <v>68</v>
+      <c r="B23" s="31" t="s">
+        <v>141</v>
+      </c>
+      <c r="C23" s="31" t="s">
+        <v>175</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E23" s="5">
         <v>0.17</v>
       </c>
-      <c r="F23" s="6">
+      <c r="F23" s="4">
         <v>36</v>
       </c>
       <c r="G23" s="5">
         <f t="shared" si="3"/>
         <v>4.7222222222222223E-3</v>
       </c>
-      <c r="H23" s="6">
+      <c r="H23" s="4">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -3984,10 +4125,10 @@
         <f t="shared" si="4"/>
         <v>1.4166666666666668E-2</v>
       </c>
-      <c r="J23" s="1">
+      <c r="J23" s="4">
         <v>36</v>
       </c>
-      <c r="K23" s="1">
+      <c r="K23" s="4">
         <v>36</v>
       </c>
       <c r="L23" s="5">
@@ -3995,30 +4136,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
+    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A24" s="4">
         <v>23</v>
       </c>
-      <c r="B24" s="2" t="s">
-        <v>155</v>
-      </c>
-      <c r="C24" s="2" t="s">
-        <v>190</v>
-      </c>
-      <c r="D24" s="4" t="s">
-        <v>68</v>
+      <c r="B24" s="31" t="s">
+        <v>142</v>
+      </c>
+      <c r="C24" s="31" t="s">
+        <v>176</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E24" s="5">
         <v>0.23</v>
       </c>
-      <c r="F24" s="6">
+      <c r="F24" s="4">
         <v>25</v>
       </c>
       <c r="G24" s="5">
         <f t="shared" si="3"/>
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="H24" s="6">
+      <c r="H24" s="4">
         <f>24/12</f>
         <v>2</v>
       </c>
@@ -4026,10 +4167,10 @@
         <f t="shared" si="4"/>
         <v>1.84E-2</v>
       </c>
-      <c r="J24" s="1">
+      <c r="J24" s="4">
         <v>25</v>
       </c>
-      <c r="K24" s="1">
+      <c r="K24" s="4">
         <v>24</v>
       </c>
       <c r="L24" s="5">
@@ -4037,30 +4178,30 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A25" s="1">
+    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A25" s="4">
         <v>24</v>
       </c>
-      <c r="B25" s="2" t="s">
-        <v>156</v>
-      </c>
-      <c r="C25" s="2" t="s">
-        <v>157</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>68</v>
+      <c r="B25" s="31" t="s">
+        <v>143</v>
+      </c>
+      <c r="C25" s="31" t="s">
+        <v>144</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E25" s="5">
         <v>0.04</v>
       </c>
-      <c r="F25" s="6">
+      <c r="F25" s="4">
         <v>12</v>
       </c>
       <c r="G25" s="5">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="H25" s="6">
+      <c r="H25" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -4068,41 +4209,41 @@
         <f t="shared" si="4"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="J25" s="26">
-        <v>12</v>
-      </c>
-      <c r="K25" s="26">
-        <v>12</v>
-      </c>
-      <c r="L25" s="27">
+      <c r="J25" s="8">
+        <v>12</v>
+      </c>
+      <c r="K25" s="8">
+        <v>12</v>
+      </c>
+      <c r="L25" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A26" s="1">
+    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="2" t="s">
-        <v>158</v>
-      </c>
-      <c r="C26" s="2" t="s">
-        <v>159</v>
-      </c>
-      <c r="D26" s="4" t="s">
-        <v>68</v>
+      <c r="B26" s="31" t="s">
+        <v>145</v>
+      </c>
+      <c r="C26" s="31" t="s">
+        <v>146</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E26" s="5">
         <v>0.08</v>
       </c>
-      <c r="F26" s="6">
+      <c r="F26" s="4">
         <v>12</v>
       </c>
       <c r="G26" s="5">
         <f t="shared" si="3"/>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="H26" s="6">
+      <c r="H26" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -4110,41 +4251,41 @@
         <f t="shared" si="4"/>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="J26" s="26">
-        <v>12</v>
-      </c>
-      <c r="K26" s="26">
-        <v>12</v>
-      </c>
-      <c r="L26" s="27">
+      <c r="J26" s="8">
+        <v>12</v>
+      </c>
+      <c r="K26" s="8">
+        <v>12</v>
+      </c>
+      <c r="L26" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A27" s="1">
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A27" s="4">
         <v>26</v>
       </c>
-      <c r="B27" s="2" t="s">
-        <v>160</v>
-      </c>
-      <c r="C27" s="2" t="s">
-        <v>161</v>
-      </c>
-      <c r="D27" s="4" t="s">
-        <v>68</v>
+      <c r="B27" s="31" t="s">
+        <v>147</v>
+      </c>
+      <c r="C27" s="31" t="s">
+        <v>148</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E27" s="5">
         <v>0.05</v>
       </c>
-      <c r="F27" s="6">
+      <c r="F27" s="4">
         <v>12</v>
       </c>
       <c r="G27" s="5">
         <f t="shared" si="0"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="H27" s="6">
+      <c r="H27" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -4152,41 +4293,41 @@
         <f t="shared" si="1"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="J27" s="26">
-        <v>12</v>
-      </c>
-      <c r="K27" s="26">
-        <v>12</v>
-      </c>
-      <c r="L27" s="27">
+      <c r="J27" s="8">
+        <v>12</v>
+      </c>
+      <c r="K27" s="8">
+        <v>12</v>
+      </c>
+      <c r="L27" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A28" s="1">
+    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A28" s="4">
         <v>27</v>
       </c>
-      <c r="B28" s="2" t="s">
-        <v>162</v>
-      </c>
-      <c r="C28" s="2" t="s">
-        <v>163</v>
-      </c>
-      <c r="D28" s="4" t="s">
-        <v>68</v>
+      <c r="B28" s="31" t="s">
+        <v>149</v>
+      </c>
+      <c r="C28" s="31" t="s">
+        <v>150</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>62</v>
       </c>
       <c r="E28" s="5">
         <v>0.11</v>
       </c>
-      <c r="F28" s="6">
+      <c r="F28" s="4">
         <v>12</v>
       </c>
       <c r="G28" s="5">
         <f t="shared" si="0"/>
         <v>9.1666666666666667E-3</v>
       </c>
-      <c r="H28" s="6">
+      <c r="H28" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -4194,41 +4335,41 @@
         <f t="shared" si="1"/>
         <v>9.1666666666666667E-3</v>
       </c>
-      <c r="J28" s="26">
-        <v>12</v>
-      </c>
-      <c r="K28" s="26">
-        <v>12</v>
-      </c>
-      <c r="L28" s="27">
+      <c r="J28" s="8">
+        <v>12</v>
+      </c>
+      <c r="K28" s="8">
+        <v>12</v>
+      </c>
+      <c r="L28" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A29" s="1">
+    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A29" s="4">
         <v>28</v>
       </c>
-      <c r="B29" s="2" t="s">
-        <v>165</v>
-      </c>
-      <c r="C29" s="2" t="s">
-        <v>166</v>
-      </c>
-      <c r="D29" s="4" t="s">
-        <v>126</v>
+      <c r="B29" s="31" t="s">
+        <v>152</v>
+      </c>
+      <c r="C29" s="31" t="s">
+        <v>153</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="E29" s="5">
         <v>10.84</v>
       </c>
-      <c r="F29" s="6">
+      <c r="F29" s="4">
         <v>36</v>
       </c>
       <c r="G29" s="5">
         <f t="shared" si="0"/>
         <v>0.30111111111111111</v>
       </c>
-      <c r="H29" s="6">
+      <c r="H29" s="4">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
@@ -4236,41 +4377,41 @@
         <f t="shared" si="1"/>
         <v>0.90333333333333332</v>
       </c>
-      <c r="J29" s="26">
+      <c r="J29" s="8">
         <v>36</v>
       </c>
-      <c r="K29" s="26">
+      <c r="K29" s="8">
         <v>36</v>
       </c>
-      <c r="L29" s="27">
+      <c r="L29" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A30" s="1">
+    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A30" s="4">
         <v>29</v>
       </c>
-      <c r="B30" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="C30" s="2" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="4" t="s">
-        <v>126</v>
+      <c r="B30" s="31" t="s">
+        <v>154</v>
+      </c>
+      <c r="C30" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="E30" s="5">
         <v>3.62</v>
       </c>
-      <c r="F30" s="6">
+      <c r="F30" s="4">
         <v>24</v>
       </c>
       <c r="G30" s="5">
         <f t="shared" si="0"/>
         <v>0.15083333333333335</v>
       </c>
-      <c r="H30" s="6">
+      <c r="H30" s="4">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
@@ -4278,41 +4419,41 @@
         <f t="shared" si="1"/>
         <v>0.30166666666666669</v>
       </c>
-      <c r="J30" s="26">
+      <c r="J30" s="8">
         <v>24</v>
       </c>
-      <c r="K30" s="26">
+      <c r="K30" s="8">
         <v>24</v>
       </c>
-      <c r="L30" s="27">
+      <c r="L30" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A31" s="1">
+    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A31" s="4">
         <v>30</v>
       </c>
-      <c r="B31" s="2" t="s">
-        <v>169</v>
-      </c>
-      <c r="C31" s="2" t="s">
-        <v>170</v>
-      </c>
-      <c r="D31" s="4" t="s">
-        <v>126</v>
+      <c r="B31" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="C31" s="31" t="s">
+        <v>157</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="E31" s="5">
         <v>6.71</v>
       </c>
-      <c r="F31" s="6">
+      <c r="F31" s="4">
         <v>12</v>
       </c>
       <c r="G31" s="5">
         <f t="shared" si="0"/>
         <v>0.5591666666666667</v>
       </c>
-      <c r="H31" s="6">
+      <c r="H31" s="4">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
@@ -4320,41 +4461,41 @@
         <f t="shared" si="1"/>
         <v>0.5591666666666667</v>
       </c>
-      <c r="J31" s="26">
-        <v>12</v>
-      </c>
-      <c r="K31" s="26">
-        <v>12</v>
-      </c>
-      <c r="L31" s="27">
+      <c r="J31" s="8">
+        <v>12</v>
+      </c>
+      <c r="K31" s="8">
+        <v>12</v>
+      </c>
+      <c r="L31" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A32" s="1">
+    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A32" s="4">
         <v>31</v>
       </c>
-      <c r="B32" s="2" t="s">
-        <v>171</v>
-      </c>
-      <c r="C32" s="2" t="s">
-        <v>172</v>
-      </c>
-      <c r="D32" s="4" t="s">
-        <v>126</v>
+      <c r="B32" s="31" t="s">
+        <v>158</v>
+      </c>
+      <c r="C32" s="31" t="s">
+        <v>159</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>113</v>
       </c>
       <c r="E32" s="5">
         <v>59.67</v>
       </c>
-      <c r="F32" s="6">
+      <c r="F32" s="4">
         <v>30</v>
       </c>
       <c r="G32" s="5">
         <f t="shared" si="0"/>
         <v>1.9890000000000001</v>
       </c>
-      <c r="H32" s="6">
+      <c r="H32" s="4">
         <f>F32/5</f>
         <v>6</v>
       </c>
@@ -4362,41 +4503,41 @@
         <f t="shared" si="1"/>
         <v>11.934000000000001</v>
       </c>
-      <c r="J32" s="26">
+      <c r="J32" s="8">
         <v>30</v>
       </c>
-      <c r="K32" s="26">
+      <c r="K32" s="8">
         <v>72</v>
       </c>
-      <c r="L32" s="27">
+      <c r="L32" s="57">
         <f t="shared" si="2"/>
         <v>83.538000000000011</v>
       </c>
     </row>
-    <row r="33" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A33" s="1">
+    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A33" s="4">
         <v>32</v>
       </c>
-      <c r="B33" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="C33" s="2" t="s">
-        <v>176</v>
-      </c>
-      <c r="D33" s="4" t="s">
-        <v>164</v>
+      <c r="B33" s="31" t="s">
+        <v>162</v>
+      </c>
+      <c r="C33" s="31" t="s">
+        <v>163</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>151</v>
       </c>
       <c r="E33" s="5">
         <v>13.1</v>
       </c>
-      <c r="F33" s="6">
+      <c r="F33" s="4">
         <v>5</v>
       </c>
       <c r="G33" s="5">
         <f t="shared" si="0"/>
         <v>2.62</v>
       </c>
-      <c r="H33" s="6">
+      <c r="H33" s="4">
         <f>F33/5</f>
         <v>1</v>
       </c>
@@ -4404,343 +4545,343 @@
         <f t="shared" si="1"/>
         <v>2.62</v>
       </c>
-      <c r="J33" s="26">
+      <c r="J33" s="8">
         <v>5</v>
       </c>
-      <c r="K33" s="26">
-        <v>12</v>
-      </c>
-      <c r="L33" s="27">
+      <c r="K33" s="8">
+        <v>12</v>
+      </c>
+      <c r="L33" s="57">
         <f t="shared" si="2"/>
         <v>18.34</v>
       </c>
     </row>
-    <row r="34" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A34" s="1">
+    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A34" s="4">
         <v>33</v>
       </c>
-      <c r="B34" s="2" t="s">
-        <v>191</v>
-      </c>
-      <c r="C34" s="2" t="s">
-        <v>192</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>199</v>
+      <c r="B34" s="31" t="s">
+        <v>177</v>
+      </c>
+      <c r="C34" s="31" t="s">
+        <v>178</v>
+      </c>
+      <c r="D34" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="E34" s="5">
         <v>1.3720000000000001</v>
       </c>
-      <c r="F34" s="6">
+      <c r="F34" s="4">
         <v>10</v>
       </c>
       <c r="G34" s="5">
         <f t="shared" si="0"/>
         <v>0.13720000000000002</v>
       </c>
-      <c r="H34" s="6">
+      <c r="H34" s="4">
         <v>1</v>
       </c>
       <c r="I34" s="5">
         <f t="shared" si="1"/>
         <v>0.13720000000000002</v>
       </c>
-      <c r="J34" s="26">
+      <c r="J34" s="8">
         <v>10</v>
       </c>
-      <c r="K34" s="26">
-        <v>12</v>
-      </c>
-      <c r="L34" s="27">
+      <c r="K34" s="8">
+        <v>12</v>
+      </c>
+      <c r="L34" s="57">
         <f t="shared" si="2"/>
         <v>0.27440000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A35" s="1">
+    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A35" s="4">
         <v>34</v>
       </c>
-      <c r="B35" s="2" t="s">
-        <v>194</v>
-      </c>
-      <c r="C35" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D35" s="6" t="s">
-        <v>199</v>
+      <c r="B35" s="31" t="s">
+        <v>180</v>
+      </c>
+      <c r="C35" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="D35" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="E35" s="5">
         <v>0.63700000000000001</v>
       </c>
-      <c r="F35" s="6">
+      <c r="F35" s="4">
         <v>10</v>
       </c>
       <c r="G35" s="5">
         <f t="shared" si="0"/>
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="H35" s="6">
+      <c r="H35" s="4">
         <v>1</v>
       </c>
       <c r="I35" s="5">
         <f t="shared" si="1"/>
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="J35" s="26">
+      <c r="J35" s="8">
         <v>10</v>
       </c>
-      <c r="K35" s="26">
-        <v>12</v>
-      </c>
-      <c r="L35" s="27">
+      <c r="K35" s="8">
+        <v>12</v>
+      </c>
+      <c r="L35" s="57">
         <f t="shared" si="2"/>
         <v>0.12740000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A36" s="1">
+    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A36" s="4">
         <v>35</v>
       </c>
-      <c r="B36" s="2" t="s">
-        <v>195</v>
-      </c>
-      <c r="C36" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="D36" s="6" t="s">
-        <v>199</v>
+      <c r="B36" s="31" t="s">
+        <v>181</v>
+      </c>
+      <c r="C36" s="31" t="s">
+        <v>179</v>
+      </c>
+      <c r="D36" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="E36" s="5">
         <v>2.0169999999999999</v>
       </c>
-      <c r="F36" s="6">
+      <c r="F36" s="4">
         <v>10</v>
       </c>
       <c r="G36" s="5">
         <f t="shared" si="0"/>
         <v>0.20169999999999999</v>
       </c>
-      <c r="H36" s="6">
+      <c r="H36" s="4">
         <v>1</v>
       </c>
       <c r="I36" s="5">
         <f t="shared" si="1"/>
         <v>0.20169999999999999</v>
       </c>
-      <c r="J36" s="26">
+      <c r="J36" s="8">
         <v>10</v>
       </c>
-      <c r="K36" s="26">
-        <v>12</v>
-      </c>
-      <c r="L36" s="27">
+      <c r="K36" s="8">
+        <v>12</v>
+      </c>
+      <c r="L36" s="57">
         <f t="shared" si="2"/>
         <v>0.40339999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A37" s="1">
+    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A37" s="4">
         <v>36</v>
       </c>
-      <c r="B37" s="2" t="s">
-        <v>196</v>
-      </c>
-      <c r="C37" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>164</v>
+      <c r="B37" s="31" t="s">
+        <v>182</v>
+      </c>
+      <c r="C37" s="31" t="s">
+        <v>183</v>
+      </c>
+      <c r="D37" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="E37" s="5">
         <v>16.899999999999999</v>
       </c>
-      <c r="F37" s="6">
+      <c r="F37" s="4">
         <v>10</v>
       </c>
       <c r="G37" s="5">
         <f t="shared" si="0"/>
         <v>1.69</v>
       </c>
-      <c r="H37" s="6">
+      <c r="H37" s="4">
         <v>1</v>
       </c>
       <c r="I37" s="5">
         <f t="shared" si="1"/>
         <v>1.69</v>
       </c>
-      <c r="J37" s="26">
+      <c r="J37" s="8">
         <v>15</v>
       </c>
-      <c r="K37" s="26">
-        <v>12</v>
-      </c>
-      <c r="L37" s="27">
+      <c r="K37" s="8">
+        <v>12</v>
+      </c>
+      <c r="L37" s="57">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A38" s="1">
+    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A38" s="4">
         <v>37</v>
       </c>
-      <c r="B38" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="C38" s="2" t="s">
-        <v>204</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>164</v>
+      <c r="B38" s="31" t="s">
+        <v>184</v>
+      </c>
+      <c r="C38" s="31" t="s">
+        <v>190</v>
+      </c>
+      <c r="D38" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="E38" s="5">
         <v>15.8</v>
       </c>
-      <c r="F38" s="6">
+      <c r="F38" s="4">
         <v>10</v>
       </c>
       <c r="G38" s="5">
         <f t="shared" si="0"/>
         <v>1.58</v>
       </c>
-      <c r="H38" s="6">
+      <c r="H38" s="4">
         <v>1</v>
       </c>
       <c r="I38" s="5">
         <f t="shared" si="1"/>
         <v>1.58</v>
       </c>
-      <c r="J38" s="26">
+      <c r="J38" s="8">
         <v>5</v>
       </c>
-      <c r="K38" s="26">
-        <v>12</v>
-      </c>
-      <c r="L38" s="27">
+      <c r="K38" s="8">
+        <v>12</v>
+      </c>
+      <c r="L38" s="57">
         <f t="shared" si="2"/>
         <v>11.06</v>
       </c>
     </row>
-    <row r="39" spans="1:12" ht="17" x14ac:dyDescent="0.2">
-      <c r="A39" s="1">
+    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A39" s="4">
         <v>38</v>
       </c>
-      <c r="B39" s="2" t="s">
-        <v>201</v>
-      </c>
-      <c r="C39" s="2" t="s">
-        <v>200</v>
-      </c>
-      <c r="D39" s="6" t="s">
-        <v>164</v>
+      <c r="B39" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="C39" s="31" t="s">
+        <v>186</v>
+      </c>
+      <c r="D39" s="4" t="s">
+        <v>151</v>
       </c>
       <c r="E39" s="5">
         <v>38</v>
       </c>
-      <c r="F39" s="6">
+      <c r="F39" s="4">
         <v>10</v>
       </c>
       <c r="G39" s="5">
         <f t="shared" si="0"/>
         <v>3.8</v>
       </c>
-      <c r="H39" s="6">
+      <c r="H39" s="4">
         <v>1</v>
       </c>
       <c r="I39" s="5">
         <f t="shared" si="1"/>
         <v>3.8</v>
       </c>
-      <c r="J39" s="26">
+      <c r="J39" s="8">
         <v>5</v>
       </c>
-      <c r="K39" s="26">
-        <v>12</v>
-      </c>
-      <c r="L39" s="27">
+      <c r="K39" s="8">
+        <v>12</v>
+      </c>
+      <c r="L39" s="57">
         <f t="shared" si="2"/>
         <v>26.599999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="34" x14ac:dyDescent="0.2">
-      <c r="A40" s="1">
+    <row r="40" spans="1:12" ht="32" x14ac:dyDescent="0.4">
+      <c r="A40" s="4">
         <v>39</v>
       </c>
-      <c r="B40" s="2" t="s">
-        <v>202</v>
-      </c>
-      <c r="C40" s="2" t="s">
-        <v>203</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>199</v>
+      <c r="B40" s="31" t="s">
+        <v>188</v>
+      </c>
+      <c r="C40" s="31" t="s">
+        <v>189</v>
+      </c>
+      <c r="D40" s="4" t="s">
+        <v>185</v>
       </c>
       <c r="E40" s="5">
         <v>6.5179999999999998</v>
       </c>
-      <c r="F40" s="28">
+      <c r="F40" s="4">
         <v>10</v>
       </c>
       <c r="G40" s="5">
         <f t="shared" si="0"/>
         <v>0.65179999999999993</v>
       </c>
-      <c r="H40" s="28">
+      <c r="H40" s="4">
         <v>1</v>
       </c>
       <c r="I40" s="5">
         <f t="shared" si="1"/>
         <v>0.65179999999999993</v>
       </c>
-      <c r="J40" s="26">
+      <c r="J40" s="8">
         <v>5</v>
       </c>
-      <c r="K40" s="26">
-        <v>12</v>
-      </c>
-      <c r="L40" s="27">
+      <c r="K40" s="8">
+        <v>12</v>
+      </c>
+      <c r="L40" s="57">
         <f t="shared" si="2"/>
         <v>4.5625999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A41" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="B41" s="33"/>
-      <c r="C41" s="33"/>
-      <c r="D41" s="33"/>
-      <c r="E41" s="33"/>
-      <c r="F41" s="33"/>
-      <c r="G41" s="33"/>
-      <c r="H41" s="33"/>
-      <c r="I41" s="23">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A41" s="32" t="s">
+        <v>55</v>
+      </c>
+      <c r="B41" s="32"/>
+      <c r="C41" s="32"/>
+      <c r="D41" s="32"/>
+      <c r="E41" s="32"/>
+      <c r="F41" s="32"/>
+      <c r="G41" s="32"/>
+      <c r="H41" s="32"/>
+      <c r="I41" s="35">
         <f>SUM(I2:I40)</f>
         <v>38.513933333333327</v>
       </c>
-      <c r="J41" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="K41" s="43"/>
-      <c r="L41" s="23">
+      <c r="J41" s="34" t="s">
+        <v>195</v>
+      </c>
+      <c r="K41" s="34"/>
+      <c r="L41" s="35">
         <f>SUM(L2:L40)</f>
         <v>224.22380000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G44" s="33" t="s">
-        <v>64</v>
-      </c>
-      <c r="H44" s="33"/>
-      <c r="I44" s="24">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="G45" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="H45" s="33"/>
-      <c r="I45" s="23">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="G44" s="16" t="s">
+        <v>58</v>
+      </c>
+      <c r="H44" s="16"/>
+      <c r="I44" s="11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="G45" s="16" t="s">
+        <v>57</v>
+      </c>
+      <c r="H45" s="16"/>
+      <c r="I45" s="10">
         <f>I41*I44</f>
         <v>462.16719999999992</v>
       </c>
@@ -4797,8 +4938,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EFB1B7-3B23-654A-84A7-B98EF9661A5C}">
-  <dimension ref="A1:L28"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:L27"/>
+  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
     <col min="3" max="3" width="45.83203125" customWidth="1"/>
@@ -4810,114 +4951,114 @@
     <col min="10" max="12" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A1" s="22" t="s">
+    <row r="1" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="22" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="22" t="s">
+      <c r="B1" s="28" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="22" t="s">
+      <c r="D1" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="22" t="s">
-        <v>69</v>
-      </c>
-      <c r="F1" s="22" t="s">
-        <v>70</v>
-      </c>
-      <c r="G1" s="22" t="s">
-        <v>71</v>
-      </c>
-      <c r="H1" s="22" t="s">
+      <c r="E1" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="F1" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="G1" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="H1" s="28" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="22" t="s">
-        <v>72</v>
-      </c>
-      <c r="J1" s="22" t="s">
-        <v>210</v>
-      </c>
-      <c r="K1" s="22" t="s">
-        <v>207</v>
-      </c>
-      <c r="L1" s="22" t="s">
-        <v>208</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A2" s="1">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>73</v>
-      </c>
-      <c r="C2" s="44" t="s">
-        <v>74</v>
-      </c>
-      <c r="D2" s="45" t="s">
+      <c r="I1" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="J1" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="K1" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="L1" s="28" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="C2" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="D2" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="44">
+      <c r="E2" s="24">
         <v>29.98</v>
       </c>
-      <c r="F2" s="1">
+      <c r="F2" s="4">
         <v>0.1845</v>
       </c>
       <c r="G2" s="5">
         <f>F2*E2/2</f>
         <v>2.7656550000000002</v>
       </c>
-      <c r="H2" s="1">
+      <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="I2" s="5">
-        <f t="shared" ref="I2:I24" si="0">H2*G2</f>
+        <f t="shared" ref="I2:I23" si="0">H2*G2</f>
         <v>2.7656550000000002</v>
       </c>
-      <c r="J2" s="1">
+      <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="1">
-        <f t="shared" ref="K2:K24" si="1">H2*4</f>
+      <c r="K2" s="4">
+        <f t="shared" ref="K2:K23" si="1">H2*4</f>
         <v>4</v>
       </c>
       <c r="L2" s="5">
-        <f t="shared" ref="L2:L24" si="2">(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
+        <f t="shared" ref="L2:L23" si="2">(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
         <v>11.062620000000001</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A3" s="1">
+    <row r="3" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="4">
         <v>2</v>
       </c>
-      <c r="B3" s="1" t="s">
-        <v>75</v>
-      </c>
-      <c r="C3" s="41"/>
-      <c r="D3" s="41"/>
-      <c r="E3" s="41"/>
-      <c r="F3" s="1">
+      <c r="B3" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="C3" s="22"/>
+      <c r="D3" s="22"/>
+      <c r="E3" s="22"/>
+      <c r="F3" s="4">
         <v>0.17349999999999999</v>
       </c>
       <c r="G3" s="5">
         <f t="shared" ref="G3:G9" si="3">F3*E$2/2</f>
         <v>2.600765</v>
       </c>
-      <c r="H3" s="1">
+      <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3" s="5">
         <f t="shared" si="0"/>
         <v>2.600765</v>
       </c>
-      <c r="J3" s="1">
+      <c r="J3" s="4">
         <v>0</v>
       </c>
-      <c r="K3" s="1">
+      <c r="K3" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -4926,34 +5067,34 @@
         <v>10.40306</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A4" s="1">
+    <row r="4" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="4">
         <v>3</v>
       </c>
-      <c r="B4" s="1" t="s">
-        <v>76</v>
-      </c>
-      <c r="C4" s="41"/>
-      <c r="D4" s="41"/>
-      <c r="E4" s="41"/>
-      <c r="F4" s="1">
+      <c r="B4" s="4" t="s">
+        <v>70</v>
+      </c>
+      <c r="C4" s="22"/>
+      <c r="D4" s="22"/>
+      <c r="E4" s="22"/>
+      <c r="F4" s="4">
         <v>1.9900000000000001E-2</v>
       </c>
       <c r="G4" s="5">
         <f t="shared" si="3"/>
         <v>0.29830100000000004</v>
       </c>
-      <c r="H4" s="1">
+      <c r="H4" s="4">
         <v>1</v>
       </c>
       <c r="I4" s="5">
         <f t="shared" si="0"/>
         <v>0.29830100000000004</v>
       </c>
-      <c r="J4" s="1">
+      <c r="J4" s="4">
         <v>0</v>
       </c>
-      <c r="K4" s="1">
+      <c r="K4" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -4962,34 +5103,34 @@
         <v>1.1932040000000002</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A5" s="1">
+    <row r="5" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="4">
         <v>4</v>
       </c>
-      <c r="B5" s="1" t="s">
-        <v>77</v>
-      </c>
-      <c r="C5" s="41"/>
-      <c r="D5" s="41"/>
-      <c r="E5" s="41"/>
-      <c r="F5" s="1">
+      <c r="B5" s="4" t="s">
+        <v>71</v>
+      </c>
+      <c r="C5" s="22"/>
+      <c r="D5" s="22"/>
+      <c r="E5" s="22"/>
+      <c r="F5" s="4">
         <v>6.54E-2</v>
       </c>
       <c r="G5" s="5">
         <f t="shared" si="3"/>
         <v>0.98034600000000005</v>
       </c>
-      <c r="H5" s="1">
+      <c r="H5" s="4">
         <v>1</v>
       </c>
       <c r="I5" s="5">
         <f t="shared" si="0"/>
         <v>0.98034600000000005</v>
       </c>
-      <c r="J5" s="1">
+      <c r="J5" s="4">
         <v>0</v>
       </c>
-      <c r="K5" s="1">
+      <c r="K5" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -4998,34 +5139,34 @@
         <v>3.9213840000000002</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A6" s="1">
+    <row r="6" spans="1:12" ht="27.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="C6" s="41"/>
-      <c r="D6" s="41"/>
-      <c r="E6" s="41"/>
-      <c r="F6" s="1">
+      <c r="B6" s="4" t="s">
+        <v>72</v>
+      </c>
+      <c r="C6" s="22"/>
+      <c r="D6" s="22"/>
+      <c r="E6" s="22"/>
+      <c r="F6" s="4">
         <v>0.18579999999999999</v>
       </c>
       <c r="G6" s="5">
         <f t="shared" si="3"/>
         <v>2.785142</v>
       </c>
-      <c r="H6" s="1">
+      <c r="H6" s="4">
         <v>1</v>
       </c>
       <c r="I6" s="5">
         <f t="shared" si="0"/>
         <v>2.785142</v>
       </c>
-      <c r="J6" s="1">
+      <c r="J6" s="4">
         <v>0</v>
       </c>
-      <c r="K6" s="1">
+      <c r="K6" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5034,34 +5175,34 @@
         <v>11.140568</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A7" s="1">
+    <row r="7" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="4">
         <v>16</v>
       </c>
-      <c r="B7" s="1" t="s">
-        <v>79</v>
-      </c>
-      <c r="C7" s="41"/>
-      <c r="D7" s="41"/>
-      <c r="E7" s="41"/>
-      <c r="F7" s="1">
+      <c r="B7" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="C7" s="22"/>
+      <c r="D7" s="22"/>
+      <c r="E7" s="22"/>
+      <c r="F7" s="4">
         <v>5.9299999999999999E-2</v>
       </c>
       <c r="G7" s="5">
         <f t="shared" si="3"/>
         <v>0.888907</v>
       </c>
-      <c r="H7" s="1">
+      <c r="H7" s="4">
         <v>1</v>
       </c>
       <c r="I7" s="5">
         <f t="shared" si="0"/>
         <v>0.888907</v>
       </c>
-      <c r="J7" s="1">
+      <c r="J7" s="4">
         <v>0</v>
       </c>
-      <c r="K7" s="1">
+      <c r="K7" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5070,34 +5211,34 @@
         <v>3.555628</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A8" s="1">
+    <row r="8" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="4">
         <v>17</v>
       </c>
-      <c r="B8" s="1" t="s">
-        <v>80</v>
-      </c>
-      <c r="C8" s="41"/>
-      <c r="D8" s="41"/>
-      <c r="E8" s="41"/>
-      <c r="F8" s="1">
+      <c r="B8" s="4" t="s">
+        <v>74</v>
+      </c>
+      <c r="C8" s="22"/>
+      <c r="D8" s="22"/>
+      <c r="E8" s="22"/>
+      <c r="F8" s="4">
         <v>0.122</v>
       </c>
       <c r="G8" s="5">
         <f t="shared" si="3"/>
         <v>1.8287800000000001</v>
       </c>
-      <c r="H8" s="1">
+      <c r="H8" s="4">
         <v>1</v>
       </c>
       <c r="I8" s="5">
         <f t="shared" si="0"/>
         <v>1.8287800000000001</v>
       </c>
-      <c r="J8" s="1">
+      <c r="J8" s="4">
         <v>0</v>
       </c>
-      <c r="K8" s="1">
+      <c r="K8" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5106,34 +5247,34 @@
         <v>7.3151200000000003</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A9" s="1">
+    <row r="9" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A9" s="4">
         <v>18</v>
       </c>
-      <c r="B9" s="1" t="s">
-        <v>81</v>
-      </c>
-      <c r="C9" s="42"/>
-      <c r="D9" s="42"/>
-      <c r="E9" s="42"/>
-      <c r="F9" s="1">
+      <c r="B9" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="C9" s="23"/>
+      <c r="D9" s="23"/>
+      <c r="E9" s="23"/>
+      <c r="F9" s="4">
         <v>4.3700000000000003E-2</v>
       </c>
       <c r="G9" s="5">
         <f t="shared" si="3"/>
         <v>0.65506300000000006</v>
       </c>
-      <c r="H9" s="1">
+      <c r="H9" s="4">
         <v>2</v>
       </c>
       <c r="I9" s="5">
         <f t="shared" si="0"/>
         <v>1.3101260000000001</v>
       </c>
-      <c r="J9" s="1">
+      <c r="J9" s="4">
         <v>0</v>
       </c>
-      <c r="K9" s="1">
+      <c r="K9" s="4">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -5142,39 +5283,39 @@
         <v>5.2405040000000005</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A10" s="1">
+    <row r="10" spans="1:12" ht="24.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="4">
         <v>20</v>
       </c>
-      <c r="B10" s="1" t="s">
-        <v>82</v>
-      </c>
-      <c r="C10" s="1" t="s">
-        <v>83</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>84</v>
-      </c>
-      <c r="E10" s="1">
+      <c r="B10" s="4" t="s">
+        <v>76</v>
+      </c>
+      <c r="C10" s="4" t="s">
+        <v>77</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>78</v>
+      </c>
+      <c r="E10" s="4">
         <v>8.99</v>
       </c>
-      <c r="F10" s="1">
+      <c r="F10" s="4">
         <v>3.8800000000000001E-2</v>
       </c>
       <c r="G10" s="5">
         <v>1.3939999999999999</v>
       </c>
-      <c r="H10" s="1">
+      <c r="H10" s="4">
         <v>1</v>
       </c>
       <c r="I10" s="5">
         <f t="shared" si="0"/>
         <v>1.3939999999999999</v>
       </c>
-      <c r="J10" s="1">
+      <c r="J10" s="4">
         <v>0</v>
       </c>
-      <c r="K10" s="1">
+      <c r="K10" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
@@ -5183,39 +5324,39 @@
         <v>5.5759999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A11" s="1">
+    <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A11" s="4">
         <v>19</v>
       </c>
-      <c r="B11" s="1" t="s">
-        <v>85</v>
-      </c>
-      <c r="C11" s="1" t="s">
-        <v>86</v>
-      </c>
-      <c r="D11" s="3" t="s">
+      <c r="B11" s="4" t="s">
+        <v>79</v>
+      </c>
+      <c r="C11" s="4" t="s">
+        <v>80</v>
+      </c>
+      <c r="D11" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="1">
+      <c r="E11" s="4">
         <v>28.09</v>
       </c>
-      <c r="F11" s="1">
+      <c r="F11" s="4">
         <v>10</v>
       </c>
       <c r="G11" s="5">
         <v>2.8090000000000002</v>
       </c>
-      <c r="H11" s="1">
+      <c r="H11" s="4">
         <v>3</v>
       </c>
       <c r="I11" s="5">
         <f t="shared" si="0"/>
         <v>8.4269999999999996</v>
       </c>
-      <c r="J11" s="1">
+      <c r="J11" s="4">
         <v>0</v>
       </c>
-      <c r="K11" s="1">
+      <c r="K11" s="4">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
@@ -5224,39 +5365,39 @@
         <v>33.707999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A12" s="1">
+    <row r="12" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A12" s="4">
         <v>21</v>
       </c>
-      <c r="B12" s="1" t="s">
-        <v>87</v>
-      </c>
-      <c r="C12" s="1" t="s">
-        <v>54</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>55</v>
-      </c>
-      <c r="E12" s="1">
+      <c r="B12" s="4" t="s">
+        <v>81</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>50</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="E12" s="4">
         <v>9.19</v>
       </c>
-      <c r="F12" s="1">
+      <c r="F12" s="4">
         <v>100</v>
       </c>
       <c r="G12" s="5">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="H12" s="1">
+      <c r="H12" s="4">
         <v>12</v>
       </c>
       <c r="I12" s="5">
         <f t="shared" si="0"/>
         <v>1.1040000000000001</v>
       </c>
-      <c r="J12" s="1">
+      <c r="J12" s="4">
         <v>0</v>
       </c>
-      <c r="K12" s="1">
+      <c r="K12" s="4">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
@@ -5265,39 +5406,39 @@
         <v>4.4160000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A13" s="1">
+    <row r="13" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A13" s="4">
         <v>22</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>88</v>
-      </c>
-      <c r="C13" s="1" t="s">
-        <v>89</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E13" s="1">
+      <c r="B13" s="4" t="s">
+        <v>82</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>83</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>206</v>
+      </c>
+      <c r="E13" s="4">
         <v>2.48</v>
       </c>
-      <c r="F13" s="1">
+      <c r="F13" s="4">
         <v>5</v>
       </c>
       <c r="G13" s="5">
         <v>0.496</v>
       </c>
-      <c r="H13" s="1">
+      <c r="H13" s="4">
         <v>2</v>
       </c>
       <c r="I13" s="5">
         <f t="shared" si="0"/>
         <v>0.99199999999999999</v>
       </c>
-      <c r="J13" s="1">
+      <c r="J13" s="4">
         <v>9</v>
       </c>
-      <c r="K13" s="1">
+      <c r="K13" s="4">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
@@ -5306,495 +5447,460 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A14" s="1">
+    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="4">
         <v>23</v>
       </c>
-      <c r="B14" s="1" t="s">
+      <c r="B14" s="4" t="s">
+        <v>84</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>85</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>207</v>
+      </c>
+      <c r="E14" s="4">
+        <v>5.99</v>
+      </c>
+      <c r="F14" s="4">
+        <v>200</v>
+      </c>
+      <c r="G14" s="5">
+        <f>E14/F14</f>
+        <v>2.9950000000000001E-2</v>
+      </c>
+      <c r="H14" s="4">
+        <v>24</v>
+      </c>
+      <c r="I14" s="5">
+        <f t="shared" si="0"/>
+        <v>0.71879999999999999</v>
+      </c>
+      <c r="J14" s="4">
+        <v>0</v>
+      </c>
+      <c r="K14" s="4">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="L14" s="5">
+        <f t="shared" si="2"/>
+        <v>2.8752</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A15" s="4">
+        <v>6</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>86</v>
+      </c>
+      <c r="C15" s="4" t="s">
+        <v>87</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="E15" s="4">
+        <v>6.99</v>
+      </c>
+      <c r="F15" s="4">
+        <v>10</v>
+      </c>
+      <c r="G15" s="5">
+        <v>0.69899999999999995</v>
+      </c>
+      <c r="H15" s="4">
+        <v>7</v>
+      </c>
+      <c r="I15" s="5">
+        <f t="shared" si="0"/>
+        <v>4.8929999999999998</v>
+      </c>
+      <c r="J15" s="4">
+        <v>0</v>
+      </c>
+      <c r="K15" s="4">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="L15" s="5">
+        <f t="shared" si="2"/>
+        <v>19.571999999999999</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A16" s="4">
+        <v>7</v>
+      </c>
+      <c r="B16" s="4" t="s">
+        <v>89</v>
+      </c>
+      <c r="C16" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D16" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="C14" s="1" t="s">
+      <c r="E16" s="4">
+        <v>7.29</v>
+      </c>
+      <c r="F16" s="4">
+        <v>50</v>
+      </c>
+      <c r="G16" s="5">
+        <v>0.14599999999999999</v>
+      </c>
+      <c r="H16" s="4">
+        <v>7</v>
+      </c>
+      <c r="I16" s="5">
+        <f t="shared" si="0"/>
+        <v>1.022</v>
+      </c>
+      <c r="J16" s="4">
+        <v>19</v>
+      </c>
+      <c r="K16" s="4">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="L16" s="5">
+        <f t="shared" si="2"/>
+        <v>1.3139999999999998</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A17" s="4">
+        <v>8</v>
+      </c>
+      <c r="B17" s="4" t="s">
         <v>92</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="E14" s="1">
-        <v>1.71</v>
-      </c>
-      <c r="F14" s="1">
-        <v>50</v>
-      </c>
-      <c r="G14" s="5">
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="H14" s="1">
-        <v>1</v>
-      </c>
-      <c r="I14" s="5">
-        <f t="shared" si="0"/>
-        <v>3.4000000000000002E-2</v>
-      </c>
-      <c r="J14" s="1">
+      <c r="C17" s="4" t="s">
+        <v>209</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>208</v>
+      </c>
+      <c r="E17" s="4">
+        <v>8.19</v>
+      </c>
+      <c r="F17" s="4">
+        <v>100</v>
+      </c>
+      <c r="G17" s="5">
+        <f>E17/F17</f>
+        <v>8.1900000000000001E-2</v>
+      </c>
+      <c r="H17" s="4">
+        <v>24</v>
+      </c>
+      <c r="I17" s="5">
+        <f t="shared" si="0"/>
+        <v>1.9656</v>
+      </c>
+      <c r="J17" s="4">
         <v>0</v>
       </c>
-      <c r="K14" s="1">
+      <c r="K17" s="4">
+        <f t="shared" si="1"/>
+        <v>96</v>
+      </c>
+      <c r="L17" s="5">
+        <f t="shared" si="2"/>
+        <v>7.8624000000000001</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="4">
+        <v>9</v>
+      </c>
+      <c r="B18" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="C18" s="4" t="s">
+        <v>210</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>95</v>
+      </c>
+      <c r="E18" s="4">
+        <v>12.79</v>
+      </c>
+      <c r="F18" s="4">
+        <v>40</v>
+      </c>
+      <c r="G18" s="5">
+        <v>0.32</v>
+      </c>
+      <c r="H18" s="4">
+        <v>7</v>
+      </c>
+      <c r="I18" s="5">
+        <f t="shared" si="0"/>
+        <v>2.2400000000000002</v>
+      </c>
+      <c r="J18" s="4">
+        <v>0</v>
+      </c>
+      <c r="K18" s="4">
+        <f t="shared" si="1"/>
+        <v>28</v>
+      </c>
+      <c r="L18" s="5">
+        <f t="shared" si="2"/>
+        <v>8.9600000000000009</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="24.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A19" s="4">
+        <v>10</v>
+      </c>
+      <c r="B19" s="4" t="s">
+        <v>96</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>97</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>98</v>
+      </c>
+      <c r="E19" s="4">
+        <v>8.2899999999999991</v>
+      </c>
+      <c r="F19" s="4">
+        <v>10</v>
+      </c>
+      <c r="G19" s="5">
+        <v>0.82899999999999996</v>
+      </c>
+      <c r="H19" s="4">
+        <v>5</v>
+      </c>
+      <c r="I19" s="5">
+        <f t="shared" si="0"/>
+        <v>4.1449999999999996</v>
+      </c>
+      <c r="J19" s="4">
+        <v>8</v>
+      </c>
+      <c r="K19" s="4">
+        <f t="shared" si="1"/>
+        <v>20</v>
+      </c>
+      <c r="L19" s="5">
+        <f t="shared" si="2"/>
+        <v>9.9480000000000004</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A20" s="4">
+        <v>11</v>
+      </c>
+      <c r="B20" s="4" t="s">
+        <v>99</v>
+      </c>
+      <c r="C20" s="4" t="s">
+        <v>100</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E20" s="4">
+        <v>8.69</v>
+      </c>
+      <c r="F20" s="4">
+        <v>8</v>
+      </c>
+      <c r="G20" s="5">
+        <f>E20/F20</f>
+        <v>1.0862499999999999</v>
+      </c>
+      <c r="H20" s="4">
+        <v>1</v>
+      </c>
+      <c r="I20" s="5">
+        <f t="shared" si="0"/>
+        <v>1.0862499999999999</v>
+      </c>
+      <c r="J20" s="4">
+        <v>0</v>
+      </c>
+      <c r="K20" s="4">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L14" s="5">
-        <f t="shared" si="2"/>
-        <v>0.13600000000000001</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A15" s="1">
-        <v>6</v>
-      </c>
-      <c r="B15" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="C15" s="1" t="s">
+      <c r="L20" s="5">
+        <f t="shared" si="2"/>
+        <v>4.3449999999999998</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A21" s="4">
+        <v>12</v>
+      </c>
+      <c r="B21" s="4" t="s">
+        <v>101</v>
+      </c>
+      <c r="C21" s="4" t="s">
+        <v>102</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>212</v>
+      </c>
+      <c r="E21" s="4">
+        <v>6.29</v>
+      </c>
+      <c r="F21" s="4">
+        <v>100</v>
+      </c>
+      <c r="G21" s="5">
+        <f>E21/F21</f>
+        <v>6.2899999999999998E-2</v>
+      </c>
+      <c r="H21" s="4">
+        <v>3</v>
+      </c>
+      <c r="I21" s="5">
+        <f t="shared" si="0"/>
+        <v>0.18869999999999998</v>
+      </c>
+      <c r="J21" s="4">
+        <v>40</v>
+      </c>
+      <c r="K21" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L21" s="5">
+        <f>(IF(K21-J21&lt;0,0,K21-J21))*G21</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="4">
+        <v>14</v>
+      </c>
+      <c r="B22" s="4" t="s">
+        <v>103</v>
+      </c>
+      <c r="C22" s="4" t="s">
         <v>94</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>95</v>
-      </c>
-      <c r="E15" s="1">
-        <v>6.99</v>
-      </c>
-      <c r="F15" s="1">
+      <c r="D22" s="2" t="s">
+        <v>104</v>
+      </c>
+      <c r="E22" s="4">
+        <v>13.29</v>
+      </c>
+      <c r="F22" s="4">
+        <v>40</v>
+      </c>
+      <c r="G22" s="5">
+        <f>E22/F22</f>
+        <v>0.33224999999999999</v>
+      </c>
+      <c r="H22" s="4">
+        <v>3</v>
+      </c>
+      <c r="I22" s="5">
+        <f t="shared" si="0"/>
+        <v>0.99675000000000002</v>
+      </c>
+      <c r="J22" s="4">
         <v>10</v>
       </c>
-      <c r="G15" s="5">
-        <v>0.69899999999999995</v>
-      </c>
-      <c r="H15" s="1">
-        <v>7</v>
-      </c>
-      <c r="I15" s="5">
-        <f t="shared" si="0"/>
-        <v>4.8929999999999998</v>
-      </c>
-      <c r="J15" s="1">
+      <c r="K22" s="4">
+        <f t="shared" si="1"/>
+        <v>12</v>
+      </c>
+      <c r="L22" s="5">
+        <f t="shared" si="2"/>
+        <v>0.66449999999999998</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A23" s="4">
+        <v>15</v>
+      </c>
+      <c r="B23" s="4" t="s">
+        <v>214</v>
+      </c>
+      <c r="C23" s="4" t="s">
+        <v>105</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>213</v>
+      </c>
+      <c r="E23" s="4">
+        <v>7.39</v>
+      </c>
+      <c r="F23" s="4">
+        <v>50</v>
+      </c>
+      <c r="G23" s="5">
+        <f>E23/F23</f>
+        <v>0.14779999999999999</v>
+      </c>
+      <c r="H23" s="4">
+        <v>18</v>
+      </c>
+      <c r="I23" s="5">
+        <f t="shared" si="0"/>
+        <v>2.6603999999999997</v>
+      </c>
+      <c r="J23" s="4">
         <v>0</v>
       </c>
-      <c r="K15" s="1">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="L15" s="5">
-        <f t="shared" si="2"/>
-        <v>19.571999999999999</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A16" s="1">
-        <v>7</v>
-      </c>
-      <c r="B16" s="1" t="s">
-        <v>96</v>
-      </c>
-      <c r="C16" s="1" t="s">
-        <v>97</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>98</v>
-      </c>
-      <c r="E16" s="1">
-        <v>7.29</v>
-      </c>
-      <c r="F16" s="1">
-        <v>50</v>
-      </c>
-      <c r="G16" s="5">
-        <v>0.14599999999999999</v>
-      </c>
-      <c r="H16" s="1">
-        <v>7</v>
-      </c>
-      <c r="I16" s="5">
-        <f t="shared" si="0"/>
-        <v>1.022</v>
-      </c>
-      <c r="J16" s="1">
-        <v>19</v>
-      </c>
-      <c r="K16" s="1">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="L16" s="5">
-        <f t="shared" si="2"/>
-        <v>1.3139999999999998</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A17" s="1">
-        <v>8</v>
-      </c>
-      <c r="B17" s="1" t="s">
-        <v>99</v>
-      </c>
-      <c r="C17" s="1" t="s">
-        <v>100</v>
-      </c>
-      <c r="D17" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E17" s="1">
-        <v>3.35</v>
-      </c>
-      <c r="F17" s="1">
-        <v>50</v>
-      </c>
-      <c r="G17" s="5">
-        <v>6.7000000000000004E-2</v>
-      </c>
-      <c r="H17" s="1">
-        <v>24</v>
-      </c>
-      <c r="I17" s="5">
-        <f t="shared" si="0"/>
-        <v>1.6080000000000001</v>
-      </c>
-      <c r="J17" s="1">
-        <v>0</v>
-      </c>
-      <c r="K17" s="1">
-        <f t="shared" si="1"/>
-        <v>96</v>
-      </c>
-      <c r="L17" s="5">
-        <f t="shared" si="2"/>
-        <v>6.4320000000000004</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A18" s="1">
-        <v>9</v>
-      </c>
-      <c r="B18" s="1" t="s">
-        <v>101</v>
-      </c>
-      <c r="C18" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>103</v>
-      </c>
-      <c r="E18" s="1">
-        <v>12.79</v>
-      </c>
-      <c r="F18" s="1">
-        <v>40</v>
-      </c>
-      <c r="G18" s="5">
-        <v>0.32</v>
-      </c>
-      <c r="H18" s="1">
-        <v>7</v>
-      </c>
-      <c r="I18" s="5">
-        <f t="shared" si="0"/>
-        <v>2.2400000000000002</v>
-      </c>
-      <c r="J18" s="1">
-        <v>0</v>
-      </c>
-      <c r="K18" s="1">
-        <f t="shared" si="1"/>
-        <v>28</v>
-      </c>
-      <c r="L18" s="5">
-        <f t="shared" si="2"/>
-        <v>8.9600000000000009</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A19" s="1">
-        <v>10</v>
-      </c>
-      <c r="B19" s="1" t="s">
-        <v>104</v>
-      </c>
-      <c r="C19" s="1" t="s">
-        <v>105</v>
-      </c>
-      <c r="D19" s="3" t="s">
-        <v>106</v>
-      </c>
-      <c r="E19" s="1">
-        <v>8.2899999999999991</v>
-      </c>
-      <c r="F19" s="1">
-        <v>10</v>
-      </c>
-      <c r="G19" s="5">
-        <v>0.82899999999999996</v>
-      </c>
-      <c r="H19" s="1">
-        <v>5</v>
-      </c>
-      <c r="I19" s="5">
-        <f t="shared" si="0"/>
-        <v>4.1449999999999996</v>
-      </c>
-      <c r="J19" s="1">
-        <v>10</v>
-      </c>
-      <c r="K19" s="1">
-        <f t="shared" si="1"/>
-        <v>20</v>
-      </c>
-      <c r="L19" s="5">
-        <f t="shared" si="2"/>
-        <v>8.2899999999999991</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A20" s="1">
-        <v>11</v>
-      </c>
-      <c r="B20" s="1" t="s">
-        <v>107</v>
-      </c>
-      <c r="C20" s="1" t="s">
-        <v>108</v>
-      </c>
-      <c r="D20" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="E20" s="1">
-        <v>2.69</v>
-      </c>
-      <c r="F20" s="1">
-        <v>5</v>
-      </c>
-      <c r="G20" s="5">
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="H20" s="1">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5">
-        <f t="shared" si="0"/>
-        <v>0.53800000000000003</v>
-      </c>
-      <c r="J20" s="1">
-        <v>0</v>
-      </c>
-      <c r="K20" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L20" s="5">
-        <f t="shared" si="2"/>
-        <v>2.1520000000000001</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A21" s="1">
-        <v>12</v>
-      </c>
-      <c r="B21" s="1" t="s">
-        <v>109</v>
-      </c>
-      <c r="C21" s="1" t="s">
-        <v>110</v>
-      </c>
-      <c r="D21" s="3" t="s">
-        <v>111</v>
-      </c>
-      <c r="E21" s="1">
-        <v>2.5499999999999998</v>
-      </c>
-      <c r="F21" s="1">
-        <v>50</v>
-      </c>
-      <c r="G21" s="5">
-        <v>5.0999999999999997E-2</v>
-      </c>
-      <c r="H21" s="1">
-        <v>3</v>
-      </c>
-      <c r="I21" s="5">
-        <f t="shared" si="0"/>
-        <v>0.153</v>
-      </c>
-      <c r="J21" s="1">
-        <v>40</v>
-      </c>
-      <c r="K21" s="1">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="L21" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A22" s="1">
-        <v>13</v>
-      </c>
-      <c r="B22" s="1" t="s">
-        <v>112</v>
-      </c>
-      <c r="C22" s="1" t="s">
-        <v>92</v>
-      </c>
-      <c r="D22" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="E22" s="1">
-        <v>2.21</v>
-      </c>
-      <c r="F22" s="1">
-        <v>10</v>
-      </c>
-      <c r="G22" s="5">
-        <v>0.221</v>
-      </c>
-      <c r="H22" s="1">
-        <v>1</v>
-      </c>
-      <c r="I22" s="5">
-        <f t="shared" si="0"/>
-        <v>0.221</v>
-      </c>
-      <c r="J22" s="1">
-        <v>0</v>
-      </c>
-      <c r="K22" s="1">
-        <f t="shared" si="1"/>
-        <v>4</v>
-      </c>
-      <c r="L22" s="5">
-        <f t="shared" si="2"/>
-        <v>0.88400000000000001</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A23" s="1">
-        <v>14</v>
-      </c>
-      <c r="B23" s="1" t="s">
-        <v>114</v>
-      </c>
-      <c r="C23" s="1" t="s">
-        <v>102</v>
-      </c>
-      <c r="D23" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="E23" s="1">
-        <v>11.29</v>
-      </c>
-      <c r="F23" s="1">
-        <v>40</v>
-      </c>
-      <c r="G23" s="5">
-        <v>0.28199999999999997</v>
-      </c>
-      <c r="H23" s="1">
-        <v>3</v>
-      </c>
-      <c r="I23" s="5">
-        <f t="shared" si="0"/>
-        <v>0.84599999999999986</v>
-      </c>
-      <c r="J23" s="1">
-        <v>15</v>
-      </c>
-      <c r="K23" s="1">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="L23" s="5">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="A24" s="1">
-        <v>15</v>
-      </c>
-      <c r="B24" s="1" t="s">
-        <v>116</v>
-      </c>
-      <c r="C24" s="1" t="s">
-        <v>117</v>
-      </c>
-      <c r="D24" s="3" t="s">
-        <v>33</v>
-      </c>
-      <c r="E24" s="1">
-        <v>3.73</v>
-      </c>
-      <c r="F24" s="1">
-        <v>50</v>
-      </c>
-      <c r="G24" s="5">
-        <v>7.4999999999999997E-2</v>
-      </c>
-      <c r="H24" s="1">
-        <v>18</v>
-      </c>
-      <c r="I24" s="5">
-        <f t="shared" si="0"/>
-        <v>1.3499999999999999</v>
-      </c>
-      <c r="J24" s="1">
-        <v>10</v>
-      </c>
-      <c r="K24" s="1">
+      <c r="K23" s="4">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="L24" s="5">
-        <f t="shared" si="2"/>
-        <v>4.6499999999999995</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A25" s="46" t="s">
-        <v>61</v>
-      </c>
-      <c r="B25" s="47"/>
-      <c r="C25" s="47"/>
-      <c r="D25" s="47"/>
-      <c r="E25" s="47"/>
-      <c r="F25" s="47"/>
-      <c r="G25" s="47"/>
-      <c r="H25" s="48"/>
-      <c r="I25" s="29">
-        <f>SUM(I2:I24)</f>
-        <v>42.425021999999984</v>
-      </c>
-      <c r="J25" s="49" t="s">
-        <v>209</v>
-      </c>
-      <c r="K25" s="50"/>
-      <c r="L25" s="29">
-        <f>SUM(L2:L24)</f>
-        <v>149.92208799999995</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.2">
-      <c r="J28" s="31"/>
-      <c r="K28" s="31"/>
-      <c r="L28" s="32"/>
+      <c r="L23" s="5">
+        <f t="shared" si="2"/>
+        <v>10.641599999999999</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" s="41" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
+      <c r="A24" s="53" t="s">
+        <v>55</v>
+      </c>
+      <c r="B24" s="54"/>
+      <c r="C24" s="54"/>
+      <c r="D24" s="54"/>
+      <c r="E24" s="54"/>
+      <c r="F24" s="54"/>
+      <c r="G24" s="54"/>
+      <c r="H24" s="55"/>
+      <c r="I24" s="56">
+        <f>SUM(I2:I23)</f>
+        <v>45.291522000000008</v>
+      </c>
+      <c r="J24" s="53" t="s">
+        <v>195</v>
+      </c>
+      <c r="K24" s="55"/>
+      <c r="L24" s="56">
+        <f>SUM(L2:L23)</f>
+        <v>163.71478800000003</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
+      <c r="J27" s="13"/>
+      <c r="K27" s="13"/>
+      <c r="L27" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="E2:E9"/>
     <mergeCell ref="D2:D9"/>
     <mergeCell ref="C2:C9"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="J25:K25"/>
+    <mergeCell ref="A24:H24"/>
+    <mergeCell ref="J24:K24"/>
   </mergeCells>
-  <conditionalFormatting sqref="A2:L2 A3:B9 F3:J9 K3:L24 A10:J24">
+  <conditionalFormatting sqref="A2:L2 A3:B9 F3:J9 K3:L23 A10:J23">
     <cfRule type="expression" dxfId="0" priority="1">
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
@@ -5813,9 +5919,8 @@
     <hyperlink ref="D19" r:id="rId11" xr:uid="{8AF02770-5A1E-0D4F-943E-F280C0374B4B}"/>
     <hyperlink ref="D20" r:id="rId12" xr:uid="{A0CCE2EF-4874-9846-A3B1-3CBF7FA70805}"/>
     <hyperlink ref="D21" r:id="rId13" xr:uid="{E37256A4-CC0F-804E-A6E9-D20623DDBEEE}"/>
-    <hyperlink ref="D22" r:id="rId14" xr:uid="{CBB3130F-3CE1-B749-96E3-72BF68699864}"/>
-    <hyperlink ref="D23" r:id="rId15" xr:uid="{E3588641-4442-5448-ABE4-7F1C5B716318}"/>
-    <hyperlink ref="D24" r:id="rId16" xr:uid="{B6D7B57A-C95F-F242-8A08-AFDE910F26FF}"/>
+    <hyperlink ref="D22" r:id="rId14" xr:uid="{E3588641-4442-5448-ABE4-7F1C5B716318}"/>
+    <hyperlink ref="D23" r:id="rId15" xr:uid="{B6D7B57A-C95F-F242-8A08-AFDE910F26FF}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/Purchasing/BOM/Ultimate BOM.xlsx
+++ b/Purchasing/BOM/Ultimate BOM.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10125"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/417d0fd5397d0872/Documentos/GitHub/Quadraped-Robot/Purchasing/BOM/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/elijahrobinson/Documents/GitHub/Robot-Dog/Purchasing/BOM/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="227" documentId="13_ncr:1_{DC9A2B99-3C50-4547-AB8C-86AC7DE28C99}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DADEC4E0-32E8-4DEC-876E-D290BBB68428}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFAC459E-53C7-2343-A829-9D53E53F14AA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" activeTab="3" xr2:uid="{B7364A64-1EA0-9049-A7FC-B4FA1E16182F}"/>
+    <workbookView xWindow="0" yWindow="660" windowWidth="25820" windowHeight="15500" xr2:uid="{B7364A64-1EA0-9049-A7FC-B4FA1E16182F}"/>
   </bookViews>
   <sheets>
     <sheet name="Total Price" sheetId="4" r:id="rId1"/>
     <sheet name="Body Assembly" sheetId="6" r:id="rId2"/>
     <sheet name="Cycloidal Gearbox" sheetId="1" r:id="rId3"/>
-    <sheet name="FOC PCB" sheetId="2" r:id="rId4"/>
+    <sheet name="FOC PCB" sheetId="2" state="hidden" r:id="rId4"/>
     <sheet name="Leg Assembly" sheetId="3" r:id="rId5"/>
   </sheets>
   <calcPr calcId="191029"/>
@@ -40,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="314" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="319" uniqueCount="231">
   <si>
     <t>ITEM NO.</t>
   </si>
@@ -615,9 +615,6 @@
     <t>N/A</t>
   </si>
   <si>
-    <t>Raspberry Pi Pico</t>
-  </si>
-  <si>
     <t>Units In Stock</t>
   </si>
   <si>
@@ -648,18 +645,6 @@
     <t>Body Assembly</t>
   </si>
   <si>
-    <t>Funding Money</t>
-  </si>
-  <si>
-    <t>Who</t>
-  </si>
-  <si>
-    <t>Amount</t>
-  </si>
-  <si>
-    <t>Chad Robinson</t>
-  </si>
-  <si>
     <t>https://a.co/d/09Na5hOE</t>
   </si>
   <si>
@@ -727,6 +712,27 @@
   </si>
   <si>
     <t>https://a.co/d/0axj8nc5</t>
+  </si>
+  <si>
+    <t>Raspberry Pi 5</t>
+  </si>
+  <si>
+    <t>https://www.canakit.com/raspberry-pi-5-8gb.html</t>
+  </si>
+  <si>
+    <t>Motor Control Dev Board</t>
+  </si>
+  <si>
+    <t>https://www.digikey.com/short/43vvtr80</t>
+  </si>
+  <si>
+    <t>In amazon cart</t>
+  </si>
+  <si>
+    <t>This is the box that you should look at.</t>
+  </si>
+  <si>
+    <t>^^^^^^^</t>
   </si>
 </sst>
 </file>
@@ -736,7 +742,7 @@
   <numFmts count="1">
     <numFmt numFmtId="44" formatCode="_(&quot;$&quot;* #,##0.00_);_(&quot;$&quot;* \(#,##0.00\);_(&quot;$&quot;* &quot;-&quot;??_);_(@_)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
@@ -768,6 +774,20 @@
     <font>
       <u/>
       <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color rgb="FFFF0000"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="12"/>
+      <color theme="6"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -911,13 +931,11 @@
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="60">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -946,36 +964,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1000,25 +988,13 @@
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="2" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1045,8 +1021,23 @@
     <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1055,6 +1046,27 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="2" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="2" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="2" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="6" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1066,16 +1078,39 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="8" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="44" fontId="0" fillId="0" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Currency" xfId="1" builtinId="4"/>
@@ -1448,282 +1483,311 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C4E62B7-8324-4D43-A746-C69356B7E16F}">
-  <dimension ref="A1:J18"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="16.33203125" customWidth="1"/>
     <col min="8" max="8" width="15.1640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A1" s="49" t="s">
-        <v>223</v>
-      </c>
-      <c r="B1" s="49" t="s">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A1" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="B1" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="C1" s="49" t="s">
+      <c r="C1" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="D1" s="49" t="s">
+      <c r="D1" s="20" t="s">
         <v>108</v>
       </c>
-      <c r="E1" s="49" t="s">
+      <c r="E1" s="20" t="s">
         <v>112</v>
       </c>
-      <c r="F1" s="41"/>
-      <c r="G1" s="49" t="s">
-        <v>223</v>
-      </c>
-      <c r="H1" s="49" t="s">
+      <c r="F1" s="25"/>
+      <c r="G1" s="20" t="s">
+        <v>218</v>
+      </c>
+      <c r="H1" s="20" t="s">
         <v>106</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="20" t="s">
         <v>107</v>
       </c>
-      <c r="J1" s="49" t="s">
+      <c r="J1" s="20" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="C2" s="30">
+      <c r="C2" s="18">
         <f>'Cycloidal Gearbox'!I28</f>
-        <v>83.953942499999997</v>
-      </c>
-      <c r="D2" s="4">
-        <v>12</v>
-      </c>
-      <c r="E2" s="30">
+        <v>84.631942500000008</v>
+      </c>
+      <c r="D2" s="2">
+        <v>12</v>
+      </c>
+      <c r="E2" s="18">
         <f>C2*D2</f>
-        <v>1007.44731</v>
-      </c>
-      <c r="F2" s="41"/>
-      <c r="G2" s="4">
-        <v>1</v>
-      </c>
-      <c r="H2" s="4" t="s">
+        <v>1015.5833100000001</v>
+      </c>
+      <c r="F2" s="25"/>
+      <c r="G2" s="2">
+        <v>1</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="I2" s="30">
+      <c r="I2" s="18">
         <f>'Cycloidal Gearbox'!I28</f>
-        <v>83.953942499999997</v>
-      </c>
-      <c r="J2" s="30">
+        <v>84.631942500000008</v>
+      </c>
+      <c r="J2" s="18">
         <f>'Cycloidal Gearbox'!L28</f>
-        <v>202.56344999999999</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+        <v>209.00445000000002</v>
+      </c>
+      <c r="K2" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="3" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="18">
         <f>'Leg Assembly'!I24</f>
-        <v>45.291522000000008</v>
-      </c>
-      <c r="D3" s="4">
-        <v>12</v>
-      </c>
-      <c r="E3" s="30">
+        <v>43.944821999999995</v>
+      </c>
+      <c r="D3" s="2">
+        <v>12</v>
+      </c>
+      <c r="E3" s="18">
         <f t="shared" ref="E3:E7" si="0">C3*D3</f>
-        <v>543.49826400000006</v>
-      </c>
-      <c r="F3" s="41"/>
-      <c r="G3" s="4">
+        <v>527.33786399999997</v>
+      </c>
+      <c r="F3" s="25"/>
+      <c r="G3" s="2">
         <v>2</v>
       </c>
-      <c r="H3" s="4" t="s">
+      <c r="H3" s="2" t="s">
         <v>110</v>
       </c>
-      <c r="I3" s="30">
+      <c r="I3" s="18">
         <f>'Leg Assembly'!I24</f>
-        <v>45.291522000000008</v>
-      </c>
-      <c r="J3" s="30">
+        <v>43.944821999999995</v>
+      </c>
+      <c r="J3" s="18">
         <f>'Leg Assembly'!L24</f>
-        <v>163.71478800000003</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+        <v>158.327988</v>
+      </c>
+      <c r="K3" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="4" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A4" s="54">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="C4" s="30">
+      <c r="C4" s="55">
         <f>'FOC PCB'!I41</f>
         <v>38.513933333333327</v>
       </c>
-      <c r="D4" s="4">
-        <v>12</v>
-      </c>
-      <c r="E4" s="30">
+      <c r="D4" s="54">
+        <v>12</v>
+      </c>
+      <c r="E4" s="55">
         <f t="shared" si="0"/>
         <v>462.16719999999992</v>
       </c>
-      <c r="F4" s="41"/>
-      <c r="G4" s="4">
+      <c r="F4" s="25"/>
+      <c r="G4" s="54">
         <v>3</v>
       </c>
-      <c r="H4" s="4" t="s">
+      <c r="H4" s="54" t="s">
         <v>111</v>
       </c>
-      <c r="I4" s="30">
-        <f>'FOC PCB'!I41</f>
-        <v>38.513933333333327</v>
-      </c>
-      <c r="J4" s="30">
-        <f>'FOC PCB'!L41</f>
-        <v>224.22380000000001</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="I4" s="55">
+        <v>0</v>
+      </c>
+      <c r="J4" s="55">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="C5" s="5">
-        <v>8</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1</v>
-      </c>
-      <c r="E5" s="30">
-        <f t="shared" si="0"/>
-        <v>8</v>
-      </c>
-      <c r="F5" s="41"/>
-      <c r="G5" s="4">
+      <c r="B5" s="2" t="s">
+        <v>224</v>
+      </c>
+      <c r="C5" s="3">
+        <v>175</v>
+      </c>
+      <c r="D5" s="2">
+        <v>1</v>
+      </c>
+      <c r="E5" s="18">
+        <f t="shared" si="0"/>
+        <v>175</v>
+      </c>
+      <c r="F5" s="25"/>
+      <c r="G5" s="57">
         <v>4</v>
       </c>
-      <c r="H5" s="4" t="s">
-        <v>191</v>
-      </c>
-      <c r="I5" s="5">
-        <v>8</v>
-      </c>
-      <c r="J5" s="30">
+      <c r="H5" s="57" t="s">
+        <v>224</v>
+      </c>
+      <c r="I5" s="58">
+        <v>175</v>
+      </c>
+      <c r="J5" s="59">
         <f>1*I5</f>
-        <v>8</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+        <v>175</v>
+      </c>
+      <c r="K5" s="53" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="6" spans="1:11" ht="34" x14ac:dyDescent="0.2">
+      <c r="A6" s="54">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
-        <v>197</v>
-      </c>
-      <c r="C6" s="5">
+      <c r="B6" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="C6" s="56">
         <v>15</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="54">
         <v>4</v>
       </c>
-      <c r="E6" s="30">
+      <c r="E6" s="55">
         <f t="shared" si="0"/>
         <v>60</v>
       </c>
-      <c r="F6" s="41"/>
-      <c r="G6" s="4">
+      <c r="F6" s="25"/>
+      <c r="G6" s="57">
         <v>5</v>
       </c>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="5"/>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="H6" s="60" t="s">
+        <v>226</v>
+      </c>
+      <c r="I6" s="58">
+        <v>19.350000000000001</v>
+      </c>
+      <c r="J6" s="58">
+        <f>I6*12+6.99</f>
+        <v>239.19000000000003</v>
+      </c>
+      <c r="K6" s="53" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="7" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="4" t="s">
-        <v>201</v>
-      </c>
-      <c r="C7" s="5">
+      <c r="B7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="C7" s="3">
         <f>'Body Assembly'!L12</f>
-        <v>489.98436000000004</v>
-      </c>
-      <c r="D7" s="4">
-        <v>1</v>
-      </c>
-      <c r="E7" s="30">
-        <f t="shared" si="0"/>
-        <v>489.98436000000004</v>
-      </c>
-      <c r="F7" s="41"/>
-      <c r="G7" s="4">
+        <v>89.984360000000009</v>
+      </c>
+      <c r="D7" s="2">
+        <v>1</v>
+      </c>
+      <c r="E7" s="18">
+        <f t="shared" si="0"/>
+        <v>89.984360000000009</v>
+      </c>
+      <c r="F7" s="25"/>
+      <c r="G7" s="2">
         <v>6</v>
       </c>
-      <c r="H7" s="4"/>
-      <c r="I7" s="5"/>
-      <c r="J7" s="5"/>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A8" s="32" t="s">
-        <v>224</v>
-      </c>
-      <c r="B8" s="32"/>
-      <c r="C8" s="32"/>
-      <c r="D8" s="32"/>
-      <c r="E8" s="33">
+      <c r="H7" s="2" t="s">
+        <v>200</v>
+      </c>
+      <c r="I7" s="3">
+        <f>'Body Assembly'!I12*2</f>
+        <v>89.984360000000009</v>
+      </c>
+      <c r="J7" s="3">
+        <f>I7</f>
+        <v>89.984360000000009</v>
+      </c>
+      <c r="K7" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="8" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A8" s="36" t="s">
+        <v>219</v>
+      </c>
+      <c r="B8" s="36"/>
+      <c r="C8" s="36"/>
+      <c r="D8" s="36"/>
+      <c r="E8" s="21">
         <f>SUM(E2:E7)</f>
-        <v>2571.0971340000001</v>
-      </c>
-      <c r="F8" s="41"/>
-      <c r="G8" s="50" t="s">
-        <v>225</v>
-      </c>
-      <c r="H8" s="51"/>
-      <c r="I8" s="52"/>
-      <c r="J8" s="33">
-        <f>SUM(J2:J6)</f>
-        <v>598.50203799999997</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A15" s="18" t="s">
-        <v>202</v>
-      </c>
-      <c r="B15" s="18"/>
-      <c r="C15" s="18"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.4">
-      <c r="A16" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="B16" s="17"/>
-      <c r="C16" s="1" t="s">
-        <v>204</v>
-      </c>
-    </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A17" s="17" t="s">
-        <v>205</v>
-      </c>
-      <c r="B17" s="17"/>
-      <c r="C17" s="3">
-        <v>250</v>
-      </c>
-    </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
-      <c r="A18" s="1"/>
-      <c r="B18" s="1"/>
-      <c r="C18" s="1"/>
+        <v>2330.0727339999999</v>
+      </c>
+      <c r="F8" s="25"/>
+      <c r="G8" s="39" t="s">
+        <v>220</v>
+      </c>
+      <c r="H8" s="40"/>
+      <c r="I8" s="41"/>
+      <c r="J8" s="21">
+        <f>SUM(J2:J6)*0.1+SUM(J2:J6)</f>
+        <v>859.67468180000014</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="H11" t="s">
+        <v>230</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="G12" t="s">
+        <v>229</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A15" s="61"/>
+      <c r="B15" s="61"/>
+      <c r="C15" s="61"/>
+    </row>
+    <row r="16" spans="1:11" x14ac:dyDescent="0.2">
+      <c r="A16" s="62"/>
+      <c r="B16" s="62"/>
+      <c r="C16" s="63"/>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A17" s="62"/>
+      <c r="B17" s="62"/>
+      <c r="C17" s="64"/>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.2">
+      <c r="A18" s="62"/>
+      <c r="B18" s="62"/>
+      <c r="C18" s="63"/>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A8:D8"/>
     <mergeCell ref="G8:I8"/>
     <mergeCell ref="A17:B17"/>
@@ -1735,6 +1799,10 @@
       <formula>MOD(ROW(),2)</formula>
     </cfRule>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="K5" r:id="rId1" xr:uid="{02BE3711-146E-3947-972D-D769919716C7}"/>
+    <hyperlink ref="K6" r:id="rId2" xr:uid="{3B76F2EE-2106-3C42-9C0A-071762E85D94}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -1742,7 +1810,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{257BEE17-54E8-714C-9FC2-0AAD6BDD2F44}">
   <dimension ref="A1:L46"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="31.33203125" customWidth="1"/>
@@ -1750,291 +1818,289 @@
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="11" max="11" width="13.08203125" customWidth="1"/>
+    <col min="11" max="11" width="13" customWidth="1"/>
     <col min="12" max="12" width="12.83203125" customWidth="1"/>
     <col min="15" max="18" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:12" ht="66" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="26" t="s">
+      <c r="J1" s="14" t="s">
+        <v>191</v>
+      </c>
+      <c r="K1" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="K1" s="26" t="s">
+      <c r="L1" s="14" t="s">
         <v>193</v>
       </c>
-      <c r="L1" s="26" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="53.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="29" t="s">
-        <v>226</v>
-      </c>
-      <c r="C2" s="29" t="s">
-        <v>227</v>
-      </c>
-      <c r="D2" s="47" t="s">
-        <v>228</v>
-      </c>
-      <c r="E2" s="7">
+    </row>
+    <row r="2" spans="1:12" ht="53.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
+        <v>221</v>
+      </c>
+      <c r="C2" s="17" t="s">
+        <v>222</v>
+      </c>
+      <c r="D2" s="31" t="s">
+        <v>223</v>
+      </c>
+      <c r="E2" s="5">
         <v>26.98</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="4">
         <v>2</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <f>E2*0.741/F2</f>
         <v>9.9960900000000006</v>
       </c>
-      <c r="H2" s="6">
+      <c r="H2" s="4">
         <v>2</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="5">
         <f>G2*H2</f>
         <v>19.992180000000001</v>
       </c>
-      <c r="J2" s="6">
+      <c r="J2" s="4">
         <v>0</v>
       </c>
-      <c r="K2" s="6">
+      <c r="K2" s="4">
         <v>2</v>
       </c>
-      <c r="L2" s="48">
+      <c r="L2" s="32">
         <f>I2*K2</f>
         <v>39.984360000000002</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+    <row r="3" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="31"/>
-      <c r="C3" s="4"/>
-      <c r="D3" s="4"/>
-      <c r="E3" s="5"/>
-      <c r="F3" s="4"/>
-      <c r="G3" s="5"/>
-      <c r="H3" s="4"/>
-      <c r="I3" s="5"/>
-      <c r="J3" s="4"/>
-      <c r="K3" s="4"/>
-      <c r="L3" s="30"/>
-    </row>
-    <row r="4" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+      <c r="B3" s="19"/>
+      <c r="C3" s="2"/>
+      <c r="D3" s="2"/>
+      <c r="E3" s="3"/>
+      <c r="F3" s="2"/>
+      <c r="G3" s="3"/>
+      <c r="H3" s="2"/>
+      <c r="I3" s="3"/>
+      <c r="J3" s="2"/>
+      <c r="K3" s="2"/>
+      <c r="L3" s="18"/>
+    </row>
+    <row r="4" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="31"/>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4"/>
-      <c r="E4" s="5"/>
-      <c r="F4" s="4"/>
-      <c r="G4" s="5"/>
-      <c r="H4" s="4"/>
-      <c r="I4" s="5"/>
-      <c r="J4" s="4"/>
-      <c r="K4" s="4"/>
-      <c r="L4" s="30"/>
-    </row>
-    <row r="5" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="B4" s="19"/>
+      <c r="C4" s="2"/>
+      <c r="D4" s="2"/>
+      <c r="E4" s="3"/>
+      <c r="F4" s="2"/>
+      <c r="G4" s="3"/>
+      <c r="H4" s="2"/>
+      <c r="I4" s="3"/>
+      <c r="J4" s="2"/>
+      <c r="K4" s="2"/>
+      <c r="L4" s="18"/>
+    </row>
+    <row r="5" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="31"/>
-      <c r="C5" s="4"/>
-      <c r="D5" s="4"/>
-      <c r="E5" s="5"/>
-      <c r="F5" s="4"/>
-      <c r="G5" s="5"/>
-      <c r="H5" s="4"/>
-      <c r="I5" s="5"/>
-      <c r="J5" s="4"/>
-      <c r="K5" s="4"/>
-      <c r="L5" s="30"/>
-    </row>
-    <row r="6" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+      <c r="B5" s="19"/>
+      <c r="C5" s="2"/>
+      <c r="D5" s="2"/>
+      <c r="E5" s="3"/>
+      <c r="F5" s="2"/>
+      <c r="G5" s="3"/>
+      <c r="H5" s="2"/>
+      <c r="I5" s="3"/>
+      <c r="J5" s="2"/>
+      <c r="K5" s="2"/>
+      <c r="L5" s="18"/>
+    </row>
+    <row r="6" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="31"/>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4"/>
-      <c r="E6" s="5"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="5"/>
-      <c r="H6" s="4"/>
-      <c r="I6" s="5"/>
-      <c r="J6" s="4"/>
-      <c r="K6" s="4"/>
-      <c r="L6" s="30"/>
-    </row>
-    <row r="7" spans="1:12" ht="24.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="B6" s="19"/>
+      <c r="C6" s="2"/>
+      <c r="D6" s="2"/>
+      <c r="E6" s="3"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="3"/>
+      <c r="H6" s="2"/>
+      <c r="I6" s="3"/>
+      <c r="J6" s="2"/>
+      <c r="K6" s="2"/>
+      <c r="L6" s="18"/>
+    </row>
+    <row r="7" spans="1:12" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="31" t="s">
-        <v>200</v>
-      </c>
-      <c r="C7" s="4" t="s">
+      <c r="B7" s="19" t="s">
+        <v>199</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>197</v>
+      </c>
+      <c r="D7" s="1" t="s">
         <v>198</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>199</v>
-      </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>25</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>2</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="3">
         <f>E7/F7</f>
         <v>12.5</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="2">
         <v>2</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="3">
         <f>G7*H7</f>
         <v>25</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="2">
         <v>0</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="2">
         <v>4</v>
       </c>
-      <c r="L7" s="30">
+      <c r="L7" s="18">
         <f>K7*G7</f>
         <v>50</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+    <row r="8" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="31"/>
-      <c r="C8" s="4"/>
-      <c r="D8" s="4"/>
-      <c r="E8" s="5"/>
-      <c r="F8" s="4"/>
-      <c r="G8" s="5"/>
-      <c r="H8" s="4"/>
-      <c r="I8" s="5"/>
-      <c r="J8" s="4"/>
-      <c r="K8" s="4"/>
-      <c r="L8" s="30"/>
-    </row>
-    <row r="9" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+      <c r="B8" s="19"/>
+      <c r="C8" s="2"/>
+      <c r="D8" s="2"/>
+      <c r="E8" s="3"/>
+      <c r="F8" s="2"/>
+      <c r="G8" s="3"/>
+      <c r="H8" s="2"/>
+      <c r="I8" s="3"/>
+      <c r="J8" s="2"/>
+      <c r="K8" s="2"/>
+      <c r="L8" s="18"/>
+    </row>
+    <row r="9" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="31"/>
-      <c r="C9" s="4"/>
-      <c r="D9" s="4"/>
-      <c r="E9" s="5"/>
-      <c r="F9" s="4"/>
-      <c r="G9" s="5"/>
-      <c r="H9" s="4"/>
-      <c r="I9" s="5"/>
-      <c r="J9" s="4"/>
-      <c r="K9" s="4"/>
-      <c r="L9" s="30"/>
-    </row>
-    <row r="10" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+      <c r="B9" s="19"/>
+      <c r="C9" s="2"/>
+      <c r="D9" s="2"/>
+      <c r="E9" s="3"/>
+      <c r="F9" s="2"/>
+      <c r="G9" s="3"/>
+      <c r="H9" s="2"/>
+      <c r="I9" s="3"/>
+      <c r="J9" s="2"/>
+      <c r="K9" s="2"/>
+      <c r="L9" s="18"/>
+    </row>
+    <row r="10" spans="1:12" ht="25" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="31"/>
-      <c r="C10" s="4"/>
-      <c r="D10" s="4"/>
-      <c r="E10" s="5"/>
-      <c r="F10" s="4"/>
-      <c r="G10" s="5"/>
-      <c r="H10" s="4"/>
-      <c r="I10" s="5"/>
-      <c r="J10" s="4"/>
-      <c r="K10" s="4"/>
-      <c r="L10" s="30"/>
-    </row>
-    <row r="11" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+      <c r="B10" s="19"/>
+      <c r="C10" s="2"/>
+      <c r="D10" s="2"/>
+      <c r="E10" s="3"/>
+      <c r="F10" s="2"/>
+      <c r="G10" s="3"/>
+      <c r="H10" s="2"/>
+      <c r="I10" s="3"/>
+      <c r="J10" s="2"/>
+      <c r="K10" s="2"/>
+      <c r="L10" s="18"/>
+    </row>
+    <row r="11" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="31"/>
-      <c r="C11" s="4"/>
-      <c r="D11" s="4"/>
-      <c r="E11" s="5"/>
-      <c r="F11" s="4"/>
-      <c r="G11" s="5"/>
-      <c r="H11" s="4"/>
-      <c r="I11" s="5"/>
-      <c r="J11" s="4"/>
-      <c r="K11" s="4"/>
-      <c r="L11" s="30">
-        <v>400</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="39.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="32" t="s">
+      <c r="B11" s="19"/>
+      <c r="C11" s="2"/>
+      <c r="D11" s="2"/>
+      <c r="E11" s="3"/>
+      <c r="F11" s="2"/>
+      <c r="G11" s="3"/>
+      <c r="H11" s="2"/>
+      <c r="I11" s="3"/>
+      <c r="J11" s="2"/>
+      <c r="K11" s="2"/>
+      <c r="L11" s="18"/>
+    </row>
+    <row r="12" spans="1:12" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B12" s="32"/>
-      <c r="C12" s="32"/>
-      <c r="D12" s="32"/>
-      <c r="E12" s="32"/>
-      <c r="F12" s="32"/>
-      <c r="G12" s="32"/>
-      <c r="H12" s="32"/>
-      <c r="I12" s="33">
+      <c r="B12" s="36"/>
+      <c r="C12" s="36"/>
+      <c r="D12" s="36"/>
+      <c r="E12" s="36"/>
+      <c r="F12" s="36"/>
+      <c r="G12" s="36"/>
+      <c r="H12" s="36"/>
+      <c r="I12" s="21">
         <f>SUM(I2:I10)</f>
         <v>44.992180000000005</v>
       </c>
-      <c r="J12" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="K12" s="34"/>
-      <c r="L12" s="35">
+      <c r="J12" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="K12" s="38"/>
+      <c r="L12" s="22">
         <f>SUM(L2:L11)</f>
-        <v>489.98436000000004</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="I16" s="12"/>
-    </row>
-    <row r="43" ht="31" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="44" ht="32" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="46" ht="32" customHeight="1" x14ac:dyDescent="0.4"/>
+        <v>89.984360000000009</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I16" s="10"/>
+    </row>
+    <row r="43" ht="31" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="44" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="46" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="2">
     <mergeCell ref="A12:H12"/>
@@ -2055,8 +2121,8 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4BCE8930-9406-2043-8E02-400D939E2382}">
-  <dimension ref="A1:L62"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M62"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.33203125" customWidth="1"/>
     <col min="3" max="3" width="31.33203125" customWidth="1"/>
@@ -2064,1068 +2130,1072 @@
     <col min="5" max="5" width="12.6640625" customWidth="1"/>
     <col min="6" max="6" width="17.5" customWidth="1"/>
     <col min="7" max="7" width="13.83203125" customWidth="1"/>
-    <col min="12" max="12" width="18.4140625" customWidth="1"/>
+    <col min="12" max="12" width="18.33203125" customWidth="1"/>
     <col min="15" max="18" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="83.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
-      <c r="A1" s="26" t="s">
+    <row r="1" spans="1:13" ht="83.5" customHeight="1" thickBot="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="14" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="26" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="26" t="s">
+      <c r="B1" s="14" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="14" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="26" t="s">
+      <c r="D1" s="14" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="27" t="s">
+      <c r="E1" s="15" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="26" t="s">
+      <c r="F1" s="14" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="26" t="s">
+      <c r="G1" s="14" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="26" t="s">
+      <c r="H1" s="14" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="26" t="s">
+      <c r="I1" s="14" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="28" t="s">
+      <c r="J1" s="16" t="s">
+        <v>191</v>
+      </c>
+      <c r="K1" s="16" t="s">
         <v>192</v>
       </c>
-      <c r="K1" s="28" t="s">
+      <c r="L1" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="L1" s="28" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="6">
-        <v>1</v>
-      </c>
-      <c r="B2" s="29" t="s">
+    </row>
+    <row r="2" spans="1:13" ht="36" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A2" s="4">
+        <v>1</v>
+      </c>
+      <c r="B2" s="17" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="22" t="s">
+      <c r="C2" s="45" t="s">
         <v>56</v>
       </c>
-      <c r="D2" s="21" t="s">
+      <c r="D2" s="44" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="19">
+      <c r="E2" s="42">
         <v>29.98</v>
       </c>
-      <c r="F2" s="6">
+      <c r="F2" s="4">
         <v>3.0099999999999998E-2</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="5">
         <v>0.45100000000000001</v>
       </c>
-      <c r="H2" s="6">
-        <v>1</v>
-      </c>
-      <c r="I2" s="7">
+      <c r="H2" s="4">
+        <v>1</v>
+      </c>
+      <c r="I2" s="5">
         <v>0.45119900000000002</v>
       </c>
-      <c r="J2" s="4">
-        <v>1</v>
-      </c>
-      <c r="K2" s="4">
-        <v>12</v>
-      </c>
-      <c r="L2" s="30">
+      <c r="J2" s="2">
+        <v>1</v>
+      </c>
+      <c r="K2" s="2">
+        <v>12</v>
+      </c>
+      <c r="L2" s="18">
         <f t="shared" ref="L2:L27" si="0">(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
         <v>4.9610000000000003</v>
       </c>
     </row>
-    <row r="3" spans="1:12" ht="30.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+    <row r="3" spans="1:13" ht="30.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="19" t="s">
         <v>11</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="19"/>
-      <c r="F3" s="4">
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="2">
         <v>3.0099999999999998E-2</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="3">
         <v>0.45100000000000001</v>
       </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
         <v>0.45119900000000002</v>
       </c>
-      <c r="J3" s="4">
-        <v>1</v>
-      </c>
-      <c r="K3" s="4">
-        <v>12</v>
-      </c>
-      <c r="L3" s="30">
+      <c r="J3" s="2">
+        <v>1</v>
+      </c>
+      <c r="K3" s="2">
+        <v>12</v>
+      </c>
+      <c r="L3" s="18">
         <f t="shared" si="0"/>
         <v>4.9610000000000003</v>
       </c>
     </row>
-    <row r="4" spans="1:12" ht="39.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+    <row r="4" spans="1:13" ht="39.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="31" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="19"/>
-      <c r="F4" s="4">
+      <c r="B4" s="19" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="2">
         <v>1.15E-2</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <v>0.17199999999999999</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="2">
         <v>2</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <v>0.3444702</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="2">
         <v>2</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="2">
         <v>24</v>
       </c>
-      <c r="L4" s="30">
+      <c r="L4" s="18">
         <f t="shared" si="0"/>
         <v>3.7839999999999998</v>
       </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="M4">
+        <f>SUM(F2:F13)*12</f>
+        <v>1.8468</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="19" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="19"/>
-      <c r="F5" s="4">
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="2">
         <v>3.5999999999999999E-3</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="3">
         <v>5.3999999999999999E-2</v>
       </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
         <v>5.3514300000000001E-2</v>
       </c>
-      <c r="J5" s="4">
-        <v>1</v>
-      </c>
-      <c r="K5" s="4">
-        <v>12</v>
-      </c>
-      <c r="L5" s="30">
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2">
+        <v>12</v>
+      </c>
+      <c r="L5" s="18">
         <f t="shared" si="0"/>
         <v>0.59399999999999997</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="6">
+    <row r="6" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="4">
         <v>5</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="19" t="s">
         <v>14</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="19"/>
-      <c r="F6" s="4">
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="2">
         <v>2.0000000000000001E-4</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="3">
         <v>2E-3</v>
       </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
         <v>2.3984000000000002E-3</v>
       </c>
-      <c r="J6" s="4">
-        <v>1</v>
-      </c>
-      <c r="K6" s="4">
-        <v>12</v>
-      </c>
-      <c r="L6" s="30">
+      <c r="J6" s="2">
+        <v>1</v>
+      </c>
+      <c r="K6" s="2">
+        <v>12</v>
+      </c>
+      <c r="L6" s="18">
         <f t="shared" si="0"/>
         <v>2.1999999999999999E-2</v>
       </c>
     </row>
-    <row r="7" spans="1:12" ht="27" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+    <row r="7" spans="1:13" ht="27" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="19"/>
-      <c r="F7" s="4">
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="2">
         <v>4.0000000000000002E-4</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="3">
         <v>6.0000000000000001E-3</v>
       </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
         <v>5.5462999999999997E-3</v>
       </c>
-      <c r="J7" s="4">
-        <v>1</v>
-      </c>
-      <c r="K7" s="4">
-        <v>12</v>
-      </c>
-      <c r="L7" s="30">
+      <c r="J7" s="2">
+        <v>1</v>
+      </c>
+      <c r="K7" s="2">
+        <v>12</v>
+      </c>
+      <c r="L7" s="18">
         <f t="shared" si="0"/>
         <v>6.6000000000000003E-2</v>
       </c>
     </row>
-    <row r="8" spans="1:12" ht="25.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+    <row r="8" spans="1:13" ht="25.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="19" t="s">
         <v>16</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="19"/>
-      <c r="F8" s="4">
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="2">
         <v>4.2200000000000001E-2</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="3">
         <v>0.63300000000000001</v>
       </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5">
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
         <v>0.63272790000000001</v>
       </c>
-      <c r="J8" s="4">
-        <v>1</v>
-      </c>
-      <c r="K8" s="4">
-        <v>12</v>
-      </c>
-      <c r="L8" s="30">
+      <c r="J8" s="2">
+        <v>1</v>
+      </c>
+      <c r="K8" s="2">
+        <v>12</v>
+      </c>
+      <c r="L8" s="18">
         <f t="shared" si="0"/>
         <v>6.9630000000000001</v>
       </c>
     </row>
-    <row r="9" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+    <row r="9" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="C9" s="22"/>
-      <c r="D9" s="22"/>
-      <c r="E9" s="19"/>
-      <c r="F9" s="4">
+      <c r="C9" s="45"/>
+      <c r="D9" s="45"/>
+      <c r="E9" s="42"/>
+      <c r="F9" s="2">
         <v>5.0000000000000001E-4</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="3">
         <v>7.0000000000000001E-3</v>
       </c>
-      <c r="H9" s="4">
-        <v>1</v>
-      </c>
-      <c r="I9" s="5">
+      <c r="H9" s="2">
+        <v>1</v>
+      </c>
+      <c r="I9" s="3">
         <v>6.8954000000000003E-3</v>
       </c>
-      <c r="J9" s="4">
-        <v>1</v>
-      </c>
-      <c r="K9" s="4">
-        <v>12</v>
-      </c>
-      <c r="L9" s="30">
+      <c r="J9" s="2">
+        <v>1</v>
+      </c>
+      <c r="K9" s="2">
+        <v>12</v>
+      </c>
+      <c r="L9" s="18">
         <f t="shared" si="0"/>
         <v>7.6999999999999999E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="6">
+    <row r="10" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="4">
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="19" t="s">
         <v>18</v>
       </c>
-      <c r="C10" s="22"/>
-      <c r="D10" s="22"/>
-      <c r="E10" s="19"/>
-      <c r="F10" s="4">
+      <c r="C10" s="45"/>
+      <c r="D10" s="45"/>
+      <c r="E10" s="42"/>
+      <c r="F10" s="2">
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="3">
         <v>4.9000000000000002E-2</v>
       </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
         <v>4.8567600000000002E-2</v>
       </c>
-      <c r="J10" s="4">
-        <v>1</v>
-      </c>
-      <c r="K10" s="4">
-        <v>12</v>
-      </c>
-      <c r="L10" s="30">
+      <c r="J10" s="2">
+        <v>1</v>
+      </c>
+      <c r="K10" s="2">
+        <v>12</v>
+      </c>
+      <c r="L10" s="18">
         <f t="shared" si="0"/>
         <v>0.53900000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+    <row r="11" spans="1:13" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="19" t="s">
         <v>19</v>
       </c>
-      <c r="C11" s="22"/>
-      <c r="D11" s="22"/>
-      <c r="E11" s="19"/>
-      <c r="F11" s="4">
+      <c r="C11" s="45"/>
+      <c r="D11" s="45"/>
+      <c r="E11" s="42"/>
+      <c r="F11" s="2">
         <v>1E-4</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="3">
         <v>2E-3</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="2">
         <v>4</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="3">
         <v>7.7948000000000002E-3</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="2">
         <v>4</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="2">
         <v>48</v>
       </c>
-      <c r="L11" s="30">
+      <c r="L11" s="18">
         <f t="shared" si="0"/>
         <v>8.7999999999999995E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="22" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+    <row r="12" spans="1:13" ht="22" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="31" t="s">
+      <c r="B12" s="19" t="s">
         <v>20</v>
       </c>
-      <c r="C12" s="22"/>
-      <c r="D12" s="22"/>
-      <c r="E12" s="19"/>
-      <c r="F12" s="4">
+      <c r="C12" s="45"/>
+      <c r="D12" s="45"/>
+      <c r="E12" s="42"/>
+      <c r="F12" s="2">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="3">
         <v>0.188</v>
       </c>
-      <c r="H12" s="4">
-        <v>1</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="H12" s="2">
+        <v>1</v>
+      </c>
+      <c r="I12" s="3">
         <v>0.1876748</v>
       </c>
-      <c r="J12" s="4">
-        <v>1</v>
-      </c>
-      <c r="K12" s="4">
-        <v>12</v>
-      </c>
-      <c r="L12" s="30">
+      <c r="J12" s="2">
+        <v>1</v>
+      </c>
+      <c r="K12" s="2">
+        <v>12</v>
+      </c>
+      <c r="L12" s="18">
         <f t="shared" si="0"/>
         <v>2.0680000000000001</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="38.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="31" t="s">
+    <row r="13" spans="1:13" ht="38.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>21</v>
       </c>
-      <c r="C13" s="23"/>
-      <c r="D13" s="23"/>
-      <c r="E13" s="20"/>
-      <c r="F13" s="4">
+      <c r="C13" s="46"/>
+      <c r="D13" s="46"/>
+      <c r="E13" s="43"/>
+      <c r="F13" s="2">
         <v>1.95E-2</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="3">
         <v>0.29299999999999998</v>
       </c>
-      <c r="H13" s="4">
-        <v>1</v>
-      </c>
-      <c r="I13" s="5">
+      <c r="H13" s="2">
+        <v>1</v>
+      </c>
+      <c r="I13" s="3">
         <v>0.2926048</v>
       </c>
-      <c r="J13" s="4">
-        <v>1</v>
-      </c>
-      <c r="K13" s="4">
-        <v>12</v>
-      </c>
-      <c r="L13" s="30">
+      <c r="J13" s="2">
+        <v>1</v>
+      </c>
+      <c r="K13" s="2">
+        <v>12</v>
+      </c>
+      <c r="L13" s="18">
         <f t="shared" si="0"/>
         <v>3.2229999999999999</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="37" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="6">
+    <row r="14" spans="1:13" ht="37" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="4">
         <v>13</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="19" t="s">
         <v>22</v>
       </c>
-      <c r="C14" s="31" t="s">
+      <c r="C14" s="19" t="s">
         <v>23</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <v>28.09</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>10</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="3">
         <f>E14/F14</f>
         <v>2.8090000000000002</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="2">
         <v>2</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="3">
         <f>G14*H14</f>
         <v>5.6180000000000003</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="2">
         <v>5</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="2">
         <v>24</v>
       </c>
-      <c r="L14" s="30">
+      <c r="L14" s="18">
         <f t="shared" si="0"/>
         <v>53.371000000000002</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="32" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
+    <row r="15" spans="1:13" ht="34" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="19" t="s">
         <v>25</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="19" t="s">
         <v>26</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>215</v>
-      </c>
-      <c r="E15" s="5">
+      <c r="D15" s="1" t="s">
+        <v>210</v>
+      </c>
+      <c r="E15" s="3">
         <v>8.39</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>50</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="3">
         <f t="shared" ref="G15:G27" si="1">E15/F15</f>
         <v>0.1678</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="2">
         <v>6</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="3">
         <f t="shared" ref="I15:I27" si="2">G15*H15</f>
         <v>1.0068000000000001</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="2">
         <v>20</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="2">
         <v>72</v>
       </c>
-      <c r="L15" s="30">
+      <c r="L15" s="18">
         <f t="shared" si="0"/>
         <v>8.7256</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
+    <row r="16" spans="1:13" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="19" t="s">
         <v>27</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="19" t="s">
         <v>28</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>216</v>
-      </c>
-      <c r="E16" s="5">
+      <c r="D16" s="1" t="s">
+        <v>211</v>
+      </c>
+      <c r="E16" s="3">
         <v>9.59</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>10</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="3">
         <f t="shared" si="1"/>
         <v>0.95899999999999996</v>
       </c>
-      <c r="H16" s="4">
-        <v>1</v>
-      </c>
-      <c r="I16" s="5">
+      <c r="H16" s="2">
+        <v>1</v>
+      </c>
+      <c r="I16" s="3">
         <f t="shared" si="2"/>
         <v>0.95899999999999996</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="2">
         <v>4</v>
       </c>
-      <c r="K16" s="4">
-        <v>12</v>
-      </c>
-      <c r="L16" s="30">
+      <c r="K16" s="2">
+        <v>12</v>
+      </c>
+      <c r="L16" s="18">
         <f t="shared" si="0"/>
         <v>7.6719999999999997</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="32" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+    <row r="17" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="19" t="s">
         <v>29</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="19" t="s">
         <v>30</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>217</v>
-      </c>
-      <c r="E17" s="5">
+      <c r="D17" s="1" t="s">
+        <v>212</v>
+      </c>
+      <c r="E17" s="3">
         <v>5.99</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>50</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="3">
         <f t="shared" si="1"/>
         <v>0.1198</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="2">
         <v>6</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="3">
         <f t="shared" si="2"/>
         <v>0.71879999999999999</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="2">
         <v>0</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="2">
         <v>72</v>
       </c>
-      <c r="L17" s="30">
+      <c r="L17" s="18">
         <f t="shared" si="0"/>
         <v>8.6256000000000004</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="32" x14ac:dyDescent="0.4">
-      <c r="A18" s="6">
+    <row r="18" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A18" s="4">
         <v>17</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="19" t="s">
         <v>31</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="19" t="s">
         <v>32</v>
       </c>
-      <c r="D18" s="2" t="s">
-        <v>218</v>
-      </c>
-      <c r="E18" s="5">
+      <c r="D18" s="1" t="s">
+        <v>213</v>
+      </c>
+      <c r="E18" s="3">
         <v>7.99</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>50</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="3">
         <f t="shared" si="1"/>
         <v>0.1598</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="2">
         <v>4</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="3">
         <f t="shared" si="2"/>
         <v>0.63919999999999999</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="2">
         <v>22</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="2">
         <v>48</v>
       </c>
-      <c r="L18" s="30">
+      <c r="L18" s="18">
         <f t="shared" si="0"/>
         <v>4.1547999999999998</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="26.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="4">
+    <row r="19" spans="1:12" ht="26.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="19" t="s">
         <v>33</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="19" t="s">
         <v>34</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E19" s="5">
+      <c r="D19" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E19" s="3">
         <v>5.49</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>200</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="3">
         <f t="shared" si="1"/>
         <v>2.7450000000000002E-2</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="2">
         <v>8</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="3">
         <f t="shared" si="2"/>
         <v>0.21960000000000002</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="2">
         <v>25</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="2">
         <v>48</v>
       </c>
-      <c r="L19" s="30">
+      <c r="L19" s="18">
         <f t="shared" si="0"/>
         <v>0.63135000000000008</v>
       </c>
     </row>
-    <row r="20" spans="1:12" s="59" customFormat="1" ht="24" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="36">
+    <row r="20" spans="1:12" ht="24" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="37" t="s">
+      <c r="B20" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="C20" s="37" t="s">
+      <c r="C20" s="19" t="s">
         <v>36</v>
       </c>
-      <c r="D20" s="38" t="s">
+      <c r="D20" s="23" t="s">
         <v>37</v>
       </c>
-      <c r="E20" s="39">
+      <c r="E20" s="24">
         <v>60</v>
       </c>
-      <c r="F20" s="36">
-        <v>1</v>
-      </c>
-      <c r="G20" s="39">
+      <c r="F20" s="2">
+        <v>1</v>
+      </c>
+      <c r="G20" s="24">
         <f t="shared" si="1"/>
         <v>60</v>
       </c>
-      <c r="H20" s="36">
-        <v>1</v>
-      </c>
-      <c r="I20" s="39">
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="24">
         <f t="shared" si="2"/>
         <v>60</v>
       </c>
-      <c r="J20" s="36">
-        <v>12</v>
-      </c>
-      <c r="K20" s="36">
-        <v>12</v>
-      </c>
-      <c r="L20" s="40">
+      <c r="J20" s="2">
+        <v>12</v>
+      </c>
+      <c r="K20" s="2">
+        <v>12</v>
+      </c>
+      <c r="L20" s="18">
         <f t="shared" si="0"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="32.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="4">
+    <row r="21" spans="1:12" ht="32.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="19" t="s">
         <v>38</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="3">
         <v>8.2899999999999991</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>8</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="3">
         <f t="shared" si="1"/>
         <v>1.0362499999999999</v>
       </c>
-      <c r="H21" s="4">
-        <v>1</v>
-      </c>
-      <c r="I21" s="5">
+      <c r="H21" s="2">
+        <v>1</v>
+      </c>
+      <c r="I21" s="3">
         <f t="shared" si="2"/>
         <v>1.0362499999999999</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="2">
         <v>6</v>
       </c>
-      <c r="K21" s="4">
-        <v>12</v>
-      </c>
-      <c r="L21" s="30">
+      <c r="K21" s="2">
+        <v>12</v>
+      </c>
+      <c r="L21" s="18">
         <f t="shared" si="0"/>
         <v>6.2174999999999994</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="32" x14ac:dyDescent="0.4">
-      <c r="A22" s="6">
+    <row r="22" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A22" s="4">
         <v>21</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>219</v>
-      </c>
-      <c r="E22" s="5">
-        <v>8.2799999999999994</v>
-      </c>
-      <c r="F22" s="4">
-        <v>100</v>
-      </c>
-      <c r="G22" s="5">
+      <c r="D22" s="1" t="s">
+        <v>214</v>
+      </c>
+      <c r="E22" s="3">
+        <v>9.7899999999999991</v>
+      </c>
+      <c r="F22" s="2">
+        <v>50</v>
+      </c>
+      <c r="G22" s="3">
         <f t="shared" si="1"/>
-        <v>8.2799999999999999E-2</v>
-      </c>
-      <c r="H22" s="4">
+        <v>0.19579999999999997</v>
+      </c>
+      <c r="H22" s="2">
         <v>6</v>
       </c>
-      <c r="I22" s="5">
-        <f t="shared" si="2"/>
-        <v>0.49680000000000002</v>
-      </c>
-      <c r="J22" s="4">
+      <c r="I22" s="3">
+        <f t="shared" si="2"/>
+        <v>1.1747999999999998</v>
+      </c>
+      <c r="J22" s="2">
         <v>15</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="2">
         <v>72</v>
       </c>
-      <c r="L22" s="30">
-        <f t="shared" si="0"/>
-        <v>4.7195999999999998</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="32" x14ac:dyDescent="0.4">
-      <c r="A23" s="4">
+      <c r="L22" s="18">
+        <f t="shared" si="0"/>
+        <v>11.160599999999999</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="19" t="s">
         <v>44</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="3">
         <v>7.19</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>8</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="3">
         <f t="shared" si="1"/>
         <v>0.89875000000000005</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="2">
         <v>6</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="3">
         <f t="shared" si="2"/>
         <v>5.3925000000000001</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="2">
         <v>24</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="2">
         <v>72</v>
       </c>
-      <c r="L23" s="30">
+      <c r="L23" s="18">
         <f t="shared" si="0"/>
         <v>43.14</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="48" x14ac:dyDescent="0.4">
-      <c r="A24" s="4">
+    <row r="24" spans="1:12" ht="51" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="19" t="s">
         <v>46</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>48</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="3">
         <v>13.19</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>10</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="3">
         <f t="shared" si="1"/>
         <v>1.319</v>
       </c>
-      <c r="H24" s="4">
-        <v>1</v>
-      </c>
-      <c r="I24" s="5">
+      <c r="H24" s="2">
+        <v>1</v>
+      </c>
+      <c r="I24" s="3">
         <f t="shared" si="2"/>
         <v>1.319</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="2">
         <v>9</v>
       </c>
-      <c r="K24" s="4">
-        <v>12</v>
-      </c>
-      <c r="L24" s="30">
+      <c r="K24" s="2">
+        <v>12</v>
+      </c>
+      <c r="L24" s="18">
         <f t="shared" si="0"/>
         <v>3.9569999999999999</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A25" s="4">
+    <row r="25" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="19" t="s">
         <v>49</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D25" s="2" t="s">
-        <v>220</v>
-      </c>
-      <c r="E25" s="5">
+      <c r="D25" s="1" t="s">
+        <v>215</v>
+      </c>
+      <c r="E25" s="3">
         <v>9.19</v>
       </c>
-      <c r="F25" s="4">
+      <c r="F25" s="2">
         <v>100</v>
       </c>
-      <c r="G25" s="5">
+      <c r="G25" s="3">
         <f t="shared" si="1"/>
         <v>9.1899999999999996E-2</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="2">
         <v>30</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="3">
         <f t="shared" si="2"/>
         <v>2.7569999999999997</v>
       </c>
-      <c r="J25" s="4">
+      <c r="J25" s="2">
         <v>18</v>
       </c>
-      <c r="K25" s="4">
+      <c r="K25" s="2">
         <v>360</v>
       </c>
-      <c r="L25" s="30">
+      <c r="L25" s="18">
         <f t="shared" si="0"/>
         <v>31.4298</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A26" s="6">
+    <row r="26" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A26" s="4">
         <v>25</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="19" t="s">
         <v>52</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="19" t="s">
         <v>50</v>
       </c>
-      <c r="D26" s="2" t="s">
-        <v>221</v>
-      </c>
-      <c r="E26" s="5">
+      <c r="D26" s="1" t="s">
+        <v>216</v>
+      </c>
+      <c r="E26" s="3">
         <v>9.19</v>
       </c>
-      <c r="F26" s="4">
+      <c r="F26" s="2">
         <v>100</v>
       </c>
-      <c r="G26" s="5">
+      <c r="G26" s="3">
         <f t="shared" si="1"/>
         <v>9.1899999999999996E-2</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="2">
         <v>6</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="3">
         <f t="shared" si="2"/>
         <v>0.5514</v>
       </c>
-      <c r="J26" s="4">
+      <c r="J26" s="2">
         <v>44</v>
       </c>
-      <c r="K26" s="4">
+      <c r="K26" s="2">
         <v>72</v>
       </c>
-      <c r="L26" s="30">
+      <c r="L26" s="18">
         <f t="shared" si="0"/>
         <v>2.5731999999999999</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="32" x14ac:dyDescent="0.4">
-      <c r="A27" s="42">
+    <row r="27" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A27" s="26">
         <v>26</v>
       </c>
-      <c r="B27" s="43" t="s">
+      <c r="B27" s="27" t="s">
         <v>53</v>
       </c>
-      <c r="C27" s="43" t="s">
+      <c r="C27" s="27" t="s">
         <v>54</v>
       </c>
-      <c r="D27" s="44" t="s">
-        <v>222</v>
-      </c>
-      <c r="E27" s="45">
+      <c r="D27" s="28" t="s">
+        <v>217</v>
+      </c>
+      <c r="E27" s="29">
         <v>15.1</v>
       </c>
-      <c r="F27" s="42">
+      <c r="F27" s="26">
         <v>20</v>
       </c>
-      <c r="G27" s="45">
+      <c r="G27" s="29">
         <f t="shared" si="1"/>
         <v>0.755</v>
       </c>
-      <c r="H27" s="42">
-        <v>1</v>
-      </c>
-      <c r="I27" s="45">
+      <c r="H27" s="26">
+        <v>1</v>
+      </c>
+      <c r="I27" s="29">
         <f t="shared" si="2"/>
         <v>0.755</v>
       </c>
-      <c r="J27" s="42">
+      <c r="J27" s="26">
         <v>15</v>
       </c>
-      <c r="K27" s="42">
+      <c r="K27" s="26">
+        <v>12</v>
+      </c>
+      <c r="L27" s="30">
+        <f t="shared" si="0"/>
         <v>0</v>
       </c>
-      <c r="L27" s="46">
-        <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" s="15" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A28" s="32" t="s">
+    </row>
+    <row r="28" spans="1:12" s="13" customFormat="1" ht="32" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A28" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B28" s="32"/>
-      <c r="C28" s="32"/>
-      <c r="D28" s="32"/>
-      <c r="E28" s="32"/>
-      <c r="F28" s="32"/>
-      <c r="G28" s="32"/>
-      <c r="H28" s="32"/>
-      <c r="I28" s="33">
+      <c r="B28" s="36"/>
+      <c r="C28" s="36"/>
+      <c r="D28" s="36"/>
+      <c r="E28" s="36"/>
+      <c r="F28" s="36"/>
+      <c r="G28" s="36"/>
+      <c r="H28" s="36"/>
+      <c r="I28" s="21">
         <f>SUM(I2:I27)</f>
-        <v>83.953942499999997</v>
-      </c>
-      <c r="J28" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="K28" s="34"/>
-      <c r="L28" s="35">
+        <v>84.631942500000008</v>
+      </c>
+      <c r="J28" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="K28" s="38"/>
+      <c r="L28" s="22">
         <f>SUM(L2:L27)</f>
-        <v>202.56344999999999</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A29" s="41"/>
-      <c r="B29" s="41"/>
-      <c r="C29" s="41"/>
-      <c r="D29" s="41"/>
-      <c r="E29" s="41"/>
-      <c r="F29" s="41"/>
-      <c r="G29" s="41"/>
-      <c r="H29" s="41"/>
-      <c r="I29" s="41"/>
-      <c r="J29" s="41"/>
-      <c r="K29" s="41"/>
-      <c r="L29" s="41"/>
-    </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="I32" s="12"/>
-    </row>
-    <row r="59" ht="31" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="60" ht="32" customHeight="1" x14ac:dyDescent="0.4"/>
-    <row r="62" ht="32" customHeight="1" x14ac:dyDescent="0.4"/>
+        <v>209.00445000000002</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A29" s="25"/>
+      <c r="B29" s="25"/>
+      <c r="C29" s="25"/>
+      <c r="D29" s="25"/>
+      <c r="E29" s="25"/>
+      <c r="F29" s="25"/>
+      <c r="G29" s="25"/>
+      <c r="H29" s="25"/>
+      <c r="I29" s="25"/>
+      <c r="J29" s="25"/>
+      <c r="K29" s="25"/>
+      <c r="L29" s="25"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="I32" s="10"/>
+    </row>
+    <row r="59" ht="31" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="60" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
+    <row r="62" ht="32" customHeight="1" x14ac:dyDescent="0.2"/>
   </sheetData>
   <mergeCells count="5">
     <mergeCell ref="J28:K28"/>
@@ -3163,7 +3233,7 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4B2A752E-49A0-D348-9E27-6206B0A59C47}">
   <dimension ref="A1:L45"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="16.33203125" customWidth="1"/>
     <col min="2" max="2" width="29.6640625" customWidth="1"/>
@@ -3176,1712 +3246,1712 @@
     <col min="9" max="9" width="10.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="64" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:12" ht="68" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="28" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="16" t="s">
         <v>5</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="16" t="s">
         <v>6</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="16" t="s">
         <v>8</v>
       </c>
-      <c r="J1" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="K1" s="28" t="s">
+      <c r="J1" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="L1" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="L1" s="28" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="31" t="s">
+    </row>
+    <row r="2" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="19" t="s">
         <v>59</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>61</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2" s="3">
         <v>34.97</v>
       </c>
-      <c r="F2" s="4">
+      <c r="F2" s="2">
         <v>5</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="3">
         <f>E2/F2</f>
         <v>6.9939999999999998</v>
       </c>
-      <c r="H2" s="4">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5">
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
         <f>G2*H2</f>
         <v>6.9939999999999998</v>
       </c>
-      <c r="J2" s="4">
+      <c r="J2" s="2">
         <v>5</v>
       </c>
-      <c r="K2" s="4">
-        <v>12</v>
-      </c>
-      <c r="L2" s="5">
+      <c r="K2" s="2">
+        <v>12</v>
+      </c>
+      <c r="L2" s="3">
         <f>(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
         <v>48.957999999999998</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+    <row r="3" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="31" t="s">
+      <c r="B3" s="19" t="s">
         <v>160</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>161</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3" s="3">
         <v>30.36</v>
       </c>
-      <c r="F3" s="4">
+      <c r="F3" s="2">
         <v>6</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="3">
         <f t="shared" ref="G3:G40" si="0">E3/F3</f>
         <v>5.0599999999999996</v>
       </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
         <f t="shared" ref="I3:I40" si="1">G3*H3</f>
         <v>5.0599999999999996</v>
       </c>
-      <c r="J3" s="4">
+      <c r="J3" s="2">
         <v>6</v>
       </c>
-      <c r="K3" s="4">
-        <v>12</v>
-      </c>
-      <c r="L3" s="5">
+      <c r="K3" s="2">
+        <v>12</v>
+      </c>
+      <c r="L3" s="3">
         <f t="shared" ref="L3:L40" si="2">(IF(K3-J3&lt;0,0,K3-J3))*G3</f>
         <v>30.36</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+    <row r="4" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="31" t="s">
+      <c r="B4" s="19" t="s">
         <v>116</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>170</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4" s="3">
         <v>0.36</v>
       </c>
-      <c r="F4" s="4">
+      <c r="F4" s="2">
         <v>180</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <f>E4/F4</f>
         <v>2E-3</v>
       </c>
-      <c r="H4" s="4">
+      <c r="H4" s="2">
         <f>F4/12</f>
         <v>15</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4" s="3">
         <f>G4*H4</f>
         <v>0.03</v>
       </c>
-      <c r="J4" s="4">
+      <c r="J4" s="2">
         <v>180</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="2">
         <v>180</v>
       </c>
-      <c r="L4" s="5">
+      <c r="L4" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+    <row r="5" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="31" t="s">
+      <c r="B5" s="19" t="s">
         <v>115</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>164</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5" s="3">
         <v>5.88</v>
       </c>
-      <c r="F5" s="4">
+      <c r="F5" s="2">
         <v>50</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="3">
         <f t="shared" ref="G5:G26" si="3">E5/F5</f>
         <v>0.1176</v>
       </c>
-      <c r="H5" s="4">
+      <c r="H5" s="2">
         <f>48/12</f>
         <v>4</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5" s="3">
         <f t="shared" ref="I5:I26" si="4">G5*H5</f>
         <v>0.47039999999999998</v>
       </c>
-      <c r="J5" s="4">
+      <c r="J5" s="2">
         <v>50</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="2">
         <v>48</v>
       </c>
-      <c r="L5" s="5">
+      <c r="L5" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+    <row r="6" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="19" t="s">
         <v>114</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6" s="3">
         <v>0.45</v>
       </c>
-      <c r="F6" s="4">
+      <c r="F6" s="2">
         <v>72</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="3">
         <f t="shared" si="3"/>
         <v>6.2500000000000003E-3</v>
       </c>
-      <c r="H6" s="4">
+      <c r="H6" s="2">
         <f t="shared" ref="H6:H31" si="5">F6/12</f>
         <v>6</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6" s="3">
         <f t="shared" si="4"/>
         <v>3.7500000000000006E-2</v>
       </c>
-      <c r="J6" s="4">
+      <c r="J6" s="2">
         <v>72</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="2">
         <v>72</v>
       </c>
-      <c r="L6" s="5">
+      <c r="L6" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+    <row r="7" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>6</v>
       </c>
-      <c r="B7" s="31" t="s">
+      <c r="B7" s="19" t="s">
         <v>117</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>165</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7" s="3">
         <v>0.76</v>
       </c>
-      <c r="F7" s="4">
+      <c r="F7" s="2">
         <v>36</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="3">
         <f t="shared" si="3"/>
         <v>2.1111111111111112E-2</v>
       </c>
-      <c r="H7" s="4">
+      <c r="H7" s="2">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7" s="3">
         <f t="shared" si="4"/>
         <v>6.3333333333333339E-2</v>
       </c>
-      <c r="J7" s="4">
+      <c r="J7" s="2">
         <v>36</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="2">
         <v>36</v>
       </c>
-      <c r="L7" s="5">
+      <c r="L7" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+    <row r="8" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>7</v>
       </c>
-      <c r="B8" s="31" t="s">
+      <c r="B8" s="19" t="s">
         <v>118</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>171</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E8" s="5">
+      <c r="E8" s="3">
         <v>0.65</v>
       </c>
-      <c r="F8" s="4">
+      <c r="F8" s="2">
         <v>24</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="3">
         <f t="shared" si="3"/>
         <v>2.7083333333333334E-2</v>
       </c>
-      <c r="H8" s="4">
+      <c r="H8" s="2">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="I8" s="5">
+      <c r="I8" s="3">
         <f t="shared" si="4"/>
         <v>5.4166666666666669E-2</v>
       </c>
-      <c r="J8" s="4">
+      <c r="J8" s="2">
         <v>24</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="2">
         <v>24</v>
       </c>
-      <c r="L8" s="5">
+      <c r="L8" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+    <row r="9" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>8</v>
       </c>
-      <c r="B9" s="31" t="s">
+      <c r="B9" s="19" t="s">
         <v>119</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>166</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E9" s="5">
+      <c r="E9" s="3">
         <v>0.04</v>
       </c>
-      <c r="F9" s="4">
-        <v>12</v>
-      </c>
-      <c r="G9" s="5">
+      <c r="F9" s="2">
+        <v>12</v>
+      </c>
+      <c r="G9" s="3">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="H9" s="4">
+      <c r="H9" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I9" s="5">
+      <c r="I9" s="3">
         <f t="shared" si="4"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="J9" s="4">
-        <v>12</v>
-      </c>
-      <c r="K9" s="4">
-        <v>12</v>
-      </c>
-      <c r="L9" s="5">
+      <c r="J9" s="2">
+        <v>12</v>
+      </c>
+      <c r="K9" s="2">
+        <v>12</v>
+      </c>
+      <c r="L9" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+    <row r="10" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <v>9</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="19" t="s">
         <v>120</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>167</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E10" s="5">
+      <c r="E10" s="3">
         <v>1.61</v>
       </c>
-      <c r="F10" s="4">
-        <v>12</v>
-      </c>
-      <c r="G10" s="5">
+      <c r="F10" s="2">
+        <v>12</v>
+      </c>
+      <c r="G10" s="3">
         <f t="shared" si="3"/>
         <v>0.13416666666666668</v>
       </c>
-      <c r="H10" s="4">
+      <c r="H10" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I10" s="5">
+      <c r="I10" s="3">
         <f t="shared" si="4"/>
         <v>0.13416666666666668</v>
       </c>
-      <c r="J10" s="4">
-        <v>12</v>
-      </c>
-      <c r="K10" s="4">
-        <v>12</v>
-      </c>
-      <c r="L10" s="5">
+      <c r="J10" s="2">
+        <v>12</v>
+      </c>
+      <c r="K10" s="2">
+        <v>12</v>
+      </c>
+      <c r="L10" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+    <row r="11" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>10</v>
       </c>
-      <c r="B11" s="31" t="s">
+      <c r="B11" s="19" t="s">
         <v>121</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>168</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E11" s="5">
+      <c r="E11" s="3">
         <v>0.17</v>
       </c>
-      <c r="F11" s="4">
-        <v>12</v>
-      </c>
-      <c r="G11" s="5">
+      <c r="F11" s="2">
+        <v>12</v>
+      </c>
+      <c r="G11" s="3">
         <f t="shared" si="3"/>
         <v>1.4166666666666668E-2</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="3">
         <f t="shared" si="4"/>
         <v>1.4166666666666668E-2</v>
       </c>
-      <c r="J11" s="4">
-        <v>12</v>
-      </c>
-      <c r="K11" s="4">
-        <v>12</v>
-      </c>
-      <c r="L11" s="5">
+      <c r="J11" s="2">
+        <v>12</v>
+      </c>
+      <c r="K11" s="2">
+        <v>12</v>
+      </c>
+      <c r="L11" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+    <row r="12" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>11</v>
       </c>
-      <c r="B12" s="58" t="s">
+      <c r="B12" s="35" t="s">
         <v>126</v>
       </c>
-      <c r="C12" s="8" t="s">
+      <c r="C12" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="D12" s="9" t="s">
+      <c r="D12" s="7" t="s">
         <v>113</v>
       </c>
-      <c r="E12" s="57">
+      <c r="E12" s="34">
         <v>0.84</v>
       </c>
-      <c r="F12" s="8">
+      <c r="F12" s="6">
         <v>24</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="3">
         <f t="shared" si="3"/>
         <v>3.4999999999999996E-2</v>
       </c>
-      <c r="H12" s="4">
+      <c r="H12" s="2">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="I12" s="5">
+      <c r="I12" s="3">
         <f t="shared" si="4"/>
         <v>6.9999999999999993E-2</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="2">
         <v>24</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="2">
         <v>24</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
-        <v>12</v>
-      </c>
-      <c r="B13" s="31" t="s">
+    <row r="13" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
+        <v>12</v>
+      </c>
+      <c r="B13" s="19" t="s">
         <v>122</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E13" s="5">
+      <c r="E13" s="3">
         <v>2.48</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>36</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="3">
         <f t="shared" si="3"/>
         <v>6.8888888888888888E-2</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="2">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="3">
         <f t="shared" si="4"/>
         <v>0.20666666666666667</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="2">
         <v>36</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="2">
         <v>36</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
+    <row r="14" spans="1:12" ht="16" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
         <v>13</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="19" t="s">
         <v>124</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E14" s="5">
+      <c r="E14" s="3">
         <v>5.93</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>24</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="3">
         <f t="shared" si="3"/>
         <v>0.24708333333333332</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="2">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="3">
         <f t="shared" si="4"/>
         <v>0.49416666666666664</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="2">
         <v>24</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="2">
         <v>24</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
+    <row r="15" spans="1:12" ht="17" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
         <v>14</v>
       </c>
-      <c r="B15" s="31" t="s">
+      <c r="B15" s="19" t="s">
         <v>127</v>
       </c>
-      <c r="C15" s="31" t="s">
+      <c r="C15" s="19" t="s">
         <v>129</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E15" s="5">
+      <c r="E15" s="3">
         <v>0.52</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>25</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="3">
         <f t="shared" si="3"/>
         <v>2.0799999999999999E-2</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="2">
         <f>24/12</f>
         <v>2</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="3">
         <f t="shared" si="4"/>
         <v>4.1599999999999998E-2</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="2">
         <v>25</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="2">
         <v>24</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
+    <row r="16" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <v>15</v>
       </c>
-      <c r="B16" s="31" t="s">
+      <c r="B16" s="19" t="s">
         <v>130</v>
       </c>
-      <c r="C16" s="31" t="s">
+      <c r="C16" s="19" t="s">
         <v>131</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E16" s="5">
+      <c r="E16" s="3">
         <v>0.83</v>
       </c>
-      <c r="F16" s="4">
-        <v>12</v>
-      </c>
-      <c r="G16" s="5">
+      <c r="F16" s="2">
+        <v>12</v>
+      </c>
+      <c r="G16" s="3">
         <f t="shared" si="3"/>
         <v>6.9166666666666668E-2</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="3">
         <f t="shared" si="4"/>
         <v>6.9166666666666668E-2</v>
       </c>
-      <c r="J16" s="4">
-        <v>12</v>
-      </c>
-      <c r="K16" s="4">
-        <v>12</v>
-      </c>
-      <c r="L16" s="5">
+      <c r="J16" s="2">
+        <v>12</v>
+      </c>
+      <c r="K16" s="2">
+        <v>12</v>
+      </c>
+      <c r="L16" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="17" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+    <row r="17" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <v>16</v>
       </c>
-      <c r="B17" s="31" t="s">
+      <c r="B17" s="19" t="s">
         <v>132</v>
       </c>
-      <c r="C17" s="31" t="s">
+      <c r="C17" s="19" t="s">
         <v>172</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E17" s="5">
+      <c r="E17" s="3">
         <v>0.04</v>
       </c>
-      <c r="F17" s="4">
-        <v>12</v>
-      </c>
-      <c r="G17" s="5">
+      <c r="F17" s="2">
+        <v>12</v>
+      </c>
+      <c r="G17" s="3">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="3">
         <f t="shared" si="4"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="J17" s="4">
-        <v>12</v>
-      </c>
-      <c r="K17" s="4">
-        <v>12</v>
-      </c>
-      <c r="L17" s="5">
+      <c r="J17" s="2">
+        <v>12</v>
+      </c>
+      <c r="K17" s="2">
+        <v>12</v>
+      </c>
+      <c r="L17" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="18" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A18" s="4">
+    <row r="18" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
         <v>17</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="19" t="s">
         <v>133</v>
       </c>
-      <c r="C18" s="31" t="s">
+      <c r="C18" s="19" t="s">
         <v>173</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E18" s="5">
+      <c r="E18" s="3">
         <v>0.16</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>50</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="3">
         <f t="shared" si="3"/>
         <v>3.2000000000000002E-3</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="2">
         <f>48/12</f>
         <v>4</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="3">
         <f t="shared" si="4"/>
         <v>1.2800000000000001E-2</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="2">
         <v>50</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="2">
         <v>48</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A19" s="4">
+    <row r="19" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
         <v>18</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="19" t="s">
         <v>134</v>
       </c>
-      <c r="C19" s="31" t="s">
+      <c r="C19" s="19" t="s">
         <v>174</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E19" s="5">
+      <c r="E19" s="3">
         <v>0.24</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>24</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="3">
         <f t="shared" si="3"/>
         <v>0.01</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="2">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="3">
         <f t="shared" si="4"/>
         <v>0.02</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="2">
         <v>24</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="2">
         <v>24</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
+    <row r="20" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
         <v>19</v>
       </c>
-      <c r="B20" s="31" t="s">
+      <c r="B20" s="19" t="s">
         <v>135</v>
       </c>
-      <c r="C20" s="31" t="s">
+      <c r="C20" s="19" t="s">
         <v>136</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E20" s="5">
+      <c r="E20" s="3">
         <v>2.74</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>36</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="3">
         <f>E20/F20</f>
         <v>7.6111111111111115E-2</v>
       </c>
-      <c r="H20" s="4">
+      <c r="H20" s="2">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I20" s="5">
+      <c r="I20" s="3">
         <f t="shared" si="4"/>
         <v>0.22833333333333333</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="2">
         <v>36</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="2">
         <v>36</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A21" s="4">
+    <row r="21" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
         <v>20</v>
       </c>
-      <c r="B21" s="31" t="s">
+      <c r="B21" s="19" t="s">
         <v>137</v>
       </c>
-      <c r="C21" s="31" t="s">
+      <c r="C21" s="19" t="s">
         <v>138</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E21" s="5">
+      <c r="E21" s="3">
         <v>0.05</v>
       </c>
-      <c r="F21" s="4">
-        <v>12</v>
-      </c>
-      <c r="G21" s="5">
+      <c r="F21" s="2">
+        <v>12</v>
+      </c>
+      <c r="G21" s="3">
         <f t="shared" si="3"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="3">
         <f t="shared" si="4"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="J21" s="4">
-        <v>12</v>
-      </c>
-      <c r="K21" s="4">
-        <v>12</v>
-      </c>
-      <c r="L21" s="5">
+      <c r="J21" s="2">
+        <v>12</v>
+      </c>
+      <c r="K21" s="2">
+        <v>12</v>
+      </c>
+      <c r="L21" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A22" s="4">
+    <row r="22" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
         <v>21</v>
       </c>
-      <c r="B22" s="31" t="s">
+      <c r="B22" s="19" t="s">
         <v>139</v>
       </c>
-      <c r="C22" s="31" t="s">
+      <c r="C22" s="19" t="s">
         <v>140</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E22" s="5">
+      <c r="E22" s="3">
         <v>0.05</v>
       </c>
-      <c r="F22" s="4">
-        <v>12</v>
-      </c>
-      <c r="G22" s="5">
+      <c r="F22" s="2">
+        <v>12</v>
+      </c>
+      <c r="G22" s="3">
         <f>E22/F22</f>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="3">
         <f t="shared" si="4"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="J22" s="4">
-        <v>12</v>
-      </c>
-      <c r="K22" s="4">
-        <v>12</v>
-      </c>
-      <c r="L22" s="5">
+      <c r="J22" s="2">
+        <v>12</v>
+      </c>
+      <c r="K22" s="2">
+        <v>12</v>
+      </c>
+      <c r="L22" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A23" s="4">
+    <row r="23" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
         <v>22</v>
       </c>
-      <c r="B23" s="31" t="s">
+      <c r="B23" s="19" t="s">
         <v>141</v>
       </c>
-      <c r="C23" s="31" t="s">
+      <c r="C23" s="19" t="s">
         <v>175</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E23" s="5">
+      <c r="E23" s="3">
         <v>0.17</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>36</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="3">
         <f t="shared" si="3"/>
         <v>4.7222222222222223E-3</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="2">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="3">
         <f t="shared" si="4"/>
         <v>1.4166666666666668E-2</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="2">
         <v>36</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="2">
         <v>36</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A24" s="4">
+    <row r="24" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A24" s="2">
         <v>23</v>
       </c>
-      <c r="B24" s="31" t="s">
+      <c r="B24" s="19" t="s">
         <v>142</v>
       </c>
-      <c r="C24" s="31" t="s">
+      <c r="C24" s="19" t="s">
         <v>176</v>
       </c>
-      <c r="D24" s="2" t="s">
+      <c r="D24" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E24" s="5">
+      <c r="E24" s="3">
         <v>0.23</v>
       </c>
-      <c r="F24" s="4">
+      <c r="F24" s="2">
         <v>25</v>
       </c>
-      <c r="G24" s="5">
+      <c r="G24" s="3">
         <f t="shared" si="3"/>
         <v>9.1999999999999998E-3</v>
       </c>
-      <c r="H24" s="4">
+      <c r="H24" s="2">
         <f>24/12</f>
         <v>2</v>
       </c>
-      <c r="I24" s="5">
+      <c r="I24" s="3">
         <f t="shared" si="4"/>
         <v>1.84E-2</v>
       </c>
-      <c r="J24" s="4">
+      <c r="J24" s="2">
         <v>25</v>
       </c>
-      <c r="K24" s="4">
+      <c r="K24" s="2">
         <v>24</v>
       </c>
-      <c r="L24" s="5">
+      <c r="L24" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A25" s="4">
+    <row r="25" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A25" s="2">
         <v>24</v>
       </c>
-      <c r="B25" s="31" t="s">
+      <c r="B25" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="C25" s="31" t="s">
+      <c r="C25" s="19" t="s">
         <v>144</v>
       </c>
-      <c r="D25" s="2" t="s">
+      <c r="D25" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E25" s="5">
+      <c r="E25" s="3">
         <v>0.04</v>
       </c>
-      <c r="F25" s="4">
-        <v>12</v>
-      </c>
-      <c r="G25" s="5">
+      <c r="F25" s="2">
+        <v>12</v>
+      </c>
+      <c r="G25" s="3">
         <f t="shared" si="3"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="H25" s="4">
+      <c r="H25" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I25" s="5">
+      <c r="I25" s="3">
         <f t="shared" si="4"/>
         <v>3.3333333333333335E-3</v>
       </c>
-      <c r="J25" s="8">
-        <v>12</v>
-      </c>
-      <c r="K25" s="8">
-        <v>12</v>
-      </c>
-      <c r="L25" s="57">
+      <c r="J25" s="6">
+        <v>12</v>
+      </c>
+      <c r="K25" s="6">
+        <v>12</v>
+      </c>
+      <c r="L25" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="26" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A26" s="4">
+    <row r="26" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A26" s="2">
         <v>25</v>
       </c>
-      <c r="B26" s="31" t="s">
+      <c r="B26" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="C26" s="31" t="s">
+      <c r="C26" s="19" t="s">
         <v>146</v>
       </c>
-      <c r="D26" s="2" t="s">
+      <c r="D26" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E26" s="5">
+      <c r="E26" s="3">
         <v>0.08</v>
       </c>
-      <c r="F26" s="4">
-        <v>12</v>
-      </c>
-      <c r="G26" s="5">
+      <c r="F26" s="2">
+        <v>12</v>
+      </c>
+      <c r="G26" s="3">
         <f t="shared" si="3"/>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="H26" s="4">
+      <c r="H26" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I26" s="5">
+      <c r="I26" s="3">
         <f t="shared" si="4"/>
         <v>6.6666666666666671E-3</v>
       </c>
-      <c r="J26" s="8">
-        <v>12</v>
-      </c>
-      <c r="K26" s="8">
-        <v>12</v>
-      </c>
-      <c r="L26" s="57">
+      <c r="J26" s="6">
+        <v>12</v>
+      </c>
+      <c r="K26" s="6">
+        <v>12</v>
+      </c>
+      <c r="L26" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A27" s="4">
+    <row r="27" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A27" s="2">
         <v>26</v>
       </c>
-      <c r="B27" s="31" t="s">
+      <c r="B27" s="19" t="s">
         <v>147</v>
       </c>
-      <c r="C27" s="31" t="s">
+      <c r="C27" s="19" t="s">
         <v>148</v>
       </c>
-      <c r="D27" s="2" t="s">
+      <c r="D27" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E27" s="5">
+      <c r="E27" s="3">
         <v>0.05</v>
       </c>
-      <c r="F27" s="4">
-        <v>12</v>
-      </c>
-      <c r="G27" s="5">
+      <c r="F27" s="2">
+        <v>12</v>
+      </c>
+      <c r="G27" s="3">
         <f t="shared" si="0"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="H27" s="4">
+      <c r="H27" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I27" s="5">
+      <c r="I27" s="3">
         <f t="shared" si="1"/>
         <v>4.1666666666666666E-3</v>
       </c>
-      <c r="J27" s="8">
-        <v>12</v>
-      </c>
-      <c r="K27" s="8">
-        <v>12</v>
-      </c>
-      <c r="L27" s="57">
+      <c r="J27" s="6">
+        <v>12</v>
+      </c>
+      <c r="K27" s="6">
+        <v>12</v>
+      </c>
+      <c r="L27" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="28" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A28" s="4">
+    <row r="28" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A28" s="2">
         <v>27</v>
       </c>
-      <c r="B28" s="31" t="s">
+      <c r="B28" s="19" t="s">
         <v>149</v>
       </c>
-      <c r="C28" s="31" t="s">
+      <c r="C28" s="19" t="s">
         <v>150</v>
       </c>
-      <c r="D28" s="2" t="s">
+      <c r="D28" s="1" t="s">
         <v>62</v>
       </c>
-      <c r="E28" s="5">
+      <c r="E28" s="3">
         <v>0.11</v>
       </c>
-      <c r="F28" s="4">
-        <v>12</v>
-      </c>
-      <c r="G28" s="5">
+      <c r="F28" s="2">
+        <v>12</v>
+      </c>
+      <c r="G28" s="3">
         <f t="shared" si="0"/>
         <v>9.1666666666666667E-3</v>
       </c>
-      <c r="H28" s="4">
+      <c r="H28" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I28" s="5">
+      <c r="I28" s="3">
         <f t="shared" si="1"/>
         <v>9.1666666666666667E-3</v>
       </c>
-      <c r="J28" s="8">
-        <v>12</v>
-      </c>
-      <c r="K28" s="8">
-        <v>12</v>
-      </c>
-      <c r="L28" s="57">
+      <c r="J28" s="6">
+        <v>12</v>
+      </c>
+      <c r="K28" s="6">
+        <v>12</v>
+      </c>
+      <c r="L28" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="29" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A29" s="4">
+    <row r="29" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A29" s="2">
         <v>28</v>
       </c>
-      <c r="B29" s="31" t="s">
+      <c r="B29" s="19" t="s">
         <v>152</v>
       </c>
-      <c r="C29" s="31" t="s">
+      <c r="C29" s="19" t="s">
         <v>153</v>
       </c>
-      <c r="D29" s="2" t="s">
+      <c r="D29" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E29" s="5">
+      <c r="E29" s="3">
         <v>10.84</v>
       </c>
-      <c r="F29" s="4">
+      <c r="F29" s="2">
         <v>36</v>
       </c>
-      <c r="G29" s="5">
+      <c r="G29" s="3">
         <f t="shared" si="0"/>
         <v>0.30111111111111111</v>
       </c>
-      <c r="H29" s="4">
+      <c r="H29" s="2">
         <f t="shared" si="5"/>
         <v>3</v>
       </c>
-      <c r="I29" s="5">
+      <c r="I29" s="3">
         <f t="shared" si="1"/>
         <v>0.90333333333333332</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="6">
         <v>36</v>
       </c>
-      <c r="K29" s="8">
+      <c r="K29" s="6">
         <v>36</v>
       </c>
-      <c r="L29" s="57">
+      <c r="L29" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="30" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A30" s="4">
+    <row r="30" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A30" s="2">
         <v>29</v>
       </c>
-      <c r="B30" s="31" t="s">
+      <c r="B30" s="19" t="s">
         <v>154</v>
       </c>
-      <c r="C30" s="31" t="s">
+      <c r="C30" s="19" t="s">
         <v>155</v>
       </c>
-      <c r="D30" s="2" t="s">
+      <c r="D30" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E30" s="5">
+      <c r="E30" s="3">
         <v>3.62</v>
       </c>
-      <c r="F30" s="4">
+      <c r="F30" s="2">
         <v>24</v>
       </c>
-      <c r="G30" s="5">
+      <c r="G30" s="3">
         <f t="shared" si="0"/>
         <v>0.15083333333333335</v>
       </c>
-      <c r="H30" s="4">
+      <c r="H30" s="2">
         <f t="shared" si="5"/>
         <v>2</v>
       </c>
-      <c r="I30" s="5">
+      <c r="I30" s="3">
         <f t="shared" si="1"/>
         <v>0.30166666666666669</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="6">
         <v>24</v>
       </c>
-      <c r="K30" s="8">
+      <c r="K30" s="6">
         <v>24</v>
       </c>
-      <c r="L30" s="57">
+      <c r="L30" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="31" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A31" s="4">
+    <row r="31" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A31" s="2">
         <v>30</v>
       </c>
-      <c r="B31" s="31" t="s">
+      <c r="B31" s="19" t="s">
         <v>156</v>
       </c>
-      <c r="C31" s="31" t="s">
+      <c r="C31" s="19" t="s">
         <v>157</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E31" s="5">
+      <c r="E31" s="3">
         <v>6.71</v>
       </c>
-      <c r="F31" s="4">
-        <v>12</v>
-      </c>
-      <c r="G31" s="5">
+      <c r="F31" s="2">
+        <v>12</v>
+      </c>
+      <c r="G31" s="3">
         <f t="shared" si="0"/>
         <v>0.5591666666666667</v>
       </c>
-      <c r="H31" s="4">
+      <c r="H31" s="2">
         <f t="shared" si="5"/>
         <v>1</v>
       </c>
-      <c r="I31" s="5">
+      <c r="I31" s="3">
         <f t="shared" si="1"/>
         <v>0.5591666666666667</v>
       </c>
-      <c r="J31" s="8">
-        <v>12</v>
-      </c>
-      <c r="K31" s="8">
-        <v>12</v>
-      </c>
-      <c r="L31" s="57">
+      <c r="J31" s="6">
+        <v>12</v>
+      </c>
+      <c r="K31" s="6">
+        <v>12</v>
+      </c>
+      <c r="L31" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="32" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A32" s="4">
+    <row r="32" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A32" s="2">
         <v>31</v>
       </c>
-      <c r="B32" s="31" t="s">
+      <c r="B32" s="19" t="s">
         <v>158</v>
       </c>
-      <c r="C32" s="31" t="s">
+      <c r="C32" s="19" t="s">
         <v>159</v>
       </c>
-      <c r="D32" s="2" t="s">
+      <c r="D32" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="E32" s="5">
+      <c r="E32" s="3">
         <v>59.67</v>
       </c>
-      <c r="F32" s="4">
+      <c r="F32" s="2">
         <v>30</v>
       </c>
-      <c r="G32" s="5">
+      <c r="G32" s="3">
         <f t="shared" si="0"/>
         <v>1.9890000000000001</v>
       </c>
-      <c r="H32" s="4">
+      <c r="H32" s="2">
         <f>F32/5</f>
         <v>6</v>
       </c>
-      <c r="I32" s="5">
+      <c r="I32" s="3">
         <f t="shared" si="1"/>
         <v>11.934000000000001</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="6">
         <v>30</v>
       </c>
-      <c r="K32" s="8">
+      <c r="K32" s="6">
         <v>72</v>
       </c>
-      <c r="L32" s="57">
+      <c r="L32" s="34">
         <f t="shared" si="2"/>
         <v>83.538000000000011</v>
       </c>
     </row>
-    <row r="33" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A33" s="4">
+    <row r="33" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A33" s="2">
         <v>32</v>
       </c>
-      <c r="B33" s="31" t="s">
+      <c r="B33" s="19" t="s">
         <v>162</v>
       </c>
-      <c r="C33" s="31" t="s">
+      <c r="C33" s="19" t="s">
         <v>163</v>
       </c>
-      <c r="D33" s="2" t="s">
+      <c r="D33" s="1" t="s">
         <v>151</v>
       </c>
-      <c r="E33" s="5">
+      <c r="E33" s="3">
         <v>13.1</v>
       </c>
-      <c r="F33" s="4">
+      <c r="F33" s="2">
         <v>5</v>
       </c>
-      <c r="G33" s="5">
+      <c r="G33" s="3">
         <f t="shared" si="0"/>
         <v>2.62</v>
       </c>
-      <c r="H33" s="4">
+      <c r="H33" s="2">
         <f>F33/5</f>
         <v>1</v>
       </c>
-      <c r="I33" s="5">
+      <c r="I33" s="3">
         <f t="shared" si="1"/>
         <v>2.62</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="6">
         <v>5</v>
       </c>
-      <c r="K33" s="8">
-        <v>12</v>
-      </c>
-      <c r="L33" s="57">
+      <c r="K33" s="6">
+        <v>12</v>
+      </c>
+      <c r="L33" s="34">
         <f t="shared" si="2"/>
         <v>18.34</v>
       </c>
     </row>
-    <row r="34" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A34" s="4">
+    <row r="34" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A34" s="2">
         <v>33</v>
       </c>
-      <c r="B34" s="31" t="s">
+      <c r="B34" s="19" t="s">
         <v>177</v>
       </c>
-      <c r="C34" s="31" t="s">
+      <c r="C34" s="19" t="s">
         <v>178</v>
       </c>
-      <c r="D34" s="4" t="s">
+      <c r="D34" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E34" s="5">
+      <c r="E34" s="3">
         <v>1.3720000000000001</v>
       </c>
-      <c r="F34" s="4">
+      <c r="F34" s="2">
         <v>10</v>
       </c>
-      <c r="G34" s="5">
+      <c r="G34" s="3">
         <f t="shared" si="0"/>
         <v>0.13720000000000002</v>
       </c>
-      <c r="H34" s="4">
-        <v>1</v>
-      </c>
-      <c r="I34" s="5">
+      <c r="H34" s="2">
+        <v>1</v>
+      </c>
+      <c r="I34" s="3">
         <f t="shared" si="1"/>
         <v>0.13720000000000002</v>
       </c>
-      <c r="J34" s="8">
+      <c r="J34" s="6">
         <v>10</v>
       </c>
-      <c r="K34" s="8">
-        <v>12</v>
-      </c>
-      <c r="L34" s="57">
+      <c r="K34" s="6">
+        <v>12</v>
+      </c>
+      <c r="L34" s="34">
         <f t="shared" si="2"/>
         <v>0.27440000000000003</v>
       </c>
     </row>
-    <row r="35" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A35" s="4">
+    <row r="35" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A35" s="2">
         <v>34</v>
       </c>
-      <c r="B35" s="31" t="s">
+      <c r="B35" s="19" t="s">
         <v>180</v>
       </c>
-      <c r="C35" s="31" t="s">
+      <c r="C35" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="D35" s="4" t="s">
+      <c r="D35" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E35" s="5">
+      <c r="E35" s="3">
         <v>0.63700000000000001</v>
       </c>
-      <c r="F35" s="4">
+      <c r="F35" s="2">
         <v>10</v>
       </c>
-      <c r="G35" s="5">
+      <c r="G35" s="3">
         <f t="shared" si="0"/>
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="H35" s="4">
-        <v>1</v>
-      </c>
-      <c r="I35" s="5">
+      <c r="H35" s="2">
+        <v>1</v>
+      </c>
+      <c r="I35" s="3">
         <f t="shared" si="1"/>
         <v>6.3700000000000007E-2</v>
       </c>
-      <c r="J35" s="8">
+      <c r="J35" s="6">
         <v>10</v>
       </c>
-      <c r="K35" s="8">
-        <v>12</v>
-      </c>
-      <c r="L35" s="57">
+      <c r="K35" s="6">
+        <v>12</v>
+      </c>
+      <c r="L35" s="34">
         <f t="shared" si="2"/>
         <v>0.12740000000000001</v>
       </c>
     </row>
-    <row r="36" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A36" s="4">
+    <row r="36" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A36" s="2">
         <v>35</v>
       </c>
-      <c r="B36" s="31" t="s">
+      <c r="B36" s="19" t="s">
         <v>181</v>
       </c>
-      <c r="C36" s="31" t="s">
+      <c r="C36" s="19" t="s">
         <v>179</v>
       </c>
-      <c r="D36" s="4" t="s">
+      <c r="D36" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E36" s="5">
+      <c r="E36" s="3">
         <v>2.0169999999999999</v>
       </c>
-      <c r="F36" s="4">
+      <c r="F36" s="2">
         <v>10</v>
       </c>
-      <c r="G36" s="5">
+      <c r="G36" s="3">
         <f t="shared" si="0"/>
         <v>0.20169999999999999</v>
       </c>
-      <c r="H36" s="4">
-        <v>1</v>
-      </c>
-      <c r="I36" s="5">
+      <c r="H36" s="2">
+        <v>1</v>
+      </c>
+      <c r="I36" s="3">
         <f t="shared" si="1"/>
         <v>0.20169999999999999</v>
       </c>
-      <c r="J36" s="8">
+      <c r="J36" s="6">
         <v>10</v>
       </c>
-      <c r="K36" s="8">
-        <v>12</v>
-      </c>
-      <c r="L36" s="57">
+      <c r="K36" s="6">
+        <v>12</v>
+      </c>
+      <c r="L36" s="34">
         <f t="shared" si="2"/>
         <v>0.40339999999999998</v>
       </c>
     </row>
-    <row r="37" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A37" s="4">
+    <row r="37" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A37" s="2">
         <v>36</v>
       </c>
-      <c r="B37" s="31" t="s">
+      <c r="B37" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="C37" s="31" t="s">
+      <c r="C37" s="19" t="s">
         <v>183</v>
       </c>
-      <c r="D37" s="4" t="s">
+      <c r="D37" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E37" s="5">
+      <c r="E37" s="3">
         <v>16.899999999999999</v>
       </c>
-      <c r="F37" s="4">
+      <c r="F37" s="2">
         <v>10</v>
       </c>
-      <c r="G37" s="5">
+      <c r="G37" s="3">
         <f t="shared" si="0"/>
         <v>1.69</v>
       </c>
-      <c r="H37" s="4">
-        <v>1</v>
-      </c>
-      <c r="I37" s="5">
+      <c r="H37" s="2">
+        <v>1</v>
+      </c>
+      <c r="I37" s="3">
         <f t="shared" si="1"/>
         <v>1.69</v>
       </c>
-      <c r="J37" s="8">
+      <c r="J37" s="6">
         <v>15</v>
       </c>
-      <c r="K37" s="8">
-        <v>12</v>
-      </c>
-      <c r="L37" s="57">
+      <c r="K37" s="6">
+        <v>12</v>
+      </c>
+      <c r="L37" s="34">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="38" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A38" s="4">
+    <row r="38" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A38" s="2">
         <v>37</v>
       </c>
-      <c r="B38" s="31" t="s">
+      <c r="B38" s="19" t="s">
         <v>184</v>
       </c>
-      <c r="C38" s="31" t="s">
+      <c r="C38" s="19" t="s">
         <v>190</v>
       </c>
-      <c r="D38" s="4" t="s">
+      <c r="D38" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E38" s="5">
+      <c r="E38" s="3">
         <v>15.8</v>
       </c>
-      <c r="F38" s="4">
+      <c r="F38" s="2">
         <v>10</v>
       </c>
-      <c r="G38" s="5">
+      <c r="G38" s="3">
         <f t="shared" si="0"/>
         <v>1.58</v>
       </c>
-      <c r="H38" s="4">
-        <v>1</v>
-      </c>
-      <c r="I38" s="5">
+      <c r="H38" s="2">
+        <v>1</v>
+      </c>
+      <c r="I38" s="3">
         <f t="shared" si="1"/>
         <v>1.58</v>
       </c>
-      <c r="J38" s="8">
+      <c r="J38" s="6">
         <v>5</v>
       </c>
-      <c r="K38" s="8">
-        <v>12</v>
-      </c>
-      <c r="L38" s="57">
+      <c r="K38" s="6">
+        <v>12</v>
+      </c>
+      <c r="L38" s="34">
         <f t="shared" si="2"/>
         <v>11.06</v>
       </c>
     </row>
-    <row r="39" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A39" s="4">
+    <row r="39" spans="1:12" ht="17" x14ac:dyDescent="0.2">
+      <c r="A39" s="2">
         <v>38</v>
       </c>
-      <c r="B39" s="31" t="s">
+      <c r="B39" s="19" t="s">
         <v>187</v>
       </c>
-      <c r="C39" s="31" t="s">
+      <c r="C39" s="19" t="s">
         <v>186</v>
       </c>
-      <c r="D39" s="4" t="s">
+      <c r="D39" s="2" t="s">
         <v>151</v>
       </c>
-      <c r="E39" s="5">
+      <c r="E39" s="3">
         <v>38</v>
       </c>
-      <c r="F39" s="4">
+      <c r="F39" s="2">
         <v>10</v>
       </c>
-      <c r="G39" s="5">
+      <c r="G39" s="3">
         <f t="shared" si="0"/>
         <v>3.8</v>
       </c>
-      <c r="H39" s="4">
-        <v>1</v>
-      </c>
-      <c r="I39" s="5">
+      <c r="H39" s="2">
+        <v>1</v>
+      </c>
+      <c r="I39" s="3">
         <f t="shared" si="1"/>
         <v>3.8</v>
       </c>
-      <c r="J39" s="8">
+      <c r="J39" s="6">
         <v>5</v>
       </c>
-      <c r="K39" s="8">
-        <v>12</v>
-      </c>
-      <c r="L39" s="57">
+      <c r="K39" s="6">
+        <v>12</v>
+      </c>
+      <c r="L39" s="34">
         <f t="shared" si="2"/>
         <v>26.599999999999998</v>
       </c>
     </row>
-    <row r="40" spans="1:12" ht="32" x14ac:dyDescent="0.4">
-      <c r="A40" s="4">
+    <row r="40" spans="1:12" ht="34" x14ac:dyDescent="0.2">
+      <c r="A40" s="2">
         <v>39</v>
       </c>
-      <c r="B40" s="31" t="s">
+      <c r="B40" s="19" t="s">
         <v>188</v>
       </c>
-      <c r="C40" s="31" t="s">
+      <c r="C40" s="19" t="s">
         <v>189</v>
       </c>
-      <c r="D40" s="4" t="s">
+      <c r="D40" s="2" t="s">
         <v>185</v>
       </c>
-      <c r="E40" s="5">
+      <c r="E40" s="3">
         <v>6.5179999999999998</v>
       </c>
-      <c r="F40" s="4">
+      <c r="F40" s="2">
         <v>10</v>
       </c>
-      <c r="G40" s="5">
+      <c r="G40" s="3">
         <f t="shared" si="0"/>
         <v>0.65179999999999993</v>
       </c>
-      <c r="H40" s="4">
-        <v>1</v>
-      </c>
-      <c r="I40" s="5">
+      <c r="H40" s="2">
+        <v>1</v>
+      </c>
+      <c r="I40" s="3">
         <f t="shared" si="1"/>
         <v>0.65179999999999993</v>
       </c>
-      <c r="J40" s="8">
+      <c r="J40" s="6">
         <v>5</v>
       </c>
-      <c r="K40" s="8">
-        <v>12</v>
-      </c>
-      <c r="L40" s="57">
+      <c r="K40" s="6">
+        <v>12</v>
+      </c>
+      <c r="L40" s="34">
         <f t="shared" si="2"/>
         <v>4.5625999999999998</v>
       </c>
     </row>
-    <row r="41" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A41" s="32" t="s">
+    <row r="41" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="A41" s="36" t="s">
         <v>55</v>
       </c>
-      <c r="B41" s="32"/>
-      <c r="C41" s="32"/>
-      <c r="D41" s="32"/>
-      <c r="E41" s="32"/>
-      <c r="F41" s="32"/>
-      <c r="G41" s="32"/>
-      <c r="H41" s="32"/>
-      <c r="I41" s="35">
+      <c r="B41" s="36"/>
+      <c r="C41" s="36"/>
+      <c r="D41" s="36"/>
+      <c r="E41" s="36"/>
+      <c r="F41" s="36"/>
+      <c r="G41" s="36"/>
+      <c r="H41" s="36"/>
+      <c r="I41" s="22">
         <f>SUM(I2:I40)</f>
         <v>38.513933333333327</v>
       </c>
-      <c r="J41" s="34" t="s">
-        <v>195</v>
-      </c>
-      <c r="K41" s="34"/>
-      <c r="L41" s="35">
+      <c r="J41" s="38" t="s">
+        <v>194</v>
+      </c>
+      <c r="K41" s="38"/>
+      <c r="L41" s="22">
         <f>SUM(L2:L40)</f>
         <v>224.22380000000001</v>
       </c>
     </row>
-    <row r="44" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="G44" s="16" t="s">
+    <row r="44" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G44" s="37" t="s">
         <v>58</v>
       </c>
-      <c r="H44" s="16"/>
-      <c r="I44" s="11">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="G45" s="16" t="s">
+      <c r="H44" s="37"/>
+      <c r="I44" s="9">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="G45" s="37" t="s">
         <v>57</v>
       </c>
-      <c r="H45" s="16"/>
-      <c r="I45" s="10">
+      <c r="H45" s="37"/>
+      <c r="I45" s="8">
         <f>I41*I44</f>
         <v>462.16719999999992</v>
       </c>
@@ -4938,8 +5008,8 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0EFB1B7-3B23-654A-84A7-B98EF9661A5C}">
-  <dimension ref="A1:L27"/>
-  <sheetFormatPr defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:M27"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="10.6640625" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="2" max="2" width="33.83203125" customWidth="1"/>
     <col min="3" max="3" width="45.83203125" customWidth="1"/>
@@ -4951,946 +5021,950 @@
     <col min="10" max="12" width="10.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="51" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A1" s="28" t="s">
+    <row r="1" spans="1:13" ht="51" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A1" s="16" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="28" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="28" t="s">
+      <c r="B1" s="16" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="16" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="28" t="s">
+      <c r="D1" s="16" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="28" t="s">
+      <c r="E1" s="16" t="s">
         <v>63</v>
       </c>
-      <c r="F1" s="28" t="s">
+      <c r="F1" s="16" t="s">
         <v>64</v>
       </c>
-      <c r="G1" s="28" t="s">
+      <c r="G1" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="H1" s="28" t="s">
+      <c r="H1" s="16" t="s">
         <v>7</v>
       </c>
-      <c r="I1" s="28" t="s">
+      <c r="I1" s="16" t="s">
         <v>66</v>
       </c>
-      <c r="J1" s="28" t="s">
-        <v>196</v>
-      </c>
-      <c r="K1" s="28" t="s">
+      <c r="J1" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="K1" s="16" t="s">
+        <v>192</v>
+      </c>
+      <c r="L1" s="16" t="s">
         <v>193</v>
       </c>
-      <c r="L1" s="28" t="s">
-        <v>194</v>
-      </c>
-    </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="A2" s="4">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="s">
+    </row>
+    <row r="2" spans="1:13" x14ac:dyDescent="0.2">
+      <c r="A2" s="2">
+        <v>1</v>
+      </c>
+      <c r="B2" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="47" t="s">
         <v>68</v>
       </c>
-      <c r="D2" s="25" t="s">
+      <c r="D2" s="48" t="s">
         <v>10</v>
       </c>
-      <c r="E2" s="24">
-        <v>29.98</v>
-      </c>
-      <c r="F2" s="4">
+      <c r="E2" s="52">
+        <v>26.98</v>
+      </c>
+      <c r="F2" s="2">
         <v>0.1845</v>
       </c>
-      <c r="G2" s="5">
+      <c r="G2" s="3">
         <f>F2*E2/2</f>
-        <v>2.7656550000000002</v>
-      </c>
-      <c r="H2" s="4">
-        <v>1</v>
-      </c>
-      <c r="I2" s="5">
+        <v>2.4889049999999999</v>
+      </c>
+      <c r="H2" s="2">
+        <v>1</v>
+      </c>
+      <c r="I2" s="3">
         <f t="shared" ref="I2:I23" si="0">H2*G2</f>
-        <v>2.7656550000000002</v>
-      </c>
-      <c r="J2" s="4">
+        <v>2.4889049999999999</v>
+      </c>
+      <c r="J2" s="2">
         <v>0</v>
       </c>
-      <c r="K2" s="4">
+      <c r="K2" s="2">
         <f t="shared" ref="K2:K23" si="1">H2*4</f>
         <v>4</v>
       </c>
-      <c r="L2" s="5">
+      <c r="L2" s="3">
         <f t="shared" ref="L2:L23" si="2">(IF(K2-J2&lt;0,0,K2-J2))*G2</f>
-        <v>11.062620000000001</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="29" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="4">
+        <v>9.9556199999999997</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" ht="29" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A3" s="2">
         <v>2</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="C3" s="22"/>
-      <c r="D3" s="22"/>
-      <c r="E3" s="22"/>
-      <c r="F3" s="4">
+      <c r="C3" s="45"/>
+      <c r="D3" s="45"/>
+      <c r="E3" s="42"/>
+      <c r="F3" s="2">
         <v>0.17349999999999999</v>
       </c>
-      <c r="G3" s="5">
+      <c r="G3" s="3">
         <f t="shared" ref="G3:G9" si="3">F3*E$2/2</f>
-        <v>2.600765</v>
-      </c>
-      <c r="H3" s="4">
-        <v>1</v>
-      </c>
-      <c r="I3" s="5">
-        <f t="shared" si="0"/>
-        <v>2.600765</v>
-      </c>
-      <c r="J3" s="4">
+        <v>2.3405149999999999</v>
+      </c>
+      <c r="H3" s="2">
+        <v>1</v>
+      </c>
+      <c r="I3" s="3">
+        <f t="shared" si="0"/>
+        <v>2.3405149999999999</v>
+      </c>
+      <c r="J3" s="2">
         <v>0</v>
       </c>
-      <c r="K3" s="4">
+      <c r="K3" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L3" s="5">
-        <f t="shared" si="2"/>
-        <v>10.40306</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="26" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="4">
+      <c r="L3" s="3">
+        <f t="shared" si="2"/>
+        <v>9.3620599999999996</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" ht="26" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A4" s="2">
         <v>3</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="C4" s="22"/>
-      <c r="D4" s="22"/>
-      <c r="E4" s="22"/>
-      <c r="F4" s="4">
+      <c r="C4" s="45"/>
+      <c r="D4" s="45"/>
+      <c r="E4" s="42"/>
+      <c r="F4" s="2">
         <v>1.9900000000000001E-2</v>
       </c>
-      <c r="G4" s="5">
+      <c r="G4" s="3">
         <f t="shared" si="3"/>
-        <v>0.29830100000000004</v>
-      </c>
-      <c r="H4" s="4">
-        <v>1</v>
-      </c>
-      <c r="I4" s="5">
-        <f t="shared" si="0"/>
-        <v>0.29830100000000004</v>
-      </c>
-      <c r="J4" s="4">
+        <v>0.268451</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1</v>
+      </c>
+      <c r="I4" s="3">
+        <f t="shared" si="0"/>
+        <v>0.268451</v>
+      </c>
+      <c r="J4" s="2">
         <v>0</v>
       </c>
-      <c r="K4" s="4">
+      <c r="K4" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L4" s="5">
-        <f t="shared" si="2"/>
-        <v>1.1932040000000002</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="4">
+      <c r="L4" s="3">
+        <f t="shared" si="2"/>
+        <v>1.073804</v>
+      </c>
+      <c r="M4">
+        <f>SUM(F2:F9)*4</f>
+        <v>3.4163999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A5" s="2">
         <v>4</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="C5" s="22"/>
-      <c r="D5" s="22"/>
-      <c r="E5" s="22"/>
-      <c r="F5" s="4">
+      <c r="C5" s="45"/>
+      <c r="D5" s="45"/>
+      <c r="E5" s="42"/>
+      <c r="F5" s="2">
         <v>6.54E-2</v>
       </c>
-      <c r="G5" s="5">
+      <c r="G5" s="3">
         <f t="shared" si="3"/>
-        <v>0.98034600000000005</v>
-      </c>
-      <c r="H5" s="4">
-        <v>1</v>
-      </c>
-      <c r="I5" s="5">
-        <f t="shared" si="0"/>
-        <v>0.98034600000000005</v>
-      </c>
-      <c r="J5" s="4">
+        <v>0.88224599999999997</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1</v>
+      </c>
+      <c r="I5" s="3">
+        <f t="shared" si="0"/>
+        <v>0.88224599999999997</v>
+      </c>
+      <c r="J5" s="2">
         <v>0</v>
       </c>
-      <c r="K5" s="4">
+      <c r="K5" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L5" s="5">
-        <f t="shared" si="2"/>
-        <v>3.9213840000000002</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="27.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="4">
+      <c r="L5" s="3">
+        <f t="shared" si="2"/>
+        <v>3.5289839999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" ht="27.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A6" s="2">
         <v>5</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C6" s="22"/>
-      <c r="D6" s="22"/>
-      <c r="E6" s="22"/>
-      <c r="F6" s="4">
+      <c r="C6" s="45"/>
+      <c r="D6" s="45"/>
+      <c r="E6" s="42"/>
+      <c r="F6" s="2">
         <v>0.18579999999999999</v>
       </c>
-      <c r="G6" s="5">
+      <c r="G6" s="3">
         <f t="shared" si="3"/>
-        <v>2.785142</v>
-      </c>
-      <c r="H6" s="4">
-        <v>1</v>
-      </c>
-      <c r="I6" s="5">
-        <f t="shared" si="0"/>
-        <v>2.785142</v>
-      </c>
-      <c r="J6" s="4">
+        <v>2.5064419999999998</v>
+      </c>
+      <c r="H6" s="2">
+        <v>1</v>
+      </c>
+      <c r="I6" s="3">
+        <f t="shared" si="0"/>
+        <v>2.5064419999999998</v>
+      </c>
+      <c r="J6" s="2">
         <v>0</v>
       </c>
-      <c r="K6" s="4">
+      <c r="K6" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L6" s="5">
-        <f t="shared" si="2"/>
-        <v>11.140568</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="28" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="4">
+      <c r="L6" s="3">
+        <f t="shared" si="2"/>
+        <v>10.025767999999999</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" ht="28" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A7" s="2">
         <v>16</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="C7" s="22"/>
-      <c r="D7" s="22"/>
-      <c r="E7" s="22"/>
-      <c r="F7" s="4">
+      <c r="C7" s="45"/>
+      <c r="D7" s="45"/>
+      <c r="E7" s="42"/>
+      <c r="F7" s="2">
         <v>5.9299999999999999E-2</v>
       </c>
-      <c r="G7" s="5">
+      <c r="G7" s="3">
         <f t="shared" si="3"/>
-        <v>0.888907</v>
-      </c>
-      <c r="H7" s="4">
-        <v>1</v>
-      </c>
-      <c r="I7" s="5">
-        <f t="shared" si="0"/>
-        <v>0.888907</v>
-      </c>
-      <c r="J7" s="4">
+        <v>0.79995700000000003</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="3">
+        <f t="shared" si="0"/>
+        <v>0.79995700000000003</v>
+      </c>
+      <c r="J7" s="2">
         <v>0</v>
       </c>
-      <c r="K7" s="4">
+      <c r="K7" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L7" s="5">
-        <f t="shared" si="2"/>
-        <v>3.555628</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="31" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="4">
+      <c r="L7" s="3">
+        <f t="shared" si="2"/>
+        <v>3.1998280000000001</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" ht="31" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A8" s="2">
         <v>17</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C8" s="22"/>
-      <c r="D8" s="22"/>
-      <c r="E8" s="22"/>
-      <c r="F8" s="4">
+      <c r="C8" s="45"/>
+      <c r="D8" s="45"/>
+      <c r="E8" s="42"/>
+      <c r="F8" s="2">
         <v>0.122</v>
       </c>
-      <c r="G8" s="5">
+      <c r="G8" s="3">
         <f t="shared" si="3"/>
-        <v>1.8287800000000001</v>
-      </c>
-      <c r="H8" s="4">
-        <v>1</v>
-      </c>
-      <c r="I8" s="5">
-        <f t="shared" si="0"/>
-        <v>1.8287800000000001</v>
-      </c>
-      <c r="J8" s="4">
+        <v>1.64578</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1</v>
+      </c>
+      <c r="I8" s="3">
+        <f t="shared" si="0"/>
+        <v>1.64578</v>
+      </c>
+      <c r="J8" s="2">
         <v>0</v>
       </c>
-      <c r="K8" s="4">
+      <c r="K8" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L8" s="5">
-        <f t="shared" si="2"/>
-        <v>7.3151200000000003</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A9" s="4">
+      <c r="L8" s="3">
+        <f t="shared" si="2"/>
+        <v>6.5831200000000001</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A9" s="2">
         <v>18</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="C9" s="23"/>
-      <c r="D9" s="23"/>
-      <c r="E9" s="23"/>
-      <c r="F9" s="4">
+      <c r="C9" s="46"/>
+      <c r="D9" s="46"/>
+      <c r="E9" s="43"/>
+      <c r="F9" s="2">
         <v>4.3700000000000003E-2</v>
       </c>
-      <c r="G9" s="5">
+      <c r="G9" s="3">
         <f t="shared" si="3"/>
-        <v>0.65506300000000006</v>
-      </c>
-      <c r="H9" s="4">
+        <v>0.58951300000000006</v>
+      </c>
+      <c r="H9" s="2">
         <v>2</v>
       </c>
-      <c r="I9" s="5">
-        <f t="shared" si="0"/>
-        <v>1.3101260000000001</v>
-      </c>
-      <c r="J9" s="4">
+      <c r="I9" s="3">
+        <f t="shared" si="0"/>
+        <v>1.1790260000000001</v>
+      </c>
+      <c r="J9" s="2">
         <v>0</v>
       </c>
-      <c r="K9" s="4">
+      <c r="K9" s="2">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="L9" s="5">
-        <f t="shared" si="2"/>
-        <v>5.2405040000000005</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="24.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="4">
+      <c r="L9" s="3">
+        <f t="shared" si="2"/>
+        <v>4.7161040000000005</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A10" s="2">
         <v>20</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>78</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="3">
         <v>8.99</v>
       </c>
-      <c r="F10" s="4">
+      <c r="F10" s="2">
         <v>3.8800000000000001E-2</v>
       </c>
-      <c r="G10" s="5">
+      <c r="G10" s="3">
         <v>1.3939999999999999</v>
       </c>
-      <c r="H10" s="4">
-        <v>1</v>
-      </c>
-      <c r="I10" s="5">
+      <c r="H10" s="2">
+        <v>1</v>
+      </c>
+      <c r="I10" s="3">
         <f t="shared" si="0"/>
         <v>1.3939999999999999</v>
       </c>
-      <c r="J10" s="4">
+      <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="K10" s="4">
+      <c r="K10" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L10" s="5">
+      <c r="L10" s="3">
         <f t="shared" si="2"/>
         <v>5.5759999999999996</v>
       </c>
     </row>
-    <row r="11" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A11" s="4">
+    <row r="11" spans="1:13" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A11" s="2">
         <v>19</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="E11" s="4">
+      <c r="E11" s="3">
         <v>28.09</v>
       </c>
-      <c r="F11" s="4">
+      <c r="F11" s="2">
         <v>10</v>
       </c>
-      <c r="G11" s="5">
+      <c r="G11" s="3">
         <v>2.8090000000000002</v>
       </c>
-      <c r="H11" s="4">
+      <c r="H11" s="2">
         <v>3</v>
       </c>
-      <c r="I11" s="5">
+      <c r="I11" s="3">
         <f t="shared" si="0"/>
         <v>8.4269999999999996</v>
       </c>
-      <c r="J11" s="4">
+      <c r="J11" s="2">
         <v>0</v>
       </c>
-      <c r="K11" s="4">
+      <c r="K11" s="2">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L11" s="5">
+      <c r="L11" s="3">
         <f t="shared" si="2"/>
         <v>33.707999999999998</v>
       </c>
     </row>
-    <row r="12" spans="1:12" ht="23" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A12" s="4">
+    <row r="12" spans="1:13" ht="23" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A12" s="2">
         <v>21</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>51</v>
       </c>
-      <c r="E12" s="4">
+      <c r="E12" s="3">
         <v>9.19</v>
       </c>
-      <c r="F12" s="4">
+      <c r="F12" s="2">
         <v>100</v>
       </c>
-      <c r="G12" s="5">
+      <c r="G12" s="3">
         <v>9.1999999999999998E-2</v>
       </c>
-      <c r="H12" s="4">
-        <v>12</v>
-      </c>
-      <c r="I12" s="5">
+      <c r="H12" s="2">
+        <v>12</v>
+      </c>
+      <c r="I12" s="3">
         <f t="shared" si="0"/>
         <v>1.1040000000000001</v>
       </c>
-      <c r="J12" s="4">
+      <c r="J12" s="2">
         <v>0</v>
       </c>
-      <c r="K12" s="4">
+      <c r="K12" s="2">
         <f t="shared" si="1"/>
         <v>48</v>
       </c>
-      <c r="L12" s="5">
+      <c r="L12" s="3">
         <f t="shared" si="2"/>
         <v>4.4160000000000004</v>
       </c>
     </row>
-    <row r="13" spans="1:12" ht="19.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="4">
+    <row r="13" spans="1:13" ht="19.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A13" s="2">
         <v>22</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>206</v>
-      </c>
-      <c r="E13" s="4">
+      <c r="D13" s="1" t="s">
+        <v>201</v>
+      </c>
+      <c r="E13" s="3">
         <v>2.48</v>
       </c>
-      <c r="F13" s="4">
+      <c r="F13" s="2">
         <v>5</v>
       </c>
-      <c r="G13" s="5">
+      <c r="G13" s="3">
         <v>0.496</v>
       </c>
-      <c r="H13" s="4">
+      <c r="H13" s="2">
         <v>2</v>
       </c>
-      <c r="I13" s="5">
+      <c r="I13" s="3">
         <f t="shared" si="0"/>
         <v>0.99199999999999999</v>
       </c>
-      <c r="J13" s="4">
+      <c r="J13" s="2">
         <v>9</v>
       </c>
-      <c r="K13" s="4">
+      <c r="K13" s="2">
         <f t="shared" si="1"/>
         <v>8</v>
       </c>
-      <c r="L13" s="5">
+      <c r="L13" s="3">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="4">
+    <row r="14" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A14" s="2">
         <v>23</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>207</v>
-      </c>
-      <c r="E14" s="4">
+      <c r="D14" s="1" t="s">
+        <v>202</v>
+      </c>
+      <c r="E14" s="3">
         <v>5.99</v>
       </c>
-      <c r="F14" s="4">
+      <c r="F14" s="2">
         <v>200</v>
       </c>
-      <c r="G14" s="5">
+      <c r="G14" s="3">
         <f>E14/F14</f>
         <v>2.9950000000000001E-2</v>
       </c>
-      <c r="H14" s="4">
+      <c r="H14" s="2">
         <v>24</v>
       </c>
-      <c r="I14" s="5">
+      <c r="I14" s="3">
         <f t="shared" si="0"/>
         <v>0.71879999999999999</v>
       </c>
-      <c r="J14" s="4">
+      <c r="J14" s="2">
         <v>0</v>
       </c>
-      <c r="K14" s="4">
+      <c r="K14" s="2">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="L14" s="5">
+      <c r="L14" s="3">
         <f t="shared" si="2"/>
         <v>2.8752</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="20" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A15" s="4">
+    <row r="15" spans="1:13" ht="20" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A15" s="2">
         <v>6</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>88</v>
       </c>
-      <c r="E15" s="4">
+      <c r="E15" s="3">
         <v>6.99</v>
       </c>
-      <c r="F15" s="4">
+      <c r="F15" s="2">
         <v>10</v>
       </c>
-      <c r="G15" s="5">
+      <c r="G15" s="3">
         <v>0.69899999999999995</v>
       </c>
-      <c r="H15" s="4">
+      <c r="H15" s="2">
         <v>7</v>
       </c>
-      <c r="I15" s="5">
+      <c r="I15" s="3">
         <f t="shared" si="0"/>
         <v>4.8929999999999998</v>
       </c>
-      <c r="J15" s="4">
+      <c r="J15" s="2">
         <v>0</v>
       </c>
-      <c r="K15" s="4">
+      <c r="K15" s="2">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="L15" s="5">
+      <c r="L15" s="3">
         <f t="shared" si="2"/>
         <v>19.571999999999999</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="18" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A16" s="4">
+    <row r="16" spans="1:13" ht="18" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A16" s="2">
         <v>7</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="E16" s="4">
+      <c r="E16" s="3">
         <v>7.29</v>
       </c>
-      <c r="F16" s="4">
+      <c r="F16" s="2">
         <v>50</v>
       </c>
-      <c r="G16" s="5">
+      <c r="G16" s="3">
         <v>0.14599999999999999</v>
       </c>
-      <c r="H16" s="4">
+      <c r="H16" s="2">
         <v>7</v>
       </c>
-      <c r="I16" s="5">
+      <c r="I16" s="3">
         <f t="shared" si="0"/>
         <v>1.022</v>
       </c>
-      <c r="J16" s="4">
+      <c r="J16" s="2">
         <v>19</v>
       </c>
-      <c r="K16" s="4">
+      <c r="K16" s="2">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="L16" s="5">
+      <c r="L16" s="3">
         <f t="shared" si="2"/>
         <v>1.3139999999999998</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="21.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A17" s="4">
+    <row r="17" spans="1:12" ht="21.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A17" s="2">
         <v>8</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="C17" s="4" t="s">
-        <v>209</v>
-      </c>
-      <c r="D17" s="2" t="s">
-        <v>208</v>
-      </c>
-      <c r="E17" s="4">
+      <c r="C17" s="2" t="s">
+        <v>204</v>
+      </c>
+      <c r="D17" s="1" t="s">
+        <v>203</v>
+      </c>
+      <c r="E17" s="3">
         <v>8.19</v>
       </c>
-      <c r="F17" s="4">
+      <c r="F17" s="2">
         <v>100</v>
       </c>
-      <c r="G17" s="5">
+      <c r="G17" s="3">
         <f>E17/F17</f>
         <v>8.1900000000000001E-2</v>
       </c>
-      <c r="H17" s="4">
+      <c r="H17" s="2">
         <v>24</v>
       </c>
-      <c r="I17" s="5">
+      <c r="I17" s="3">
         <f t="shared" si="0"/>
         <v>1.9656</v>
       </c>
-      <c r="J17" s="4">
+      <c r="J17" s="2">
         <v>0</v>
       </c>
-      <c r="K17" s="4">
+      <c r="K17" s="2">
         <f t="shared" si="1"/>
         <v>96</v>
       </c>
-      <c r="L17" s="5">
+      <c r="L17" s="3">
         <f t="shared" si="2"/>
         <v>7.8624000000000001</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="4">
+    <row r="18" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A18" s="2">
         <v>9</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C18" s="4" t="s">
-        <v>210</v>
-      </c>
-      <c r="D18" s="2" t="s">
+      <c r="C18" s="2" t="s">
+        <v>205</v>
+      </c>
+      <c r="D18" s="1" t="s">
         <v>95</v>
       </c>
-      <c r="E18" s="4">
+      <c r="E18" s="3">
         <v>12.79</v>
       </c>
-      <c r="F18" s="4">
+      <c r="F18" s="2">
         <v>40</v>
       </c>
-      <c r="G18" s="5">
+      <c r="G18" s="3">
         <v>0.32</v>
       </c>
-      <c r="H18" s="4">
+      <c r="H18" s="2">
         <v>7</v>
       </c>
-      <c r="I18" s="5">
+      <c r="I18" s="3">
         <f t="shared" si="0"/>
         <v>2.2400000000000002</v>
       </c>
-      <c r="J18" s="4">
+      <c r="J18" s="2">
         <v>0</v>
       </c>
-      <c r="K18" s="4">
+      <c r="K18" s="2">
         <f t="shared" si="1"/>
         <v>28</v>
       </c>
-      <c r="L18" s="5">
+      <c r="L18" s="3">
         <f t="shared" si="2"/>
         <v>8.9600000000000009</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="24.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A19" s="4">
+    <row r="19" spans="1:12" ht="24.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A19" s="2">
         <v>10</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>98</v>
       </c>
-      <c r="E19" s="4">
+      <c r="E19" s="3">
         <v>8.2899999999999991</v>
       </c>
-      <c r="F19" s="4">
+      <c r="F19" s="2">
         <v>10</v>
       </c>
-      <c r="G19" s="5">
+      <c r="G19" s="3">
         <v>0.82899999999999996</v>
       </c>
-      <c r="H19" s="4">
+      <c r="H19" s="2">
         <v>5</v>
       </c>
-      <c r="I19" s="5">
+      <c r="I19" s="3">
         <f t="shared" si="0"/>
         <v>4.1449999999999996</v>
       </c>
-      <c r="J19" s="4">
+      <c r="J19" s="2">
         <v>8</v>
       </c>
-      <c r="K19" s="4">
+      <c r="K19" s="2">
         <f t="shared" si="1"/>
         <v>20</v>
       </c>
-      <c r="L19" s="5">
+      <c r="L19" s="3">
         <f t="shared" si="2"/>
         <v>9.9480000000000004</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A20" s="4">
+    <row r="20" spans="1:12" ht="19" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A20" s="2">
         <v>11</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C20" s="4" t="s">
+      <c r="C20" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="D20" s="2" t="s">
-        <v>211</v>
-      </c>
-      <c r="E20" s="4">
+      <c r="D20" s="1" t="s">
+        <v>206</v>
+      </c>
+      <c r="E20" s="3">
         <v>8.69</v>
       </c>
-      <c r="F20" s="4">
+      <c r="F20" s="2">
         <v>8</v>
       </c>
-      <c r="G20" s="5">
+      <c r="G20" s="3">
         <f>E20/F20</f>
         <v>1.0862499999999999</v>
       </c>
-      <c r="H20" s="4">
-        <v>1</v>
-      </c>
-      <c r="I20" s="5">
+      <c r="H20" s="2">
+        <v>1</v>
+      </c>
+      <c r="I20" s="3">
         <f t="shared" si="0"/>
         <v>1.0862499999999999</v>
       </c>
-      <c r="J20" s="4">
+      <c r="J20" s="2">
         <v>0</v>
       </c>
-      <c r="K20" s="4">
+      <c r="K20" s="2">
         <f t="shared" si="1"/>
         <v>4</v>
       </c>
-      <c r="L20" s="5">
+      <c r="L20" s="3">
         <f t="shared" si="2"/>
         <v>4.3449999999999998</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A21" s="4">
-        <v>12</v>
-      </c>
-      <c r="B21" s="4" t="s">
+    <row r="21" spans="1:12" ht="20.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A21" s="2">
+        <v>12</v>
+      </c>
+      <c r="B21" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="C21" s="4" t="s">
+      <c r="C21" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="D21" s="2" t="s">
-        <v>212</v>
-      </c>
-      <c r="E21" s="4">
+      <c r="D21" s="1" t="s">
+        <v>207</v>
+      </c>
+      <c r="E21" s="3">
         <v>6.29</v>
       </c>
-      <c r="F21" s="4">
+      <c r="F21" s="2">
         <v>100</v>
       </c>
-      <c r="G21" s="5">
+      <c r="G21" s="3">
         <f>E21/F21</f>
         <v>6.2899999999999998E-2</v>
       </c>
-      <c r="H21" s="4">
+      <c r="H21" s="2">
         <v>3</v>
       </c>
-      <c r="I21" s="5">
+      <c r="I21" s="3">
         <f t="shared" si="0"/>
         <v>0.18869999999999998</v>
       </c>
-      <c r="J21" s="4">
+      <c r="J21" s="2">
         <v>40</v>
       </c>
-      <c r="K21" s="4">
+      <c r="K21" s="2">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L21" s="5">
+      <c r="L21" s="3">
         <f>(IF(K21-J21&lt;0,0,K21-J21))*G21</f>
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="4">
+    <row r="22" spans="1:12" ht="23.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A22" s="2">
         <v>14</v>
       </c>
-      <c r="B22" s="4" t="s">
+      <c r="B22" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="C22" s="4" t="s">
+      <c r="C22" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="E22" s="4">
+      <c r="E22" s="3">
         <v>13.29</v>
       </c>
-      <c r="F22" s="4">
+      <c r="F22" s="2">
         <v>40</v>
       </c>
-      <c r="G22" s="5">
+      <c r="G22" s="3">
         <f>E22/F22</f>
         <v>0.33224999999999999</v>
       </c>
-      <c r="H22" s="4">
+      <c r="H22" s="2">
         <v>3</v>
       </c>
-      <c r="I22" s="5">
+      <c r="I22" s="3">
         <f t="shared" si="0"/>
         <v>0.99675000000000002</v>
       </c>
-      <c r="J22" s="4">
+      <c r="J22" s="2">
         <v>10</v>
       </c>
-      <c r="K22" s="4">
+      <c r="K22" s="2">
         <f t="shared" si="1"/>
         <v>12</v>
       </c>
-      <c r="L22" s="5">
+      <c r="L22" s="3">
         <f t="shared" si="2"/>
         <v>0.66449999999999998</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A23" s="4">
+    <row r="23" spans="1:12" ht="21" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A23" s="2">
         <v>15</v>
       </c>
-      <c r="B23" s="4" t="s">
-        <v>214</v>
-      </c>
-      <c r="C23" s="4" t="s">
+      <c r="B23" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="C23" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E23" s="4">
+      <c r="D23" s="1" t="s">
+        <v>208</v>
+      </c>
+      <c r="E23" s="3">
         <v>7.39</v>
       </c>
-      <c r="F23" s="4">
+      <c r="F23" s="2">
         <v>50</v>
       </c>
-      <c r="G23" s="5">
+      <c r="G23" s="3">
         <f>E23/F23</f>
         <v>0.14779999999999999</v>
       </c>
-      <c r="H23" s="4">
+      <c r="H23" s="2">
         <v>18</v>
       </c>
-      <c r="I23" s="5">
+      <c r="I23" s="3">
         <f t="shared" si="0"/>
         <v>2.6603999999999997</v>
       </c>
-      <c r="J23" s="4">
+      <c r="J23" s="2">
         <v>0</v>
       </c>
-      <c r="K23" s="4">
+      <c r="K23" s="2">
         <f t="shared" si="1"/>
         <v>72</v>
       </c>
-      <c r="L23" s="5">
+      <c r="L23" s="3">
         <f t="shared" si="2"/>
         <v>10.641599999999999</v>
       </c>
     </row>
-    <row r="24" spans="1:12" s="41" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.4">
-      <c r="A24" s="53" t="s">
+    <row r="24" spans="1:12" s="25" customFormat="1" ht="33" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A24" s="49" t="s">
         <v>55</v>
       </c>
-      <c r="B24" s="54"/>
-      <c r="C24" s="54"/>
-      <c r="D24" s="54"/>
-      <c r="E24" s="54"/>
-      <c r="F24" s="54"/>
-      <c r="G24" s="54"/>
-      <c r="H24" s="55"/>
-      <c r="I24" s="56">
+      <c r="B24" s="50"/>
+      <c r="C24" s="50"/>
+      <c r="D24" s="50"/>
+      <c r="E24" s="50"/>
+      <c r="F24" s="50"/>
+      <c r="G24" s="50"/>
+      <c r="H24" s="51"/>
+      <c r="I24" s="33">
         <f>SUM(I2:I23)</f>
-        <v>45.291522000000008</v>
-      </c>
-      <c r="J24" s="53" t="s">
-        <v>195</v>
-      </c>
-      <c r="K24" s="55"/>
-      <c r="L24" s="56">
+        <v>43.944821999999995</v>
+      </c>
+      <c r="J24" s="49" t="s">
+        <v>194</v>
+      </c>
+      <c r="K24" s="51"/>
+      <c r="L24" s="33">
         <f>SUM(L2:L23)</f>
-        <v>163.71478800000003</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" x14ac:dyDescent="0.4">
-      <c r="J27" s="13"/>
-      <c r="K27" s="13"/>
-      <c r="L27" s="14"/>
+        <v>158.327988</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.2">
+      <c r="J27" s="11"/>
+      <c r="K27" s="11"/>
+      <c r="L27" s="12"/>
     </row>
   </sheetData>
   <mergeCells count="5">
